--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -491,124 +491,124 @@
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>SG Armaturen</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Plejd</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Hide-a-lite</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Let it light</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Designlight</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Exaktor</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Designlight</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Exaktor</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Hide-a-lite</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Let it light</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>SG Armaturen</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>a-collection</t>
         </is>
       </c>
     </row>
@@ -619,76 +619,155 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
+        <v>1402</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>885</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>527</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>25</v>
       </c>
       <c r="K2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1402</v>
+      </c>
+      <c r="C3" t="n">
+        <v>885</v>
+      </c>
+      <c r="D3" t="n">
+        <v>527</v>
+      </c>
+      <c r="E3" t="n">
+        <v>233</v>
+      </c>
+      <c r="F3" t="n">
+        <v>223</v>
+      </c>
+      <c r="G3" t="n">
+        <v>93</v>
+      </c>
+      <c r="H3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I3" t="n">
         <v>33</v>
       </c>
-      <c r="L2" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="M2" s="5" t="n">
+      <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="n">
         <v>17</v>
       </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>1402</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>233</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="5" t="n">
-        <v>885</v>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +808,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-07)</t>
+          <t>Lager (2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1555,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1496,7 +1575,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1516,7 +1595,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1536,7 +1615,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1556,7 +1635,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1576,7 +1655,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -1596,7 +1675,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1616,7 +1695,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1636,7 +1715,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1656,7 +1735,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1676,7 +1755,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1696,7 +1775,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1716,7 +1795,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1736,7 +1815,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
         </is>
       </c>
     </row>
@@ -767,6 +767,85 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1391</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>874</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>523</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -808,7 +887,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-08)</t>
+          <t>Lager (2026-07-09)</t>
         </is>
       </c>
     </row>
@@ -829,7 +908,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
@@ -9089,7 +9168,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="416">
@@ -13089,7 +13168,7 @@
         </is>
       </c>
       <c r="D615" s="6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="616">
@@ -18429,7 +18508,7 @@
         </is>
       </c>
       <c r="D882" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="883">
@@ -18569,7 +18648,7 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>1308</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="890">
@@ -19009,7 +19088,7 @@
         </is>
       </c>
       <c r="D911" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="912">
@@ -23189,7 +23268,7 @@
         </is>
       </c>
       <c r="D1120" s="4" t="n">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="1121">
@@ -23209,7 +23288,7 @@
         </is>
       </c>
       <c r="D1121" s="6" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -846,6 +846,85 @@
         <v>0</v>
       </c>
       <c r="Y4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1384</v>
+      </c>
+      <c r="C5" t="n">
+        <v>871</v>
+      </c>
+      <c r="D5" t="n">
+        <v>522</v>
+      </c>
+      <c r="E5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F5" t="n">
+        <v>221</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1121"/>
+  <dimension ref="A1:D1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -887,7 +966,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-09)</t>
+          <t>Lager (2026-07-10)</t>
         </is>
       </c>
     </row>
@@ -908,7 +987,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3">
@@ -1634,7 +1713,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1654,7 +1733,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1674,7 +1753,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1694,7 +1773,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1714,7 +1793,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1734,7 +1813,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -1754,7 +1833,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1774,7 +1853,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1794,7 +1873,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1814,7 +1893,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1834,7 +1913,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1854,7 +1933,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1874,7 +1953,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1894,7 +1973,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -6448,7 +6527,7 @@
         </is>
       </c>
       <c r="D279" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="280">
@@ -9168,7 +9247,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="416">
@@ -17714,17 +17793,17 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7026517</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D843" s="6" t="n">
@@ -17734,17 +17813,17 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7026518</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D844" s="4" t="n">
@@ -17754,17 +17833,17 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7026519</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D845" s="6" t="n">
@@ -17774,17 +17853,17 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7026520</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D846" s="4" t="n">
@@ -17794,17 +17873,17 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7026521</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D847" s="6" t="n">
@@ -17814,17 +17893,17 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7026522</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D848" s="4" t="n">
@@ -17834,17 +17913,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7026523</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -17854,17 +17933,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7026524</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -17874,7 +17953,7 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -17894,7 +17973,7 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
@@ -17914,7 +17993,7 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -17934,7 +18013,7 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
@@ -17954,7 +18033,7 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -17974,7 +18053,7 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -17994,7 +18073,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -18014,7 +18093,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -18034,7 +18113,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -18054,7 +18133,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -18074,7 +18153,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -18094,7 +18173,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -18114,7 +18193,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -18134,7 +18213,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -18154,7 +18233,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -18174,7 +18253,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -18194,7 +18273,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -18214,7 +18293,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -18234,12 +18313,12 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -18254,12 +18333,12 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C870" s="5" t="inlineStr">
@@ -18274,12 +18353,12 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -18294,12 +18373,12 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C872" s="5" t="inlineStr">
@@ -18314,12 +18393,12 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -18334,12 +18413,12 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C874" s="5" t="inlineStr">
@@ -18348,18 +18427,18 @@
         </is>
       </c>
       <c r="D874" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -18368,18 +18447,18 @@
         </is>
       </c>
       <c r="D875" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -18394,12 +18473,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -18414,12 +18493,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -18434,12 +18513,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -18454,12 +18533,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -18474,12 +18553,12 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -18488,18 +18567,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>0</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -18508,18 +18587,18 @@
         </is>
       </c>
       <c r="D882" s="4" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -18528,18 +18607,18 @@
         </is>
       </c>
       <c r="D883" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -18554,12 +18633,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -18574,12 +18653,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -18594,12 +18673,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -18614,12 +18693,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -18634,12 +18713,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -18648,18 +18727,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -18668,18 +18747,18 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -18688,18 +18767,18 @@
         </is>
       </c>
       <c r="D891" s="6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -18714,12 +18793,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -18734,12 +18813,12 @@
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -18754,12 +18833,12 @@
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -18774,12 +18853,12 @@
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -18794,12 +18873,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -18814,12 +18893,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -18834,12 +18913,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -18848,18 +18927,18 @@
         </is>
       </c>
       <c r="D899" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -18874,12 +18953,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -18894,12 +18973,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -18914,12 +18993,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -18928,18 +19007,18 @@
         </is>
       </c>
       <c r="D903" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -18954,12 +19033,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -18974,12 +19053,12 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C906" s="5" t="inlineStr">
@@ -18994,12 +19073,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -19008,18 +19087,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -19034,12 +19113,12 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -19048,18 +19127,18 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -19074,12 +19153,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -19088,18 +19167,18 @@
         </is>
       </c>
       <c r="D911" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -19114,12 +19193,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -19134,12 +19213,12 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C914" s="5" t="inlineStr">
@@ -19154,12 +19233,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -19174,12 +19253,12 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -19194,12 +19273,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -19208,18 +19287,18 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -19234,12 +19313,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -19254,12 +19333,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -19274,12 +19353,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -19294,12 +19373,12 @@
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -19314,12 +19393,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -19334,12 +19413,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -19354,12 +19433,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -19374,12 +19453,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -19394,12 +19473,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -19414,12 +19493,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -19434,12 +19513,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -19454,12 +19533,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -19474,12 +19553,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -19494,12 +19573,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -19514,12 +19593,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -19534,12 +19613,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -19554,12 +19633,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -19574,12 +19653,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -19594,12 +19673,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -19614,12 +19693,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -19634,12 +19713,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -19654,12 +19733,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -19674,12 +19753,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -19694,17 +19773,17 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7027837</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D942" s="4" t="n">
@@ -19714,17 +19793,17 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7027838</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D943" s="6" t="n">
@@ -19734,17 +19813,17 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7027841</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D944" s="4" t="n">
@@ -19754,17 +19833,17 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7027842</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D945" s="6" t="n">
@@ -19774,17 +19853,17 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7027835</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D946" s="4" t="n">
@@ -19794,17 +19873,17 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7027836</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D947" s="6" t="n">
@@ -19814,17 +19893,17 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7027839</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D948" s="4" t="n">
@@ -19834,17 +19913,17 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7027840</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D949" s="6" t="n">
@@ -19854,12 +19933,12 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7027837</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -19874,12 +19953,12 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7027838</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -19894,12 +19973,12 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7027841</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -19914,12 +19993,12 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7027842</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -19934,12 +20013,12 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7027835</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
@@ -19954,12 +20033,12 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027836</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -19974,12 +20053,12 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027839</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
@@ -19994,12 +20073,12 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027840</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -20014,7 +20093,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -20034,17 +20113,17 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D959" s="6" t="n">
@@ -20054,17 +20133,17 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D960" s="4" t="n">
@@ -20074,17 +20153,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -20094,17 +20173,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -20114,17 +20193,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -20134,17 +20213,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -20154,17 +20233,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -20174,17 +20253,17 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D966" s="4" t="n">
@@ -20194,17 +20273,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -20214,17 +20293,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -20234,7 +20313,7 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -20254,7 +20333,7 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
@@ -20274,7 +20353,7 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -20294,12 +20373,12 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
@@ -20314,12 +20393,12 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -20328,18 +20407,18 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
@@ -20354,7 +20433,7 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -20374,7 +20453,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
@@ -20388,18 +20467,18 @@
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -20414,12 +20493,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -20434,12 +20513,12 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -20454,12 +20533,12 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -20474,12 +20553,12 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -20494,7 +20573,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
@@ -20514,7 +20593,7 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -20534,7 +20613,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
@@ -20554,17 +20633,17 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D985" s="6" t="n">
@@ -20574,17 +20653,17 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D986" s="4" t="n">
@@ -20594,17 +20673,17 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D987" s="6" t="n">
@@ -20614,7 +20693,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -20634,12 +20713,12 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -20654,12 +20733,12 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
@@ -20674,12 +20753,12 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -20694,12 +20773,12 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
@@ -20714,12 +20793,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -20734,7 +20813,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
@@ -20754,12 +20833,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -20774,12 +20853,12 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
@@ -20794,12 +20873,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -20814,12 +20893,12 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -20834,12 +20913,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -20854,7 +20933,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
@@ -20874,12 +20953,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -20894,12 +20973,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -20914,12 +20993,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -20934,7 +21013,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -20954,12 +21033,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -20974,12 +21053,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -20994,12 +21073,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -21014,7 +21093,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -21034,7 +21113,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -21054,7 +21133,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -21074,7 +21153,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -21094,7 +21173,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -21114,7 +21193,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -21134,7 +21213,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -21154,7 +21233,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -21174,7 +21253,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -21194,7 +21273,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -21214,7 +21293,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -21234,7 +21313,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -21254,7 +21333,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -21274,7 +21353,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -21294,7 +21373,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -21314,7 +21393,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -21334,7 +21413,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -21354,7 +21433,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -21374,7 +21453,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -21394,7 +21473,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -21414,7 +21493,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -21434,7 +21513,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -21454,7 +21533,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -21474,7 +21553,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -21494,7 +21573,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -21514,12 +21593,12 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -21534,12 +21613,12 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1034" s="5" t="inlineStr">
@@ -21554,12 +21633,12 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -21574,7 +21653,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -21594,7 +21673,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -21614,7 +21693,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -21634,7 +21713,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -21654,7 +21733,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -21674,7 +21753,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -21694,7 +21773,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -21714,7 +21793,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -21734,7 +21813,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -21754,7 +21833,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -21774,7 +21853,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -21794,7 +21873,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -21814,7 +21893,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -21834,7 +21913,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -21854,7 +21933,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -21874,7 +21953,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -21894,7 +21973,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -21914,7 +21993,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -21934,7 +22013,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -21954,7 +22033,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -21974,7 +22053,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -21994,7 +22073,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -22014,7 +22093,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -22034,7 +22113,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -22054,7 +22133,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -22074,7 +22153,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -22094,7 +22173,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -22114,7 +22193,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -22134,7 +22213,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -22154,7 +22233,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -22174,7 +22253,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -22194,7 +22273,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -22214,7 +22293,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -22234,12 +22313,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -22254,12 +22333,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -22274,12 +22353,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -22294,7 +22373,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -22314,7 +22393,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -22334,7 +22413,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -22354,7 +22433,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -22374,7 +22453,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -22394,7 +22473,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -22414,7 +22493,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -22434,7 +22513,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -22454,7 +22533,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -22474,12 +22553,12 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -22494,12 +22573,12 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1082" s="5" t="inlineStr">
@@ -22514,12 +22593,12 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -22534,7 +22613,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -22554,12 +22633,12 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -22574,12 +22653,12 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
@@ -22594,12 +22673,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -22614,12 +22693,12 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
@@ -22634,7 +22713,7 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -22654,12 +22733,12 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
@@ -22674,12 +22753,12 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -22694,12 +22773,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -22714,12 +22793,12 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -22734,12 +22813,12 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -22754,12 +22833,12 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -22774,12 +22853,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -22794,12 +22873,12 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -22814,7 +22893,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
@@ -22834,7 +22913,7 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -22854,7 +22933,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -22874,7 +22953,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -22894,7 +22973,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -22914,7 +22993,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -22934,7 +23013,7 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
@@ -22954,7 +23033,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -22974,7 +23053,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -22994,17 +23073,17 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1107" s="6" t="n">
@@ -23014,17 +23093,17 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1108" s="4" t="n">
@@ -23034,17 +23113,17 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1109" s="6" t="n">
@@ -23054,57 +23133,57 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1110" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1112" s="4" t="n">
@@ -23114,12 +23193,12 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -23128,18 +23207,18 @@
         </is>
       </c>
       <c r="D1113" s="6" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1114" s="5" t="inlineStr">
@@ -23148,18 +23227,18 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -23174,12 +23253,12 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1116" s="5" t="inlineStr">
@@ -23188,18 +23267,18 @@
         </is>
       </c>
       <c r="D1116" s="4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -23208,18 +23287,18 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>38</v>
+        <v>410</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1118" s="5" t="inlineStr">
@@ -23228,66 +23307,6 @@
         </is>
       </c>
       <c r="D1118" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" s="6" t="inlineStr">
-        <is>
-          <t>7028002</t>
-        </is>
-      </c>
-      <c r="B1119" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1119" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1119" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" s="4" t="inlineStr">
-        <is>
-          <t>7027999</t>
-        </is>
-      </c>
-      <c r="B1120" s="5" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1120" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1120" s="4" t="n">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" s="6" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1121" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1121" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1121" s="6" t="n">
         <v>366</v>
       </c>
     </row>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>Legrand</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -925,6 +925,85 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1377</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>920</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -966,7 +1045,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-10)</t>
+          <t>Lager (2026-07-11)</t>
         </is>
       </c>
     </row>
@@ -987,7 +1066,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3">
@@ -1713,7 +1792,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1733,7 +1812,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1753,7 +1832,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1773,7 +1852,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1793,7 +1872,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1813,7 +1892,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -1833,7 +1912,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1853,7 +1932,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1873,7 +1952,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1893,7 +1972,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1913,7 +1992,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1933,7 +2012,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1953,7 +2032,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1973,7 +2052,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -9247,7 +9326,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="416">
@@ -18427,7 +18506,7 @@
         </is>
       </c>
       <c r="D874" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="875">
@@ -18567,7 +18646,7 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="882">
@@ -19007,7 +19086,7 @@
         </is>
       </c>
       <c r="D903" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="904">
@@ -20407,7 +20486,7 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="974">
@@ -23287,7 +23366,7 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1118">
@@ -23307,7 +23386,7 @@
         </is>
       </c>
       <c r="D1118" s="4" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>THORN</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -1159,6 +1159,85 @@
         <v>0</v>
       </c>
       <c r="Y8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1385</v>
+      </c>
+      <c r="C9" t="n">
+        <v>941</v>
+      </c>
+      <c r="D9" t="n">
+        <v>532</v>
+      </c>
+      <c r="E9" t="n">
+        <v>232</v>
+      </c>
+      <c r="F9" t="n">
+        <v>214</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>52</v>
+      </c>
+      <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1173,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1121"/>
+  <dimension ref="A1:D1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1279,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-13)</t>
+          <t>Lager (2026-07-14)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1300,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3">
@@ -9481,7 +9560,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="416">
@@ -18027,17 +18106,17 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7026517</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D843" s="6" t="n">
@@ -18047,17 +18126,17 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7026518</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D844" s="4" t="n">
@@ -18067,17 +18146,17 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7026519</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D845" s="6" t="n">
@@ -18087,17 +18166,17 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7026520</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D846" s="4" t="n">
@@ -18107,17 +18186,17 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7026521</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D847" s="6" t="n">
@@ -18127,17 +18206,17 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7026522</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D848" s="4" t="n">
@@ -18147,17 +18226,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7026523</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -18167,17 +18246,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7026524</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueCircle infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -18187,7 +18266,7 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -18207,7 +18286,7 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
@@ -18227,7 +18306,7 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -18247,7 +18326,7 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
@@ -18267,7 +18346,7 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -18287,7 +18366,7 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -18307,7 +18386,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -18327,7 +18406,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -18347,7 +18426,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -18367,7 +18446,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -18387,7 +18466,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -18407,7 +18486,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -18427,7 +18506,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -18447,7 +18526,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -18467,7 +18546,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -18487,7 +18566,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -18507,7 +18586,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -18527,7 +18606,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -18547,12 +18626,12 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -18567,12 +18646,12 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C870" s="5" t="inlineStr">
@@ -18587,12 +18666,12 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -18607,12 +18686,12 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C872" s="5" t="inlineStr">
@@ -18627,12 +18706,12 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -18647,12 +18726,12 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C874" s="5" t="inlineStr">
@@ -18661,18 +18740,18 @@
         </is>
       </c>
       <c r="D874" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -18681,18 +18760,18 @@
         </is>
       </c>
       <c r="D875" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -18707,12 +18786,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -18727,12 +18806,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -18747,12 +18826,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -18767,12 +18846,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -18787,12 +18866,12 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -18801,18 +18880,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>0</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -18821,18 +18900,18 @@
         </is>
       </c>
       <c r="D882" s="4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -18841,18 +18920,18 @@
         </is>
       </c>
       <c r="D883" s="6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -18867,12 +18946,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -18887,12 +18966,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -18907,12 +18986,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -18927,12 +19006,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -18947,12 +19026,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -18961,18 +19040,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>1302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -18981,18 +19060,18 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -19001,18 +19080,18 @@
         </is>
       </c>
       <c r="D891" s="6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -19027,12 +19106,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -19047,12 +19126,12 @@
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -19067,12 +19146,12 @@
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -19087,12 +19166,12 @@
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -19107,12 +19186,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -19127,12 +19206,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -19147,12 +19226,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -19161,18 +19240,18 @@
         </is>
       </c>
       <c r="D899" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -19187,12 +19266,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -19207,12 +19286,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -19227,12 +19306,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -19241,18 +19320,18 @@
         </is>
       </c>
       <c r="D903" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -19267,12 +19346,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -19287,12 +19366,12 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C906" s="5" t="inlineStr">
@@ -19307,12 +19386,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -19321,18 +19400,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -19347,12 +19426,12 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -19361,18 +19440,18 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -19387,12 +19466,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -19401,18 +19480,18 @@
         </is>
       </c>
       <c r="D911" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -19427,12 +19506,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -19447,12 +19526,12 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C914" s="5" t="inlineStr">
@@ -19467,12 +19546,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -19487,12 +19566,12 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -19507,12 +19586,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -19521,18 +19600,18 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -19547,12 +19626,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -19567,12 +19646,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -19587,12 +19666,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -19607,12 +19686,12 @@
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -19627,12 +19706,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -19647,12 +19726,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -19667,12 +19746,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -19687,12 +19766,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -19707,12 +19786,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -19727,12 +19806,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -19747,12 +19826,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -19767,12 +19846,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -19787,12 +19866,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -19807,12 +19886,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -19827,12 +19906,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -19847,12 +19926,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -19867,12 +19946,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -19887,12 +19966,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -19907,12 +19986,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -19927,12 +20006,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -19947,12 +20026,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -19967,12 +20046,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -19987,12 +20066,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -20007,17 +20086,17 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7027837</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D942" s="4" t="n">
@@ -20027,17 +20106,17 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7027838</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D943" s="6" t="n">
@@ -20047,17 +20126,17 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7027841</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D944" s="4" t="n">
@@ -20067,17 +20146,17 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7027842</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D945" s="6" t="n">
@@ -20087,17 +20166,17 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7027835</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D946" s="4" t="n">
@@ -20107,17 +20186,17 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7027836</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D947" s="6" t="n">
@@ -20127,17 +20206,17 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7027839</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D948" s="4" t="n">
@@ -20147,17 +20226,17 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7027840</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D949" s="6" t="n">
@@ -20167,12 +20246,12 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7027837</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -20187,12 +20266,12 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7027838</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -20207,12 +20286,12 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7027841</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -20227,12 +20306,12 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7027842</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -20247,12 +20326,12 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7027835</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
@@ -20267,12 +20346,12 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027836</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -20287,12 +20366,12 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027839</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
@@ -20307,12 +20386,12 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027840</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -20327,7 +20406,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -20347,17 +20426,17 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D959" s="6" t="n">
@@ -20367,17 +20446,17 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D960" s="4" t="n">
@@ -20387,17 +20466,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -20407,17 +20486,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -20427,17 +20506,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -20447,17 +20526,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -20467,17 +20546,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -20487,17 +20566,17 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D966" s="4" t="n">
@@ -20507,17 +20586,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -20527,17 +20606,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -20547,7 +20626,7 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -20567,7 +20646,7 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
@@ -20587,7 +20666,7 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -20607,12 +20686,12 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
@@ -20627,12 +20706,12 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -20641,18 +20720,18 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
@@ -20667,7 +20746,7 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -20687,7 +20766,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
@@ -20701,18 +20780,18 @@
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -20727,12 +20806,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -20747,12 +20826,12 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -20767,12 +20846,12 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -20787,12 +20866,12 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -20807,7 +20886,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
@@ -20827,7 +20906,7 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -20847,7 +20926,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
@@ -20867,17 +20946,17 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D985" s="6" t="n">
@@ -20887,17 +20966,17 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D986" s="4" t="n">
@@ -20907,17 +20986,17 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D987" s="6" t="n">
@@ -20927,7 +21006,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -20947,12 +21026,12 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -20967,12 +21046,12 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
@@ -20987,12 +21066,12 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -21007,12 +21086,12 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
@@ -21027,12 +21106,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -21047,7 +21126,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
@@ -21067,12 +21146,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -21087,12 +21166,12 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
@@ -21107,12 +21186,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -21127,12 +21206,12 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -21147,12 +21226,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -21167,7 +21246,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
@@ -21187,12 +21266,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -21207,12 +21286,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -21227,12 +21306,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -21247,7 +21326,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -21267,12 +21346,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -21287,12 +21366,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -21307,12 +21386,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -21327,7 +21406,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -21347,7 +21426,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -21367,7 +21446,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -21387,7 +21466,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -21407,7 +21486,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -21427,7 +21506,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -21447,7 +21526,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -21467,7 +21546,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -21487,7 +21566,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -21507,7 +21586,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -21527,7 +21606,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -21547,7 +21626,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -21567,7 +21646,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -21587,7 +21666,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -21607,7 +21686,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -21627,7 +21706,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -21647,7 +21726,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -21667,7 +21746,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -21687,7 +21766,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -21707,7 +21786,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -21727,7 +21806,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -21747,7 +21826,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -21767,7 +21846,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -21787,7 +21866,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -21807,7 +21886,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -21827,12 +21906,12 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -21847,12 +21926,12 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1034" s="5" t="inlineStr">
@@ -21867,12 +21946,12 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -21887,7 +21966,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -21907,7 +21986,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -21927,7 +22006,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -21947,7 +22026,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -21967,7 +22046,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -21987,7 +22066,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -22007,7 +22086,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -22027,7 +22106,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -22047,7 +22126,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -22067,7 +22146,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -22087,7 +22166,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -22107,7 +22186,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -22127,7 +22206,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -22147,7 +22226,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -22167,7 +22246,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -22187,7 +22266,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -22207,7 +22286,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -22227,7 +22306,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -22247,7 +22326,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -22267,7 +22346,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -22287,7 +22366,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -22307,7 +22386,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -22327,7 +22406,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -22347,7 +22426,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -22367,7 +22446,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -22387,7 +22466,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -22407,7 +22486,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -22427,7 +22506,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -22447,7 +22526,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -22467,7 +22546,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -22487,7 +22566,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -22507,7 +22586,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -22527,7 +22606,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -22547,12 +22626,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -22567,12 +22646,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -22587,12 +22666,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -22607,7 +22686,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -22627,7 +22706,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -22647,7 +22726,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -22667,7 +22746,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -22687,7 +22766,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -22707,7 +22786,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -22727,7 +22806,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -22747,7 +22826,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -22767,7 +22846,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -22787,12 +22866,12 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -22807,12 +22886,12 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1082" s="5" t="inlineStr">
@@ -22827,12 +22906,12 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -22847,7 +22926,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -22867,12 +22946,12 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -22887,12 +22966,12 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
@@ -22907,12 +22986,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -22927,12 +23006,12 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
@@ -22947,7 +23026,7 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -22967,12 +23046,12 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
@@ -22987,12 +23066,12 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -23007,12 +23086,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -23027,12 +23106,12 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -23047,12 +23126,12 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -23067,12 +23146,12 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -23087,12 +23166,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -23107,12 +23186,12 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -23127,7 +23206,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
@@ -23147,7 +23226,7 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -23167,7 +23246,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -23187,7 +23266,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -23207,7 +23286,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -23227,7 +23306,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -23247,7 +23326,7 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
@@ -23267,7 +23346,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -23287,7 +23366,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -23307,17 +23386,17 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1107" s="6" t="n">
@@ -23327,17 +23406,17 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1108" s="4" t="n">
@@ -23347,17 +23426,17 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1109" s="6" t="n">
@@ -23367,57 +23446,57 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1110" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1112" s="4" t="n">
@@ -23427,12 +23506,12 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -23441,18 +23520,18 @@
         </is>
       </c>
       <c r="D1113" s="6" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1114" s="5" t="inlineStr">
@@ -23461,18 +23540,18 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -23487,12 +23566,12 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1116" s="5" t="inlineStr">
@@ -23501,18 +23580,18 @@
         </is>
       </c>
       <c r="D1116" s="4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -23521,18 +23600,18 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>38</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1118" s="5" t="inlineStr">
@@ -23541,67 +23620,7 @@
         </is>
       </c>
       <c r="D1118" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" s="6" t="inlineStr">
-        <is>
-          <t>7028002</t>
-        </is>
-      </c>
-      <c r="B1119" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1119" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1119" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" s="4" t="inlineStr">
-        <is>
-          <t>7027999</t>
-        </is>
-      </c>
-      <c r="B1120" s="5" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1120" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1120" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" s="6" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1121" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1121" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1121" s="6" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
         </is>
       </c>
     </row>
@@ -1238,6 +1238,85 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1381</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>931</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>544</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1279,7 +1358,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-14)</t>
+          <t>Lager (2026-07-15)</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1379,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>532</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3">
@@ -2026,7 +2105,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2046,7 +2125,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2066,7 +2145,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2086,7 +2165,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2106,7 +2185,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2126,7 +2205,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2146,7 +2225,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2166,7 +2245,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2186,7 +2265,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2206,7 +2285,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2226,7 +2305,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2246,7 +2325,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -2266,7 +2345,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2286,7 +2365,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -9560,7 +9639,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="416">
@@ -9640,7 +9719,7 @@
         </is>
       </c>
       <c r="D419" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="420">
@@ -18880,7 +18959,7 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>1294</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="882">
@@ -20720,7 +20799,7 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="974">
@@ -23600,7 +23679,7 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1118">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -548,67 +548,67 @@
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -1317,6 +1317,85 @@
         <v>0</v>
       </c>
       <c r="Y10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1385</v>
+      </c>
+      <c r="C11" t="n">
+        <v>916</v>
+      </c>
+      <c r="D11" t="n">
+        <v>544</v>
+      </c>
+      <c r="E11" t="n">
+        <v>231</v>
+      </c>
+      <c r="F11" t="n">
+        <v>225</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>52</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1331,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1118"/>
+  <dimension ref="A1:D1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1358,7 +1437,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-15)</t>
+          <t>Lager (2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2184,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2125,7 +2204,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2145,7 +2224,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2165,7 +2244,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2185,7 +2264,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2205,7 +2284,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2225,7 +2304,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2245,7 +2324,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2265,7 +2344,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2285,7 +2364,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2305,7 +2384,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2325,7 +2404,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -2345,7 +2424,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2365,7 +2444,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -9639,7 +9718,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="416">
@@ -18185,17 +18264,17 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D843" s="6" t="n">
@@ -18205,17 +18284,17 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D844" s="4" t="n">
@@ -18225,17 +18304,17 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D845" s="6" t="n">
@@ -18245,17 +18324,17 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D846" s="4" t="n">
@@ -18265,17 +18344,17 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D847" s="6" t="n">
@@ -18285,17 +18364,17 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D848" s="4" t="n">
@@ -18305,17 +18384,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -18325,17 +18404,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -18345,7 +18424,7 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -18365,7 +18444,7 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
@@ -18385,7 +18464,7 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -18405,7 +18484,7 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
@@ -18425,7 +18504,7 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -18445,7 +18524,7 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -18465,7 +18544,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -18485,7 +18564,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -18505,7 +18584,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -18525,7 +18604,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -18545,7 +18624,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -18565,7 +18644,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -18585,7 +18664,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -18605,7 +18684,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -18625,7 +18704,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -18645,7 +18724,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -18665,7 +18744,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -18685,7 +18764,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -18705,12 +18784,12 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -18725,12 +18804,12 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C870" s="5" t="inlineStr">
@@ -18745,12 +18824,12 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -18765,12 +18844,12 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C872" s="5" t="inlineStr">
@@ -18785,12 +18864,12 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -18805,12 +18884,12 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C874" s="5" t="inlineStr">
@@ -18819,18 +18898,18 @@
         </is>
       </c>
       <c r="D874" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -18839,18 +18918,18 @@
         </is>
       </c>
       <c r="D875" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -18865,12 +18944,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -18885,12 +18964,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -18905,12 +18984,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -18925,12 +19004,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -18945,12 +19024,12 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -18959,18 +19038,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -18979,18 +19058,18 @@
         </is>
       </c>
       <c r="D882" s="4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -18999,18 +19078,18 @@
         </is>
       </c>
       <c r="D883" s="6" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -19025,12 +19104,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -19045,12 +19124,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -19065,12 +19144,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -19085,12 +19164,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -19105,12 +19184,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -19119,18 +19198,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>0</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -19139,18 +19218,18 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -19159,18 +19238,18 @@
         </is>
       </c>
       <c r="D891" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -19185,12 +19264,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -19205,12 +19284,12 @@
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -19225,12 +19304,12 @@
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -19245,12 +19324,12 @@
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -19265,12 +19344,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -19285,12 +19364,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -19305,12 +19384,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -19319,18 +19398,18 @@
         </is>
       </c>
       <c r="D899" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -19345,12 +19424,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -19365,12 +19444,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -19385,12 +19464,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -19399,18 +19478,18 @@
         </is>
       </c>
       <c r="D903" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -19425,12 +19504,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -19445,12 +19524,12 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C906" s="5" t="inlineStr">
@@ -19465,12 +19544,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -19479,18 +19558,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -19505,12 +19584,12 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -19519,18 +19598,18 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -19545,12 +19624,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -19559,18 +19638,18 @@
         </is>
       </c>
       <c r="D911" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -19585,12 +19664,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -19605,12 +19684,12 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C914" s="5" t="inlineStr">
@@ -19625,12 +19704,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -19645,12 +19724,12 @@
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -19665,12 +19744,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -19679,18 +19758,18 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -19705,12 +19784,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -19725,12 +19804,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -19745,12 +19824,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -19765,12 +19844,12 @@
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -19785,12 +19864,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -19805,12 +19884,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -19825,12 +19904,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -19845,12 +19924,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -19865,12 +19944,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -19885,12 +19964,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -19905,12 +19984,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -19925,12 +20004,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -19945,12 +20024,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -19965,12 +20044,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -19985,12 +20064,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -20005,12 +20084,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -20025,12 +20104,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -20045,12 +20124,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -20065,12 +20144,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -20085,12 +20164,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -20105,12 +20184,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -20125,12 +20204,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -20145,12 +20224,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -20165,17 +20244,17 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7027837</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D942" s="4" t="n">
@@ -20185,17 +20264,17 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7027838</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D943" s="6" t="n">
@@ -20205,17 +20284,17 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7027841</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D944" s="4" t="n">
@@ -20225,17 +20304,17 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7027842</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D945" s="6" t="n">
@@ -20245,17 +20324,17 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7027835</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D946" s="4" t="n">
@@ -20265,17 +20344,17 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7027836</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D947" s="6" t="n">
@@ -20285,17 +20364,17 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7027839</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D948" s="4" t="n">
@@ -20305,17 +20384,17 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7027840</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D949" s="6" t="n">
@@ -20325,12 +20404,12 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027837</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -20345,12 +20424,12 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7027838</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -20365,12 +20444,12 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7027841</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -20385,12 +20464,12 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7027842</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -20405,12 +20484,12 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7027835</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
@@ -20425,12 +20504,12 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7027836</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -20445,12 +20524,12 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7027839</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
@@ -20465,12 +20544,12 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7027840</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -20485,7 +20564,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -20505,17 +20584,17 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D959" s="6" t="n">
@@ -20525,17 +20604,17 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D960" s="4" t="n">
@@ -20545,17 +20624,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -20565,17 +20644,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -20585,17 +20664,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -20605,17 +20684,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -20625,17 +20704,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -20645,17 +20724,17 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D966" s="4" t="n">
@@ -20665,17 +20744,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -20685,17 +20764,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -20705,7 +20784,7 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -20725,7 +20804,7 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
@@ -20745,7 +20824,7 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -20765,12 +20844,12 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
@@ -20785,12 +20864,12 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -20799,18 +20878,18 @@
         </is>
       </c>
       <c r="D973" s="6" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
@@ -20825,7 +20904,7 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -20845,7 +20924,7 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
@@ -20859,18 +20938,18 @@
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -20885,12 +20964,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -20905,12 +20984,12 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -20925,12 +21004,12 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -20945,12 +21024,12 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -20965,7 +21044,7 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
@@ -20985,7 +21064,7 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -21005,7 +21084,7 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
@@ -21025,17 +21104,17 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D985" s="6" t="n">
@@ -21045,17 +21124,17 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D986" s="4" t="n">
@@ -21065,17 +21144,17 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D987" s="6" t="n">
@@ -21085,7 +21164,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -21105,12 +21184,12 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -21125,12 +21204,12 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
@@ -21145,12 +21224,12 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -21165,12 +21244,12 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
@@ -21185,12 +21264,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -21205,7 +21284,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
@@ -21225,12 +21304,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -21245,12 +21324,12 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
@@ -21265,12 +21344,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -21285,12 +21364,12 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -21305,12 +21384,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -21325,7 +21404,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
@@ -21345,12 +21424,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -21365,12 +21444,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -21385,12 +21464,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -21405,7 +21484,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -21425,12 +21504,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -21445,12 +21524,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -21465,12 +21544,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -21485,7 +21564,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -21505,7 +21584,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -21525,7 +21604,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -21545,7 +21624,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -21565,7 +21644,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -21585,7 +21664,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -21605,7 +21684,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -21625,7 +21704,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -21645,7 +21724,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -21665,7 +21744,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -21685,7 +21764,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -21705,7 +21784,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -21725,7 +21804,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -21745,7 +21824,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -21765,7 +21844,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -21785,7 +21864,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -21805,7 +21884,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -21825,7 +21904,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -21845,7 +21924,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -21865,7 +21944,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -21885,7 +21964,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -21905,7 +21984,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -21925,7 +22004,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -21945,7 +22024,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -21965,7 +22044,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -21985,12 +22064,12 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -22005,12 +22084,12 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1034" s="5" t="inlineStr">
@@ -22025,12 +22104,12 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -22045,7 +22124,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -22065,7 +22144,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -22085,7 +22164,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -22105,7 +22184,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -22125,7 +22204,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -22145,7 +22224,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -22165,7 +22244,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -22185,7 +22264,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -22205,7 +22284,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -22225,7 +22304,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -22245,7 +22324,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -22265,7 +22344,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -22285,7 +22364,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -22305,7 +22384,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -22325,7 +22404,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -22345,7 +22424,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -22365,7 +22444,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -22385,7 +22464,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -22405,7 +22484,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -22425,7 +22504,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -22445,7 +22524,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -22465,7 +22544,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -22485,7 +22564,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -22505,7 +22584,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -22525,7 +22604,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -22545,7 +22624,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -22565,7 +22644,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -22585,7 +22664,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -22605,7 +22684,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -22625,7 +22704,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -22645,7 +22724,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -22665,7 +22744,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -22685,7 +22764,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -22705,12 +22784,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -22725,12 +22804,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -22745,12 +22824,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -22765,7 +22844,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -22785,7 +22864,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -22805,7 +22884,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -22825,7 +22904,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -22845,7 +22924,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -22865,7 +22944,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -22885,7 +22964,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -22905,7 +22984,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -22925,7 +23004,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -22945,12 +23024,12 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -22965,12 +23044,12 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1082" s="5" t="inlineStr">
@@ -22985,12 +23064,12 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -23005,7 +23084,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -23025,12 +23104,12 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -23045,12 +23124,12 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
@@ -23065,12 +23144,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -23085,12 +23164,12 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
@@ -23105,7 +23184,7 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -23125,12 +23204,12 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
@@ -23145,12 +23224,12 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -23165,12 +23244,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -23185,12 +23264,12 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -23205,12 +23284,12 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -23225,12 +23304,12 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -23245,12 +23324,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -23265,12 +23344,12 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -23285,7 +23364,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
@@ -23305,7 +23384,7 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -23325,7 +23404,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -23345,7 +23424,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -23365,7 +23444,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -23385,7 +23464,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -23405,7 +23484,7 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
@@ -23425,7 +23504,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -23445,7 +23524,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -23465,17 +23544,17 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1107" s="6" t="n">
@@ -23485,17 +23564,17 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1108" s="4" t="n">
@@ -23505,17 +23584,17 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1109" s="6" t="n">
@@ -23525,57 +23604,57 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1110" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1112" s="4" t="n">
@@ -23585,12 +23664,12 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -23599,18 +23678,18 @@
         </is>
       </c>
       <c r="D1113" s="6" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1114" s="5" t="inlineStr">
@@ -23619,18 +23698,18 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -23645,12 +23724,12 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1116" s="5" t="inlineStr">
@@ -23659,18 +23738,18 @@
         </is>
       </c>
       <c r="D1116" s="4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -23679,27 +23758,87 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>447</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
+          <t>7028001</t>
+        </is>
+      </c>
+      <c r="B1118" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1118" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1118" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="6" t="inlineStr">
+        <is>
+          <t>7028002</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1119" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="4" t="inlineStr">
+        <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1120" s="5" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1120" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1120" s="4" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="6" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1118" s="5" t="inlineStr">
+      <c r="B1121" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1118" s="5" t="inlineStr">
+      <c r="C1121" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1118" s="4" t="n">
-        <v>389</v>
+      <c r="D1121" s="6" t="n">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Hide-a-lite</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Tupex</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Hide-a-lite</t>
-        </is>
-      </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Let it light</t>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         <v>527</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>223</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>93</v>
@@ -707,10 +707,10 @@
         <v>527</v>
       </c>
       <c r="E3" t="n">
+        <v>223</v>
+      </c>
+      <c r="F3" t="n">
         <v>233</v>
-      </c>
-      <c r="F3" t="n">
-        <v>223</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
@@ -786,10 +786,10 @@
         <v>523</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>100</v>
@@ -865,10 +865,10 @@
         <v>522</v>
       </c>
       <c r="E5" t="n">
+        <v>221</v>
+      </c>
+      <c r="F5" t="n">
         <v>233</v>
-      </c>
-      <c r="F5" t="n">
-        <v>221</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -944,10 +944,10 @@
         <v>528</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>100</v>
@@ -1020,10 +1020,10 @@
         <v>920</v>
       </c>
       <c r="E7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F7" t="n">
         <v>232</v>
-      </c>
-      <c r="F7" t="n">
-        <v>215</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -1099,10 +1099,10 @@
         <v>528</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>100</v>
@@ -1178,10 +1178,10 @@
         <v>532</v>
       </c>
       <c r="E9" t="n">
+        <v>214</v>
+      </c>
+      <c r="F9" t="n">
         <v>232</v>
-      </c>
-      <c r="F9" t="n">
-        <v>214</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -1257,10 +1257,10 @@
         <v>544</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>231</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>218</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>100</v>
@@ -1336,10 +1336,10 @@
         <v>544</v>
       </c>
       <c r="E11" t="n">
+        <v>225</v>
+      </c>
+      <c r="F11" t="n">
         <v>231</v>
-      </c>
-      <c r="F11" t="n">
-        <v>225</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -1396,6 +1396,85 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>890</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>544</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1410,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1121"/>
+  <dimension ref="A1:D1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1437,7 +1516,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-16)</t>
+          <t>Lager (2026-07-17)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9703,7 @@
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
         <is>
-          <t>7013214</t>
+          <t>7013277</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -9644,7 +9723,7 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>7013277</t>
+          <t>7014513</t>
         </is>
       </c>
       <c r="B412" s="5" t="inlineStr">
@@ -9664,47 +9743,47 @@
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
         <is>
-          <t>7013649</t>
+          <t>7019640</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Tillbehör takarmatur Moln BAS/PRO LED</t>
+          <t>Infälld Interiörarmatur Sky</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Exaktor</t>
+          <t>Hide-a-lite</t>
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>7014513</t>
+          <t>7019641</t>
         </is>
       </c>
       <c r="B414" s="5" t="inlineStr">
         <is>
-          <t>Tillbehör takarmatur Moln BAS/PRO LED</t>
+          <t>Infälld Interiörarmatur Sky</t>
         </is>
       </c>
       <c r="C414" s="5" t="inlineStr">
         <is>
-          <t>Exaktor</t>
+          <t>Hide-a-lite</t>
         </is>
       </c>
       <c r="D414" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
         <is>
-          <t>7019640</t>
+          <t>7019642</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9718,13 +9797,13 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>7019641</t>
+          <t>7019643</t>
         </is>
       </c>
       <c r="B416" s="5" t="inlineStr">
@@ -9738,13 +9817,13 @@
         </is>
       </c>
       <c r="D416" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
-          <t>7019642</t>
+          <t>7019646</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -9758,13 +9837,13 @@
         </is>
       </c>
       <c r="D417" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>7019643</t>
+          <t>7019647</t>
         </is>
       </c>
       <c r="B418" s="5" t="inlineStr">
@@ -9778,13 +9857,13 @@
         </is>
       </c>
       <c r="D418" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
         <is>
-          <t>7019646</t>
+          <t>7019648</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -9798,13 +9877,13 @@
         </is>
       </c>
       <c r="D419" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>7019647</t>
+          <t>7019649</t>
         </is>
       </c>
       <c r="B420" s="5" t="inlineStr">
@@ -9818,13 +9897,13 @@
         </is>
       </c>
       <c r="D420" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
         <is>
-          <t>7019648</t>
+          <t>7019644</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -9844,7 +9923,7 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>7019649</t>
+          <t>7019645</t>
         </is>
       </c>
       <c r="B422" s="5" t="inlineStr">
@@ -9858,13 +9937,13 @@
         </is>
       </c>
       <c r="D422" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
         <is>
-          <t>7019644</t>
+          <t>7019650</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -9884,7 +9963,7 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>7019645</t>
+          <t>7019651</t>
         </is>
       </c>
       <c r="B424" s="5" t="inlineStr">
@@ -9898,13 +9977,13 @@
         </is>
       </c>
       <c r="D424" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
         <is>
-          <t>7019650</t>
+          <t>7027003</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -9924,7 +10003,7 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>7019651</t>
+          <t>7027004</t>
         </is>
       </c>
       <c r="B426" s="5" t="inlineStr">
@@ -9944,7 +10023,7 @@
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
         <is>
-          <t>7027003</t>
+          <t>7027005</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -9964,7 +10043,7 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>7027004</t>
+          <t>7027006</t>
         </is>
       </c>
       <c r="B428" s="5" t="inlineStr">
@@ -9984,7 +10063,7 @@
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
         <is>
-          <t>7027005</t>
+          <t>7027007</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -10004,7 +10083,7 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>7027006</t>
+          <t>7027008</t>
         </is>
       </c>
       <c r="B430" s="5" t="inlineStr">
@@ -10024,7 +10103,7 @@
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
         <is>
-          <t>7027007</t>
+          <t>7027009</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -10044,7 +10123,7 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>7027008</t>
+          <t>7027010</t>
         </is>
       </c>
       <c r="B432" s="5" t="inlineStr">
@@ -10064,7 +10143,7 @@
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
         <is>
-          <t>7027009</t>
+          <t>7027011</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -10084,7 +10163,7 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>7027010</t>
+          <t>7027012</t>
         </is>
       </c>
       <c r="B434" s="5" t="inlineStr">
@@ -10104,7 +10183,7 @@
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
         <is>
-          <t>7027011</t>
+          <t>7028423</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -10124,7 +10203,7 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>7027012</t>
+          <t>7028424</t>
         </is>
       </c>
       <c r="B436" s="5" t="inlineStr">
@@ -10144,7 +10223,7 @@
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
         <is>
-          <t>7028423</t>
+          <t>7028425</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -10164,7 +10243,7 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>7028424</t>
+          <t>7028426</t>
         </is>
       </c>
       <c r="B438" s="5" t="inlineStr">
@@ -10184,12 +10263,12 @@
     <row r="439">
       <c r="A439" s="6" t="inlineStr">
         <is>
-          <t>7028425</t>
+          <t>7028394</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Sky</t>
+          <t>Infälld interiörarmatur Sky CLO</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10204,12 +10283,12 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>7028426</t>
+          <t>7028395</t>
         </is>
       </c>
       <c r="B440" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Sky</t>
+          <t>Infälld interiörarmatur Sky CLO</t>
         </is>
       </c>
       <c r="C440" s="5" t="inlineStr">
@@ -10224,7 +10303,7 @@
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
         <is>
-          <t>7028394</t>
+          <t>7028396</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -10244,7 +10323,7 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>7028395</t>
+          <t>7028397</t>
         </is>
       </c>
       <c r="B442" s="5" t="inlineStr">
@@ -10264,17 +10343,17 @@
     <row r="443">
       <c r="A443" s="6" t="inlineStr">
         <is>
-          <t>7028396</t>
+          <t>7019215</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Sky CLO</t>
+          <t>Infälld armatur Indiviled</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Hide-a-lite</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D443" s="6" t="n">
@@ -10284,17 +10363,17 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>7028397</t>
+          <t>7019216</t>
         </is>
       </c>
       <c r="B444" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Sky CLO</t>
+          <t>Infälld armatur Indiviled</t>
         </is>
       </c>
       <c r="C444" s="5" t="inlineStr">
         <is>
-          <t>Hide-a-lite</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D444" s="4" t="n">
@@ -10304,12 +10383,12 @@
     <row r="445">
       <c r="A445" s="6" t="inlineStr">
         <is>
-          <t>7019215</t>
+          <t>7019227</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Infälld armatur Indiviled</t>
+          <t>Infälld armatur Performance</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10324,12 +10403,12 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>7019216</t>
+          <t>7019237</t>
         </is>
       </c>
       <c r="B446" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Indiviled</t>
+          <t>Infälld armatur Performance</t>
         </is>
       </c>
       <c r="C446" s="5" t="inlineStr">
@@ -10344,7 +10423,7 @@
     <row r="447">
       <c r="A447" s="6" t="inlineStr">
         <is>
-          <t>7019227</t>
+          <t>7021007</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -10358,13 +10437,13 @@
         </is>
       </c>
       <c r="D447" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>7019237</t>
+          <t>7021008</t>
         </is>
       </c>
       <c r="B448" s="5" t="inlineStr">
@@ -10384,12 +10463,12 @@
     <row r="449">
       <c r="A449" s="6" t="inlineStr">
         <is>
-          <t>7021007</t>
+          <t>7024350</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Infälld armatur Performance</t>
+          <t>Interiörarmatur Biolux HCL TW</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10398,18 +10477,18 @@
         </is>
       </c>
       <c r="D449" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>7021008</t>
+          <t>7024351</t>
         </is>
       </c>
       <c r="B450" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Performance</t>
+          <t>Interiörarmatur Biolux HCL TW</t>
         </is>
       </c>
       <c r="C450" s="5" t="inlineStr">
@@ -10424,12 +10503,12 @@
     <row r="451">
       <c r="A451" s="6" t="inlineStr">
         <is>
-          <t>7024350</t>
+          <t>7024374</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Interiörarmatur Biolux HCL TW</t>
+          <t>Interiörarmatur Comfort 1200x300</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10444,12 +10523,12 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>7024351</t>
+          <t>7024375</t>
         </is>
       </c>
       <c r="B452" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Biolux HCL TW</t>
+          <t>Interiörarmatur Comfort 1200x300</t>
         </is>
       </c>
       <c r="C452" s="5" t="inlineStr">
@@ -10464,7 +10543,7 @@
     <row r="453">
       <c r="A453" s="6" t="inlineStr">
         <is>
-          <t>7024374</t>
+          <t>7024378</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -10484,7 +10563,7 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>7024375</t>
+          <t>7024379</t>
         </is>
       </c>
       <c r="B454" s="5" t="inlineStr">
@@ -10504,7 +10583,7 @@
     <row r="455">
       <c r="A455" s="6" t="inlineStr">
         <is>
-          <t>7024378</t>
+          <t>7024397</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -10524,7 +10603,7 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>7024379</t>
+          <t>7024401</t>
         </is>
       </c>
       <c r="B456" s="5" t="inlineStr">
@@ -10544,12 +10623,12 @@
     <row r="457">
       <c r="A457" s="6" t="inlineStr">
         <is>
-          <t>7024397</t>
+          <t>7024404</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort 1200x300</t>
+          <t>Interiörarmatur Comfort 1200x600</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10564,12 +10643,12 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>7024401</t>
+          <t>7024352</t>
         </is>
       </c>
       <c r="B458" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort 1200x300</t>
+          <t>Interiörarmatur Comfort 600x600</t>
         </is>
       </c>
       <c r="C458" s="5" t="inlineStr">
@@ -10584,12 +10663,12 @@
     <row r="459">
       <c r="A459" s="6" t="inlineStr">
         <is>
-          <t>7024404</t>
+          <t>7024353</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort 1200x600</t>
+          <t>Interiörarmatur Comfort 600x600</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10604,7 +10683,7 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>7024352</t>
+          <t>7024354</t>
         </is>
       </c>
       <c r="B460" s="5" t="inlineStr">
@@ -10624,7 +10703,7 @@
     <row r="461">
       <c r="A461" s="6" t="inlineStr">
         <is>
-          <t>7024353</t>
+          <t>7024355</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -10644,7 +10723,7 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>7024354</t>
+          <t>7024360</t>
         </is>
       </c>
       <c r="B462" s="5" t="inlineStr">
@@ -10664,7 +10743,7 @@
     <row r="463">
       <c r="A463" s="6" t="inlineStr">
         <is>
-          <t>7024355</t>
+          <t>7024361</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -10684,7 +10763,7 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>7024360</t>
+          <t>7024362</t>
         </is>
       </c>
       <c r="B464" s="5" t="inlineStr">
@@ -10704,7 +10783,7 @@
     <row r="465">
       <c r="A465" s="6" t="inlineStr">
         <is>
-          <t>7024361</t>
+          <t>7024363</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -10724,7 +10803,7 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>7024362</t>
+          <t>7024364</t>
         </is>
       </c>
       <c r="B466" s="5" t="inlineStr">
@@ -10744,7 +10823,7 @@
     <row r="467">
       <c r="A467" s="6" t="inlineStr">
         <is>
-          <t>7024363</t>
+          <t>7024365</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -10764,7 +10843,7 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>7024364</t>
+          <t>7024366</t>
         </is>
       </c>
       <c r="B468" s="5" t="inlineStr">
@@ -10784,7 +10863,7 @@
     <row r="469">
       <c r="A469" s="6" t="inlineStr">
         <is>
-          <t>7024365</t>
+          <t>7024382</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -10798,13 +10877,13 @@
         </is>
       </c>
       <c r="D469" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>7024366</t>
+          <t>7024383</t>
         </is>
       </c>
       <c r="B470" s="5" t="inlineStr">
@@ -10818,13 +10897,13 @@
         </is>
       </c>
       <c r="D470" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="6" t="inlineStr">
         <is>
-          <t>7024382</t>
+          <t>7024384</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -10838,13 +10917,13 @@
         </is>
       </c>
       <c r="D471" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>7024383</t>
+          <t>7024390</t>
         </is>
       </c>
       <c r="B472" s="5" t="inlineStr">
@@ -10858,13 +10937,13 @@
         </is>
       </c>
       <c r="D472" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="6" t="inlineStr">
         <is>
-          <t>7024384</t>
+          <t>7024391</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -10884,7 +10963,7 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>7024390</t>
+          <t>7024392</t>
         </is>
       </c>
       <c r="B474" s="5" t="inlineStr">
@@ -10904,12 +10983,12 @@
     <row r="475">
       <c r="A475" s="6" t="inlineStr">
         <is>
-          <t>7024391</t>
+          <t>7024376</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort 600x600</t>
+          <t>Interiörarmatur Comfort UGR19 1200x300</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10924,12 +11003,12 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>7024392</t>
+          <t>7024377</t>
         </is>
       </c>
       <c r="B476" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort 600x600</t>
+          <t>Interiörarmatur Comfort UGR19 1200x300</t>
         </is>
       </c>
       <c r="C476" s="5" t="inlineStr">
@@ -10944,7 +11023,7 @@
     <row r="477">
       <c r="A477" s="6" t="inlineStr">
         <is>
-          <t>7024376</t>
+          <t>7024380</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -10964,7 +11043,7 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>7024377</t>
+          <t>7024381</t>
         </is>
       </c>
       <c r="B478" s="5" t="inlineStr">
@@ -10984,7 +11063,7 @@
     <row r="479">
       <c r="A479" s="6" t="inlineStr">
         <is>
-          <t>7024380</t>
+          <t>7024398</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -11004,7 +11083,7 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>7024381</t>
+          <t>7024399</t>
         </is>
       </c>
       <c r="B480" s="5" t="inlineStr">
@@ -11024,7 +11103,7 @@
     <row r="481">
       <c r="A481" s="6" t="inlineStr">
         <is>
-          <t>7024398</t>
+          <t>7024402</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -11044,7 +11123,7 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>7024399</t>
+          <t>7024403</t>
         </is>
       </c>
       <c r="B482" s="5" t="inlineStr">
@@ -11064,12 +11143,12 @@
     <row r="483">
       <c r="A483" s="6" t="inlineStr">
         <is>
-          <t>7024402</t>
+          <t>7024400</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort UGR19 1200x300</t>
+          <t>Interiörarmatur Comfort UGR19 1200x600</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -11084,12 +11163,12 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>7024403</t>
+          <t>7024356</t>
         </is>
       </c>
       <c r="B484" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort UGR19 1200x300</t>
+          <t>Interiörarmatur Comfort UGR19 600x600</t>
         </is>
       </c>
       <c r="C484" s="5" t="inlineStr">
@@ -11104,12 +11183,12 @@
     <row r="485">
       <c r="A485" s="6" t="inlineStr">
         <is>
-          <t>7024400</t>
+          <t>7024357</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort UGR19 1200x600</t>
+          <t>Interiörarmatur Comfort UGR19 600x600</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11124,7 +11203,7 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>7024356</t>
+          <t>7024358</t>
         </is>
       </c>
       <c r="B486" s="5" t="inlineStr">
@@ -11144,7 +11223,7 @@
     <row r="487">
       <c r="A487" s="6" t="inlineStr">
         <is>
-          <t>7024357</t>
+          <t>7024359</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -11164,7 +11243,7 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>7024358</t>
+          <t>7024367</t>
         </is>
       </c>
       <c r="B488" s="5" t="inlineStr">
@@ -11184,7 +11263,7 @@
     <row r="489">
       <c r="A489" s="6" t="inlineStr">
         <is>
-          <t>7024359</t>
+          <t>7024368</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -11204,7 +11283,7 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>7024367</t>
+          <t>7024369</t>
         </is>
       </c>
       <c r="B490" s="5" t="inlineStr">
@@ -11224,7 +11303,7 @@
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
         <is>
-          <t>7024368</t>
+          <t>7024370</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -11244,7 +11323,7 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>7024369</t>
+          <t>7024371</t>
         </is>
       </c>
       <c r="B492" s="5" t="inlineStr">
@@ -11264,7 +11343,7 @@
     <row r="493">
       <c r="A493" s="6" t="inlineStr">
         <is>
-          <t>7024370</t>
+          <t>7024372</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -11284,7 +11363,7 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>7024371</t>
+          <t>7024373</t>
         </is>
       </c>
       <c r="B494" s="5" t="inlineStr">
@@ -11304,7 +11383,7 @@
     <row r="495">
       <c r="A495" s="6" t="inlineStr">
         <is>
-          <t>7024372</t>
+          <t>7024386</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -11324,7 +11403,7 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>7024373</t>
+          <t>7024387</t>
         </is>
       </c>
       <c r="B496" s="5" t="inlineStr">
@@ -11344,7 +11423,7 @@
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
         <is>
-          <t>7024386</t>
+          <t>7024388</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -11364,7 +11443,7 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>7024387</t>
+          <t>7024389</t>
         </is>
       </c>
       <c r="B498" s="5" t="inlineStr">
@@ -11384,7 +11463,7 @@
     <row r="499">
       <c r="A499" s="6" t="inlineStr">
         <is>
-          <t>7024388</t>
+          <t>7024394</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -11404,7 +11483,7 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>7024389</t>
+          <t>7024395</t>
         </is>
       </c>
       <c r="B500" s="5" t="inlineStr">
@@ -11424,7 +11503,7 @@
     <row r="501">
       <c r="A501" s="6" t="inlineStr">
         <is>
-          <t>7024394</t>
+          <t>7024396</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -11444,7 +11523,7 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>7024395</t>
+          <t>7027289</t>
         </is>
       </c>
       <c r="B502" s="5" t="inlineStr">
@@ -11464,7 +11543,7 @@
     <row r="503">
       <c r="A503" s="6" t="inlineStr">
         <is>
-          <t>7024396</t>
+          <t>7027290</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -11484,12 +11563,12 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>7027289</t>
+          <t>7029544</t>
         </is>
       </c>
       <c r="B504" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort UGR19 600x600</t>
+          <t>Interiörarmatur IndiviLED Dali, 1200</t>
         </is>
       </c>
       <c r="C504" s="5" t="inlineStr">
@@ -11504,12 +11583,12 @@
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
         <is>
-          <t>7027290</t>
+          <t>7029545</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Interiörarmatur Comfort UGR19 600x600</t>
+          <t>Interiörarmatur IndiviLED Dali, 1200</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11524,7 +11603,7 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>7029544</t>
+          <t>7029546</t>
         </is>
       </c>
       <c r="B506" s="5" t="inlineStr">
@@ -11544,7 +11623,7 @@
     <row r="507">
       <c r="A507" s="6" t="inlineStr">
         <is>
-          <t>7029545</t>
+          <t>7029547</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -11564,12 +11643,12 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>7029546</t>
+          <t>7029540</t>
         </is>
       </c>
       <c r="B508" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IndiviLED Dali, 1200</t>
+          <t>Interiörarmatur IndiviLED Dali, 600</t>
         </is>
       </c>
       <c r="C508" s="5" t="inlineStr">
@@ -11584,12 +11663,12 @@
     <row r="509">
       <c r="A509" s="6" t="inlineStr">
         <is>
-          <t>7029547</t>
+          <t>7029541</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Interiörarmatur IndiviLED Dali, 1200</t>
+          <t>Interiörarmatur IndiviLED Dali, 600</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -11604,7 +11683,7 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>7029540</t>
+          <t>7029542</t>
         </is>
       </c>
       <c r="B510" s="5" t="inlineStr">
@@ -11624,7 +11703,7 @@
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
         <is>
-          <t>7029541</t>
+          <t>7029543</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -11644,12 +11723,12 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>7029542</t>
+          <t>7019467</t>
         </is>
       </c>
       <c r="B512" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IndiviLED Dali, 600</t>
+          <t>Interiörarmatur IndiviLED VR ZB</t>
         </is>
       </c>
       <c r="C512" s="5" t="inlineStr">
@@ -11664,12 +11743,12 @@
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
         <is>
-          <t>7029543</t>
+          <t>7019744</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Interiörarmatur IndiviLED Dali, 600</t>
+          <t>Interiörarmatur Panel 600 smart + Wifi RGBW</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -11684,12 +11763,12 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>7019467</t>
+          <t>7029504</t>
         </is>
       </c>
       <c r="B514" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IndiviLED VR ZB</t>
+          <t>Interiörarmatur Panel Compact 1200x300</t>
         </is>
       </c>
       <c r="C514" s="5" t="inlineStr">
@@ -11704,12 +11783,12 @@
     <row r="515">
       <c r="A515" s="6" t="inlineStr">
         <is>
-          <t>7019744</t>
+          <t>7029505</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel 600 smart + Wifi RGBW</t>
+          <t>Interiörarmatur Panel Compact 1200x300</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11724,7 +11803,7 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>7029504</t>
+          <t>7029506</t>
         </is>
       </c>
       <c r="B516" s="5" t="inlineStr">
@@ -11744,7 +11823,7 @@
     <row r="517">
       <c r="A517" s="6" t="inlineStr">
         <is>
-          <t>7029505</t>
+          <t>7029507</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -11764,7 +11843,7 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>7029506</t>
+          <t>7029508</t>
         </is>
       </c>
       <c r="B518" s="5" t="inlineStr">
@@ -11784,7 +11863,7 @@
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
         <is>
-          <t>7029507</t>
+          <t>7029509</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -11804,7 +11883,7 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>7029508</t>
+          <t>7029510</t>
         </is>
       </c>
       <c r="B520" s="5" t="inlineStr">
@@ -11824,7 +11903,7 @@
     <row r="521">
       <c r="A521" s="6" t="inlineStr">
         <is>
-          <t>7029509</t>
+          <t>7029511</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -11844,7 +11923,7 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>7029510</t>
+          <t>7029512</t>
         </is>
       </c>
       <c r="B522" s="5" t="inlineStr">
@@ -11864,7 +11943,7 @@
     <row r="523">
       <c r="A523" s="6" t="inlineStr">
         <is>
-          <t>7029511</t>
+          <t>7029513</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -11884,7 +11963,7 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>7029512</t>
+          <t>7029514</t>
         </is>
       </c>
       <c r="B524" s="5" t="inlineStr">
@@ -11904,7 +11983,7 @@
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
         <is>
-          <t>7029513</t>
+          <t>7029515</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -11924,12 +12003,12 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>7029514</t>
+          <t>7026615</t>
         </is>
       </c>
       <c r="B526" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 1200x300</t>
+          <t>Interiörarmatur Panel Compact 1200x600</t>
         </is>
       </c>
       <c r="C526" s="5" t="inlineStr">
@@ -11944,12 +12023,12 @@
     <row r="527">
       <c r="A527" s="6" t="inlineStr">
         <is>
-          <t>7029515</t>
+          <t>7029516</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 1200x300</t>
+          <t>Interiörarmatur Panel Compact 1200x600</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -11964,7 +12043,7 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>7026615</t>
+          <t>7029517</t>
         </is>
       </c>
       <c r="B528" s="5" t="inlineStr">
@@ -11984,7 +12063,7 @@
     <row r="529">
       <c r="A529" s="6" t="inlineStr">
         <is>
-          <t>7029516</t>
+          <t>7029518</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -12004,7 +12083,7 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>7029517</t>
+          <t>7029519</t>
         </is>
       </c>
       <c r="B530" s="5" t="inlineStr">
@@ -12024,12 +12103,12 @@
     <row r="531">
       <c r="A531" s="6" t="inlineStr">
         <is>
-          <t>7029518</t>
+          <t>7029486</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 1200x600</t>
+          <t>Interiörarmatur Panel Compact 600x600</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -12044,12 +12123,12 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>7029519</t>
+          <t>7029487</t>
         </is>
       </c>
       <c r="B532" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 1200x600</t>
+          <t>Interiörarmatur Panel Compact 600x600</t>
         </is>
       </c>
       <c r="C532" s="5" t="inlineStr">
@@ -12064,7 +12143,7 @@
     <row r="533">
       <c r="A533" s="6" t="inlineStr">
         <is>
-          <t>7029486</t>
+          <t>7029488</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -12084,7 +12163,7 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>7029487</t>
+          <t>7029489</t>
         </is>
       </c>
       <c r="B534" s="5" t="inlineStr">
@@ -12104,7 +12183,7 @@
     <row r="535">
       <c r="A535" s="6" t="inlineStr">
         <is>
-          <t>7029488</t>
+          <t>7029490</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -12124,7 +12203,7 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>7029489</t>
+          <t>7029491</t>
         </is>
       </c>
       <c r="B536" s="5" t="inlineStr">
@@ -12144,7 +12223,7 @@
     <row r="537">
       <c r="A537" s="6" t="inlineStr">
         <is>
-          <t>7029490</t>
+          <t>7029492</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -12164,7 +12243,7 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>7029491</t>
+          <t>7029493</t>
         </is>
       </c>
       <c r="B538" s="5" t="inlineStr">
@@ -12184,7 +12263,7 @@
     <row r="539">
       <c r="A539" s="6" t="inlineStr">
         <is>
-          <t>7029492</t>
+          <t>7029494</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -12204,7 +12283,7 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>7029493</t>
+          <t>7029495</t>
         </is>
       </c>
       <c r="B540" s="5" t="inlineStr">
@@ -12224,7 +12303,7 @@
     <row r="541">
       <c r="A541" s="6" t="inlineStr">
         <is>
-          <t>7029494</t>
+          <t>7029496</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -12244,7 +12323,7 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>7029495</t>
+          <t>7029497</t>
         </is>
       </c>
       <c r="B542" s="5" t="inlineStr">
@@ -12264,7 +12343,7 @@
     <row r="543">
       <c r="A543" s="6" t="inlineStr">
         <is>
-          <t>7029496</t>
+          <t>7029498</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -12284,7 +12363,7 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>7029497</t>
+          <t>7029499</t>
         </is>
       </c>
       <c r="B544" s="5" t="inlineStr">
@@ -12304,7 +12383,7 @@
     <row r="545">
       <c r="A545" s="6" t="inlineStr">
         <is>
-          <t>7029498</t>
+          <t>7029500</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -12324,7 +12403,7 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>7029499</t>
+          <t>7029501</t>
         </is>
       </c>
       <c r="B546" s="5" t="inlineStr">
@@ -12344,7 +12423,7 @@
     <row r="547">
       <c r="A547" s="6" t="inlineStr">
         <is>
-          <t>7029500</t>
+          <t>7029502</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -12364,7 +12443,7 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>7029501</t>
+          <t>7029503</t>
         </is>
       </c>
       <c r="B548" s="5" t="inlineStr">
@@ -12384,12 +12463,12 @@
     <row r="549">
       <c r="A549" s="6" t="inlineStr">
         <is>
-          <t>7029502</t>
+          <t>7027829</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 600x600</t>
+          <t>Interiörarmatur Panel Flex 600</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -12404,12 +12483,12 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>7029503</t>
+          <t>7027830</t>
         </is>
       </c>
       <c r="B550" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Compact 600x600</t>
+          <t>Interiörarmatur Panel Flex 600</t>
         </is>
       </c>
       <c r="C550" s="5" t="inlineStr">
@@ -12424,7 +12503,7 @@
     <row r="551">
       <c r="A551" s="6" t="inlineStr">
         <is>
-          <t>7027829</t>
+          <t>7027831</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -12444,7 +12523,7 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>7027830</t>
+          <t>7027832</t>
         </is>
       </c>
       <c r="B552" s="5" t="inlineStr">
@@ -12464,7 +12543,7 @@
     <row r="553">
       <c r="A553" s="6" t="inlineStr">
         <is>
-          <t>7027831</t>
+          <t>7027833</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -12484,7 +12563,7 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>7027832</t>
+          <t>7027834</t>
         </is>
       </c>
       <c r="B554" s="5" t="inlineStr">
@@ -12504,12 +12583,12 @@
     <row r="555">
       <c r="A555" s="6" t="inlineStr">
         <is>
-          <t>7027833</t>
+          <t>7028850</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Flex 600</t>
+          <t>Interiörarmatur Print Sky</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -12524,12 +12603,12 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>7027834</t>
+          <t>7028851</t>
         </is>
       </c>
       <c r="B556" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Panel Flex 600</t>
+          <t>Interiörarmatur Print Sky</t>
         </is>
       </c>
       <c r="C556" s="5" t="inlineStr">
@@ -12544,7 +12623,7 @@
     <row r="557">
       <c r="A557" s="6" t="inlineStr">
         <is>
-          <t>7028850</t>
+          <t>7028852</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -12564,7 +12643,7 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>7028851</t>
+          <t>7028853</t>
         </is>
       </c>
       <c r="B558" s="5" t="inlineStr">
@@ -12584,7 +12663,7 @@
     <row r="559">
       <c r="A559" s="6" t="inlineStr">
         <is>
-          <t>7028852</t>
+          <t>7028854</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -12604,7 +12683,7 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>7028853</t>
+          <t>7028855</t>
         </is>
       </c>
       <c r="B560" s="5" t="inlineStr">
@@ -12624,12 +12703,12 @@
     <row r="561">
       <c r="A561" s="6" t="inlineStr">
         <is>
-          <t>7028854</t>
+          <t>7026608</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Interiörarmatur Print Sky</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -12644,12 +12723,12 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>7028855</t>
+          <t>7026609</t>
         </is>
       </c>
       <c r="B562" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Print Sky</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C562" s="5" t="inlineStr">
@@ -12664,7 +12743,7 @@
     <row r="563">
       <c r="A563" s="6" t="inlineStr">
         <is>
-          <t>7026608</t>
+          <t>7026610</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -12684,7 +12763,7 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>7026609</t>
+          <t>7026611</t>
         </is>
       </c>
       <c r="B564" s="5" t="inlineStr">
@@ -12704,7 +12783,7 @@
     <row r="565">
       <c r="A565" s="6" t="inlineStr">
         <is>
-          <t>7026610</t>
+          <t>7026612</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -12724,7 +12803,7 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>7026611</t>
+          <t>7026613</t>
         </is>
       </c>
       <c r="B566" s="5" t="inlineStr">
@@ -12744,12 +12823,12 @@
     <row r="567">
       <c r="A567" s="6" t="inlineStr">
         <is>
-          <t>7026612</t>
+          <t>7029551</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Smart + Panel RGBTW</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -12764,12 +12843,12 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>7026613</t>
+          <t>7029548</t>
         </is>
       </c>
       <c r="B568" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Smart + Panel RGBW</t>
         </is>
       </c>
       <c r="C568" s="5" t="inlineStr">
@@ -12784,12 +12863,12 @@
     <row r="569">
       <c r="A569" s="6" t="inlineStr">
         <is>
-          <t>7029551</t>
+          <t>7029549</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBTW</t>
+          <t>Interiörarmatur Smart + Panel RGBW</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -12804,7 +12883,7 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>7029548</t>
+          <t>7029550</t>
         </is>
       </c>
       <c r="B570" s="5" t="inlineStr">
@@ -12824,17 +12903,17 @@
     <row r="571">
       <c r="A571" s="6" t="inlineStr">
         <is>
-          <t>7029549</t>
+          <t>7028787</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBW</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Ledvance</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D571" s="6" t="n">
@@ -12844,17 +12923,17 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>7029550</t>
+          <t>7028795</t>
         </is>
       </c>
       <c r="B572" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBW</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C572" s="5" t="inlineStr">
         <is>
-          <t>Ledvance</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D572" s="4" t="n">
@@ -12864,7 +12943,7 @@
     <row r="573">
       <c r="A573" s="6" t="inlineStr">
         <is>
-          <t>7028787</t>
+          <t>7028788</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -12884,7 +12963,7 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>7028795</t>
+          <t>7028796</t>
         </is>
       </c>
       <c r="B574" s="5" t="inlineStr">
@@ -12904,7 +12983,7 @@
     <row r="575">
       <c r="A575" s="6" t="inlineStr">
         <is>
-          <t>7028788</t>
+          <t>7028783</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -12924,7 +13003,7 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>7028796</t>
+          <t>7028791</t>
         </is>
       </c>
       <c r="B576" s="5" t="inlineStr">
@@ -12944,7 +13023,7 @@
     <row r="577">
       <c r="A577" s="6" t="inlineStr">
         <is>
-          <t>7028783</t>
+          <t>7028784</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -12964,7 +13043,7 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>7028791</t>
+          <t>7028792</t>
         </is>
       </c>
       <c r="B578" s="5" t="inlineStr">
@@ -12984,7 +13063,7 @@
     <row r="579">
       <c r="A579" s="6" t="inlineStr">
         <is>
-          <t>7028784</t>
+          <t>7028807</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -13004,7 +13083,7 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>7028792</t>
+          <t>7028808</t>
         </is>
       </c>
       <c r="B580" s="5" t="inlineStr">
@@ -13024,7 +13103,7 @@
     <row r="581">
       <c r="A581" s="6" t="inlineStr">
         <is>
-          <t>7028807</t>
+          <t>7028809</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -13044,7 +13123,7 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>7028808</t>
+          <t>7028810</t>
         </is>
       </c>
       <c r="B582" s="5" t="inlineStr">
@@ -13064,7 +13143,7 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>7028809</t>
+          <t>7028799</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -13084,7 +13163,7 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>7028810</t>
+          <t>7028800</t>
         </is>
       </c>
       <c r="B584" s="5" t="inlineStr">
@@ -13104,7 +13183,7 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>7028799</t>
+          <t>7028801</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -13124,7 +13203,7 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>7028800</t>
+          <t>7028802</t>
         </is>
       </c>
       <c r="B586" s="5" t="inlineStr">
@@ -13144,7 +13223,7 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>7028801</t>
+          <t>7028816</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -13164,7 +13243,7 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>7028802</t>
+          <t>7028815</t>
         </is>
       </c>
       <c r="B588" s="5" t="inlineStr">
@@ -13184,7 +13263,7 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>7028816</t>
+          <t>7028819</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -13204,7 +13283,7 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>7028815</t>
+          <t>7028820</t>
         </is>
       </c>
       <c r="B590" s="5" t="inlineStr">
@@ -13224,12 +13303,12 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>7028819</t>
+          <t>7028789</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -13244,12 +13323,12 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>7028820</t>
+          <t>7028797</t>
         </is>
       </c>
       <c r="B592" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C592" s="5" t="inlineStr">
@@ -13264,7 +13343,7 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>7028789</t>
+          <t>7028790</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -13284,7 +13363,7 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>7028797</t>
+          <t>7028798</t>
         </is>
       </c>
       <c r="B594" s="5" t="inlineStr">
@@ -13304,7 +13383,7 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>7028790</t>
+          <t>7028785</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -13324,7 +13403,7 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>7028798</t>
+          <t>7028793</t>
         </is>
       </c>
       <c r="B596" s="5" t="inlineStr">
@@ -13344,7 +13423,7 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>7028785</t>
+          <t>7028786</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -13364,7 +13443,7 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>7028793</t>
+          <t>7028794</t>
         </is>
       </c>
       <c r="B598" s="5" t="inlineStr">
@@ -13384,7 +13463,7 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>7028786</t>
+          <t>7028811</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -13404,7 +13483,7 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>7028794</t>
+          <t>7028812</t>
         </is>
       </c>
       <c r="B600" s="5" t="inlineStr">
@@ -13424,7 +13503,7 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>7028811</t>
+          <t>7028813</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -13444,7 +13523,7 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>7028812</t>
+          <t>7028814</t>
         </is>
       </c>
       <c r="B602" s="5" t="inlineStr">
@@ -13464,7 +13543,7 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>7028813</t>
+          <t>7028803</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -13484,7 +13563,7 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>7028814</t>
+          <t>7028804</t>
         </is>
       </c>
       <c r="B604" s="5" t="inlineStr">
@@ -13504,7 +13583,7 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>7028803</t>
+          <t>7028805</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -13524,7 +13603,7 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>7028804</t>
+          <t>7028806</t>
         </is>
       </c>
       <c r="B606" s="5" t="inlineStr">
@@ -13544,7 +13623,7 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>7028805</t>
+          <t>7028818</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -13564,7 +13643,7 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>7028806</t>
+          <t>7028817</t>
         </is>
       </c>
       <c r="B608" s="5" t="inlineStr">
@@ -13584,7 +13663,7 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>7028818</t>
+          <t>7028821</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -13604,7 +13683,7 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>7028817</t>
+          <t>7028822</t>
         </is>
       </c>
       <c r="B610" s="5" t="inlineStr">
@@ -13624,17 +13703,17 @@
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>7028821</t>
+          <t>7019477</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld interiörarmatur Cefalu</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D611" s="6" t="n">
@@ -13644,17 +13723,17 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>7028822</t>
+          <t>7021120</t>
         </is>
       </c>
       <c r="B612" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld interiörarmatur Grönby</t>
         </is>
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D612" s="4" t="n">
@@ -13664,12 +13743,12 @@
     <row r="613">
       <c r="A613" s="6" t="inlineStr">
         <is>
-          <t>7019477</t>
+          <t>7021121</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Cefalu</t>
+          <t>Infälld interiörarmatur Grönby</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -13678,13 +13757,13 @@
         </is>
       </c>
       <c r="D613" s="6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>7021120</t>
+          <t>7021122</t>
         </is>
       </c>
       <c r="B614" s="5" t="inlineStr">
@@ -13698,18 +13777,18 @@
         </is>
       </c>
       <c r="D614" s="4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="6" t="inlineStr">
         <is>
-          <t>7021121</t>
+          <t>7012494</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Grönby</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -13718,18 +13797,18 @@
         </is>
       </c>
       <c r="D615" s="6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>7021122</t>
+          <t>7012495</t>
         </is>
       </c>
       <c r="B616" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Grönby</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C616" s="5" t="inlineStr">
@@ -13738,13 +13817,13 @@
         </is>
       </c>
       <c r="D616" s="4" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="6" t="inlineStr">
         <is>
-          <t>7012494</t>
+          <t>7012496</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -13764,7 +13843,7 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>7012495</t>
+          <t>7012497</t>
         </is>
       </c>
       <c r="B618" s="5" t="inlineStr">
@@ -13784,7 +13863,7 @@
     <row r="619">
       <c r="A619" s="6" t="inlineStr">
         <is>
-          <t>7012496</t>
+          <t>7015180</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -13804,7 +13883,7 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>7012497</t>
+          <t>7015181</t>
         </is>
       </c>
       <c r="B620" s="5" t="inlineStr">
@@ -13824,7 +13903,7 @@
     <row r="621">
       <c r="A621" s="6" t="inlineStr">
         <is>
-          <t>7015180</t>
+          <t>7050196</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -13844,7 +13923,7 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>7015181</t>
+          <t>7050197</t>
         </is>
       </c>
       <c r="B622" s="5" t="inlineStr">
@@ -13864,7 +13943,7 @@
     <row r="623">
       <c r="A623" s="6" t="inlineStr">
         <is>
-          <t>7050196</t>
+          <t>7012498</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -13884,7 +13963,7 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>7050197</t>
+          <t>7012499</t>
         </is>
       </c>
       <c r="B624" s="5" t="inlineStr">
@@ -13904,7 +13983,7 @@
     <row r="625">
       <c r="A625" s="6" t="inlineStr">
         <is>
-          <t>7012498</t>
+          <t>7012500</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -13924,7 +14003,7 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>7012499</t>
+          <t>7012501</t>
         </is>
       </c>
       <c r="B626" s="5" t="inlineStr">
@@ -13944,7 +14023,7 @@
     <row r="627">
       <c r="A627" s="6" t="inlineStr">
         <is>
-          <t>7012500</t>
+          <t>7013292</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -13964,7 +14043,7 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>7012501</t>
+          <t>7013293</t>
         </is>
       </c>
       <c r="B628" s="5" t="inlineStr">
@@ -13984,12 +14063,12 @@
     <row r="629">
       <c r="A629" s="6" t="inlineStr">
         <is>
-          <t>7013292</t>
+          <t>7019475</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -13998,18 +14077,18 @@
         </is>
       </c>
       <c r="D629" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>7013293</t>
+          <t>7019476</t>
         </is>
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C630" s="5" t="inlineStr">
@@ -14024,37 +14103,37 @@
     <row r="631">
       <c r="A631" s="6" t="inlineStr">
         <is>
-          <t>7019475</t>
+          <t>7013795</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D631" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>7019476</t>
+          <t>7013796</t>
         </is>
       </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D632" s="4" t="n">
@@ -14064,7 +14143,7 @@
     <row r="633">
       <c r="A633" s="6" t="inlineStr">
         <is>
-          <t>7013795</t>
+          <t>7013797</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -14084,7 +14163,7 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>7013796</t>
+          <t>7013798</t>
         </is>
       </c>
       <c r="B634" s="5" t="inlineStr">
@@ -14104,7 +14183,7 @@
     <row r="635">
       <c r="A635" s="6" t="inlineStr">
         <is>
-          <t>7013797</t>
+          <t>7018767</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -14124,7 +14203,7 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>7013798</t>
+          <t>7018768</t>
         </is>
       </c>
       <c r="B636" s="5" t="inlineStr">
@@ -14144,7 +14223,7 @@
     <row r="637">
       <c r="A637" s="6" t="inlineStr">
         <is>
-          <t>7018767</t>
+          <t>7018769</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -14164,7 +14243,7 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>7018768</t>
+          <t>7018771</t>
         </is>
       </c>
       <c r="B638" s="5" t="inlineStr">
@@ -14184,7 +14263,7 @@
     <row r="639">
       <c r="A639" s="6" t="inlineStr">
         <is>
-          <t>7018769</t>
+          <t>7019623</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -14204,7 +14283,7 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>7018771</t>
+          <t>7019624</t>
         </is>
       </c>
       <c r="B640" s="5" t="inlineStr">
@@ -14224,7 +14303,7 @@
     <row r="641">
       <c r="A641" s="6" t="inlineStr">
         <is>
-          <t>7019623</t>
+          <t>7019653</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -14244,7 +14323,7 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>7019624</t>
+          <t>7019654</t>
         </is>
       </c>
       <c r="B642" s="5" t="inlineStr">
@@ -14264,12 +14343,12 @@
     <row r="643">
       <c r="A643" s="6" t="inlineStr">
         <is>
-          <t>7019653</t>
+          <t>7011878</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -14284,12 +14363,12 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>7019654</t>
+          <t>7013748</t>
         </is>
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
@@ -14304,7 +14383,7 @@
     <row r="645">
       <c r="A645" s="6" t="inlineStr">
         <is>
-          <t>7011878</t>
+          <t>7011879</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -14324,7 +14403,7 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>7013748</t>
+          <t>7013749</t>
         </is>
       </c>
       <c r="B646" s="5" t="inlineStr">
@@ -14344,7 +14423,7 @@
     <row r="647">
       <c r="A647" s="6" t="inlineStr">
         <is>
-          <t>7011879</t>
+          <t>7011548</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -14364,7 +14443,7 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>7013749</t>
+          <t>7011549</t>
         </is>
       </c>
       <c r="B648" s="5" t="inlineStr">
@@ -14384,7 +14463,7 @@
     <row r="649">
       <c r="A649" s="6" t="inlineStr">
         <is>
-          <t>7011548</t>
+          <t>7011550</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -14404,7 +14483,7 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>7011549</t>
+          <t>7011554</t>
         </is>
       </c>
       <c r="B650" s="5" t="inlineStr">
@@ -14424,12 +14503,12 @@
     <row r="651">
       <c r="A651" s="6" t="inlineStr">
         <is>
-          <t>7011550</t>
+          <t>7010891</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -14444,12 +14523,12 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>7011554</t>
+          <t>7010892</t>
         </is>
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
@@ -14464,7 +14543,7 @@
     <row r="653">
       <c r="A653" s="6" t="inlineStr">
         <is>
-          <t>7010891</t>
+          <t>7010893</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -14484,7 +14563,7 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>7010892</t>
+          <t>7010894</t>
         </is>
       </c>
       <c r="B654" s="5" t="inlineStr">
@@ -14504,7 +14583,7 @@
     <row r="655">
       <c r="A655" s="6" t="inlineStr">
         <is>
-          <t>7010893</t>
+          <t>7010895</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -14524,7 +14603,7 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>7010894</t>
+          <t>7010896</t>
         </is>
       </c>
       <c r="B656" s="5" t="inlineStr">
@@ -14544,7 +14623,7 @@
     <row r="657">
       <c r="A657" s="6" t="inlineStr">
         <is>
-          <t>7010895</t>
+          <t>7010897</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -14564,7 +14643,7 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>7010896</t>
+          <t>7010898</t>
         </is>
       </c>
       <c r="B658" s="5" t="inlineStr">
@@ -14584,7 +14663,7 @@
     <row r="659">
       <c r="A659" s="6" t="inlineStr">
         <is>
-          <t>7010897</t>
+          <t>7016266</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -14604,7 +14683,7 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>7010898</t>
+          <t>7016267E</t>
         </is>
       </c>
       <c r="B660" s="5" t="inlineStr">
@@ -14624,7 +14703,7 @@
     <row r="661">
       <c r="A661" s="6" t="inlineStr">
         <is>
-          <t>7016266</t>
+          <t>7016268</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -14644,7 +14723,7 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>7016267E</t>
+          <t>7016269</t>
         </is>
       </c>
       <c r="B662" s="5" t="inlineStr">
@@ -14664,12 +14743,12 @@
     <row r="663">
       <c r="A663" s="6" t="inlineStr">
         <is>
-          <t>7016268</t>
+          <t>7010869</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -14684,12 +14763,12 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>7016269</t>
+          <t>7010883</t>
         </is>
       </c>
       <c r="B664" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C664" s="5" t="inlineStr">
@@ -14704,7 +14783,7 @@
     <row r="665">
       <c r="A665" s="6" t="inlineStr">
         <is>
-          <t>7010869</t>
+          <t>7010886</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -14724,7 +14803,7 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>7010883</t>
+          <t>7010887</t>
         </is>
       </c>
       <c r="B666" s="5" t="inlineStr">
@@ -14744,7 +14823,7 @@
     <row r="667">
       <c r="A667" s="6" t="inlineStr">
         <is>
-          <t>7010886</t>
+          <t>7054167</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -14764,7 +14843,7 @@
     <row r="668">
       <c r="A668" s="4" t="inlineStr">
         <is>
-          <t>7010887</t>
+          <t>7054168</t>
         </is>
       </c>
       <c r="B668" s="5" t="inlineStr">
@@ -14784,7 +14863,7 @@
     <row r="669">
       <c r="A669" s="6" t="inlineStr">
         <is>
-          <t>7054167</t>
+          <t>7054169</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -14804,7 +14883,7 @@
     <row r="670">
       <c r="A670" s="4" t="inlineStr">
         <is>
-          <t>7054168</t>
+          <t>7016931</t>
         </is>
       </c>
       <c r="B670" s="5" t="inlineStr">
@@ -14824,7 +14903,7 @@
     <row r="671">
       <c r="A671" s="6" t="inlineStr">
         <is>
-          <t>7054169</t>
+          <t>7016932</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -14844,7 +14923,7 @@
     <row r="672">
       <c r="A672" s="4" t="inlineStr">
         <is>
-          <t>7016931</t>
+          <t>7016933</t>
         </is>
       </c>
       <c r="B672" s="5" t="inlineStr">
@@ -14864,7 +14943,7 @@
     <row r="673">
       <c r="A673" s="6" t="inlineStr">
         <is>
-          <t>7016932</t>
+          <t>7016934</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -14884,7 +14963,7 @@
     <row r="674">
       <c r="A674" s="4" t="inlineStr">
         <is>
-          <t>7016933</t>
+          <t>7027327</t>
         </is>
       </c>
       <c r="B674" s="5" t="inlineStr">
@@ -14904,12 +14983,12 @@
     <row r="675">
       <c r="A675" s="6" t="inlineStr">
         <is>
-          <t>7016934</t>
+          <t>7010848</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -14924,12 +15003,12 @@
     <row r="676">
       <c r="A676" s="4" t="inlineStr">
         <is>
-          <t>7027327</t>
+          <t>7010849</t>
         </is>
       </c>
       <c r="B676" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C676" s="5" t="inlineStr">
@@ -14944,7 +15023,7 @@
     <row r="677">
       <c r="A677" s="6" t="inlineStr">
         <is>
-          <t>7010848</t>
+          <t>7010851</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -14964,7 +15043,7 @@
     <row r="678">
       <c r="A678" s="4" t="inlineStr">
         <is>
-          <t>7010849</t>
+          <t>7010854</t>
         </is>
       </c>
       <c r="B678" s="5" t="inlineStr">
@@ -14984,7 +15063,7 @@
     <row r="679">
       <c r="A679" s="6" t="inlineStr">
         <is>
-          <t>7010851</t>
+          <t>7010855</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -15004,7 +15083,7 @@
     <row r="680">
       <c r="A680" s="4" t="inlineStr">
         <is>
-          <t>7010854</t>
+          <t>7010857</t>
         </is>
       </c>
       <c r="B680" s="5" t="inlineStr">
@@ -15024,7 +15103,7 @@
     <row r="681">
       <c r="A681" s="6" t="inlineStr">
         <is>
-          <t>7010855</t>
+          <t>7010858</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -15044,7 +15123,7 @@
     <row r="682">
       <c r="A682" s="4" t="inlineStr">
         <is>
-          <t>7010857</t>
+          <t>7010859</t>
         </is>
       </c>
       <c r="B682" s="5" t="inlineStr">
@@ -15064,7 +15143,7 @@
     <row r="683">
       <c r="A683" s="6" t="inlineStr">
         <is>
-          <t>7010858</t>
+          <t>7019619</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -15084,7 +15163,7 @@
     <row r="684">
       <c r="A684" s="4" t="inlineStr">
         <is>
-          <t>7010859</t>
+          <t>7019620</t>
         </is>
       </c>
       <c r="B684" s="5" t="inlineStr">
@@ -15104,7 +15183,7 @@
     <row r="685">
       <c r="A685" s="6" t="inlineStr">
         <is>
-          <t>7019619</t>
+          <t>7019621</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -15124,7 +15203,7 @@
     <row r="686">
       <c r="A686" s="4" t="inlineStr">
         <is>
-          <t>7019620</t>
+          <t>7019622</t>
         </is>
       </c>
       <c r="B686" s="5" t="inlineStr">
@@ -15144,12 +15223,12 @@
     <row r="687">
       <c r="A687" s="6" t="inlineStr">
         <is>
-          <t>7019621</t>
+          <t>7019479</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -15164,12 +15243,12 @@
     <row r="688">
       <c r="A688" s="4" t="inlineStr">
         <is>
-          <t>7019622</t>
+          <t>7010844E</t>
         </is>
       </c>
       <c r="B688" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C688" s="5" t="inlineStr">
@@ -15184,7 +15263,7 @@
     <row r="689">
       <c r="A689" s="6" t="inlineStr">
         <is>
-          <t>7019479</t>
+          <t>7010845</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -15204,7 +15283,7 @@
     <row r="690">
       <c r="A690" s="4" t="inlineStr">
         <is>
-          <t>7010844E</t>
+          <t>7010846E</t>
         </is>
       </c>
       <c r="B690" s="5" t="inlineStr">
@@ -15224,7 +15303,7 @@
     <row r="691">
       <c r="A691" s="6" t="inlineStr">
         <is>
-          <t>7010845</t>
+          <t>7010847</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -15244,7 +15323,7 @@
     <row r="692">
       <c r="A692" s="4" t="inlineStr">
         <is>
-          <t>7010846E</t>
+          <t>7054160</t>
         </is>
       </c>
       <c r="B692" s="5" t="inlineStr">
@@ -15264,7 +15343,7 @@
     <row r="693">
       <c r="A693" s="6" t="inlineStr">
         <is>
-          <t>7010847</t>
+          <t>7054163</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -15284,7 +15363,7 @@
     <row r="694">
       <c r="A694" s="4" t="inlineStr">
         <is>
-          <t>7054160</t>
+          <t>7054166</t>
         </is>
       </c>
       <c r="B694" s="5" t="inlineStr">
@@ -15304,12 +15383,12 @@
     <row r="695">
       <c r="A695" s="6" t="inlineStr">
         <is>
-          <t>7054163</t>
+          <t>7010833</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -15324,12 +15403,12 @@
     <row r="696">
       <c r="A696" s="4" t="inlineStr">
         <is>
-          <t>7054166</t>
+          <t>7010842E</t>
         </is>
       </c>
       <c r="B696" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C696" s="5" t="inlineStr">
@@ -15344,7 +15423,7 @@
     <row r="697">
       <c r="A697" s="6" t="inlineStr">
         <is>
-          <t>7010833</t>
+          <t>7010834</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -15364,7 +15443,7 @@
     <row r="698">
       <c r="A698" s="4" t="inlineStr">
         <is>
-          <t>7010842E</t>
+          <t>7010843</t>
         </is>
       </c>
       <c r="B698" s="5" t="inlineStr">
@@ -15384,7 +15463,7 @@
     <row r="699">
       <c r="A699" s="6" t="inlineStr">
         <is>
-          <t>7010834</t>
+          <t>7010829</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -15404,7 +15483,7 @@
     <row r="700">
       <c r="A700" s="4" t="inlineStr">
         <is>
-          <t>7010843</t>
+          <t>7010835</t>
         </is>
       </c>
       <c r="B700" s="5" t="inlineStr">
@@ -15424,7 +15503,7 @@
     <row r="701">
       <c r="A701" s="6" t="inlineStr">
         <is>
-          <t>7010829</t>
+          <t>7010832</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -15444,7 +15523,7 @@
     <row r="702">
       <c r="A702" s="4" t="inlineStr">
         <is>
-          <t>7010835</t>
+          <t>7010841</t>
         </is>
       </c>
       <c r="B702" s="5" t="inlineStr">
@@ -15464,7 +15543,7 @@
     <row r="703">
       <c r="A703" s="6" t="inlineStr">
         <is>
-          <t>7010832</t>
+          <t>7054170</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -15484,7 +15563,7 @@
     <row r="704">
       <c r="A704" s="4" t="inlineStr">
         <is>
-          <t>7010841</t>
+          <t>7054171</t>
         </is>
       </c>
       <c r="B704" s="5" t="inlineStr">
@@ -15504,7 +15583,7 @@
     <row r="705">
       <c r="A705" s="6" t="inlineStr">
         <is>
-          <t>7054170</t>
+          <t>7054172</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -15524,7 +15603,7 @@
     <row r="706">
       <c r="A706" s="4" t="inlineStr">
         <is>
-          <t>7054171</t>
+          <t>7054173</t>
         </is>
       </c>
       <c r="B706" s="5" t="inlineStr">
@@ -15544,7 +15623,7 @@
     <row r="707">
       <c r="A707" s="6" t="inlineStr">
         <is>
-          <t>7054172</t>
+          <t>7054174</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -15564,7 +15643,7 @@
     <row r="708">
       <c r="A708" s="4" t="inlineStr">
         <is>
-          <t>7054173</t>
+          <t>7054175</t>
         </is>
       </c>
       <c r="B708" s="5" t="inlineStr">
@@ -15584,7 +15663,7 @@
     <row r="709">
       <c r="A709" s="6" t="inlineStr">
         <is>
-          <t>7054174</t>
+          <t>7054176</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -15604,7 +15683,7 @@
     <row r="710">
       <c r="A710" s="4" t="inlineStr">
         <is>
-          <t>7054175</t>
+          <t>7016845</t>
         </is>
       </c>
       <c r="B710" s="5" t="inlineStr">
@@ -15624,7 +15703,7 @@
     <row r="711">
       <c r="A711" s="6" t="inlineStr">
         <is>
-          <t>7054176</t>
+          <t>7016846E</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -15644,7 +15723,7 @@
     <row r="712">
       <c r="A712" s="4" t="inlineStr">
         <is>
-          <t>7016845</t>
+          <t>7016847E</t>
         </is>
       </c>
       <c r="B712" s="5" t="inlineStr">
@@ -15664,7 +15743,7 @@
     <row r="713">
       <c r="A713" s="6" t="inlineStr">
         <is>
-          <t>7016846E</t>
+          <t>7016848E</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -15684,7 +15763,7 @@
     <row r="714">
       <c r="A714" s="4" t="inlineStr">
         <is>
-          <t>7016847E</t>
+          <t>7015420</t>
         </is>
       </c>
       <c r="B714" s="5" t="inlineStr">
@@ -15704,7 +15783,7 @@
     <row r="715">
       <c r="A715" s="6" t="inlineStr">
         <is>
-          <t>7016848E</t>
+          <t>7015423</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -15724,7 +15803,7 @@
     <row r="716">
       <c r="A716" s="4" t="inlineStr">
         <is>
-          <t>7015420</t>
+          <t>7015428</t>
         </is>
       </c>
       <c r="B716" s="5" t="inlineStr">
@@ -15744,7 +15823,7 @@
     <row r="717">
       <c r="A717" s="6" t="inlineStr">
         <is>
-          <t>7015423</t>
+          <t>7015429</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -15764,7 +15843,7 @@
     <row r="718">
       <c r="A718" s="4" t="inlineStr">
         <is>
-          <t>7015428</t>
+          <t>7018058</t>
         </is>
       </c>
       <c r="B718" s="5" t="inlineStr">
@@ -15784,7 +15863,7 @@
     <row r="719">
       <c r="A719" s="6" t="inlineStr">
         <is>
-          <t>7015429</t>
+          <t>7018059</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -15804,7 +15883,7 @@
     <row r="720">
       <c r="A720" s="4" t="inlineStr">
         <is>
-          <t>7018058</t>
+          <t>7018060</t>
         </is>
       </c>
       <c r="B720" s="5" t="inlineStr">
@@ -15824,7 +15903,7 @@
     <row r="721">
       <c r="A721" s="6" t="inlineStr">
         <is>
-          <t>7018059</t>
+          <t>7018061</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -15844,7 +15923,7 @@
     <row r="722">
       <c r="A722" s="4" t="inlineStr">
         <is>
-          <t>7018060</t>
+          <t>7019484</t>
         </is>
       </c>
       <c r="B722" s="5" t="inlineStr">
@@ -15864,12 +15943,12 @@
     <row r="723">
       <c r="A723" s="6" t="inlineStr">
         <is>
-          <t>7018061</t>
+          <t>7013787</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -15884,12 +15963,12 @@
     <row r="724">
       <c r="A724" s="4" t="inlineStr">
         <is>
-          <t>7019484</t>
+          <t>7013788</t>
         </is>
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
@@ -15904,7 +15983,7 @@
     <row r="725">
       <c r="A725" s="6" t="inlineStr">
         <is>
-          <t>7013787</t>
+          <t>7013789</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -15924,7 +16003,7 @@
     <row r="726">
       <c r="A726" s="4" t="inlineStr">
         <is>
-          <t>7013788</t>
+          <t>7013790</t>
         </is>
       </c>
       <c r="B726" s="5" t="inlineStr">
@@ -15944,7 +16023,7 @@
     <row r="727">
       <c r="A727" s="6" t="inlineStr">
         <is>
-          <t>7013789</t>
+          <t>7013791</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -15964,7 +16043,7 @@
     <row r="728">
       <c r="A728" s="4" t="inlineStr">
         <is>
-          <t>7013790</t>
+          <t>7013792</t>
         </is>
       </c>
       <c r="B728" s="5" t="inlineStr">
@@ -15984,7 +16063,7 @@
     <row r="729">
       <c r="A729" s="6" t="inlineStr">
         <is>
-          <t>7013791</t>
+          <t>7013793</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -16004,7 +16083,7 @@
     <row r="730">
       <c r="A730" s="4" t="inlineStr">
         <is>
-          <t>7013792</t>
+          <t>7013794</t>
         </is>
       </c>
       <c r="B730" s="5" t="inlineStr">
@@ -16024,7 +16103,7 @@
     <row r="731">
       <c r="A731" s="6" t="inlineStr">
         <is>
-          <t>7013793</t>
+          <t>7017853</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -16044,7 +16123,7 @@
     <row r="732">
       <c r="A732" s="4" t="inlineStr">
         <is>
-          <t>7013794</t>
+          <t>7017854</t>
         </is>
       </c>
       <c r="B732" s="5" t="inlineStr">
@@ -16064,7 +16143,7 @@
     <row r="733">
       <c r="A733" s="6" t="inlineStr">
         <is>
-          <t>7017853</t>
+          <t>7017855</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -16084,7 +16163,7 @@
     <row r="734">
       <c r="A734" s="4" t="inlineStr">
         <is>
-          <t>7017854</t>
+          <t>7017856</t>
         </is>
       </c>
       <c r="B734" s="5" t="inlineStr">
@@ -16104,12 +16183,12 @@
     <row r="735">
       <c r="A735" s="6" t="inlineStr">
         <is>
-          <t>7017855</t>
+          <t>7029050</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -16124,12 +16203,12 @@
     <row r="736">
       <c r="A736" s="4" t="inlineStr">
         <is>
-          <t>7017856</t>
+          <t>7029051</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -16144,7 +16223,7 @@
     <row r="737">
       <c r="A737" s="6" t="inlineStr">
         <is>
-          <t>7029050</t>
+          <t>7029052</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -16164,7 +16243,7 @@
     <row r="738">
       <c r="A738" s="4" t="inlineStr">
         <is>
-          <t>7029051</t>
+          <t>7029053</t>
         </is>
       </c>
       <c r="B738" s="5" t="inlineStr">
@@ -16184,7 +16263,7 @@
     <row r="739">
       <c r="A739" s="6" t="inlineStr">
         <is>
-          <t>7029052</t>
+          <t>7029054</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -16204,7 +16283,7 @@
     <row r="740">
       <c r="A740" s="4" t="inlineStr">
         <is>
-          <t>7029053</t>
+          <t>7029055</t>
         </is>
       </c>
       <c r="B740" s="5" t="inlineStr">
@@ -16224,12 +16303,12 @@
     <row r="741">
       <c r="A741" s="6" t="inlineStr">
         <is>
-          <t>7029054</t>
+          <t>7019046</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -16244,12 +16323,12 @@
     <row r="742">
       <c r="A742" s="4" t="inlineStr">
         <is>
-          <t>7029055</t>
+          <t>7019047</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
@@ -16264,7 +16343,7 @@
     <row r="743">
       <c r="A743" s="6" t="inlineStr">
         <is>
-          <t>7019046</t>
+          <t>7019053</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -16284,7 +16363,7 @@
     <row r="744">
       <c r="A744" s="4" t="inlineStr">
         <is>
-          <t>7019047</t>
+          <t>7019058</t>
         </is>
       </c>
       <c r="B744" s="5" t="inlineStr">
@@ -16304,7 +16383,7 @@
     <row r="745">
       <c r="A745" s="6" t="inlineStr">
         <is>
-          <t>7019053</t>
+          <t>7019059</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -16324,7 +16403,7 @@
     <row r="746">
       <c r="A746" s="4" t="inlineStr">
         <is>
-          <t>7019058</t>
+          <t>7019060</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
@@ -16344,7 +16423,7 @@
     <row r="747">
       <c r="A747" s="6" t="inlineStr">
         <is>
-          <t>7019059</t>
+          <t>7019073</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -16364,7 +16443,7 @@
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>7019060</t>
+          <t>7019074</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
@@ -16384,12 +16463,12 @@
     <row r="749">
       <c r="A749" s="6" t="inlineStr">
         <is>
-          <t>7019073</t>
+          <t>7019315</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -16404,12 +16483,12 @@
     <row r="750">
       <c r="A750" s="4" t="inlineStr">
         <is>
-          <t>7019074</t>
+          <t>7019344</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
@@ -16424,7 +16503,7 @@
     <row r="751">
       <c r="A751" s="6" t="inlineStr">
         <is>
-          <t>7019315</t>
+          <t>7019345</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -16444,7 +16523,7 @@
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>7019344</t>
+          <t>7019346</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
@@ -16464,7 +16543,7 @@
     <row r="753">
       <c r="A753" s="6" t="inlineStr">
         <is>
-          <t>7019345</t>
+          <t>7019347</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -16484,7 +16563,7 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>7019346</t>
+          <t>7019358</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
@@ -16504,7 +16583,7 @@
     <row r="755">
       <c r="A755" s="6" t="inlineStr">
         <is>
-          <t>7019347</t>
+          <t>7019359</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -16524,7 +16603,7 @@
     <row r="756">
       <c r="A756" s="4" t="inlineStr">
         <is>
-          <t>7019358</t>
+          <t>7019360</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
@@ -16544,7 +16623,7 @@
     <row r="757">
       <c r="A757" s="6" t="inlineStr">
         <is>
-          <t>7019359</t>
+          <t>7019361</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -16564,7 +16643,7 @@
     <row r="758">
       <c r="A758" s="4" t="inlineStr">
         <is>
-          <t>7019360</t>
+          <t>7019348</t>
         </is>
       </c>
       <c r="B758" s="5" t="inlineStr">
@@ -16584,7 +16663,7 @@
     <row r="759">
       <c r="A759" s="6" t="inlineStr">
         <is>
-          <t>7019361</t>
+          <t>7019349</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -16604,7 +16683,7 @@
     <row r="760">
       <c r="A760" s="4" t="inlineStr">
         <is>
-          <t>7019348</t>
+          <t>7019350</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -16624,7 +16703,7 @@
     <row r="761">
       <c r="A761" s="6" t="inlineStr">
         <is>
-          <t>7019349</t>
+          <t>7019351</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -16644,7 +16723,7 @@
     <row r="762">
       <c r="A762" s="4" t="inlineStr">
         <is>
-          <t>7019350</t>
+          <t>7019352</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -16664,7 +16743,7 @@
     <row r="763">
       <c r="A763" s="6" t="inlineStr">
         <is>
-          <t>7019351</t>
+          <t>7019353</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -16684,7 +16763,7 @@
     <row r="764">
       <c r="A764" s="4" t="inlineStr">
         <is>
-          <t>7019352</t>
+          <t>7019354</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -16704,7 +16783,7 @@
     <row r="765">
       <c r="A765" s="6" t="inlineStr">
         <is>
-          <t>7019353</t>
+          <t>7019355</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -16724,7 +16803,7 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>7019354</t>
+          <t>7019356</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
@@ -16744,7 +16823,7 @@
     <row r="767">
       <c r="A767" s="6" t="inlineStr">
         <is>
-          <t>7019355</t>
+          <t>7019357</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -16764,12 +16843,12 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>7019356</t>
+          <t>7021449</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
@@ -16784,12 +16863,12 @@
     <row r="769">
       <c r="A769" s="6" t="inlineStr">
         <is>
-          <t>7019357</t>
+          <t>7021450</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -16804,12 +16883,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>7018887</t>
+          <t>7021451</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
@@ -16824,12 +16903,12 @@
     <row r="771">
       <c r="A771" s="6" t="inlineStr">
         <is>
-          <t>7018888</t>
+          <t>7021452</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -16844,12 +16923,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>7028566</t>
+          <t>7021453</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
@@ -16864,12 +16943,12 @@
     <row r="773">
       <c r="A773" s="6" t="inlineStr">
         <is>
-          <t>7028567</t>
+          <t>7021454</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -16884,12 +16963,12 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>7028568</t>
+          <t>7021443</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C774" s="5" t="inlineStr">
@@ -16904,12 +16983,12 @@
     <row r="775">
       <c r="A775" s="6" t="inlineStr">
         <is>
-          <t>7028569</t>
+          <t>7021444</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -16924,12 +17003,12 @@
     <row r="776">
       <c r="A776" s="4" t="inlineStr">
         <is>
-          <t>7028570</t>
+          <t>7021445</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C776" s="5" t="inlineStr">
@@ -16944,12 +17023,12 @@
     <row r="777">
       <c r="A777" s="6" t="inlineStr">
         <is>
-          <t>7028571</t>
+          <t>7021446</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -16964,12 +17043,12 @@
     <row r="778">
       <c r="A778" s="4" t="inlineStr">
         <is>
-          <t>7028572</t>
+          <t>7021447</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C778" s="5" t="inlineStr">
@@ -16984,12 +17063,12 @@
     <row r="779">
       <c r="A779" s="6" t="inlineStr">
         <is>
-          <t>7028573</t>
+          <t>7021448</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -17004,12 +17083,12 @@
     <row r="780">
       <c r="A780" s="4" t="inlineStr">
         <is>
-          <t>7028574</t>
+          <t>7018887</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C780" s="5" t="inlineStr">
@@ -17024,12 +17103,12 @@
     <row r="781">
       <c r="A781" s="6" t="inlineStr">
         <is>
-          <t>7028575</t>
+          <t>7018888</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -17044,7 +17123,7 @@
     <row r="782">
       <c r="A782" s="4" t="inlineStr">
         <is>
-          <t>7028576</t>
+          <t>7028566</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
@@ -17064,7 +17143,7 @@
     <row r="783">
       <c r="A783" s="6" t="inlineStr">
         <is>
-          <t>7028577</t>
+          <t>7028567</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -17084,7 +17163,7 @@
     <row r="784">
       <c r="A784" s="4" t="inlineStr">
         <is>
-          <t>7028578</t>
+          <t>7028568</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
@@ -17104,7 +17183,7 @@
     <row r="785">
       <c r="A785" s="6" t="inlineStr">
         <is>
-          <t>7028579</t>
+          <t>7028569</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -17124,7 +17203,7 @@
     <row r="786">
       <c r="A786" s="4" t="inlineStr">
         <is>
-          <t>7028580</t>
+          <t>7028570</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
@@ -17144,7 +17223,7 @@
     <row r="787">
       <c r="A787" s="6" t="inlineStr">
         <is>
-          <t>7028581</t>
+          <t>7028571</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -17164,17 +17243,17 @@
     <row r="788">
       <c r="A788" s="4" t="inlineStr">
         <is>
-          <t>7029244</t>
+          <t>7028572</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C788" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D788" s="4" t="n">
@@ -17184,17 +17263,17 @@
     <row r="789">
       <c r="A789" s="6" t="inlineStr">
         <is>
-          <t>7029245</t>
+          <t>7028573</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D789" s="6" t="n">
@@ -17204,17 +17283,17 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>7029246</t>
+          <t>7028574</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C790" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D790" s="4" t="n">
@@ -17224,17 +17303,17 @@
     <row r="791">
       <c r="A791" s="6" t="inlineStr">
         <is>
-          <t>7029247</t>
+          <t>7028575</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D791" s="6" t="n">
@@ -17244,17 +17323,17 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>7029248</t>
+          <t>7028576</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C792" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D792" s="4" t="n">
@@ -17264,17 +17343,17 @@
     <row r="793">
       <c r="A793" s="6" t="inlineStr">
         <is>
-          <t>7029249</t>
+          <t>7028577</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D793" s="6" t="n">
@@ -17284,17 +17363,17 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>7029250</t>
+          <t>7028578</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C794" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D794" s="4" t="n">
@@ -17304,17 +17383,17 @@
     <row r="795">
       <c r="A795" s="6" t="inlineStr">
         <is>
-          <t>7029251</t>
+          <t>7028579</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D795" s="6" t="n">
@@ -17324,17 +17403,17 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7028580</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C796" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D796" s="4" t="n">
@@ -17344,17 +17423,17 @@
     <row r="797">
       <c r="A797" s="6" t="inlineStr">
         <is>
-          <t>7018077</t>
+          <t>7028581</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D797" s="6" t="n">
@@ -17364,17 +17443,17 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>7022954</t>
+          <t>7029244</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C798" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D798" s="4" t="n">
@@ -17384,17 +17463,17 @@
     <row r="799">
       <c r="A799" s="6" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7029245</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D799" s="6" t="n">
@@ -17404,17 +17483,17 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7029246</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D800" s="4" t="n">
@@ -17424,17 +17503,17 @@
     <row r="801">
       <c r="A801" s="6" t="inlineStr">
         <is>
-          <t>7019898</t>
+          <t>7029247</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline RC136B, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D801" s="6" t="n">
@@ -17444,17 +17523,17 @@
     <row r="802">
       <c r="A802" s="4" t="inlineStr">
         <is>
-          <t>7019874</t>
+          <t>7029248</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur RC065B</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D802" s="4" t="n">
@@ -17464,17 +17543,17 @@
     <row r="803">
       <c r="A803" s="6" t="inlineStr">
         <is>
-          <t>7019875</t>
+          <t>7029249</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur RC065B</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D803" s="6" t="n">
@@ -17484,17 +17563,17 @@
     <row r="804">
       <c r="A804" s="4" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7029250</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C804" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D804" s="4" t="n">
@@ -17504,17 +17583,17 @@
     <row r="805">
       <c r="A805" s="6" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7029251</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D805" s="6" t="n">
@@ -17524,12 +17603,12 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7028893</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld Interiörarmatur Coreline Panel</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
@@ -17544,12 +17623,12 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7018077</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -17564,12 +17643,12 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
@@ -17584,12 +17663,12 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -17604,12 +17683,12 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7019874</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld interiörarmatur RC065B</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
@@ -17624,12 +17703,12 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7019875</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Infälld interiörarmatur RC065B</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -17644,12 +17723,12 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
@@ -17664,12 +17743,12 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -17684,12 +17763,12 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C814" s="5" t="inlineStr">
@@ -17704,12 +17783,12 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -17724,12 +17803,12 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C816" s="5" t="inlineStr">
@@ -17744,12 +17823,12 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -17764,12 +17843,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
@@ -17784,7 +17863,7 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -17804,7 +17883,7 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
@@ -17824,7 +17903,7 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -17844,7 +17923,7 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -17864,7 +17943,7 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -17884,7 +17963,7 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -17904,12 +17983,12 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -17924,12 +18003,12 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C826" s="5" t="inlineStr">
@@ -17944,12 +18023,12 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -17964,12 +18043,12 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7017879</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur PowerBalance</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C828" s="5" t="inlineStr">
@@ -17984,12 +18063,12 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7017880</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Interiörarmatur PowerBalance</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -18004,12 +18083,12 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7017881</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur PowerBalance</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C830" s="5" t="inlineStr">
@@ -18024,12 +18103,12 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7017882</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Interiörarmatur PowerBalance</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -18044,12 +18123,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -18064,12 +18143,12 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -18084,12 +18163,12 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C834" s="5" t="inlineStr">
@@ -18104,12 +18183,12 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -18124,7 +18203,7 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
@@ -18144,7 +18223,7 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -18164,7 +18243,7 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
@@ -18184,7 +18263,7 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -18204,7 +18283,7 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
@@ -18224,7 +18303,7 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -18244,7 +18323,7 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
@@ -18264,12 +18343,12 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -18284,12 +18363,12 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
@@ -18304,12 +18383,12 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -18324,12 +18403,12 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
@@ -18344,7 +18423,7 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -18364,7 +18443,7 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
@@ -18384,7 +18463,7 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -18404,7 +18483,7 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
@@ -18424,17 +18503,17 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D851" s="6" t="n">
@@ -18444,17 +18523,17 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C852" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D852" s="4" t="n">
@@ -18464,17 +18543,17 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D853" s="6" t="n">
@@ -18484,17 +18563,17 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C854" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D854" s="4" t="n">
@@ -18504,7 +18583,7 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -18524,7 +18603,7 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -18544,7 +18623,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -18564,7 +18643,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -18584,7 +18663,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -18604,7 +18683,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -18624,7 +18703,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -18644,7 +18723,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -18664,7 +18743,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -18684,7 +18763,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -18704,7 +18783,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -18724,7 +18803,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -18744,7 +18823,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -18764,7 +18843,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -18784,7 +18863,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -18804,7 +18883,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -18824,7 +18903,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -18844,7 +18923,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -18864,7 +18943,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -18884,7 +18963,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -18904,7 +18983,7 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -18924,7 +19003,7 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
@@ -18944,12 +19023,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -18964,12 +19043,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -18984,12 +19063,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -19004,12 +19083,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -19024,12 +19103,12 @@
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -19044,12 +19123,12 @@
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -19058,18 +19137,18 @@
         </is>
       </c>
       <c r="D882" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -19078,18 +19157,18 @@
         </is>
       </c>
       <c r="D883" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -19104,12 +19183,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -19124,12 +19203,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -19138,18 +19217,18 @@
         </is>
       </c>
       <c r="D886" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -19158,18 +19237,18 @@
         </is>
       </c>
       <c r="D887" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -19184,12 +19263,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -19198,18 +19277,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>1294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -19218,18 +19297,18 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -19238,13 +19317,13 @@
         </is>
       </c>
       <c r="D891" s="6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
@@ -19264,12 +19343,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -19278,18 +19357,18 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>0</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -19298,18 +19377,18 @@
         </is>
       </c>
       <c r="D894" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -19318,18 +19397,18 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -19344,12 +19423,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -19364,12 +19443,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -19384,12 +19463,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -19404,12 +19483,12 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -19424,12 +19503,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -19444,12 +19523,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -19464,7 +19543,7 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -19484,7 +19563,7 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
@@ -19504,7 +19583,7 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -19524,7 +19603,7 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
@@ -19544,12 +19623,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -19558,18 +19637,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -19584,12 +19663,12 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -19604,12 +19683,12 @@
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -19624,7 +19703,7 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -19638,13 +19717,13 @@
         </is>
       </c>
       <c r="D911" s="6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
@@ -19664,7 +19743,7 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -19684,7 +19763,7 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
@@ -19704,12 +19783,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -19718,18 +19797,18 @@
         </is>
       </c>
       <c r="D915" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -19744,12 +19823,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -19758,18 +19837,18 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -19784,12 +19863,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -19804,12 +19883,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -19824,12 +19903,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -19838,18 +19917,18 @@
         </is>
       </c>
       <c r="D921" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -19864,12 +19943,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -19884,12 +19963,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -19904,12 +19983,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -19924,7 +20003,7 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
@@ -19944,7 +20023,7 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -19964,12 +20043,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -19984,12 +20063,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -20004,12 +20083,12 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -20024,12 +20103,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -20044,12 +20123,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -20064,12 +20143,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -20084,12 +20163,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -20104,12 +20183,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -20124,12 +20203,12 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -20144,12 +20223,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -20164,12 +20243,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -20184,12 +20263,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -20204,7 +20283,7 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
@@ -20224,7 +20303,7 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -20244,12 +20323,12 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
@@ -20264,12 +20343,12 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -20284,12 +20363,12 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
@@ -20304,12 +20383,12 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -20324,7 +20403,7 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
@@ -20344,7 +20423,7 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -20364,7 +20443,7 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
@@ -20384,7 +20463,7 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -20404,17 +20483,17 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7027837</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D950" s="4" t="n">
@@ -20424,17 +20503,17 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7027838</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D951" s="6" t="n">
@@ -20444,17 +20523,17 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7027841</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D952" s="4" t="n">
@@ -20464,17 +20543,17 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7027842</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Silica 31 Square</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D953" s="6" t="n">
@@ -20484,7 +20563,7 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7027835</t>
+          <t>7027837</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
@@ -20504,7 +20583,7 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027836</t>
+          <t>7027838</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -20524,7 +20603,7 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027839</t>
+          <t>7027841</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
@@ -20544,7 +20623,7 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027840</t>
+          <t>7027842</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -20564,12 +20643,12 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7027835</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C958" s="5" t="inlineStr">
@@ -20584,12 +20663,12 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7027836</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -20604,12 +20683,12 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7027839</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
@@ -20624,12 +20703,12 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7027840</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld Interiörarmatur Silica 31 Square</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -20644,7 +20723,7 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
@@ -20664,7 +20743,7 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -20684,7 +20763,7 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
@@ -20704,7 +20783,7 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -20724,7 +20803,7 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
@@ -20744,17 +20823,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -20764,17 +20843,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -20784,17 +20863,17 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D969" s="6" t="n">
@@ -20804,17 +20883,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -20824,17 +20903,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -20844,17 +20923,17 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D972" s="4" t="n">
@@ -20864,17 +20943,17 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D973" s="6" t="n">
@@ -20884,17 +20963,17 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D974" s="4" t="n">
@@ -20904,17 +20983,17 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D975" s="6" t="n">
@@ -20924,37 +21003,37 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D976" s="4" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D977" s="6" t="n">
@@ -20964,12 +21043,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -20984,12 +21063,12 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -21004,12 +21083,12 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -21024,12 +21103,12 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -21044,12 +21123,12 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
@@ -21064,12 +21143,12 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -21084,12 +21163,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -21104,12 +21183,12 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -21118,18 +21197,18 @@
         </is>
       </c>
       <c r="D985" s="6" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
@@ -21144,12 +21223,12 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -21164,17 +21243,17 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D988" s="4" t="n">
@@ -21184,17 +21263,17 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D989" s="6" t="n">
@@ -21204,17 +21283,17 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D990" s="4" t="n">
@@ -21224,17 +21303,17 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D991" s="6" t="n">
@@ -21244,17 +21323,17 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D992" s="4" t="n">
@@ -21264,17 +21343,17 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D993" s="6" t="n">
@@ -21284,17 +21363,17 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D994" s="4" t="n">
@@ -21304,17 +21383,17 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D995" s="6" t="n">
@@ -21324,17 +21403,17 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D996" s="4" t="n">
@@ -21344,12 +21423,12 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -21364,12 +21443,12 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
@@ -21384,12 +21463,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -21404,12 +21483,12 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
@@ -21424,12 +21503,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -21444,12 +21523,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -21464,12 +21543,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -21484,12 +21563,12 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
@@ -21504,12 +21583,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -21524,12 +21603,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -21544,12 +21623,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -21564,12 +21643,12 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1008" s="5" t="inlineStr">
@@ -21584,12 +21663,12 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -21604,12 +21683,12 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
@@ -21624,12 +21703,12 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -21644,12 +21723,12 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1012" s="5" t="inlineStr">
@@ -21664,12 +21743,12 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -21684,12 +21763,12 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1014" s="5" t="inlineStr">
@@ -21704,12 +21783,12 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -21724,12 +21803,12 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1016" s="5" t="inlineStr">
@@ -21744,7 +21823,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -21764,7 +21843,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -21784,7 +21863,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -21804,7 +21883,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -21824,7 +21903,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -21844,7 +21923,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -21864,7 +21943,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -21884,7 +21963,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -21904,7 +21983,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -21924,7 +22003,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -21944,7 +22023,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -21964,7 +22043,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -21984,7 +22063,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -22004,7 +22083,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -22024,7 +22103,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -22044,7 +22123,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -22064,7 +22143,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -22084,7 +22163,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -22104,7 +22183,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -22124,12 +22203,12 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1036" s="5" t="inlineStr">
@@ -22144,12 +22223,12 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -22164,12 +22243,12 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1038" s="5" t="inlineStr">
@@ -22184,12 +22263,12 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -22204,12 +22283,12 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1040" s="5" t="inlineStr">
@@ -22224,12 +22303,12 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -22244,12 +22323,12 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1042" s="5" t="inlineStr">
@@ -22264,12 +22343,12 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -22284,12 +22363,12 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1044" s="5" t="inlineStr">
@@ -22304,7 +22383,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -22324,7 +22403,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -22344,7 +22423,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -22364,7 +22443,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -22384,7 +22463,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -22404,7 +22483,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -22424,7 +22503,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -22444,7 +22523,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -22464,7 +22543,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -22484,7 +22563,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -22504,7 +22583,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -22524,7 +22603,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -22544,7 +22623,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -22564,7 +22643,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -22584,7 +22663,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -22604,7 +22683,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -22624,7 +22703,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -22644,7 +22723,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -22664,7 +22743,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -22684,7 +22763,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -22704,7 +22783,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -22724,7 +22803,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -22744,7 +22823,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -22764,7 +22843,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -22784,7 +22863,7 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -22804,7 +22883,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
@@ -22824,7 +22903,7 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -22844,12 +22923,12 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1072" s="5" t="inlineStr">
@@ -22864,12 +22943,12 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -22884,12 +22963,12 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1074" s="5" t="inlineStr">
@@ -22904,12 +22983,12 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -22924,12 +23003,12 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1076" s="5" t="inlineStr">
@@ -22944,12 +23023,12 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -22964,12 +23043,12 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1078" s="5" t="inlineStr">
@@ -22984,12 +23063,12 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -23004,12 +23083,12 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1080" s="5" t="inlineStr">
@@ -23024,7 +23103,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -23044,7 +23123,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -23064,7 +23143,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -23084,12 +23163,12 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1084" s="5" t="inlineStr">
@@ -23104,12 +23183,12 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -23124,12 +23203,12 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
@@ -23144,12 +23223,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -23164,12 +23243,12 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
@@ -23184,12 +23263,12 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -23204,12 +23283,12 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
@@ -23224,12 +23303,12 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -23244,12 +23323,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -23264,12 +23343,12 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -23284,12 +23363,12 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -23304,12 +23383,12 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -23324,12 +23403,12 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
@@ -23344,12 +23423,12 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -23364,12 +23443,12 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510127</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1098" s="5" t="inlineStr">
@@ -23384,12 +23463,12 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510128</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -23404,12 +23483,12 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510129</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1100" s="5" t="inlineStr">
@@ -23424,12 +23503,12 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510130</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
@@ -23444,12 +23523,12 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510131</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1102" s="5" t="inlineStr">
@@ -23464,12 +23543,12 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510132</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
@@ -23484,12 +23563,12 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7510139</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1104" s="5" t="inlineStr">
@@ -23504,12 +23583,12 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7510140</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
@@ -23524,12 +23603,12 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7510141</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 1x7 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1106" s="5" t="inlineStr">
@@ -23544,7 +23623,7 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7510142</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
@@ -23564,7 +23643,7 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7510143</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
@@ -23584,7 +23663,7 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7510144</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
@@ -23604,17 +23683,17 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1110" s="4" t="n">
@@ -23624,17 +23703,17 @@
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1111" s="6" t="n">
@@ -23644,17 +23723,17 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1112" s="4" t="n">
@@ -23664,57 +23743,57 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1113" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1114" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1115" s="6" t="n">
@@ -23724,57 +23803,57 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1116" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1116" s="4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1118" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1118" s="4" t="n">
@@ -23784,17 +23863,17 @@
     <row r="1119">
       <c r="A1119" s="6" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1119" s="6" t="n">
@@ -23804,41 +23883,221 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1120" s="5" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1120" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1120" s="4" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" s="6" t="inlineStr">
         <is>
+          <t>7028311</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Maya</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1121" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="4" t="inlineStr">
+        <is>
+          <t>7013475</t>
+        </is>
+      </c>
+      <c r="B1122" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED</t>
+        </is>
+      </c>
+      <c r="C1122" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1122" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="6" t="inlineStr">
+        <is>
+          <t>7021097</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1123" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="4" t="inlineStr">
+        <is>
+          <t>7018286</t>
+        </is>
+      </c>
+      <c r="B1124" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
+        </is>
+      </c>
+      <c r="C1124" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1124" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="6" t="inlineStr">
+        <is>
+          <t>7028368</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1125" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="4" t="inlineStr">
+        <is>
+          <t>7028369</t>
+        </is>
+      </c>
+      <c r="B1126" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1126" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1126" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="6" t="inlineStr">
+        <is>
+          <t>7028001</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1127" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="4" t="inlineStr">
+        <is>
+          <t>7028002</t>
+        </is>
+      </c>
+      <c r="B1128" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1128" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1128" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="6" t="inlineStr">
+        <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1129" s="6" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="4" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1121" t="inlineStr">
+      <c r="B1130" s="5" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1121" t="inlineStr">
+      <c r="C1130" s="5" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1121" s="6" t="n">
-        <v>380</v>
+      <c r="D1130" s="4" t="n">
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -1475,6 +1475,85 @@
         <v>0</v>
       </c>
       <c r="Y12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C13" t="n">
+        <v>876</v>
+      </c>
+      <c r="D13" t="n">
+        <v>545</v>
+      </c>
+      <c r="E13" t="n">
+        <v>228</v>
+      </c>
+      <c r="F13" t="n">
+        <v>224</v>
+      </c>
+      <c r="G13" t="n">
+        <v>94</v>
+      </c>
+      <c r="H13" t="n">
+        <v>52</v>
+      </c>
+      <c r="I13" t="n">
+        <v>33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,7 +1595,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-17)</t>
+          <t>Lager (2026-07-18)</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1616,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3">
@@ -19357,7 +19436,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1281</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="894">
@@ -19397,7 +19476,7 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="896">
@@ -23997,7 +24076,7 @@
         </is>
       </c>
       <c r="D1125" s="6" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1126">
@@ -24017,7 +24096,7 @@
         </is>
       </c>
       <c r="D1126" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1127">
@@ -24077,7 +24156,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Legrand</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
         </is>
       </c>
     </row>
@@ -1712,6 +1712,85 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1348</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>883</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>545</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1753,7 +1832,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-20)</t>
+          <t>Lager (2026-07-21)</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10073,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="414">
@@ -19594,7 +19673,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1271</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="894">
@@ -24314,7 +24393,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
         </is>
       </c>
     </row>
@@ -1791,6 +1791,85 @@
         <v>0</v>
       </c>
       <c r="Y16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1347</v>
+      </c>
+      <c r="C17" t="n">
+        <v>878</v>
+      </c>
+      <c r="D17" t="n">
+        <v>572</v>
+      </c>
+      <c r="E17" t="n">
+        <v>228</v>
+      </c>
+      <c r="F17" t="n">
+        <v>224</v>
+      </c>
+      <c r="G17" t="n">
+        <v>94</v>
+      </c>
+      <c r="H17" t="n">
+        <v>52</v>
+      </c>
+      <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" t="n">
+        <v>17</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,7 +1911,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-21)</t>
+          <t>Lager (2026-07-22)</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1932,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>545</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3">
@@ -10073,7 +10152,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="414">
@@ -19673,7 +19752,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="894">
@@ -24313,7 +24392,7 @@
         </is>
       </c>
       <c r="D1125" s="6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1126">
@@ -24393,7 +24472,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1130">
@@ -24413,7 +24492,7 @@
         </is>
       </c>
       <c r="D1130" s="4" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -1870,6 +1870,85 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1343</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>866</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>571</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1911,7 +1990,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-22)</t>
+          <t>Lager (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2011,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3">
@@ -10152,7 +10231,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="414">
@@ -14152,7 +14231,7 @@
         </is>
       </c>
       <c r="D613" s="6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="614">
@@ -19612,7 +19691,7 @@
         </is>
       </c>
       <c r="D886" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="887">
@@ -24472,7 +24551,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="1130">
@@ -24492,7 +24571,7 @@
         </is>
       </c>
       <c r="D1130" s="4" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
         </is>
       </c>
     </row>
@@ -1949,6 +1949,85 @@
         <v>0</v>
       </c>
       <c r="Y18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1341</v>
+      </c>
+      <c r="C19" t="n">
+        <v>848</v>
+      </c>
+      <c r="D19" t="n">
+        <v>565</v>
+      </c>
+      <c r="E19" t="n">
+        <v>233</v>
+      </c>
+      <c r="F19" t="n">
+        <v>224</v>
+      </c>
+      <c r="G19" t="n">
+        <v>102</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1990,7 +2069,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-23)</t>
+          <t>Lager (2026-07-24)</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2090,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3">
@@ -5711,7 +5790,7 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188">
@@ -5731,7 +5810,7 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -19691,7 +19770,7 @@
         </is>
       </c>
       <c r="D886" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="887">
@@ -24551,7 +24630,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -2028,6 +2028,85 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2069,7 +2148,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-24)</t>
+          <t>Lager (2026-07-25)</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10389,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="414">
@@ -19910,7 +19989,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="894">
@@ -24550,7 +24629,7 @@
         </is>
       </c>
       <c r="D1125" s="6" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1126">
@@ -24570,7 +24649,7 @@
         </is>
       </c>
       <c r="D1126" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1127">
@@ -24630,7 +24709,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
         </is>
       </c>
     </row>
@@ -2265,6 +2265,85 @@
         <v>0</v>
       </c>
       <c r="Y22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1344</v>
+      </c>
+      <c r="C23" t="n">
+        <v>860</v>
+      </c>
+      <c r="D23" t="n">
+        <v>565</v>
+      </c>
+      <c r="E23" t="n">
+        <v>229</v>
+      </c>
+      <c r="F23" t="n">
+        <v>221</v>
+      </c>
+      <c r="G23" t="n">
+        <v>102</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
+        <v>24</v>
+      </c>
+      <c r="K23" t="n">
+        <v>17</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2306,7 +2385,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-27)</t>
+          <t>Lager (2026-07-28)</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10626,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="414">
@@ -10627,7 +10706,7 @@
         </is>
       </c>
       <c r="D417" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="418">
@@ -20007,7 +20086,7 @@
         </is>
       </c>
       <c r="D886" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="887">
@@ -21987,7 +22066,7 @@
         </is>
       </c>
       <c r="D985" s="6" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="986">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
         </is>
       </c>
     </row>
@@ -2344,6 +2344,85 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1328</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>855</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2385,7 +2464,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-28)</t>
+          <t>Lager (2026-07-29)</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6145,7 @@
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186">
@@ -10626,7 +10705,7 @@
         </is>
       </c>
       <c r="D413" s="6" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="414">
@@ -20226,7 +20305,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1257</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="894">
@@ -22066,7 +22145,7 @@
         </is>
       </c>
       <c r="D985" s="6" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="986">
@@ -24946,7 +25025,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
         </is>
       </c>
     </row>
@@ -2423,6 +2423,85 @@
         <v>0</v>
       </c>
       <c r="Y24" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1316</v>
+      </c>
+      <c r="C25" t="n">
+        <v>854</v>
+      </c>
+      <c r="D25" t="n">
+        <v>565</v>
+      </c>
+      <c r="E25" t="n">
+        <v>228</v>
+      </c>
+      <c r="F25" t="n">
+        <v>219</v>
+      </c>
+      <c r="G25" t="n">
+        <v>102</v>
+      </c>
+      <c r="H25" t="n">
+        <v>48</v>
+      </c>
+      <c r="I25" t="n">
+        <v>33</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2464,7 +2543,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-07-29)</t>
+          <t>Lager (2026-07-30)</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20384,7 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>1241</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="894">
@@ -22145,7 +22224,7 @@
         </is>
       </c>
       <c r="D985" s="6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="986">
@@ -25025,7 +25104,7 @@
         </is>
       </c>
       <c r="D1129" s="6" t="n">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="1130">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>THORN</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
         </is>
       </c>
     </row>
@@ -3292,6 +3292,85 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1324</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>881</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>563</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3333,7 +3412,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-09)</t>
+          <t>Lager (2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4159,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4100,7 +4179,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4120,7 +4199,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4140,7 +4219,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4160,7 +4239,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4180,7 +4259,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4200,7 +4279,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4220,7 +4299,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4240,7 +4319,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4260,7 +4339,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4280,7 +4359,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4300,7 +4379,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4320,7 +4399,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4340,7 +4419,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Hide-a-lite</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Let it light</t>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         <v>527</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>223</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>93</v>
@@ -707,10 +707,10 @@
         <v>527</v>
       </c>
       <c r="E3" t="n">
+        <v>233</v>
+      </c>
+      <c r="F3" t="n">
         <v>223</v>
-      </c>
-      <c r="F3" t="n">
-        <v>233</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
@@ -786,10 +786,10 @@
         <v>523</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>100</v>
@@ -865,10 +865,10 @@
         <v>522</v>
       </c>
       <c r="E5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F5" t="n">
         <v>221</v>
-      </c>
-      <c r="F5" t="n">
-        <v>233</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -944,10 +944,10 @@
         <v>528</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>100</v>
@@ -1020,10 +1020,10 @@
         <v>920</v>
       </c>
       <c r="E7" t="n">
+        <v>232</v>
+      </c>
+      <c r="F7" t="n">
         <v>215</v>
-      </c>
-      <c r="F7" t="n">
-        <v>232</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -1099,10 +1099,10 @@
         <v>528</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>100</v>
@@ -1178,10 +1178,10 @@
         <v>532</v>
       </c>
       <c r="E9" t="n">
+        <v>232</v>
+      </c>
+      <c r="F9" t="n">
         <v>214</v>
-      </c>
-      <c r="F9" t="n">
-        <v>232</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -1257,10 +1257,10 @@
         <v>544</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>231</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>100</v>
@@ -1336,10 +1336,10 @@
         <v>544</v>
       </c>
       <c r="E11" t="n">
+        <v>231</v>
+      </c>
+      <c r="F11" t="n">
         <v>225</v>
-      </c>
-      <c r="F11" t="n">
-        <v>231</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -1415,10 +1415,10 @@
         <v>544</v>
       </c>
       <c r="E12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>94</v>
@@ -1494,10 +1494,10 @@
         <v>545</v>
       </c>
       <c r="E13" t="n">
+        <v>224</v>
+      </c>
+      <c r="F13" t="n">
         <v>228</v>
-      </c>
-      <c r="F13" t="n">
-        <v>224</v>
       </c>
       <c r="G13" t="n">
         <v>94</v>
@@ -1573,10 +1573,10 @@
         <v>545</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>94</v>
@@ -1652,10 +1652,10 @@
         <v>545</v>
       </c>
       <c r="E15" t="n">
+        <v>224</v>
+      </c>
+      <c r="F15" t="n">
         <v>228</v>
-      </c>
-      <c r="F15" t="n">
-        <v>224</v>
       </c>
       <c r="G15" t="n">
         <v>94</v>
@@ -1731,10 +1731,10 @@
         <v>545</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>226</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>94</v>
@@ -1810,10 +1810,10 @@
         <v>572</v>
       </c>
       <c r="E17" t="n">
+        <v>224</v>
+      </c>
+      <c r="F17" t="n">
         <v>228</v>
-      </c>
-      <c r="F17" t="n">
-        <v>224</v>
       </c>
       <c r="G17" t="n">
         <v>94</v>
@@ -1889,10 +1889,10 @@
         <v>571</v>
       </c>
       <c r="E18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>102</v>
@@ -1968,10 +1968,10 @@
         <v>565</v>
       </c>
       <c r="E19" t="n">
+        <v>224</v>
+      </c>
+      <c r="F19" t="n">
         <v>233</v>
-      </c>
-      <c r="F19" t="n">
-        <v>224</v>
       </c>
       <c r="G19" t="n">
         <v>102</v>
@@ -2047,10 +2047,10 @@
         <v>565</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>102</v>
@@ -2126,10 +2126,10 @@
         <v>565</v>
       </c>
       <c r="E21" t="n">
+        <v>224</v>
+      </c>
+      <c r="F21" t="n">
         <v>232</v>
-      </c>
-      <c r="F21" t="n">
-        <v>224</v>
       </c>
       <c r="G21" t="n">
         <v>102</v>
@@ -2205,10 +2205,10 @@
         <v>565</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>102</v>
@@ -2284,10 +2284,10 @@
         <v>565</v>
       </c>
       <c r="E23" t="n">
+        <v>221</v>
+      </c>
+      <c r="F23" t="n">
         <v>229</v>
-      </c>
-      <c r="F23" t="n">
-        <v>221</v>
       </c>
       <c r="G23" t="n">
         <v>102</v>
@@ -2363,10 +2363,10 @@
         <v>565</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>220</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>102</v>
@@ -2442,10 +2442,10 @@
         <v>565</v>
       </c>
       <c r="E25" t="n">
+        <v>219</v>
+      </c>
+      <c r="F25" t="n">
         <v>228</v>
-      </c>
-      <c r="F25" t="n">
-        <v>219</v>
       </c>
       <c r="G25" t="n">
         <v>102</v>
@@ -2521,10 +2521,10 @@
         <v>565</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>230</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>102</v>
@@ -2600,10 +2600,10 @@
         <v>565</v>
       </c>
       <c r="E27" t="n">
+        <v>217</v>
+      </c>
+      <c r="F27" t="n">
         <v>233</v>
-      </c>
-      <c r="F27" t="n">
-        <v>217</v>
       </c>
       <c r="G27" t="n">
         <v>102</v>
@@ -2679,10 +2679,10 @@
         <v>565</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>102</v>
@@ -2758,10 +2758,10 @@
         <v>565</v>
       </c>
       <c r="E29" t="n">
+        <v>217</v>
+      </c>
+      <c r="F29" t="n">
         <v>233</v>
-      </c>
-      <c r="F29" t="n">
-        <v>217</v>
       </c>
       <c r="G29" t="n">
         <v>102</v>
@@ -2837,10 +2837,10 @@
         <v>541</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>208</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>102</v>
@@ -2916,10 +2916,10 @@
         <v>544</v>
       </c>
       <c r="E31" t="n">
+        <v>217</v>
+      </c>
+      <c r="F31" t="n">
         <v>208</v>
-      </c>
-      <c r="F31" t="n">
-        <v>217</v>
       </c>
       <c r="G31" t="n">
         <v>102</v>
@@ -2995,10 +2995,10 @@
         <v>556</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>102</v>
@@ -3074,10 +3074,10 @@
         <v>564</v>
       </c>
       <c r="E33" t="n">
+        <v>216</v>
+      </c>
+      <c r="F33" t="n">
         <v>218</v>
-      </c>
-      <c r="F33" t="n">
-        <v>216</v>
       </c>
       <c r="G33" t="n">
         <v>102</v>
@@ -3153,10 +3153,10 @@
         <v>563</v>
       </c>
       <c r="E34" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>102</v>
@@ -3232,10 +3232,10 @@
         <v>563</v>
       </c>
       <c r="E35" t="n">
+        <v>216</v>
+      </c>
+      <c r="F35" t="n">
         <v>218</v>
-      </c>
-      <c r="F35" t="n">
-        <v>216</v>
       </c>
       <c r="G35" t="n">
         <v>102</v>
@@ -3311,10 +3311,10 @@
         <v>563</v>
       </c>
       <c r="E36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>102</v>
@@ -3390,10 +3390,10 @@
         <v>563</v>
       </c>
       <c r="E37" t="n">
+        <v>212</v>
+      </c>
+      <c r="F37" t="n">
         <v>216</v>
-      </c>
-      <c r="F37" t="n">
-        <v>212</v>
       </c>
       <c r="G37" t="n">
         <v>102</v>
@@ -3450,6 +3450,85 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>891</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>556</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3491,7 +3570,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-11)</t>
+          <t>Lager (2026-08-12)</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3591,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3">
@@ -11932,7 +12011,7 @@
         </is>
       </c>
       <c r="D423" s="6" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="424">
@@ -15812,7 +15891,7 @@
         </is>
       </c>
       <c r="D617" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="618">
@@ -21272,7 +21351,7 @@
         </is>
       </c>
       <c r="D890" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="891">
@@ -25812,7 +25891,7 @@
         </is>
       </c>
       <c r="D1117" s="6" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1118">
@@ -25892,7 +25971,7 @@
         </is>
       </c>
       <c r="D1121" s="6" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1122">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Hide-a-lite</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Tupex</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Hide-a-lite</t>
-        </is>
-      </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Let it light</t>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Legrand</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         <v>527</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>223</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>93</v>
@@ -707,10 +707,10 @@
         <v>527</v>
       </c>
       <c r="E3" t="n">
+        <v>223</v>
+      </c>
+      <c r="F3" t="n">
         <v>233</v>
-      </c>
-      <c r="F3" t="n">
-        <v>223</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
@@ -786,10 +786,10 @@
         <v>523</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>100</v>
@@ -865,10 +865,10 @@
         <v>522</v>
       </c>
       <c r="E5" t="n">
+        <v>221</v>
+      </c>
+      <c r="F5" t="n">
         <v>233</v>
-      </c>
-      <c r="F5" t="n">
-        <v>221</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -944,10 +944,10 @@
         <v>528</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>100</v>
@@ -1020,10 +1020,10 @@
         <v>920</v>
       </c>
       <c r="E7" t="n">
+        <v>215</v>
+      </c>
+      <c r="F7" t="n">
         <v>232</v>
-      </c>
-      <c r="F7" t="n">
-        <v>215</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -1099,10 +1099,10 @@
         <v>528</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>100</v>
@@ -1178,10 +1178,10 @@
         <v>532</v>
       </c>
       <c r="E9" t="n">
+        <v>214</v>
+      </c>
+      <c r="F9" t="n">
         <v>232</v>
-      </c>
-      <c r="F9" t="n">
-        <v>214</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -1257,10 +1257,10 @@
         <v>544</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>231</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>218</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>100</v>
@@ -1336,10 +1336,10 @@
         <v>544</v>
       </c>
       <c r="E11" t="n">
+        <v>225</v>
+      </c>
+      <c r="F11" t="n">
         <v>231</v>
-      </c>
-      <c r="F11" t="n">
-        <v>225</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -1415,10 +1415,10 @@
         <v>544</v>
       </c>
       <c r="E12" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>228</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>94</v>
@@ -1494,10 +1494,10 @@
         <v>545</v>
       </c>
       <c r="E13" t="n">
+        <v>228</v>
+      </c>
+      <c r="F13" t="n">
         <v>224</v>
-      </c>
-      <c r="F13" t="n">
-        <v>228</v>
       </c>
       <c r="G13" t="n">
         <v>94</v>
@@ -1573,10 +1573,10 @@
         <v>545</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>228</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>94</v>
@@ -1652,10 +1652,10 @@
         <v>545</v>
       </c>
       <c r="E15" t="n">
+        <v>228</v>
+      </c>
+      <c r="F15" t="n">
         <v>224</v>
-      </c>
-      <c r="F15" t="n">
-        <v>228</v>
       </c>
       <c r="G15" t="n">
         <v>94</v>
@@ -1731,10 +1731,10 @@
         <v>545</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>226</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>94</v>
@@ -1810,10 +1810,10 @@
         <v>572</v>
       </c>
       <c r="E17" t="n">
+        <v>228</v>
+      </c>
+      <c r="F17" t="n">
         <v>224</v>
-      </c>
-      <c r="F17" t="n">
-        <v>228</v>
       </c>
       <c r="G17" t="n">
         <v>94</v>
@@ -1889,10 +1889,10 @@
         <v>571</v>
       </c>
       <c r="E18" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>102</v>
@@ -1968,10 +1968,10 @@
         <v>565</v>
       </c>
       <c r="E19" t="n">
+        <v>233</v>
+      </c>
+      <c r="F19" t="n">
         <v>224</v>
-      </c>
-      <c r="F19" t="n">
-        <v>233</v>
       </c>
       <c r="G19" t="n">
         <v>102</v>
@@ -2047,10 +2047,10 @@
         <v>565</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>102</v>
@@ -2126,10 +2126,10 @@
         <v>565</v>
       </c>
       <c r="E21" t="n">
+        <v>232</v>
+      </c>
+      <c r="F21" t="n">
         <v>224</v>
-      </c>
-      <c r="F21" t="n">
-        <v>232</v>
       </c>
       <c r="G21" t="n">
         <v>102</v>
@@ -2205,10 +2205,10 @@
         <v>565</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>224</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>102</v>
@@ -2284,10 +2284,10 @@
         <v>565</v>
       </c>
       <c r="E23" t="n">
+        <v>229</v>
+      </c>
+      <c r="F23" t="n">
         <v>221</v>
-      </c>
-      <c r="F23" t="n">
-        <v>229</v>
       </c>
       <c r="G23" t="n">
         <v>102</v>
@@ -2363,10 +2363,10 @@
         <v>565</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>220</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>228</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>102</v>
@@ -2442,10 +2442,10 @@
         <v>565</v>
       </c>
       <c r="E25" t="n">
+        <v>228</v>
+      </c>
+      <c r="F25" t="n">
         <v>219</v>
-      </c>
-      <c r="F25" t="n">
-        <v>228</v>
       </c>
       <c r="G25" t="n">
         <v>102</v>
@@ -2521,10 +2521,10 @@
         <v>565</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>230</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>102</v>
@@ -2600,10 +2600,10 @@
         <v>565</v>
       </c>
       <c r="E27" t="n">
+        <v>233</v>
+      </c>
+      <c r="F27" t="n">
         <v>217</v>
-      </c>
-      <c r="F27" t="n">
-        <v>233</v>
       </c>
       <c r="G27" t="n">
         <v>102</v>
@@ -2679,10 +2679,10 @@
         <v>565</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>102</v>
@@ -2758,10 +2758,10 @@
         <v>565</v>
       </c>
       <c r="E29" t="n">
+        <v>233</v>
+      </c>
+      <c r="F29" t="n">
         <v>217</v>
-      </c>
-      <c r="F29" t="n">
-        <v>233</v>
       </c>
       <c r="G29" t="n">
         <v>102</v>
@@ -2837,10 +2837,10 @@
         <v>541</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>208</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>102</v>
@@ -2916,10 +2916,10 @@
         <v>544</v>
       </c>
       <c r="E31" t="n">
+        <v>208</v>
+      </c>
+      <c r="F31" t="n">
         <v>217</v>
-      </c>
-      <c r="F31" t="n">
-        <v>208</v>
       </c>
       <c r="G31" t="n">
         <v>102</v>
@@ -2995,10 +2995,10 @@
         <v>556</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>218</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>102</v>
@@ -3074,10 +3074,10 @@
         <v>564</v>
       </c>
       <c r="E33" t="n">
+        <v>218</v>
+      </c>
+      <c r="F33" t="n">
         <v>216</v>
-      </c>
-      <c r="F33" t="n">
-        <v>218</v>
       </c>
       <c r="G33" t="n">
         <v>102</v>
@@ -3153,10 +3153,10 @@
         <v>563</v>
       </c>
       <c r="E34" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>216</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>218</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>102</v>
@@ -3232,10 +3232,10 @@
         <v>563</v>
       </c>
       <c r="E35" t="n">
+        <v>218</v>
+      </c>
+      <c r="F35" t="n">
         <v>216</v>
-      </c>
-      <c r="F35" t="n">
-        <v>218</v>
       </c>
       <c r="G35" t="n">
         <v>102</v>
@@ -3311,10 +3311,10 @@
         <v>563</v>
       </c>
       <c r="E36" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>216</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>218</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>102</v>
@@ -3390,10 +3390,10 @@
         <v>563</v>
       </c>
       <c r="E37" t="n">
+        <v>216</v>
+      </c>
+      <c r="F37" t="n">
         <v>212</v>
-      </c>
-      <c r="F37" t="n">
-        <v>216</v>
       </c>
       <c r="G37" t="n">
         <v>102</v>
@@ -3469,10 +3469,10 @@
         <v>556</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>212</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>207</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>101</v>
@@ -3548,10 +3548,10 @@
         <v>562</v>
       </c>
       <c r="E39" t="n">
+        <v>207</v>
+      </c>
+      <c r="F39" t="n">
         <v>214</v>
-      </c>
-      <c r="F39" t="n">
-        <v>207</v>
       </c>
       <c r="G39" t="n">
         <v>101</v>
@@ -3608,6 +3608,85 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>891</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>519</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3649,7 +3728,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-13)</t>
+          <t>Lager (2026-08-14)</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3749,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>562</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3">
@@ -4396,7 +4475,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4416,7 +4495,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4436,7 +4515,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4456,7 +4535,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4476,7 +4555,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4496,7 +4575,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4516,7 +4595,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4536,7 +4615,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4556,7 +4635,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4576,7 +4655,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4596,7 +4675,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4616,7 +4695,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4636,7 +4715,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4656,7 +4735,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -12310,7 +12389,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="435">
@@ -21650,7 +21729,7 @@
         </is>
       </c>
       <c r="D901" s="6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="902">
@@ -22230,7 +22309,7 @@
         </is>
       </c>
       <c r="D930" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="931">
@@ -23530,7 +23609,7 @@
         </is>
       </c>
       <c r="D995" s="6" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="996">
@@ -25610,7 +25689,7 @@
         </is>
       </c>
       <c r="D1099" s="6" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1100">
@@ -25630,7 +25709,7 @@
         </is>
       </c>
       <c r="D1100" s="4" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
           <t>Airam</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
         </is>
       </c>
     </row>
@@ -3924,6 +3924,85 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>872</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3965,7 +4044,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-17)</t>
+          <t>Lager (2026-08-18)</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4065,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>517</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3">
@@ -4712,7 +4791,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4732,7 +4811,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4752,7 +4831,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4772,7 +4851,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4792,7 +4871,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4812,7 +4891,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4832,7 +4911,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4852,7 +4931,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4872,7 +4951,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4892,7 +4971,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4912,7 +4991,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4932,7 +5011,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4952,7 +5031,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4972,7 +5051,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -12626,7 +12705,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="435">
@@ -12646,7 +12725,7 @@
         </is>
       </c>
       <c r="D435" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="436">
@@ -21966,7 +22045,7 @@
         </is>
       </c>
       <c r="D901" s="6" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="902">
@@ -22106,7 +22185,7 @@
         </is>
       </c>
       <c r="D908" s="4" t="n">
-        <v>1187</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="909">
@@ -22146,7 +22225,7 @@
         </is>
       </c>
       <c r="D910" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="911">
@@ -22546,7 +22625,7 @@
         </is>
       </c>
       <c r="D930" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="931">
@@ -23846,7 +23925,7 @@
         </is>
       </c>
       <c r="D995" s="6" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="996">
@@ -25846,7 +25925,7 @@
         </is>
       </c>
       <c r="D1095" s="6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1096">
@@ -25926,7 +26005,7 @@
         </is>
       </c>
       <c r="D1099" s="6" t="n">
-        <v>438</v>
+        <v>425</v>
       </c>
     </row>
     <row r="1100">
@@ -25946,7 +26025,7 @@
         </is>
       </c>
       <c r="D1100" s="4" t="n">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Hide-a-lite</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Let it light</t>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         <v>527</v>
       </c>
       <c r="E2" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>223</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>93</v>
@@ -707,10 +707,10 @@
         <v>527</v>
       </c>
       <c r="E3" t="n">
+        <v>233</v>
+      </c>
+      <c r="F3" t="n">
         <v>223</v>
-      </c>
-      <c r="F3" t="n">
-        <v>233</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
@@ -786,10 +786,10 @@
         <v>523</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>217</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>233</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>100</v>
@@ -865,10 +865,10 @@
         <v>522</v>
       </c>
       <c r="E5" t="n">
+        <v>233</v>
+      </c>
+      <c r="F5" t="n">
         <v>221</v>
-      </c>
-      <c r="F5" t="n">
-        <v>233</v>
       </c>
       <c r="G5" t="n">
         <v>100</v>
@@ -944,10 +944,10 @@
         <v>528</v>
       </c>
       <c r="E6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>100</v>
@@ -1020,10 +1020,10 @@
         <v>920</v>
       </c>
       <c r="E7" t="n">
+        <v>232</v>
+      </c>
+      <c r="F7" t="n">
         <v>215</v>
-      </c>
-      <c r="F7" t="n">
-        <v>232</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
@@ -1099,10 +1099,10 @@
         <v>528</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>215</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>232</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>100</v>
@@ -1178,10 +1178,10 @@
         <v>532</v>
       </c>
       <c r="E9" t="n">
+        <v>232</v>
+      </c>
+      <c r="F9" t="n">
         <v>214</v>
-      </c>
-      <c r="F9" t="n">
-        <v>232</v>
       </c>
       <c r="G9" t="n">
         <v>100</v>
@@ -1257,10 +1257,10 @@
         <v>544</v>
       </c>
       <c r="E10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>231</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>100</v>
@@ -1336,10 +1336,10 @@
         <v>544</v>
       </c>
       <c r="E11" t="n">
+        <v>231</v>
+      </c>
+      <c r="F11" t="n">
         <v>225</v>
-      </c>
-      <c r="F11" t="n">
-        <v>231</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
@@ -1415,10 +1415,10 @@
         <v>544</v>
       </c>
       <c r="E12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>94</v>
@@ -1494,10 +1494,10 @@
         <v>545</v>
       </c>
       <c r="E13" t="n">
+        <v>224</v>
+      </c>
+      <c r="F13" t="n">
         <v>228</v>
-      </c>
-      <c r="F13" t="n">
-        <v>224</v>
       </c>
       <c r="G13" t="n">
         <v>94</v>
@@ -1573,10 +1573,10 @@
         <v>545</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>94</v>
@@ -1652,10 +1652,10 @@
         <v>545</v>
       </c>
       <c r="E15" t="n">
+        <v>224</v>
+      </c>
+      <c r="F15" t="n">
         <v>228</v>
-      </c>
-      <c r="F15" t="n">
-        <v>224</v>
       </c>
       <c r="G15" t="n">
         <v>94</v>
@@ -1731,10 +1731,10 @@
         <v>545</v>
       </c>
       <c r="E16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>226</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>94</v>
@@ -1810,10 +1810,10 @@
         <v>572</v>
       </c>
       <c r="E17" t="n">
+        <v>224</v>
+      </c>
+      <c r="F17" t="n">
         <v>228</v>
-      </c>
-      <c r="F17" t="n">
-        <v>224</v>
       </c>
       <c r="G17" t="n">
         <v>94</v>
@@ -1889,10 +1889,10 @@
         <v>571</v>
       </c>
       <c r="E18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>102</v>
@@ -1968,10 +1968,10 @@
         <v>565</v>
       </c>
       <c r="E19" t="n">
+        <v>224</v>
+      </c>
+      <c r="F19" t="n">
         <v>233</v>
-      </c>
-      <c r="F19" t="n">
-        <v>224</v>
       </c>
       <c r="G19" t="n">
         <v>102</v>
@@ -2047,10 +2047,10 @@
         <v>565</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>102</v>
@@ -2126,10 +2126,10 @@
         <v>565</v>
       </c>
       <c r="E21" t="n">
+        <v>224</v>
+      </c>
+      <c r="F21" t="n">
         <v>232</v>
-      </c>
-      <c r="F21" t="n">
-        <v>224</v>
       </c>
       <c r="G21" t="n">
         <v>102</v>
@@ -2205,10 +2205,10 @@
         <v>565</v>
       </c>
       <c r="E22" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>232</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>224</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>102</v>
@@ -2284,10 +2284,10 @@
         <v>565</v>
       </c>
       <c r="E23" t="n">
+        <v>221</v>
+      </c>
+      <c r="F23" t="n">
         <v>229</v>
-      </c>
-      <c r="F23" t="n">
-        <v>221</v>
       </c>
       <c r="G23" t="n">
         <v>102</v>
@@ -2363,10 +2363,10 @@
         <v>565</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>228</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>220</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>102</v>
@@ -2442,10 +2442,10 @@
         <v>565</v>
       </c>
       <c r="E25" t="n">
+        <v>219</v>
+      </c>
+      <c r="F25" t="n">
         <v>228</v>
-      </c>
-      <c r="F25" t="n">
-        <v>219</v>
       </c>
       <c r="G25" t="n">
         <v>102</v>
@@ -2521,10 +2521,10 @@
         <v>565</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>230</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>102</v>
@@ -2600,10 +2600,10 @@
         <v>565</v>
       </c>
       <c r="E27" t="n">
+        <v>217</v>
+      </c>
+      <c r="F27" t="n">
         <v>233</v>
-      </c>
-      <c r="F27" t="n">
-        <v>217</v>
       </c>
       <c r="G27" t="n">
         <v>102</v>
@@ -2679,10 +2679,10 @@
         <v>565</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>233</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>102</v>
@@ -2758,10 +2758,10 @@
         <v>565</v>
       </c>
       <c r="E29" t="n">
+        <v>217</v>
+      </c>
+      <c r="F29" t="n">
         <v>233</v>
-      </c>
-      <c r="F29" t="n">
-        <v>217</v>
       </c>
       <c r="G29" t="n">
         <v>102</v>
@@ -2837,10 +2837,10 @@
         <v>541</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>208</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>215</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>102</v>
@@ -2916,10 +2916,10 @@
         <v>544</v>
       </c>
       <c r="E31" t="n">
+        <v>217</v>
+      </c>
+      <c r="F31" t="n">
         <v>208</v>
-      </c>
-      <c r="F31" t="n">
-        <v>217</v>
       </c>
       <c r="G31" t="n">
         <v>102</v>
@@ -2995,10 +2995,10 @@
         <v>556</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>217</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>102</v>
@@ -3074,10 +3074,10 @@
         <v>564</v>
       </c>
       <c r="E33" t="n">
+        <v>216</v>
+      </c>
+      <c r="F33" t="n">
         <v>218</v>
-      </c>
-      <c r="F33" t="n">
-        <v>216</v>
       </c>
       <c r="G33" t="n">
         <v>102</v>
@@ -3153,10 +3153,10 @@
         <v>563</v>
       </c>
       <c r="E34" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>102</v>
@@ -3232,10 +3232,10 @@
         <v>563</v>
       </c>
       <c r="E35" t="n">
+        <v>216</v>
+      </c>
+      <c r="F35" t="n">
         <v>218</v>
-      </c>
-      <c r="F35" t="n">
-        <v>216</v>
       </c>
       <c r="G35" t="n">
         <v>102</v>
@@ -3311,10 +3311,10 @@
         <v>563</v>
       </c>
       <c r="E36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>216</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>102</v>
@@ -3390,10 +3390,10 @@
         <v>563</v>
       </c>
       <c r="E37" t="n">
+        <v>212</v>
+      </c>
+      <c r="F37" t="n">
         <v>216</v>
-      </c>
-      <c r="F37" t="n">
-        <v>212</v>
       </c>
       <c r="G37" t="n">
         <v>102</v>
@@ -3469,10 +3469,10 @@
         <v>556</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>207</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>212</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>101</v>
@@ -3548,10 +3548,10 @@
         <v>562</v>
       </c>
       <c r="E39" t="n">
+        <v>214</v>
+      </c>
+      <c r="F39" t="n">
         <v>207</v>
-      </c>
-      <c r="F39" t="n">
-        <v>214</v>
       </c>
       <c r="G39" t="n">
         <v>101</v>
@@ -3627,10 +3627,10 @@
         <v>519</v>
       </c>
       <c r="E40" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F40" s="5" t="n">
         <v>226</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>101</v>
@@ -3706,10 +3706,10 @@
         <v>517</v>
       </c>
       <c r="E41" t="n">
+        <v>210</v>
+      </c>
+      <c r="F41" t="n">
         <v>219</v>
-      </c>
-      <c r="F41" t="n">
-        <v>210</v>
       </c>
       <c r="G41" t="n">
         <v>101</v>
@@ -3785,10 +3785,10 @@
         <v>517</v>
       </c>
       <c r="E42" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F42" s="5" t="n">
         <v>219</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>210</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>101</v>
@@ -3864,10 +3864,10 @@
         <v>517</v>
       </c>
       <c r="E43" t="n">
+        <v>210</v>
+      </c>
+      <c r="F43" t="n">
         <v>219</v>
-      </c>
-      <c r="F43" t="n">
-        <v>210</v>
       </c>
       <c r="G43" t="n">
         <v>101</v>
@@ -3943,10 +3943,10 @@
         <v>531</v>
       </c>
       <c r="E44" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="F44" s="5" t="n">
         <v>214</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>208</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>101</v>
@@ -4022,10 +4022,10 @@
         <v>548</v>
       </c>
       <c r="E45" t="n">
+        <v>208</v>
+      </c>
+      <c r="F45" t="n">
         <v>214</v>
-      </c>
-      <c r="F45" t="n">
-        <v>208</v>
       </c>
       <c r="G45" t="n">
         <v>101</v>
@@ -4101,10 +4101,10 @@
         <v>548</v>
       </c>
       <c r="E46" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="F46" s="5" t="n">
         <v>218</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>203</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>101</v>
@@ -4161,6 +4161,85 @@
         <v>0</v>
       </c>
       <c r="Y46" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1235</v>
+      </c>
+      <c r="C47" t="n">
+        <v>865</v>
+      </c>
+      <c r="D47" t="n">
+        <v>554</v>
+      </c>
+      <c r="E47" t="n">
+        <v>233</v>
+      </c>
+      <c r="F47" t="n">
+        <v>214</v>
+      </c>
+      <c r="G47" t="n">
+        <v>101</v>
+      </c>
+      <c r="H47" t="n">
+        <v>48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>33</v>
+      </c>
+      <c r="J47" t="n">
+        <v>24</v>
+      </c>
+      <c r="K47" t="n">
+        <v>17</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4202,7 +4281,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-20)</t>
+          <t>Lager (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4302,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3">
@@ -12843,7 +12922,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="434">
@@ -12863,7 +12942,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -22323,7 +22402,7 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>1172</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="908">
@@ -24063,7 +24142,7 @@
         </is>
       </c>
       <c r="D994" s="4" t="n">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="995">
@@ -26463,7 +26542,7 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>433</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1115">
@@ -26483,7 +26562,7 @@
         </is>
       </c>
       <c r="D1115" s="6" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
         </is>
       </c>
     </row>
@@ -4240,6 +4240,85 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1253</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>859</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4281,7 +4360,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-21)</t>
+          <t>Lager (2026-08-22)</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4381,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3">
@@ -12922,7 +13001,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="434">
@@ -22402,7 +22481,7 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="908">
@@ -22442,7 +22521,7 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="910">
@@ -22842,7 +22921,7 @@
         </is>
       </c>
       <c r="D929" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="930">
@@ -24142,7 +24221,7 @@
         </is>
       </c>
       <c r="D994" s="4" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="995">
@@ -26462,7 +26541,7 @@
         </is>
       </c>
       <c r="D1110" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1111">
@@ -26562,7 +26641,7 @@
         </is>
       </c>
       <c r="D1115" s="6" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
         </is>
       </c>
     </row>
@@ -4477,6 +4477,85 @@
         <v>0</v>
       </c>
       <c r="Y50" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1155</v>
+      </c>
+      <c r="C51" t="n">
+        <v>847</v>
+      </c>
+      <c r="D51" t="n">
+        <v>550</v>
+      </c>
+      <c r="E51" t="n">
+        <v>227</v>
+      </c>
+      <c r="F51" t="n">
+        <v>226</v>
+      </c>
+      <c r="G51" t="n">
+        <v>101</v>
+      </c>
+      <c r="H51" t="n">
+        <v>48</v>
+      </c>
+      <c r="I51" t="n">
+        <v>33</v>
+      </c>
+      <c r="J51" t="n">
+        <v>24</v>
+      </c>
+      <c r="K51" t="n">
+        <v>17</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4518,7 +4597,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-24)</t>
+          <t>Lager (2026-08-26)</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5344,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5285,7 +5364,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -5305,7 +5384,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5325,7 +5404,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -5345,7 +5424,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5365,7 +5444,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -5385,7 +5464,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5405,7 +5484,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -5425,7 +5504,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5445,7 +5524,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -5465,7 +5544,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5485,7 +5564,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -5505,7 +5584,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5525,7 +5604,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -13159,7 +13238,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="434">
@@ -13179,7 +13258,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="435">
@@ -22499,7 +22578,7 @@
         </is>
       </c>
       <c r="D900" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="901">
@@ -22639,7 +22718,7 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>1167</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="908">
@@ -23079,7 +23158,7 @@
         </is>
       </c>
       <c r="D929" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="930">
@@ -24379,7 +24458,7 @@
         </is>
       </c>
       <c r="D994" s="4" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="995">
@@ -26779,7 +26858,7 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="1115">
@@ -26799,7 +26878,7 @@
         </is>
       </c>
       <c r="D1115" s="6" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
         </is>
       </c>
     </row>
@@ -4556,6 +4556,85 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1062</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4597,7 +4676,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-26)</t>
+          <t>Lager (2026-08-27)</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4697,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
@@ -12858,7 +12937,7 @@
         </is>
       </c>
       <c r="D414" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -13238,7 +13317,7 @@
         </is>
       </c>
       <c r="D433" s="6" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="434">
@@ -22578,7 +22657,7 @@
         </is>
       </c>
       <c r="D900" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="901">
@@ -22718,7 +22797,7 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>1078</v>
+        <v>959</v>
       </c>
     </row>
     <row r="908">
@@ -23158,7 +23237,7 @@
         </is>
       </c>
       <c r="D929" s="6" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="930">
@@ -24458,7 +24537,7 @@
         </is>
       </c>
       <c r="D994" s="4" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="995">
@@ -26858,7 +26937,7 @@
         </is>
       </c>
       <c r="D1114" s="4" t="n">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="1115">
@@ -26878,7 +26957,7 @@
         </is>
       </c>
       <c r="D1115" s="6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
         </is>
       </c>
     </row>
@@ -4714,6 +4714,85 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>988</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>844</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4755,7 +4834,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-08-28)</t>
+          <t>Lager (2026-08-29)</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4855,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3">
@@ -22656,7 +22735,7 @@
         </is>
       </c>
       <c r="D896" s="4" t="n">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="897">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y57"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -503,112 +503,112 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Tupex</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Let it light</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>SG Armaturen</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Designlight</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Exaktor</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Exaktor</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Ledvance</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Hide-a-lite</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Hide-a-lite</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Tupex</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
         </is>
       </c>
     </row>
@@ -625,26 +625,26 @@
         <v>527</v>
       </c>
       <c r="D2" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>1402</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>25</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
       </c>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="O2" s="5" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="W2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="5" t="n">
         <v>0</v>
@@ -704,26 +704,26 @@
         <v>527</v>
       </c>
       <c r="D3" t="n">
+        <v>233</v>
+      </c>
+      <c r="E3" t="n">
         <v>93</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1402</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>52</v>
-      </c>
-      <c r="G3" t="n">
-        <v>25</v>
       </c>
       <c r="H3" t="n">
         <v>33</v>
       </c>
       <c r="I3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -783,26 +783,26 @@
         <v>523</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>1391</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>25</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="O4" s="5" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="W4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="5" t="n">
         <v>0</v>
@@ -862,26 +862,26 @@
         <v>522</v>
       </c>
       <c r="D5" t="n">
+        <v>233</v>
+      </c>
+      <c r="E5" t="n">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1384</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>52</v>
-      </c>
-      <c r="G5" t="n">
-        <v>24</v>
       </c>
       <c r="H5" t="n">
         <v>33</v>
       </c>
       <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="n">
         <v>17</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -941,26 +941,26 @@
         <v>528</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>1377</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="5" t="n">
         <v>0</v>
@@ -1017,26 +1017,26 @@
         <v>920</v>
       </c>
       <c r="D7" t="n">
+        <v>232</v>
+      </c>
+      <c r="E7" t="n">
         <v>100</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1348</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>14</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24</v>
       </c>
       <c r="H7" t="n">
         <v>33</v>
       </c>
       <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="n">
         <v>17</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1096,26 +1096,26 @@
         <v>528</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>1377</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="5" t="n">
         <v>0</v>
@@ -1175,26 +1175,26 @@
         <v>532</v>
       </c>
       <c r="D9" t="n">
+        <v>232</v>
+      </c>
+      <c r="E9" t="n">
         <v>100</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1385</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>52</v>
-      </c>
-      <c r="G9" t="n">
-        <v>24</v>
       </c>
       <c r="H9" t="n">
         <v>33</v>
       </c>
       <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
         <v>17</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1254,26 +1254,26 @@
         <v>544</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>1381</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="5" t="n">
         <v>0</v>
@@ -1333,26 +1333,26 @@
         <v>544</v>
       </c>
       <c r="D11" t="n">
+        <v>231</v>
+      </c>
+      <c r="E11" t="n">
         <v>100</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1385</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>52</v>
-      </c>
-      <c r="G11" t="n">
-        <v>24</v>
       </c>
       <c r="H11" t="n">
         <v>33</v>
       </c>
       <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
         <v>17</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1412,26 +1412,26 @@
         <v>544</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>1372</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>0</v>
@@ -1491,26 +1491,26 @@
         <v>545</v>
       </c>
       <c r="D13" t="n">
+        <v>224</v>
+      </c>
+      <c r="E13" t="n">
         <v>94</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1360</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>52</v>
-      </c>
-      <c r="G13" t="n">
-        <v>24</v>
       </c>
       <c r="H13" t="n">
         <v>33</v>
       </c>
       <c r="I13" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" t="n">
         <v>17</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1570,26 +1570,26 @@
         <v>545</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>1331</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>0</v>
@@ -1649,26 +1649,26 @@
         <v>545</v>
       </c>
       <c r="D15" t="n">
+        <v>224</v>
+      </c>
+      <c r="E15" t="n">
         <v>94</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1360</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>52</v>
-      </c>
-      <c r="G15" t="n">
-        <v>24</v>
       </c>
       <c r="H15" t="n">
         <v>33</v>
       </c>
       <c r="I15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J15" t="n">
         <v>17</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1703,13 +1703,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1728,26 +1728,26 @@
         <v>545</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>1348</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0</v>
@@ -1782,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="W16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X16" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="5" t="n">
         <v>0</v>
@@ -1807,26 +1807,26 @@
         <v>572</v>
       </c>
       <c r="D17" t="n">
+        <v>224</v>
+      </c>
+      <c r="E17" t="n">
         <v>94</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1347</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>52</v>
-      </c>
-      <c r="G17" t="n">
-        <v>24</v>
       </c>
       <c r="H17" t="n">
         <v>33</v>
       </c>
       <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1861,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1886,26 +1886,26 @@
         <v>571</v>
       </c>
       <c r="D18" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>1343</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>52</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>0</v>
@@ -1940,13 +1940,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="5" t="n">
         <v>0</v>
@@ -1965,26 +1965,26 @@
         <v>565</v>
       </c>
       <c r="D19" t="n">
+        <v>224</v>
+      </c>
+      <c r="E19" t="n">
         <v>102</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1341</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>50</v>
-      </c>
-      <c r="G19" t="n">
-        <v>24</v>
       </c>
       <c r="H19" t="n">
         <v>33</v>
       </c>
       <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
         <v>17</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2019,13 +2019,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2044,26 +2044,26 @@
         <v>565</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>1340</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>50</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="5" t="n">
         <v>0</v>
@@ -2123,26 +2123,26 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
+        <v>224</v>
+      </c>
+      <c r="E21" t="n">
         <v>102</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1340</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>14</v>
-      </c>
-      <c r="G21" t="n">
-        <v>24</v>
       </c>
       <c r="H21" t="n">
         <v>33</v>
       </c>
       <c r="I21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" t="n">
         <v>17</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2202,26 +2202,26 @@
         <v>565</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>1340</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>50</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O22" s="5" t="n">
         <v>0</v>
@@ -2256,13 +2256,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X22" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="5" t="n">
         <v>0</v>
@@ -2281,26 +2281,26 @@
         <v>565</v>
       </c>
       <c r="D23" t="n">
+        <v>221</v>
+      </c>
+      <c r="E23" t="n">
         <v>102</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1344</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>50</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24</v>
       </c>
       <c r="H23" t="n">
         <v>33</v>
       </c>
       <c r="I23" t="n">
+        <v>24</v>
+      </c>
+      <c r="J23" t="n">
         <v>17</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2360,26 +2360,26 @@
         <v>565</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>1328</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O24" s="5" t="n">
         <v>0</v>
@@ -2414,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="5" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>565</v>
       </c>
       <c r="D25" t="n">
+        <v>219</v>
+      </c>
+      <c r="E25" t="n">
         <v>102</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>1316</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>48</v>
-      </c>
-      <c r="G25" t="n">
-        <v>24</v>
       </c>
       <c r="H25" t="n">
         <v>33</v>
       </c>
       <c r="I25" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" t="n">
         <v>17</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2518,26 +2518,26 @@
         <v>565</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="F26" s="5" t="n">
         <v>1322</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="V26" s="5" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="W26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>0</v>
@@ -2597,26 +2597,26 @@
         <v>565</v>
       </c>
       <c r="D27" t="n">
+        <v>217</v>
+      </c>
+      <c r="E27" t="n">
         <v>102</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>1322</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>48</v>
-      </c>
-      <c r="G27" t="n">
-        <v>24</v>
       </c>
       <c r="H27" t="n">
         <v>33</v>
       </c>
       <c r="I27" t="n">
+        <v>24</v>
+      </c>
+      <c r="J27" t="n">
         <v>17</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2651,13 +2651,13 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2676,13 +2676,13 @@
         <v>565</v>
       </c>
       <c r="D28" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>1291</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
@@ -2691,11 +2691,11 @@
         <v>33</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0</v>
       </c>
       <c r="V28" s="5" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="5" t="n">
         <v>0</v>
@@ -2755,26 +2755,26 @@
         <v>565</v>
       </c>
       <c r="D29" t="n">
+        <v>217</v>
+      </c>
+      <c r="E29" t="n">
         <v>102</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>1322</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>48</v>
-      </c>
-      <c r="G29" t="n">
-        <v>24</v>
       </c>
       <c r="H29" t="n">
         <v>33</v>
       </c>
       <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2834,26 +2834,26 @@
         <v>541</v>
       </c>
       <c r="D30" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="F30" s="5" t="n">
         <v>1284</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="V30" s="5" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -2913,26 +2913,26 @@
         <v>544</v>
       </c>
       <c r="D31" t="n">
+        <v>217</v>
+      </c>
+      <c r="E31" t="n">
         <v>102</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1284</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>48</v>
-      </c>
-      <c r="G31" t="n">
-        <v>24</v>
       </c>
       <c r="H31" t="n">
         <v>33</v>
       </c>
       <c r="I31" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" t="n">
         <v>17</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2967,13 +2967,13 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -2992,26 +2992,26 @@
         <v>556</v>
       </c>
       <c r="D32" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="F32" s="5" t="n">
         <v>1286</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O32" s="5" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="V32" s="5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X32" s="5" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="5" t="n">
         <v>0</v>
@@ -3071,26 +3071,26 @@
         <v>564</v>
       </c>
       <c r="D33" t="n">
+        <v>216</v>
+      </c>
+      <c r="E33" t="n">
         <v>102</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>1286</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>48</v>
-      </c>
-      <c r="G33" t="n">
-        <v>24</v>
       </c>
       <c r="H33" t="n">
         <v>33</v>
       </c>
       <c r="I33" t="n">
+        <v>24</v>
+      </c>
+      <c r="J33" t="n">
         <v>17</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3125,13 +3125,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3150,26 +3150,26 @@
         <v>563</v>
       </c>
       <c r="D34" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="F34" s="5" t="n">
         <v>1324</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O34" s="5" t="n">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="V34" s="5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X34" s="5" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="5" t="n">
         <v>0</v>
@@ -3229,26 +3229,26 @@
         <v>563</v>
       </c>
       <c r="D35" t="n">
+        <v>216</v>
+      </c>
+      <c r="E35" t="n">
         <v>102</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>1324</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>48</v>
-      </c>
-      <c r="G35" t="n">
-        <v>24</v>
       </c>
       <c r="H35" t="n">
         <v>33</v>
       </c>
       <c r="I35" t="n">
+        <v>24</v>
+      </c>
+      <c r="J35" t="n">
         <v>17</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3283,13 +3283,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3308,26 +3308,26 @@
         <v>563</v>
       </c>
       <c r="D36" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>1324</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>0</v>
       </c>
       <c r="V36" s="5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="5" t="n">
         <v>0</v>
@@ -3387,26 +3387,26 @@
         <v>563</v>
       </c>
       <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
         <v>102</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>1306</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>48</v>
-      </c>
-      <c r="G37" t="n">
-        <v>24</v>
       </c>
       <c r="H37" t="n">
         <v>33</v>
       </c>
       <c r="I37" t="n">
+        <v>24</v>
+      </c>
+      <c r="J37" t="n">
         <v>17</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3466,26 +3466,26 @@
         <v>556</v>
       </c>
       <c r="D38" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>1310</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" s="5" t="n">
         <v>0</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="V38" s="5" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="5" t="n">
         <v>0</v>
@@ -3545,26 +3545,26 @@
         <v>562</v>
       </c>
       <c r="D39" t="n">
+        <v>214</v>
+      </c>
+      <c r="E39" t="n">
         <v>101</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>1305</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>48</v>
-      </c>
-      <c r="G39" t="n">
-        <v>24</v>
       </c>
       <c r="H39" t="n">
         <v>33</v>
       </c>
       <c r="I39" t="n">
+        <v>24</v>
+      </c>
+      <c r="J39" t="n">
         <v>17</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3599,13 +3599,13 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3624,26 +3624,26 @@
         <v>519</v>
       </c>
       <c r="D40" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="F40" s="5" t="n">
         <v>1295</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="G40" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="O40" s="5" t="n">
         <v>0</v>
@@ -3678,13 +3678,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="5" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="W40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="5" t="n">
         <v>0</v>
@@ -3703,26 +3703,26 @@
         <v>517</v>
       </c>
       <c r="D41" t="n">
+        <v>210</v>
+      </c>
+      <c r="E41" t="n">
         <v>101</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1285</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>48</v>
-      </c>
-      <c r="G41" t="n">
-        <v>24</v>
       </c>
       <c r="H41" t="n">
         <v>33</v>
       </c>
       <c r="I41" t="n">
+        <v>24</v>
+      </c>
+      <c r="J41" t="n">
         <v>17</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3757,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3782,26 +3782,26 @@
         <v>517</v>
       </c>
       <c r="D42" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="F42" s="5" t="n">
         <v>1239</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="G42" s="5" t="n">
         <v>46</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K42" s="5" t="n">
         <v>0</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
@@ -3836,13 +3836,13 @@
         <v>0</v>
       </c>
       <c r="V42" s="5" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="W42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X42" s="5" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="5" t="n">
         <v>0</v>
@@ -3861,26 +3861,26 @@
         <v>517</v>
       </c>
       <c r="D43" t="n">
+        <v>210</v>
+      </c>
+      <c r="E43" t="n">
         <v>101</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>1270</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>48</v>
-      </c>
-      <c r="G43" t="n">
-        <v>24</v>
       </c>
       <c r="H43" t="n">
         <v>33</v>
       </c>
       <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="n">
         <v>17</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3915,13 +3915,13 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -3940,26 +3940,26 @@
         <v>531</v>
       </c>
       <c r="D44" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="F44" s="5" t="n">
         <v>1255</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="G44" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K44" s="5" t="n">
         <v>0</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O44" s="5" t="n">
         <v>0</v>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="V44" s="5" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="W44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="5" t="n">
         <v>0</v>
@@ -4019,26 +4019,26 @@
         <v>548</v>
       </c>
       <c r="D45" t="n">
+        <v>208</v>
+      </c>
+      <c r="E45" t="n">
         <v>101</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>1254</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>48</v>
-      </c>
-      <c r="G45" t="n">
-        <v>24</v>
       </c>
       <c r="H45" t="n">
         <v>33</v>
       </c>
       <c r="I45" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" t="n">
         <v>17</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4073,13 +4073,13 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4098,26 +4098,26 @@
         <v>548</v>
       </c>
       <c r="D46" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="F46" s="5" t="n">
         <v>1244</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="G46" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="V46" s="5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="W46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X46" s="5" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="5" t="n">
         <v>0</v>
@@ -4177,26 +4177,26 @@
         <v>554</v>
       </c>
       <c r="D47" t="n">
+        <v>233</v>
+      </c>
+      <c r="E47" t="n">
         <v>101</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>1235</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>48</v>
-      </c>
-      <c r="G47" t="n">
-        <v>24</v>
       </c>
       <c r="H47" t="n">
         <v>33</v>
       </c>
       <c r="I47" t="n">
+        <v>24</v>
+      </c>
+      <c r="J47" t="n">
         <v>17</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -4256,26 +4256,26 @@
         <v>550</v>
       </c>
       <c r="D48" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="F48" s="5" t="n">
         <v>1253</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="G48" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" s="5" t="n">
         <v>0</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="O48" s="5" t="n">
         <v>0</v>
@@ -4310,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="5" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="W48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X48" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>0</v>
@@ -4335,26 +4335,26 @@
         <v>550</v>
       </c>
       <c r="D49" t="n">
+        <v>232</v>
+      </c>
+      <c r="E49" t="n">
         <v>101</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>1221</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>33</v>
       </c>
       <c r="I49" t="n">
+        <v>24</v>
+      </c>
+      <c r="J49" t="n">
         <v>17</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -4414,26 +4414,26 @@
         <v>550</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="F50" s="5" t="n">
         <v>1253</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="G50" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>33</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" s="5" t="n">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="O50" s="5" t="n">
         <v>0</v>
@@ -4468,13 +4468,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="5" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="W50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="5" t="n">
         <v>0</v>
@@ -4493,26 +4493,26 @@
         <v>550</v>
       </c>
       <c r="D51" t="n">
+        <v>227</v>
+      </c>
+      <c r="E51" t="n">
         <v>101</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>1155</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>48</v>
-      </c>
-      <c r="G51" t="n">
-        <v>24</v>
       </c>
       <c r="H51" t="n">
         <v>33</v>
       </c>
       <c r="I51" t="n">
+        <v>24</v>
+      </c>
+      <c r="J51" t="n">
         <v>17</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -4572,26 +4572,26 @@
         <v>541</v>
       </c>
       <c r="D52" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="F52" s="5" t="n">
         <v>1062</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" s="5" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="O52" s="5" t="n">
         <v>0</v>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="W52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X52" s="5" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="5" t="n">
         <v>0</v>
@@ -4651,26 +4651,26 @@
         <v>539</v>
       </c>
       <c r="D53" t="n">
+        <v>224</v>
+      </c>
+      <c r="E53" t="n">
         <v>101</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>993</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>48</v>
-      </c>
-      <c r="G53" t="n">
-        <v>24</v>
       </c>
       <c r="H53" t="n">
         <v>30</v>
       </c>
       <c r="I53" t="n">
+        <v>24</v>
+      </c>
+      <c r="J53" t="n">
         <v>17</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -4730,26 +4730,26 @@
         <v>533</v>
       </c>
       <c r="D54" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="F54" s="5" t="n">
         <v>988</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="G54" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H54" s="5" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" s="5" t="n">
         <v>0</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O54" s="5" t="n">
         <v>0</v>
@@ -4784,13 +4784,13 @@
         <v>0</v>
       </c>
       <c r="V54" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X54" s="5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="5" t="n">
         <v>0</v>
@@ -4809,26 +4809,26 @@
         <v>533</v>
       </c>
       <c r="D55" t="n">
+        <v>224</v>
+      </c>
+      <c r="E55" t="n">
         <v>101</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>956</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>24</v>
       </c>
       <c r="H55" t="n">
         <v>30</v>
       </c>
       <c r="I55" t="n">
+        <v>24</v>
+      </c>
+      <c r="J55" t="n">
         <v>17</v>
       </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -4888,26 +4888,26 @@
         <v>532</v>
       </c>
       <c r="D56" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="F56" s="5" t="n">
         <v>985</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="G56" s="5" t="n">
         <v>48</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K56" s="5" t="n">
         <v>0</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="O56" s="5" t="n">
         <v>0</v>
@@ -4942,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="V56" s="5" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="W56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X56" s="5" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="5" t="n">
         <v>0</v>
@@ -4967,26 +4967,26 @@
         <v>527</v>
       </c>
       <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
         <v>101</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>72</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>48</v>
-      </c>
-      <c r="G57" t="n">
-        <v>24</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
       </c>
       <c r="I57" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" t="n">
         <v>22</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
@@ -5030,6 +5030,85 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>751</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5044,7 +5123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1143"/>
+  <dimension ref="A1:D1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5071,7 +5150,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-01)</t>
+          <t>Lager (2026-09-02)</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5171,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3">
@@ -8792,7 +8871,7 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188">
@@ -13352,7 +13431,7 @@
         </is>
       </c>
       <c r="D415" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -24278,12 +24357,12 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
@@ -24298,12 +24377,12 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -24312,18 +24391,18 @@
         </is>
       </c>
       <c r="D963" s="6" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
@@ -24338,12 +24417,12 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -24358,12 +24437,12 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
@@ -24378,7 +24457,7 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -24398,17 +24477,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -24418,17 +24497,17 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D969" s="6" t="n">
@@ -24438,17 +24517,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -24458,17 +24537,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -24478,17 +24557,17 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D972" s="4" t="n">
@@ -24498,12 +24577,12 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -24518,12 +24597,12 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
@@ -24538,12 +24617,12 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -24558,12 +24637,12 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
@@ -24578,12 +24657,12 @@
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -24598,12 +24677,12 @@
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
@@ -24618,12 +24697,12 @@
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -24638,12 +24717,12 @@
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
@@ -24658,12 +24737,12 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -24678,12 +24757,12 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
@@ -24698,12 +24777,12 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -24718,12 +24797,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7025807</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld T-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -24738,12 +24817,12 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7025808</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld T-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -24758,12 +24837,12 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7025820</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld T-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
@@ -24778,12 +24857,12 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7025819</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld T-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -24798,12 +24877,12 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
@@ -24818,7 +24897,7 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -24838,7 +24917,7 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
@@ -24858,7 +24937,7 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -24878,12 +24957,12 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7025757E</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld mittsektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
@@ -24898,7 +24977,7 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7025758</t>
+          <t>7025757E</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -24918,7 +24997,7 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7025759</t>
+          <t>7025758</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
@@ -24938,7 +25017,7 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7025760</t>
+          <t>7025759</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -24958,7 +25037,7 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7025761</t>
+          <t>7025760</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
@@ -24978,7 +25057,7 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7025762E</t>
+          <t>7025761</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -24998,7 +25077,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7025763E</t>
+          <t>7025762E</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
@@ -25018,7 +25097,7 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7025764</t>
+          <t>7025763E</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -25038,7 +25117,7 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7025765</t>
+          <t>7025764</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
@@ -25058,7 +25137,7 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025766</t>
+          <t>7025765</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -25078,7 +25157,7 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025767</t>
+          <t>7025766</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
@@ -25098,7 +25177,7 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025768</t>
+          <t>7025767</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -25118,7 +25197,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025769</t>
+          <t>7025768</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -25138,7 +25217,7 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025770</t>
+          <t>7025769</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -25158,7 +25237,7 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025785</t>
+          <t>7025770</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
@@ -25178,7 +25257,7 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025786</t>
+          <t>7025785</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -25198,7 +25277,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025787</t>
+          <t>7025786</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -25218,7 +25297,7 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025788</t>
+          <t>7025787</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -25238,7 +25317,7 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025789</t>
+          <t>7025788</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
@@ -25258,7 +25337,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025790</t>
+          <t>7025789</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -25278,7 +25357,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025791</t>
+          <t>7025790</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -25298,7 +25377,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025792</t>
+          <t>7025791</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -25318,7 +25397,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025793</t>
+          <t>7025792</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -25338,7 +25417,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025794</t>
+          <t>7025793</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -25358,7 +25437,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025795</t>
+          <t>7025794</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -25378,7 +25457,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025796</t>
+          <t>7025795</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -25398,7 +25477,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025797</t>
+          <t>7025796</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -25418,7 +25497,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025798</t>
+          <t>7025797</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -25438,12 +25517,12 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025617</t>
+          <t>7025798</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld singel</t>
+          <t>Interiörarmatur Lino infälld mittsektion</t>
         </is>
       </c>
       <c r="C1020" s="5" t="inlineStr">
@@ -25458,7 +25537,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025618</t>
+          <t>7025617</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -25478,7 +25557,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025619</t>
+          <t>7025618</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -25498,7 +25577,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025620</t>
+          <t>7025619</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -25518,7 +25597,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025621</t>
+          <t>7025620</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -25538,7 +25617,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025622</t>
+          <t>7025621</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -25558,7 +25637,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025623</t>
+          <t>7025622</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -25578,7 +25657,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025624</t>
+          <t>7025623</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -25598,7 +25677,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025625</t>
+          <t>7025624</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -25618,7 +25697,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025626</t>
+          <t>7025625</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -25638,7 +25717,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025627</t>
+          <t>7025626</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -25658,7 +25737,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025628</t>
+          <t>7025627</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -25678,7 +25757,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025629</t>
+          <t>7025628</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -25698,7 +25777,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025630</t>
+          <t>7025629</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -25718,7 +25797,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025631</t>
+          <t>7025630</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -25738,7 +25817,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025632</t>
+          <t>7025631</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -25758,7 +25837,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025633</t>
+          <t>7025632</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -25778,7 +25857,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025634</t>
+          <t>7025633</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -25798,7 +25877,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025653</t>
+          <t>7025634</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -25818,7 +25897,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025654E</t>
+          <t>7025653</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -25838,7 +25917,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025655</t>
+          <t>7025654E</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -25858,7 +25937,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025656E</t>
+          <t>7025655</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -25878,7 +25957,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025657E</t>
+          <t>7025656E</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -25898,7 +25977,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025658E</t>
+          <t>7025657E</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -25918,7 +25997,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025659E</t>
+          <t>7025658E</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -25938,7 +26017,7 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025660E</t>
+          <t>7025659E</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
@@ -25958,7 +26037,7 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025661</t>
+          <t>7025660E</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
@@ -25978,7 +26057,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025662</t>
+          <t>7025661</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -25998,7 +26077,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025663</t>
+          <t>7025662</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -26018,7 +26097,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025664</t>
+          <t>7025663</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -26038,7 +26117,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025665</t>
+          <t>7025664</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -26058,7 +26137,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025666</t>
+          <t>7025665</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -26078,7 +26157,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025667</t>
+          <t>7025666</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -26098,7 +26177,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025668</t>
+          <t>7025667</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -26118,7 +26197,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025669</t>
+          <t>7025668</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -26138,7 +26217,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025670</t>
+          <t>7025669</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -26158,12 +26237,12 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025670</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld singel</t>
         </is>
       </c>
       <c r="C1056" s="5" t="inlineStr">
@@ -26178,7 +26257,7 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
@@ -26198,7 +26277,7 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
@@ -26218,7 +26297,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -26238,7 +26317,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -26258,7 +26337,7 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -26278,7 +26357,7 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
@@ -26298,7 +26377,7 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
@@ -26318,7 +26397,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -26338,7 +26417,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -26358,7 +26437,7 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
@@ -26378,7 +26457,7 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
@@ -26398,7 +26477,7 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
@@ -26418,7 +26497,7 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
@@ -26438,7 +26517,7 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
@@ -26458,7 +26537,7 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -26478,7 +26557,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -26498,7 +26577,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -26518,7 +26597,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -26538,7 +26617,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -26558,7 +26637,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -26578,7 +26657,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -26598,7 +26677,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -26618,7 +26697,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -26638,7 +26717,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -26658,7 +26737,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -26678,7 +26757,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -26698,7 +26777,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -26718,7 +26797,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -26738,7 +26817,7 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -26758,7 +26837,7 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
@@ -26778,7 +26857,7 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
@@ -26798,7 +26877,7 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
@@ -26818,7 +26897,7 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -26838,7 +26917,7 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
@@ -26858,7 +26937,7 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -26878,12 +26957,12 @@
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -26898,7 +26977,7 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
@@ -26918,7 +26997,7 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
@@ -26938,7 +27017,7 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -26958,7 +27037,7 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
@@ -26978,7 +27057,7 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -26998,7 +27077,7 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1098" s="5" t="inlineStr">
@@ -27018,7 +27097,7 @@
     <row r="1099">
       <c r="A1099" s="6" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -27038,7 +27117,7 @@
     <row r="1100">
       <c r="A1100" s="4" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1100" s="5" t="inlineStr">
@@ -27058,7 +27137,7 @@
     <row r="1101">
       <c r="A1101" s="6" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
@@ -27078,7 +27157,7 @@
     <row r="1102">
       <c r="A1102" s="4" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1102" s="5" t="inlineStr">
@@ -27098,7 +27177,7 @@
     <row r="1103">
       <c r="A1103" s="6" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -27118,12 +27197,12 @@
     <row r="1104">
       <c r="A1104" s="4" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1104" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1104" s="5" t="inlineStr">
@@ -27138,7 +27217,7 @@
     <row r="1105">
       <c r="A1105" s="6" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
@@ -27158,7 +27237,7 @@
     <row r="1106">
       <c r="A1106" s="4" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1106" s="5" t="inlineStr">
@@ -27178,7 +27257,7 @@
     <row r="1107">
       <c r="A1107" s="6" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
@@ -27198,12 +27277,12 @@
     <row r="1108">
       <c r="A1108" s="4" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
@@ -27218,12 +27297,12 @@
     <row r="1109">
       <c r="A1109" s="6" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
@@ -27238,7 +27317,7 @@
     <row r="1110">
       <c r="A1110" s="4" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1110" s="5" t="inlineStr">
@@ -27258,7 +27337,7 @@
     <row r="1111">
       <c r="A1111" s="6" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
@@ -27278,7 +27357,7 @@
     <row r="1112">
       <c r="A1112" s="4" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1112" s="5" t="inlineStr">
@@ -27298,12 +27377,12 @@
     <row r="1113">
       <c r="A1113" s="6" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -27318,7 +27397,7 @@
     <row r="1114">
       <c r="A1114" s="4" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1114" s="5" t="inlineStr">
@@ -27338,12 +27417,12 @@
     <row r="1115">
       <c r="A1115" s="6" t="inlineStr">
         <is>
-          <t>7024618</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Dor ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -27358,7 +27437,7 @@
     <row r="1116">
       <c r="A1116" s="4" t="inlineStr">
         <is>
-          <t>7024779</t>
+          <t>7024618</t>
         </is>
       </c>
       <c r="B1116" s="5" t="inlineStr">
@@ -27378,12 +27457,12 @@
     <row r="1117">
       <c r="A1117" s="6" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7024779</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Interiörarmatur WLP Dor ActiveAhead</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -27398,12 +27477,12 @@
     <row r="1118">
       <c r="A1118" s="4" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1118" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1118" s="5" t="inlineStr">
@@ -27418,7 +27497,7 @@
     <row r="1119">
       <c r="A1119" s="6" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
@@ -27438,7 +27517,7 @@
     <row r="1120">
       <c r="A1120" s="4" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1120" s="5" t="inlineStr">
@@ -27458,7 +27537,7 @@
     <row r="1121">
       <c r="A1121" s="6" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -27478,7 +27557,7 @@
     <row r="1122">
       <c r="A1122" s="4" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1122" s="5" t="inlineStr">
@@ -27498,7 +27577,7 @@
     <row r="1123">
       <c r="A1123" s="6" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -27518,7 +27597,7 @@
     <row r="1124">
       <c r="A1124" s="4" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1124" s="5" t="inlineStr">
@@ -27538,7 +27617,7 @@
     <row r="1125">
       <c r="A1125" s="6" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -27558,7 +27637,7 @@
     <row r="1126">
       <c r="A1126" s="4" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1126" s="5" t="inlineStr">
@@ -27578,7 +27657,7 @@
     <row r="1127">
       <c r="A1127" s="6" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
@@ -27598,7 +27677,7 @@
     <row r="1128">
       <c r="A1128" s="4" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1128" s="5" t="inlineStr">
@@ -27618,7 +27697,7 @@
     <row r="1129">
       <c r="A1129" s="6" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -27638,7 +27717,7 @@
     <row r="1130">
       <c r="A1130" s="4" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1130" s="5" t="inlineStr">
@@ -27658,7 +27737,7 @@
     <row r="1131">
       <c r="A1131" s="6" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -27678,7 +27757,7 @@
     <row r="1132">
       <c r="A1132" s="4" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1132" s="5" t="inlineStr">
@@ -27698,7 +27777,7 @@
     <row r="1133">
       <c r="A1133" s="6" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
@@ -27718,17 +27797,17 @@
     <row r="1134">
       <c r="A1134" s="4" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1134" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1134" s="4" t="n">
@@ -27738,7 +27817,7 @@
     <row r="1135">
       <c r="A1135" s="6" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
@@ -27758,12 +27837,12 @@
     <row r="1136">
       <c r="A1136" s="4" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1136" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1136" s="5" t="inlineStr">
@@ -27778,32 +27857,32 @@
     <row r="1137">
       <c r="A1137" s="6" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1137" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" s="4" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1138" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1138" s="5" t="inlineStr">
@@ -27812,18 +27891,18 @@
         </is>
       </c>
       <c r="D1138" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" s="6" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -27832,18 +27911,18 @@
         </is>
       </c>
       <c r="D1139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" s="4" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1140" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1140" s="5" t="inlineStr">
@@ -27858,7 +27937,7 @@
     <row r="1141">
       <c r="A1141" s="6" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
@@ -27878,12 +27957,12 @@
     <row r="1142">
       <c r="A1142" s="4" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1142" s="5" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1142" s="5" t="inlineStr">
@@ -27892,27 +27971,47 @@
         </is>
       </c>
       <c r="D1142" s="4" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" s="6" t="inlineStr">
         <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1143" s="6" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="4" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1143" t="inlineStr">
+      <c r="B1144" s="5" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1143" t="inlineStr">
+      <c r="C1144" s="5" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1143" s="6" t="n">
-        <v>336</v>
+      <c r="D1144" s="4" t="n">
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:Y61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Exaktor</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Exaktor</t>
-        </is>
-      </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Ledvance</t>
@@ -543,67 +543,67 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>THORN</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
         </is>
       </c>
       <c r="Y1" s="3" t="inlineStr">
@@ -640,10 +640,10 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>17</v>
@@ -719,10 +719,10 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J3" t="n">
         <v>25</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33</v>
       </c>
       <c r="K3" t="n">
         <v>17</v>
@@ -798,10 +798,10 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>25</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>17</v>
@@ -877,10 +877,10 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="n">
         <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
       </c>
       <c r="K5" t="n">
         <v>17</v>
@@ -956,10 +956,10 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>17</v>
@@ -1032,10 +1032,10 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>33</v>
+      </c>
+      <c r="J7" t="n">
         <v>24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>33</v>
       </c>
       <c r="K7" t="n">
         <v>17</v>
@@ -1111,10 +1111,10 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>17</v>
@@ -1190,10 +1190,10 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
         <v>24</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33</v>
       </c>
       <c r="K9" t="n">
         <v>17</v>
@@ -1269,10 +1269,10 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>17</v>
@@ -1348,10 +1348,10 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
         <v>24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>33</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1427,10 +1427,10 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>17</v>
@@ -1506,10 +1506,10 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>33</v>
+      </c>
+      <c r="J13" t="n">
         <v>24</v>
-      </c>
-      <c r="J13" t="n">
-        <v>33</v>
       </c>
       <c r="K13" t="n">
         <v>17</v>
@@ -1585,10 +1585,10 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>6</v>
@@ -1664,10 +1664,10 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" t="n">
         <v>24</v>
-      </c>
-      <c r="J15" t="n">
-        <v>33</v>
       </c>
       <c r="K15" t="n">
         <v>17</v>
@@ -1743,10 +1743,10 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>17</v>
@@ -1822,10 +1822,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="n">
         <v>24</v>
-      </c>
-      <c r="J17" t="n">
-        <v>33</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
@@ -1901,10 +1901,10 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>17</v>
@@ -1980,10 +1980,10 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" t="n">
         <v>24</v>
-      </c>
-      <c r="J19" t="n">
-        <v>33</v>
       </c>
       <c r="K19" t="n">
         <v>17</v>
@@ -2059,10 +2059,10 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>17</v>
@@ -2138,10 +2138,10 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>33</v>
+      </c>
+      <c r="J21" t="n">
         <v>24</v>
-      </c>
-      <c r="J21" t="n">
-        <v>33</v>
       </c>
       <c r="K21" t="n">
         <v>17</v>
@@ -2217,10 +2217,10 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>17</v>
@@ -2296,10 +2296,10 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
         <v>24</v>
-      </c>
-      <c r="J23" t="n">
-        <v>33</v>
       </c>
       <c r="K23" t="n">
         <v>17</v>
@@ -2375,10 +2375,10 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>17</v>
@@ -2454,10 +2454,10 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>33</v>
+      </c>
+      <c r="J25" t="n">
         <v>24</v>
-      </c>
-      <c r="J25" t="n">
-        <v>33</v>
       </c>
       <c r="K25" t="n">
         <v>17</v>
@@ -2533,10 +2533,10 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>17</v>
@@ -2612,10 +2612,10 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>33</v>
+      </c>
+      <c r="J27" t="n">
         <v>24</v>
-      </c>
-      <c r="J27" t="n">
-        <v>33</v>
       </c>
       <c r="K27" t="n">
         <v>17</v>
@@ -2691,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>17</v>
@@ -2770,10 +2770,10 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J29" t="n">
         <v>24</v>
-      </c>
-      <c r="J29" t="n">
-        <v>33</v>
       </c>
       <c r="K29" t="n">
         <v>17</v>
@@ -2849,10 +2849,10 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>17</v>
@@ -2928,10 +2928,10 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>33</v>
+      </c>
+      <c r="J31" t="n">
         <v>24</v>
-      </c>
-      <c r="J31" t="n">
-        <v>33</v>
       </c>
       <c r="K31" t="n">
         <v>17</v>
@@ -3007,10 +3007,10 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>17</v>
@@ -3086,10 +3086,10 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>33</v>
+      </c>
+      <c r="J33" t="n">
         <v>24</v>
-      </c>
-      <c r="J33" t="n">
-        <v>33</v>
       </c>
       <c r="K33" t="n">
         <v>17</v>
@@ -3165,10 +3165,10 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>17</v>
@@ -3244,10 +3244,10 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>33</v>
+      </c>
+      <c r="J35" t="n">
         <v>24</v>
-      </c>
-      <c r="J35" t="n">
-        <v>33</v>
       </c>
       <c r="K35" t="n">
         <v>17</v>
@@ -3323,10 +3323,10 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>17</v>
@@ -3402,10 +3402,10 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>33</v>
+      </c>
+      <c r="J37" t="n">
         <v>24</v>
-      </c>
-      <c r="J37" t="n">
-        <v>33</v>
       </c>
       <c r="K37" t="n">
         <v>17</v>
@@ -3481,10 +3481,10 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>17</v>
@@ -3560,10 +3560,10 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>33</v>
+      </c>
+      <c r="J39" t="n">
         <v>24</v>
-      </c>
-      <c r="J39" t="n">
-        <v>33</v>
       </c>
       <c r="K39" t="n">
         <v>17</v>
@@ -3639,10 +3639,10 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>17</v>
@@ -3718,10 +3718,10 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>33</v>
+      </c>
+      <c r="J41" t="n">
         <v>24</v>
-      </c>
-      <c r="J41" t="n">
-        <v>33</v>
       </c>
       <c r="K41" t="n">
         <v>17</v>
@@ -3797,10 +3797,10 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>17</v>
@@ -3876,10 +3876,10 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>33</v>
+      </c>
+      <c r="J43" t="n">
         <v>24</v>
-      </c>
-      <c r="J43" t="n">
-        <v>33</v>
       </c>
       <c r="K43" t="n">
         <v>17</v>
@@ -3955,10 +3955,10 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K44" s="5" t="n">
         <v>17</v>
@@ -4034,10 +4034,10 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>33</v>
+      </c>
+      <c r="J45" t="n">
         <v>24</v>
-      </c>
-      <c r="J45" t="n">
-        <v>33</v>
       </c>
       <c r="K45" t="n">
         <v>17</v>
@@ -4113,10 +4113,10 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>17</v>
@@ -4192,10 +4192,10 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>33</v>
+      </c>
+      <c r="J47" t="n">
         <v>24</v>
-      </c>
-      <c r="J47" t="n">
-        <v>33</v>
       </c>
       <c r="K47" t="n">
         <v>17</v>
@@ -4271,10 +4271,10 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>17</v>
@@ -4350,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>33</v>
+      </c>
+      <c r="J49" t="n">
         <v>24</v>
-      </c>
-      <c r="J49" t="n">
-        <v>33</v>
       </c>
       <c r="K49" t="n">
         <v>17</v>
@@ -4429,10 +4429,10 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>17</v>
@@ -4508,10 +4508,10 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>33</v>
+      </c>
+      <c r="J51" t="n">
         <v>24</v>
-      </c>
-      <c r="J51" t="n">
-        <v>33</v>
       </c>
       <c r="K51" t="n">
         <v>17</v>
@@ -4587,10 +4587,10 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>17</v>
@@ -4666,10 +4666,10 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>30</v>
+      </c>
+      <c r="J53" t="n">
         <v>24</v>
-      </c>
-      <c r="J53" t="n">
-        <v>30</v>
       </c>
       <c r="K53" t="n">
         <v>17</v>
@@ -4745,10 +4745,10 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>17</v>
@@ -4824,10 +4824,10 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>30</v>
+      </c>
+      <c r="J55" t="n">
         <v>24</v>
-      </c>
-      <c r="J55" t="n">
-        <v>30</v>
       </c>
       <c r="K55" t="n">
         <v>17</v>
@@ -4903,10 +4903,10 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>17</v>
@@ -5061,10 +5061,10 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>26</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>22</v>
@@ -5140,10 +5140,10 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>26</v>
+      </c>
+      <c r="J59" t="n">
         <v>24</v>
-      </c>
-      <c r="J59" t="n">
-        <v>26</v>
       </c>
       <c r="K59" t="n">
         <v>16</v>
@@ -5219,10 +5219,10 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>24</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>23</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>16</v>
@@ -5267,6 +5267,85 @@
         <v>0</v>
       </c>
       <c r="Y60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>888</v>
+      </c>
+      <c r="C61" t="n">
+        <v>533</v>
+      </c>
+      <c r="D61" t="n">
+        <v>495</v>
+      </c>
+      <c r="E61" t="n">
+        <v>282</v>
+      </c>
+      <c r="F61" t="n">
+        <v>218</v>
+      </c>
+      <c r="G61" t="n">
+        <v>101</v>
+      </c>
+      <c r="H61" t="n">
+        <v>43</v>
+      </c>
+      <c r="I61" t="n">
+        <v>29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>24</v>
+      </c>
+      <c r="K61" t="n">
+        <v>16</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5281,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1096"/>
+  <dimension ref="A1:D1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5308,7 +5387,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-04)</t>
+          <t>Lager (2026-09-05)</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5408,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3">
@@ -9329,7 +9408,7 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203">
@@ -13509,7 +13588,7 @@
         </is>
       </c>
       <c r="D411" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="412">
@@ -17715,12 +17794,12 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>7019475</t>
+          <t>7012494</t>
         </is>
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
@@ -17729,18 +17808,18 @@
         </is>
       </c>
       <c r="D622" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="6" t="inlineStr">
         <is>
-          <t>7019476</t>
+          <t>7012495</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17755,17 +17834,17 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>7013795</t>
+          <t>7012496</t>
         </is>
       </c>
       <c r="B624" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D624" s="4" t="n">
@@ -17775,17 +17854,17 @@
     <row r="625">
       <c r="A625" s="6" t="inlineStr">
         <is>
-          <t>7013796</t>
+          <t>7012497</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D625" s="6" t="n">
@@ -17795,17 +17874,17 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>7013797</t>
+          <t>7015180</t>
         </is>
       </c>
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D626" s="4" t="n">
@@ -17815,17 +17894,17 @@
     <row r="627">
       <c r="A627" s="6" t="inlineStr">
         <is>
-          <t>7013798</t>
+          <t>7015181</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D627" s="6" t="n">
@@ -17835,17 +17914,17 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>7018767</t>
+          <t>7050196</t>
         </is>
       </c>
       <c r="B628" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D628" s="4" t="n">
@@ -17855,17 +17934,17 @@
     <row r="629">
       <c r="A629" s="6" t="inlineStr">
         <is>
-          <t>7018768</t>
+          <t>7050197</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D629" s="6" t="n">
@@ -17875,17 +17954,17 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>7018769</t>
+          <t>7012498</t>
         </is>
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D630" s="4" t="n">
@@ -17895,17 +17974,17 @@
     <row r="631">
       <c r="A631" s="6" t="inlineStr">
         <is>
-          <t>7018771</t>
+          <t>7012499</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D631" s="6" t="n">
@@ -17915,17 +17994,17 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>7019623</t>
+          <t>7012500</t>
         </is>
       </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D632" s="4" t="n">
@@ -17935,17 +18014,17 @@
     <row r="633">
       <c r="A633" s="6" t="inlineStr">
         <is>
-          <t>7019624</t>
+          <t>7012501</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D633" s="6" t="n">
@@ -17955,17 +18034,17 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>7019653</t>
+          <t>7013292</t>
         </is>
       </c>
       <c r="B634" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C634" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D634" s="4" t="n">
@@ -17975,17 +18054,17 @@
     <row r="635">
       <c r="A635" s="6" t="inlineStr">
         <is>
-          <t>7019654</t>
+          <t>7013293</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur Freyn</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D635" s="6" t="n">
@@ -17995,37 +18074,37 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>7011878</t>
+          <t>7019475</t>
         </is>
       </c>
       <c r="B636" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C636" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D636" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="6" t="inlineStr">
         <is>
-          <t>7013748</t>
+          <t>7019476</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D637" s="6" t="n">
@@ -18035,12 +18114,12 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>7011879</t>
+          <t>7013795</t>
         </is>
       </c>
       <c r="B638" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C638" s="5" t="inlineStr">
@@ -18055,12 +18134,12 @@
     <row r="639">
       <c r="A639" s="6" t="inlineStr">
         <is>
-          <t>7013749</t>
+          <t>7013796</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -18075,12 +18154,12 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>7011548</t>
+          <t>7013797</t>
         </is>
       </c>
       <c r="B640" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C640" s="5" t="inlineStr">
@@ -18095,12 +18174,12 @@
     <row r="641">
       <c r="A641" s="6" t="inlineStr">
         <is>
-          <t>7011549</t>
+          <t>7013798</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -18115,12 +18194,12 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>7011550</t>
+          <t>7018767</t>
         </is>
       </c>
       <c r="B642" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C642" s="5" t="inlineStr">
@@ -18135,12 +18214,12 @@
     <row r="643">
       <c r="A643" s="6" t="inlineStr">
         <is>
-          <t>7011554</t>
+          <t>7018768</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -18155,12 +18234,12 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>7010891</t>
+          <t>7018769</t>
         </is>
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
@@ -18175,12 +18254,12 @@
     <row r="645">
       <c r="A645" s="6" t="inlineStr">
         <is>
-          <t>7010892</t>
+          <t>7018771</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -18195,12 +18274,12 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>7010893</t>
+          <t>7019623</t>
         </is>
       </c>
       <c r="B646" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C646" s="5" t="inlineStr">
@@ -18215,12 +18294,12 @@
     <row r="647">
       <c r="A647" s="6" t="inlineStr">
         <is>
-          <t>7010894</t>
+          <t>7019624</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -18235,12 +18314,12 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>7010895</t>
+          <t>7019653</t>
         </is>
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
@@ -18255,12 +18334,12 @@
     <row r="649">
       <c r="A649" s="6" t="inlineStr">
         <is>
-          <t>7010896</t>
+          <t>7019654</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -18275,12 +18354,12 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>7010897</t>
+          <t>7011878</t>
         </is>
       </c>
       <c r="B650" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C650" s="5" t="inlineStr">
@@ -18295,12 +18374,12 @@
     <row r="651">
       <c r="A651" s="6" t="inlineStr">
         <is>
-          <t>7010898</t>
+          <t>7013748</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -18315,12 +18394,12 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>7016266</t>
+          <t>7011879</t>
         </is>
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
@@ -18335,12 +18414,12 @@
     <row r="653">
       <c r="A653" s="6" t="inlineStr">
         <is>
-          <t>7016267E</t>
+          <t>7013749</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -18355,12 +18434,12 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>7016268</t>
+          <t>7011548</t>
         </is>
       </c>
       <c r="B654" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C654" s="5" t="inlineStr">
@@ -18375,12 +18454,12 @@
     <row r="655">
       <c r="A655" s="6" t="inlineStr">
         <is>
-          <t>7016269</t>
+          <t>7011549</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -18395,12 +18474,12 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>7010869</t>
+          <t>7011550</t>
         </is>
       </c>
       <c r="B656" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C656" s="5" t="inlineStr">
@@ -18415,12 +18494,12 @@
     <row r="657">
       <c r="A657" s="6" t="inlineStr">
         <is>
-          <t>7010883</t>
+          <t>7011554</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18435,12 +18514,12 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>7010886</t>
+          <t>7010891</t>
         </is>
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C658" s="5" t="inlineStr">
@@ -18455,12 +18534,12 @@
     <row r="659">
       <c r="A659" s="6" t="inlineStr">
         <is>
-          <t>7010887</t>
+          <t>7010892</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18475,12 +18554,12 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>7054167</t>
+          <t>7010893</t>
         </is>
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C660" s="5" t="inlineStr">
@@ -18495,12 +18574,12 @@
     <row r="661">
       <c r="A661" s="6" t="inlineStr">
         <is>
-          <t>7054168</t>
+          <t>7010894</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18515,12 +18594,12 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>7054169</t>
+          <t>7010895</t>
         </is>
       </c>
       <c r="B662" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C662" s="5" t="inlineStr">
@@ -18535,12 +18614,12 @@
     <row r="663">
       <c r="A663" s="6" t="inlineStr">
         <is>
-          <t>7016931</t>
+          <t>7010896</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18555,12 +18634,12 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>7016932</t>
+          <t>7010897</t>
         </is>
       </c>
       <c r="B664" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C664" s="5" t="inlineStr">
@@ -18575,12 +18654,12 @@
     <row r="665">
       <c r="A665" s="6" t="inlineStr">
         <is>
-          <t>7016933</t>
+          <t>7010898</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18595,12 +18674,12 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>7016934</t>
+          <t>7016266</t>
         </is>
       </c>
       <c r="B666" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C666" s="5" t="inlineStr">
@@ -18615,12 +18694,12 @@
     <row r="667">
       <c r="A667" s="6" t="inlineStr">
         <is>
-          <t>7027327</t>
+          <t>7016267E</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18635,12 +18714,12 @@
     <row r="668">
       <c r="A668" s="4" t="inlineStr">
         <is>
-          <t>7010848</t>
+          <t>7016268</t>
         </is>
       </c>
       <c r="B668" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C668" s="5" t="inlineStr">
@@ -18655,12 +18734,12 @@
     <row r="669">
       <c r="A669" s="6" t="inlineStr">
         <is>
-          <t>7010849</t>
+          <t>7016269</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18675,12 +18754,12 @@
     <row r="670">
       <c r="A670" s="4" t="inlineStr">
         <is>
-          <t>7010851</t>
+          <t>7010869</t>
         </is>
       </c>
       <c r="B670" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C670" s="5" t="inlineStr">
@@ -18695,12 +18774,12 @@
     <row r="671">
       <c r="A671" s="6" t="inlineStr">
         <is>
-          <t>7010854</t>
+          <t>7010883</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18715,12 +18794,12 @@
     <row r="672">
       <c r="A672" s="4" t="inlineStr">
         <is>
-          <t>7010855</t>
+          <t>7010886</t>
         </is>
       </c>
       <c r="B672" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C672" s="5" t="inlineStr">
@@ -18735,12 +18814,12 @@
     <row r="673">
       <c r="A673" s="6" t="inlineStr">
         <is>
-          <t>7010857</t>
+          <t>7010887</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -18755,12 +18834,12 @@
     <row r="674">
       <c r="A674" s="4" t="inlineStr">
         <is>
-          <t>7010858</t>
+          <t>7054167</t>
         </is>
       </c>
       <c r="B674" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C674" s="5" t="inlineStr">
@@ -18775,12 +18854,12 @@
     <row r="675">
       <c r="A675" s="6" t="inlineStr">
         <is>
-          <t>7010859</t>
+          <t>7054168</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -18795,12 +18874,12 @@
     <row r="676">
       <c r="A676" s="4" t="inlineStr">
         <is>
-          <t>7019619</t>
+          <t>7054169</t>
         </is>
       </c>
       <c r="B676" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C676" s="5" t="inlineStr">
@@ -18815,12 +18894,12 @@
     <row r="677">
       <c r="A677" s="6" t="inlineStr">
         <is>
-          <t>7019620</t>
+          <t>7016931</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18835,12 +18914,12 @@
     <row r="678">
       <c r="A678" s="4" t="inlineStr">
         <is>
-          <t>7019621</t>
+          <t>7016932</t>
         </is>
       </c>
       <c r="B678" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C678" s="5" t="inlineStr">
@@ -18855,12 +18934,12 @@
     <row r="679">
       <c r="A679" s="6" t="inlineStr">
         <is>
-          <t>7019622</t>
+          <t>7016933</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -18875,12 +18954,12 @@
     <row r="680">
       <c r="A680" s="4" t="inlineStr">
         <is>
-          <t>7019479</t>
+          <t>7016934</t>
         </is>
       </c>
       <c r="B680" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C680" s="5" t="inlineStr">
@@ -18895,12 +18974,12 @@
     <row r="681">
       <c r="A681" s="6" t="inlineStr">
         <is>
-          <t>7010844E</t>
+          <t>7027327</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -18915,12 +18994,12 @@
     <row r="682">
       <c r="A682" s="4" t="inlineStr">
         <is>
-          <t>7010845</t>
+          <t>7010848</t>
         </is>
       </c>
       <c r="B682" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C682" s="5" t="inlineStr">
@@ -18935,12 +19014,12 @@
     <row r="683">
       <c r="A683" s="6" t="inlineStr">
         <is>
-          <t>7010846E</t>
+          <t>7010849</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -18955,12 +19034,12 @@
     <row r="684">
       <c r="A684" s="4" t="inlineStr">
         <is>
-          <t>7010847</t>
+          <t>7010851</t>
         </is>
       </c>
       <c r="B684" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C684" s="5" t="inlineStr">
@@ -18975,12 +19054,12 @@
     <row r="685">
       <c r="A685" s="6" t="inlineStr">
         <is>
-          <t>7054160</t>
+          <t>7010854</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -18995,12 +19074,12 @@
     <row r="686">
       <c r="A686" s="4" t="inlineStr">
         <is>
-          <t>7054163</t>
+          <t>7010855</t>
         </is>
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C686" s="5" t="inlineStr">
@@ -19015,12 +19094,12 @@
     <row r="687">
       <c r="A687" s="6" t="inlineStr">
         <is>
-          <t>7054166</t>
+          <t>7010857</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -19035,12 +19114,12 @@
     <row r="688">
       <c r="A688" s="4" t="inlineStr">
         <is>
-          <t>7010833</t>
+          <t>7010858</t>
         </is>
       </c>
       <c r="B688" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C688" s="5" t="inlineStr">
@@ -19055,12 +19134,12 @@
     <row r="689">
       <c r="A689" s="6" t="inlineStr">
         <is>
-          <t>7010842E</t>
+          <t>7010859</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19075,12 +19154,12 @@
     <row r="690">
       <c r="A690" s="4" t="inlineStr">
         <is>
-          <t>7010834</t>
+          <t>7019619</t>
         </is>
       </c>
       <c r="B690" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C690" s="5" t="inlineStr">
@@ -19095,12 +19174,12 @@
     <row r="691">
       <c r="A691" s="6" t="inlineStr">
         <is>
-          <t>7010843</t>
+          <t>7019620</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19115,12 +19194,12 @@
     <row r="692">
       <c r="A692" s="4" t="inlineStr">
         <is>
-          <t>7010829</t>
+          <t>7019621</t>
         </is>
       </c>
       <c r="B692" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C692" s="5" t="inlineStr">
@@ -19135,12 +19214,12 @@
     <row r="693">
       <c r="A693" s="6" t="inlineStr">
         <is>
-          <t>7010835</t>
+          <t>7019622</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19155,12 +19234,12 @@
     <row r="694">
       <c r="A694" s="4" t="inlineStr">
         <is>
-          <t>7010832</t>
+          <t>7019479</t>
         </is>
       </c>
       <c r="B694" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C694" s="5" t="inlineStr">
@@ -19175,12 +19254,12 @@
     <row r="695">
       <c r="A695" s="6" t="inlineStr">
         <is>
-          <t>7010841</t>
+          <t>7010844E</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19195,12 +19274,12 @@
     <row r="696">
       <c r="A696" s="4" t="inlineStr">
         <is>
-          <t>7054170</t>
+          <t>7010845</t>
         </is>
       </c>
       <c r="B696" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C696" s="5" t="inlineStr">
@@ -19215,12 +19294,12 @@
     <row r="697">
       <c r="A697" s="6" t="inlineStr">
         <is>
-          <t>7054171</t>
+          <t>7010846E</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19235,12 +19314,12 @@
     <row r="698">
       <c r="A698" s="4" t="inlineStr">
         <is>
-          <t>7054172</t>
+          <t>7010847</t>
         </is>
       </c>
       <c r="B698" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C698" s="5" t="inlineStr">
@@ -19255,12 +19334,12 @@
     <row r="699">
       <c r="A699" s="6" t="inlineStr">
         <is>
-          <t>7054173</t>
+          <t>7054160</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19275,12 +19354,12 @@
     <row r="700">
       <c r="A700" s="4" t="inlineStr">
         <is>
-          <t>7054174</t>
+          <t>7054163</t>
         </is>
       </c>
       <c r="B700" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C700" s="5" t="inlineStr">
@@ -19295,12 +19374,12 @@
     <row r="701">
       <c r="A701" s="6" t="inlineStr">
         <is>
-          <t>7054175</t>
+          <t>7054166</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -19315,7 +19394,7 @@
     <row r="702">
       <c r="A702" s="4" t="inlineStr">
         <is>
-          <t>7054176</t>
+          <t>7010833</t>
         </is>
       </c>
       <c r="B702" s="5" t="inlineStr">
@@ -19335,7 +19414,7 @@
     <row r="703">
       <c r="A703" s="6" t="inlineStr">
         <is>
-          <t>7016845</t>
+          <t>7010842E</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -19355,7 +19434,7 @@
     <row r="704">
       <c r="A704" s="4" t="inlineStr">
         <is>
-          <t>7016846E</t>
+          <t>7010834</t>
         </is>
       </c>
       <c r="B704" s="5" t="inlineStr">
@@ -19375,7 +19454,7 @@
     <row r="705">
       <c r="A705" s="6" t="inlineStr">
         <is>
-          <t>7016847E</t>
+          <t>7010843</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19395,7 +19474,7 @@
     <row r="706">
       <c r="A706" s="4" t="inlineStr">
         <is>
-          <t>7016848E</t>
+          <t>7010829</t>
         </is>
       </c>
       <c r="B706" s="5" t="inlineStr">
@@ -19415,7 +19494,7 @@
     <row r="707">
       <c r="A707" s="6" t="inlineStr">
         <is>
-          <t>7015420</t>
+          <t>7010835</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19435,7 +19514,7 @@
     <row r="708">
       <c r="A708" s="4" t="inlineStr">
         <is>
-          <t>7015423</t>
+          <t>7010832</t>
         </is>
       </c>
       <c r="B708" s="5" t="inlineStr">
@@ -19455,7 +19534,7 @@
     <row r="709">
       <c r="A709" s="6" t="inlineStr">
         <is>
-          <t>7015428</t>
+          <t>7010841</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19475,7 +19554,7 @@
     <row r="710">
       <c r="A710" s="4" t="inlineStr">
         <is>
-          <t>7015429</t>
+          <t>7054170</t>
         </is>
       </c>
       <c r="B710" s="5" t="inlineStr">
@@ -19495,7 +19574,7 @@
     <row r="711">
       <c r="A711" s="6" t="inlineStr">
         <is>
-          <t>7018058</t>
+          <t>7054171</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19515,7 +19594,7 @@
     <row r="712">
       <c r="A712" s="4" t="inlineStr">
         <is>
-          <t>7018059</t>
+          <t>7054172</t>
         </is>
       </c>
       <c r="B712" s="5" t="inlineStr">
@@ -19535,7 +19614,7 @@
     <row r="713">
       <c r="A713" s="6" t="inlineStr">
         <is>
-          <t>7018060</t>
+          <t>7054173</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19555,7 +19634,7 @@
     <row r="714">
       <c r="A714" s="4" t="inlineStr">
         <is>
-          <t>7018061</t>
+          <t>7054174</t>
         </is>
       </c>
       <c r="B714" s="5" t="inlineStr">
@@ -19575,7 +19654,7 @@
     <row r="715">
       <c r="A715" s="6" t="inlineStr">
         <is>
-          <t>7019484</t>
+          <t>7054175</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19595,12 +19674,12 @@
     <row r="716">
       <c r="A716" s="4" t="inlineStr">
         <is>
-          <t>7013787</t>
+          <t>7054176</t>
         </is>
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
@@ -19615,12 +19694,12 @@
     <row r="717">
       <c r="A717" s="6" t="inlineStr">
         <is>
-          <t>7013788</t>
+          <t>7016845</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19635,12 +19714,12 @@
     <row r="718">
       <c r="A718" s="4" t="inlineStr">
         <is>
-          <t>7013789</t>
+          <t>7016846E</t>
         </is>
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
@@ -19655,12 +19734,12 @@
     <row r="719">
       <c r="A719" s="6" t="inlineStr">
         <is>
-          <t>7013790</t>
+          <t>7016847E</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19675,12 +19754,12 @@
     <row r="720">
       <c r="A720" s="4" t="inlineStr">
         <is>
-          <t>7013791</t>
+          <t>7016848E</t>
         </is>
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
@@ -19695,12 +19774,12 @@
     <row r="721">
       <c r="A721" s="6" t="inlineStr">
         <is>
-          <t>7013792</t>
+          <t>7015420</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19715,12 +19794,12 @@
     <row r="722">
       <c r="A722" s="4" t="inlineStr">
         <is>
-          <t>7013793</t>
+          <t>7015423</t>
         </is>
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
@@ -19735,12 +19814,12 @@
     <row r="723">
       <c r="A723" s="6" t="inlineStr">
         <is>
-          <t>7013794</t>
+          <t>7015428</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -19755,12 +19834,12 @@
     <row r="724">
       <c r="A724" s="4" t="inlineStr">
         <is>
-          <t>7017853</t>
+          <t>7015429</t>
         </is>
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
@@ -19775,12 +19854,12 @@
     <row r="725">
       <c r="A725" s="6" t="inlineStr">
         <is>
-          <t>7017854</t>
+          <t>7018058</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -19795,12 +19874,12 @@
     <row r="726">
       <c r="A726" s="4" t="inlineStr">
         <is>
-          <t>7017855</t>
+          <t>7018059</t>
         </is>
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
@@ -19815,12 +19894,12 @@
     <row r="727">
       <c r="A727" s="6" t="inlineStr">
         <is>
-          <t>7017856</t>
+          <t>7018060</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -19835,12 +19914,12 @@
     <row r="728">
       <c r="A728" s="4" t="inlineStr">
         <is>
-          <t>7015170</t>
+          <t>7018061</t>
         </is>
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
@@ -19855,12 +19934,12 @@
     <row r="729">
       <c r="A729" s="6" t="inlineStr">
         <is>
-          <t>7015171</t>
+          <t>7019484</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -19875,12 +19954,12 @@
     <row r="730">
       <c r="A730" s="4" t="inlineStr">
         <is>
-          <t>7015172</t>
+          <t>7013787</t>
         </is>
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
@@ -19895,12 +19974,12 @@
     <row r="731">
       <c r="A731" s="6" t="inlineStr">
         <is>
-          <t>7015173</t>
+          <t>7013788</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -19915,12 +19994,12 @@
     <row r="732">
       <c r="A732" s="4" t="inlineStr">
         <is>
-          <t>7029050</t>
+          <t>7013789</t>
         </is>
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
@@ -19935,12 +20014,12 @@
     <row r="733">
       <c r="A733" s="6" t="inlineStr">
         <is>
-          <t>7029051</t>
+          <t>7013790</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -19955,12 +20034,12 @@
     <row r="734">
       <c r="A734" s="4" t="inlineStr">
         <is>
-          <t>7029052</t>
+          <t>7013791</t>
         </is>
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
@@ -19975,12 +20054,12 @@
     <row r="735">
       <c r="A735" s="6" t="inlineStr">
         <is>
-          <t>7029053</t>
+          <t>7013792</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -19995,12 +20074,12 @@
     <row r="736">
       <c r="A736" s="4" t="inlineStr">
         <is>
-          <t>7029054</t>
+          <t>7013793</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -20015,12 +20094,12 @@
     <row r="737">
       <c r="A737" s="6" t="inlineStr">
         <is>
-          <t>7029055</t>
+          <t>7013794</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20035,12 +20114,12 @@
     <row r="738">
       <c r="A738" s="4" t="inlineStr">
         <is>
-          <t>7019046</t>
+          <t>7017853</t>
         </is>
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
@@ -20055,12 +20134,12 @@
     <row r="739">
       <c r="A739" s="6" t="inlineStr">
         <is>
-          <t>7019047</t>
+          <t>7017854</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20075,12 +20154,12 @@
     <row r="740">
       <c r="A740" s="4" t="inlineStr">
         <is>
-          <t>7019053</t>
+          <t>7017855</t>
         </is>
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
@@ -20095,12 +20174,12 @@
     <row r="741">
       <c r="A741" s="6" t="inlineStr">
         <is>
-          <t>7019058</t>
+          <t>7017856</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20115,12 +20194,12 @@
     <row r="742">
       <c r="A742" s="4" t="inlineStr">
         <is>
-          <t>7019059</t>
+          <t>7015170</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
@@ -20135,12 +20214,12 @@
     <row r="743">
       <c r="A743" s="6" t="inlineStr">
         <is>
-          <t>7019060</t>
+          <t>7015171</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20155,12 +20234,12 @@
     <row r="744">
       <c r="A744" s="4" t="inlineStr">
         <is>
-          <t>7019073</t>
+          <t>7015172</t>
         </is>
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
@@ -20175,12 +20254,12 @@
     <row r="745">
       <c r="A745" s="6" t="inlineStr">
         <is>
-          <t>7019074</t>
+          <t>7015173</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20195,12 +20274,12 @@
     <row r="746">
       <c r="A746" s="4" t="inlineStr">
         <is>
-          <t>7019315</t>
+          <t>7029050</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C746" s="5" t="inlineStr">
@@ -20215,12 +20294,12 @@
     <row r="747">
       <c r="A747" s="6" t="inlineStr">
         <is>
-          <t>7019344</t>
+          <t>7029051</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20235,12 +20314,12 @@
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>7019345</t>
+          <t>7029052</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C748" s="5" t="inlineStr">
@@ -20255,12 +20334,12 @@
     <row r="749">
       <c r="A749" s="6" t="inlineStr">
         <is>
-          <t>7019346</t>
+          <t>7029053</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20275,12 +20354,12 @@
     <row r="750">
       <c r="A750" s="4" t="inlineStr">
         <is>
-          <t>7019347</t>
+          <t>7029054</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
@@ -20295,12 +20374,12 @@
     <row r="751">
       <c r="A751" s="6" t="inlineStr">
         <is>
-          <t>7019358</t>
+          <t>7029055</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20315,12 +20394,12 @@
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>7019359</t>
+          <t>7019046</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C752" s="5" t="inlineStr">
@@ -20335,12 +20414,12 @@
     <row r="753">
       <c r="A753" s="6" t="inlineStr">
         <is>
-          <t>7019360</t>
+          <t>7019047</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20355,12 +20434,12 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>7019361</t>
+          <t>7019053</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C754" s="5" t="inlineStr">
@@ -20375,12 +20454,12 @@
     <row r="755">
       <c r="A755" s="6" t="inlineStr">
         <is>
-          <t>7019348</t>
+          <t>7019058</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -20395,12 +20474,12 @@
     <row r="756">
       <c r="A756" s="4" t="inlineStr">
         <is>
-          <t>7019349</t>
+          <t>7019059</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C756" s="5" t="inlineStr">
@@ -20415,12 +20494,12 @@
     <row r="757">
       <c r="A757" s="6" t="inlineStr">
         <is>
-          <t>7019350</t>
+          <t>7019060</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -20435,12 +20514,12 @@
     <row r="758">
       <c r="A758" s="4" t="inlineStr">
         <is>
-          <t>7019351</t>
+          <t>7019073</t>
         </is>
       </c>
       <c r="B758" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C758" s="5" t="inlineStr">
@@ -20455,12 +20534,12 @@
     <row r="759">
       <c r="A759" s="6" t="inlineStr">
         <is>
-          <t>7019352</t>
+          <t>7019074</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -20475,7 +20554,7 @@
     <row r="760">
       <c r="A760" s="4" t="inlineStr">
         <is>
-          <t>7019353</t>
+          <t>7019315</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -20495,7 +20574,7 @@
     <row r="761">
       <c r="A761" s="6" t="inlineStr">
         <is>
-          <t>7019354</t>
+          <t>7019344</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -20515,7 +20594,7 @@
     <row r="762">
       <c r="A762" s="4" t="inlineStr">
         <is>
-          <t>7019355</t>
+          <t>7019345</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -20535,7 +20614,7 @@
     <row r="763">
       <c r="A763" s="6" t="inlineStr">
         <is>
-          <t>7019356</t>
+          <t>7019346</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -20555,7 +20634,7 @@
     <row r="764">
       <c r="A764" s="4" t="inlineStr">
         <is>
-          <t>7019357</t>
+          <t>7019347</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -20575,12 +20654,12 @@
     <row r="765">
       <c r="A765" s="6" t="inlineStr">
         <is>
-          <t>7021449</t>
+          <t>7019358</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -20595,12 +20674,12 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>7021450</t>
+          <t>7019359</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C766" s="5" t="inlineStr">
@@ -20615,12 +20694,12 @@
     <row r="767">
       <c r="A767" s="6" t="inlineStr">
         <is>
-          <t>7021451</t>
+          <t>7019360</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -20635,12 +20714,12 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>7021452</t>
+          <t>7019361</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
@@ -20655,12 +20734,12 @@
     <row r="769">
       <c r="A769" s="6" t="inlineStr">
         <is>
-          <t>7021453</t>
+          <t>7019348</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -20675,12 +20754,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>7021454</t>
+          <t>7019349</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
@@ -20695,12 +20774,12 @@
     <row r="771">
       <c r="A771" s="6" t="inlineStr">
         <is>
-          <t>7021443</t>
+          <t>7019350</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -20715,12 +20794,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>7021444</t>
+          <t>7019351</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
@@ -20735,12 +20814,12 @@
     <row r="773">
       <c r="A773" s="6" t="inlineStr">
         <is>
-          <t>7021445</t>
+          <t>7019352</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -20755,12 +20834,12 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>7021446</t>
+          <t>7019353</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C774" s="5" t="inlineStr">
@@ -20775,12 +20854,12 @@
     <row r="775">
       <c r="A775" s="6" t="inlineStr">
         <is>
-          <t>7021447</t>
+          <t>7019354</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -20795,12 +20874,12 @@
     <row r="776">
       <c r="A776" s="4" t="inlineStr">
         <is>
-          <t>7021448</t>
+          <t>7019355</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C776" s="5" t="inlineStr">
@@ -20815,12 +20894,12 @@
     <row r="777">
       <c r="A777" s="6" t="inlineStr">
         <is>
-          <t>7018887</t>
+          <t>7019356</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -20835,12 +20914,12 @@
     <row r="778">
       <c r="A778" s="4" t="inlineStr">
         <is>
-          <t>7018888</t>
+          <t>7019357</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C778" s="5" t="inlineStr">
@@ -20855,12 +20934,12 @@
     <row r="779">
       <c r="A779" s="6" t="inlineStr">
         <is>
-          <t>7028566</t>
+          <t>7021449</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -20875,12 +20954,12 @@
     <row r="780">
       <c r="A780" s="4" t="inlineStr">
         <is>
-          <t>7028567</t>
+          <t>7021450</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C780" s="5" t="inlineStr">
@@ -20895,12 +20974,12 @@
     <row r="781">
       <c r="A781" s="6" t="inlineStr">
         <is>
-          <t>7028568</t>
+          <t>7021451</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -20915,12 +20994,12 @@
     <row r="782">
       <c r="A782" s="4" t="inlineStr">
         <is>
-          <t>7028569</t>
+          <t>7021452</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C782" s="5" t="inlineStr">
@@ -20935,12 +21014,12 @@
     <row r="783">
       <c r="A783" s="6" t="inlineStr">
         <is>
-          <t>7028570</t>
+          <t>7021453</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -20955,12 +21034,12 @@
     <row r="784">
       <c r="A784" s="4" t="inlineStr">
         <is>
-          <t>7028571</t>
+          <t>7021454</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C784" s="5" t="inlineStr">
@@ -20975,12 +21054,12 @@
     <row r="785">
       <c r="A785" s="6" t="inlineStr">
         <is>
-          <t>7028572</t>
+          <t>7021443</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -20995,12 +21074,12 @@
     <row r="786">
       <c r="A786" s="4" t="inlineStr">
         <is>
-          <t>7028573</t>
+          <t>7021444</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C786" s="5" t="inlineStr">
@@ -21015,12 +21094,12 @@
     <row r="787">
       <c r="A787" s="6" t="inlineStr">
         <is>
-          <t>7028574</t>
+          <t>7021445</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -21035,12 +21114,12 @@
     <row r="788">
       <c r="A788" s="4" t="inlineStr">
         <is>
-          <t>7028575</t>
+          <t>7021446</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C788" s="5" t="inlineStr">
@@ -21055,12 +21134,12 @@
     <row r="789">
       <c r="A789" s="6" t="inlineStr">
         <is>
-          <t>7028576</t>
+          <t>7021447</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -21075,12 +21154,12 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>7028577</t>
+          <t>7021448</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C790" s="5" t="inlineStr">
@@ -21095,12 +21174,12 @@
     <row r="791">
       <c r="A791" s="6" t="inlineStr">
         <is>
-          <t>7028578</t>
+          <t>7018887</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -21115,12 +21194,12 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>7028579</t>
+          <t>7018888</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C792" s="5" t="inlineStr">
@@ -21135,7 +21214,7 @@
     <row r="793">
       <c r="A793" s="6" t="inlineStr">
         <is>
-          <t>7028580</t>
+          <t>7028566</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -21155,7 +21234,7 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>7028581</t>
+          <t>7028567</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
@@ -21175,17 +21254,17 @@
     <row r="795">
       <c r="A795" s="6" t="inlineStr">
         <is>
-          <t>7029244</t>
+          <t>7028568</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D795" s="6" t="n">
@@ -21195,17 +21274,17 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>7029245</t>
+          <t>7028569</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C796" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D796" s="4" t="n">
@@ -21215,17 +21294,17 @@
     <row r="797">
       <c r="A797" s="6" t="inlineStr">
         <is>
-          <t>7029246</t>
+          <t>7028570</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D797" s="6" t="n">
@@ -21235,17 +21314,17 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>7029247</t>
+          <t>7028571</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C798" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D798" s="4" t="n">
@@ -21255,17 +21334,17 @@
     <row r="799">
       <c r="A799" s="6" t="inlineStr">
         <is>
-          <t>7029248</t>
+          <t>7028572</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D799" s="6" t="n">
@@ -21275,17 +21354,17 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>7029249</t>
+          <t>7028573</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D800" s="4" t="n">
@@ -21295,17 +21374,17 @@
     <row r="801">
       <c r="A801" s="6" t="inlineStr">
         <is>
-          <t>7029250</t>
+          <t>7028574</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D801" s="6" t="n">
@@ -21315,17 +21394,17 @@
     <row r="802">
       <c r="A802" s="4" t="inlineStr">
         <is>
-          <t>7029251</t>
+          <t>7028575</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D802" s="4" t="n">
@@ -21335,17 +21414,17 @@
     <row r="803">
       <c r="A803" s="6" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7028576</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D803" s="6" t="n">
@@ -21355,17 +21434,17 @@
     <row r="804">
       <c r="A804" s="4" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7028577</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C804" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D804" s="4" t="n">
@@ -21375,17 +21454,17 @@
     <row r="805">
       <c r="A805" s="6" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7028578</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D805" s="6" t="n">
@@ -21395,17 +21474,17 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7028579</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D806" s="4" t="n">
@@ -21415,17 +21494,17 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7028580</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D807" s="6" t="n">
@@ -21435,17 +21514,17 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7028581</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D808" s="4" t="n">
@@ -21455,17 +21534,17 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7029244</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D809" s="6" t="n">
@@ -21475,17 +21554,17 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7029245</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D810" s="4" t="n">
@@ -21495,17 +21574,17 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7029246</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D811" s="6" t="n">
@@ -21515,17 +21594,17 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7029247</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D812" s="4" t="n">
@@ -21535,17 +21614,17 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7029248</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D813" s="6" t="n">
@@ -21555,17 +21634,17 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7029249</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C814" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D814" s="4" t="n">
@@ -21575,17 +21654,17 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7029250</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D815" s="6" t="n">
@@ -21595,17 +21674,17 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7029251</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C816" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D816" s="4" t="n">
@@ -21615,12 +21694,12 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7028893</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Infälld Interiörarmatur Coreline Panel</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -21635,12 +21714,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
@@ -21655,12 +21734,12 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -21675,12 +21754,12 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C820" s="5" t="inlineStr">
@@ -21695,12 +21774,12 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -21715,12 +21794,12 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C822" s="5" t="inlineStr">
@@ -21735,12 +21814,12 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -21755,12 +21834,12 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C824" s="5" t="inlineStr">
@@ -21775,12 +21854,12 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -21795,12 +21874,12 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C826" s="5" t="inlineStr">
@@ -21815,12 +21894,12 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -21835,12 +21914,12 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C828" s="5" t="inlineStr">
@@ -21855,12 +21934,12 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -21875,12 +21954,12 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C830" s="5" t="inlineStr">
@@ -21895,12 +21974,12 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -21915,12 +21994,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -21935,12 +22014,12 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -21955,12 +22034,12 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C834" s="5" t="inlineStr">
@@ -21975,12 +22054,12 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -21995,12 +22074,12 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C836" s="5" t="inlineStr">
@@ -22015,12 +22094,12 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -22035,12 +22114,12 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C838" s="5" t="inlineStr">
@@ -22055,12 +22134,12 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -22075,12 +22154,12 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C840" s="5" t="inlineStr">
@@ -22095,12 +22174,12 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -22115,12 +22194,12 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C842" s="5" t="inlineStr">
@@ -22135,12 +22214,12 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -22155,12 +22234,12 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
@@ -22175,12 +22254,12 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -22195,12 +22274,12 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
@@ -22215,12 +22294,12 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -22235,12 +22314,12 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
@@ -22255,17 +22334,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -22275,17 +22354,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -22295,17 +22374,17 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D851" s="6" t="n">
@@ -22315,17 +22394,17 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C852" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D852" s="4" t="n">
@@ -22335,17 +22414,17 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D853" s="6" t="n">
@@ -22355,17 +22434,17 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C854" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D854" s="4" t="n">
@@ -22375,17 +22454,17 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D855" s="6" t="n">
@@ -22395,17 +22474,17 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C856" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D856" s="4" t="n">
@@ -22415,17 +22494,17 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D857" s="6" t="n">
@@ -22435,17 +22514,17 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C858" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D858" s="4" t="n">
@@ -22455,17 +22534,17 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D859" s="6" t="n">
@@ -22475,17 +22554,17 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C860" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D860" s="4" t="n">
@@ -22495,17 +22574,17 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D861" s="6" t="n">
@@ -22515,17 +22594,17 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C862" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D862" s="4" t="n">
@@ -22535,7 +22614,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -22555,7 +22634,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -22575,7 +22654,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -22595,7 +22674,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -22615,7 +22694,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -22635,7 +22714,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -22655,7 +22734,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -22675,7 +22754,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -22695,7 +22774,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -22715,7 +22794,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -22735,7 +22814,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -22755,7 +22834,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -22775,12 +22854,12 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -22795,12 +22874,12 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -22815,12 +22894,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -22835,12 +22914,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -22855,12 +22934,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -22875,12 +22954,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -22889,18 +22968,18 @@
         </is>
       </c>
       <c r="D880" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -22909,18 +22988,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7019423</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -22935,12 +23014,12 @@
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7019424</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -22955,12 +23034,12 @@
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7019428</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -22975,12 +23054,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019417</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -22995,12 +23074,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7019429</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -23015,12 +23094,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7019430</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -23035,12 +23114,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -23055,12 +23134,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -23075,12 +23154,12 @@
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -23095,12 +23174,12 @@
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -23115,12 +23194,12 @@
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -23135,12 +23214,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -23149,18 +23228,18 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -23169,18 +23248,18 @@
         </is>
       </c>
       <c r="D894" s="4" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -23189,18 +23268,18 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7019423</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -23215,12 +23294,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7019424</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -23235,12 +23314,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7019428</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -23255,12 +23334,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7019417</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -23275,12 +23354,12 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7019429</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -23295,12 +23374,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7019430</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -23315,12 +23394,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -23335,12 +23414,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -23355,12 +23434,12 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -23375,12 +23454,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -23395,12 +23474,12 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C906" s="5" t="inlineStr">
@@ -23415,12 +23494,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -23429,18 +23508,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -23449,18 +23528,18 @@
         </is>
       </c>
       <c r="D908" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -23469,18 +23548,18 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -23495,12 +23574,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -23515,12 +23594,12 @@
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -23535,12 +23614,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -23555,12 +23634,12 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C914" s="5" t="inlineStr">
@@ -23575,12 +23654,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -23589,18 +23668,18 @@
         </is>
       </c>
       <c r="D915" s="6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -23615,12 +23694,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -23635,12 +23714,12 @@
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -23655,12 +23734,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -23675,12 +23754,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -23695,12 +23774,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -23709,18 +23788,18 @@
         </is>
       </c>
       <c r="D921" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -23735,12 +23814,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -23755,12 +23834,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -23775,12 +23854,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -23795,12 +23874,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -23815,12 +23894,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -23835,12 +23914,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -23855,12 +23934,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -23869,18 +23948,18 @@
         </is>
       </c>
       <c r="D929" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -23895,12 +23974,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -23915,12 +23994,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -23935,12 +24014,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -23955,12 +24034,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -23975,12 +24054,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -23989,18 +24068,18 @@
         </is>
       </c>
       <c r="D935" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -24015,12 +24094,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -24035,12 +24114,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -24055,12 +24134,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -24075,12 +24154,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -24095,12 +24174,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -24115,12 +24194,12 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
@@ -24135,12 +24214,12 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -24155,12 +24234,12 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
@@ -24175,12 +24254,12 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -24195,12 +24274,12 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
@@ -24215,12 +24294,12 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -24235,12 +24314,12 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
@@ -24255,12 +24334,12 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -24275,12 +24354,12 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -24295,12 +24374,12 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -24315,12 +24394,12 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -24335,12 +24414,12 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -24355,17 +24434,17 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D954" s="4" t="n">
@@ -24375,17 +24454,17 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D955" s="6" t="n">
@@ -24395,17 +24474,17 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D956" s="4" t="n">
@@ -24415,17 +24494,17 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D957" s="6" t="n">
@@ -24435,17 +24514,17 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C958" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D958" s="4" t="n">
@@ -24455,17 +24534,17 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D959" s="6" t="n">
@@ -24475,17 +24554,17 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D960" s="4" t="n">
@@ -24495,17 +24574,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -24515,17 +24594,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -24535,17 +24614,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -24555,17 +24634,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -24575,17 +24654,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -24595,17 +24674,17 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D966" s="4" t="n">
@@ -24615,17 +24694,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -24635,17 +24714,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -24655,17 +24734,17 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D969" s="6" t="n">
@@ -24675,17 +24754,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -24695,17 +24774,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -24715,17 +24794,17 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D972" s="4" t="n">
@@ -24735,17 +24814,17 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D973" s="6" t="n">
@@ -24755,17 +24834,17 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D974" s="4" t="n">
@@ -24775,17 +24854,17 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D975" s="6" t="n">
@@ -24795,17 +24874,17 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D976" s="4" t="n">
@@ -24815,77 +24894,77 @@
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D977" s="6" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D978" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D980" s="4" t="n">
@@ -24895,17 +24974,17 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D981" s="6" t="n">
@@ -24915,17 +24994,17 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D982" s="4" t="n">
@@ -24935,17 +25014,17 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D983" s="6" t="n">
@@ -24955,12 +25034,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -24975,12 +25054,12 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -24995,12 +25074,12 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
@@ -25015,12 +25094,12 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -25035,12 +25114,12 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
@@ -25055,17 +25134,17 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D989" s="6" t="n">
@@ -25075,17 +25154,17 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D990" s="4" t="n">
@@ -25095,77 +25174,77 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D991" s="6" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D992" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D993" s="6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D994" s="4" t="n">
@@ -25175,17 +25254,17 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D995" s="6" t="n">
@@ -25195,17 +25274,17 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D996" s="4" t="n">
@@ -25215,17 +25294,17 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D997" s="6" t="n">
@@ -25235,17 +25314,17 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D998" s="4" t="n">
@@ -25255,17 +25334,17 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D999" s="6" t="n">
@@ -25275,17 +25354,17 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D1000" s="4" t="n">
@@ -25295,12 +25374,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -25315,12 +25394,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -25335,12 +25414,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -25355,12 +25434,12 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
@@ -25375,12 +25454,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -25395,12 +25474,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -25415,12 +25494,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -25435,12 +25514,12 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1008" s="5" t="inlineStr">
@@ -25455,12 +25534,12 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -25475,12 +25554,12 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
@@ -25495,12 +25574,12 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -25515,12 +25594,12 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1012" s="5" t="inlineStr">
@@ -25535,12 +25614,12 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -25555,12 +25634,12 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1014" s="5" t="inlineStr">
@@ -25575,12 +25654,12 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -25595,12 +25674,12 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1016" s="5" t="inlineStr">
@@ -25615,12 +25694,12 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -25635,12 +25714,12 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1018" s="5" t="inlineStr">
@@ -25655,12 +25734,12 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -25675,12 +25754,12 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1020" s="5" t="inlineStr">
@@ -25695,7 +25774,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -25715,7 +25794,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -25735,7 +25814,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -25755,7 +25834,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -25775,7 +25854,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -25795,7 +25874,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -25815,7 +25894,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -25835,7 +25914,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -25855,7 +25934,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -25875,7 +25954,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -25895,7 +25974,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -25915,7 +25994,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -25935,7 +26014,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -25955,7 +26034,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -25975,7 +26054,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -25995,7 +26074,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -26015,7 +26094,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -26035,7 +26114,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -26055,7 +26134,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -26075,7 +26154,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -26095,7 +26174,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -26115,7 +26194,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -26135,7 +26214,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -26155,7 +26234,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -26175,12 +26254,12 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -26195,12 +26274,12 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1046" s="5" t="inlineStr">
@@ -26215,12 +26294,12 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -26235,12 +26314,12 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1048" s="5" t="inlineStr">
@@ -26255,12 +26334,12 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -26275,12 +26354,12 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1050" s="5" t="inlineStr">
@@ -26295,12 +26374,12 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -26315,12 +26394,12 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1052" s="5" t="inlineStr">
@@ -26335,12 +26414,12 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -26355,12 +26434,12 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1054" s="5" t="inlineStr">
@@ -26375,12 +26454,12 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -26395,12 +26474,12 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1056" s="5" t="inlineStr">
@@ -26415,12 +26494,12 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -26435,12 +26514,12 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1058" s="5" t="inlineStr">
@@ -26455,12 +26534,12 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -26475,12 +26554,12 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1060" s="5" t="inlineStr">
@@ -26495,12 +26574,12 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -26515,12 +26594,12 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1062" s="5" t="inlineStr">
@@ -26535,12 +26614,12 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -26555,12 +26634,12 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1064" s="5" t="inlineStr">
@@ -26575,12 +26654,12 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -26595,12 +26674,12 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1066" s="5" t="inlineStr">
@@ -26615,12 +26694,12 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -26635,12 +26714,12 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1068" s="5" t="inlineStr">
@@ -26655,12 +26734,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -26675,12 +26754,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -26695,12 +26774,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -26715,12 +26794,12 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1072" s="5" t="inlineStr">
@@ -26735,12 +26814,12 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -26755,12 +26834,12 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1074" s="5" t="inlineStr">
@@ -26775,12 +26854,12 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -26795,12 +26874,12 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1076" s="5" t="inlineStr">
@@ -26815,12 +26894,12 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -26835,12 +26914,12 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1078" s="5" t="inlineStr">
@@ -26855,12 +26934,12 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -26875,12 +26954,12 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1080" s="5" t="inlineStr">
@@ -26895,7 +26974,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -26915,7 +26994,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -26935,7 +27014,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -26955,7 +27034,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -26975,17 +27054,17 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1085" s="6" t="n">
@@ -26995,17 +27074,17 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1086" s="4" t="n">
@@ -27015,17 +27094,17 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1087" s="6" t="n">
@@ -27035,57 +27114,57 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1088" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1089" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1090" s="4" t="n">
@@ -27095,57 +27174,57 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1091" s="6" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1092" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1093" s="6" t="n">
@@ -27155,17 +27234,17 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1094" s="4" t="n">
@@ -27175,41 +27254,281 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1095" s="6" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
+          <t>7510120</t>
+        </is>
+      </c>
+      <c r="B1096" s="5" t="inlineStr">
+        <is>
+          <t>Takarmatur Mira 2x2 infälld</t>
+        </is>
+      </c>
+      <c r="C1096" s="5" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="D1096" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="6" t="inlineStr">
+        <is>
+          <t>7028323</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Beta Force</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1097" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="4" t="inlineStr">
+        <is>
+          <t>7028324</t>
+        </is>
+      </c>
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Beta Force</t>
+        </is>
+      </c>
+      <c r="C1098" s="5" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1098" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="6" t="inlineStr">
+        <is>
+          <t>7028311</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Maya</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1099" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="4" t="inlineStr">
+        <is>
+          <t>7013475</t>
+        </is>
+      </c>
+      <c r="B1100" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED</t>
+        </is>
+      </c>
+      <c r="C1100" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="6" t="inlineStr">
+        <is>
+          <t>7021097</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1101" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="4" t="inlineStr">
+        <is>
+          <t>7018286</t>
+        </is>
+      </c>
+      <c r="B1102" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
+        </is>
+      </c>
+      <c r="C1102" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="6" t="inlineStr">
+        <is>
+          <t>7028368</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1103" s="6" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="4" t="inlineStr">
+        <is>
+          <t>7028369</t>
+        </is>
+      </c>
+      <c r="B1104" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1104" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="6" t="inlineStr">
+        <is>
+          <t>7028001</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1105" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="4" t="inlineStr">
+        <is>
+          <t>7028002</t>
+        </is>
+      </c>
+      <c r="B1106" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1106" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="6" t="inlineStr">
+        <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1107" s="6" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="4" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1096" s="5" t="inlineStr">
+      <c r="B1108" s="5" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1096" s="5" t="inlineStr">
+      <c r="C1108" s="5" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1096" s="4" t="n">
-        <v>352</v>
+      <c r="D1108" s="4" t="n">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>Legrand</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
         </is>
       </c>
     </row>
@@ -5346,6 +5346,85 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>888</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>495</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5387,7 +5466,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-05)</t>
+          <t>Lager (2026-09-06)</t>
         </is>
       </c>
     </row>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -543,72 +543,72 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>ZG Lighting</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Siteco</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
         </is>
       </c>
     </row>
@@ -5425,6 +5425,85 @@
         <v>0</v>
       </c>
       <c r="Y62" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>887</v>
+      </c>
+      <c r="C63" t="n">
+        <v>533</v>
+      </c>
+      <c r="D63" t="n">
+        <v>495</v>
+      </c>
+      <c r="E63" t="n">
+        <v>282</v>
+      </c>
+      <c r="F63" t="n">
+        <v>218</v>
+      </c>
+      <c r="G63" t="n">
+        <v>101</v>
+      </c>
+      <c r="H63" t="n">
+        <v>43</v>
+      </c>
+      <c r="I63" t="n">
+        <v>29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>24</v>
+      </c>
+      <c r="K63" t="n">
+        <v>16</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5439,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1108"/>
+  <dimension ref="A1:D1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5466,7 +5545,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-06)</t>
+          <t>Lager (2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -17873,12 +17952,12 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>7012494</t>
+          <t>7019475</t>
         </is>
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
@@ -17887,18 +17966,18 @@
         </is>
       </c>
       <c r="D622" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="6" t="inlineStr">
         <is>
-          <t>7012495</t>
+          <t>7019476</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17913,17 +17992,17 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>7012496</t>
+          <t>7013795</t>
         </is>
       </c>
       <c r="B624" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D624" s="4" t="n">
@@ -17933,17 +18012,17 @@
     <row r="625">
       <c r="A625" s="6" t="inlineStr">
         <is>
-          <t>7012497</t>
+          <t>7013796</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D625" s="6" t="n">
@@ -17953,17 +18032,17 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>7015180</t>
+          <t>7013797</t>
         </is>
       </c>
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D626" s="4" t="n">
@@ -17973,17 +18052,17 @@
     <row r="627">
       <c r="A627" s="6" t="inlineStr">
         <is>
-          <t>7015181</t>
+          <t>7013798</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D627" s="6" t="n">
@@ -17993,17 +18072,17 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>7050196</t>
+          <t>7018767</t>
         </is>
       </c>
       <c r="B628" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D628" s="4" t="n">
@@ -18013,17 +18092,17 @@
     <row r="629">
       <c r="A629" s="6" t="inlineStr">
         <is>
-          <t>7050197</t>
+          <t>7018768</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D629" s="6" t="n">
@@ -18033,17 +18112,17 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>7012498</t>
+          <t>7018769</t>
         </is>
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D630" s="4" t="n">
@@ -18053,17 +18132,17 @@
     <row r="631">
       <c r="A631" s="6" t="inlineStr">
         <is>
-          <t>7012499</t>
+          <t>7018771</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D631" s="6" t="n">
@@ -18073,17 +18152,17 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>7012500</t>
+          <t>7019623</t>
         </is>
       </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D632" s="4" t="n">
@@ -18093,17 +18172,17 @@
     <row r="633">
       <c r="A633" s="6" t="inlineStr">
         <is>
-          <t>7012501</t>
+          <t>7019624</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D633" s="6" t="n">
@@ -18113,17 +18192,17 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>7013292</t>
+          <t>7019653</t>
         </is>
       </c>
       <c r="B634" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C634" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D634" s="4" t="n">
@@ -18133,17 +18212,17 @@
     <row r="635">
       <c r="A635" s="6" t="inlineStr">
         <is>
-          <t>7013293</t>
+          <t>7019654</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Interiörarmatur Freyn</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D635" s="6" t="n">
@@ -18153,37 +18232,37 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>7019475</t>
+          <t>7011878</t>
         </is>
       </c>
       <c r="B636" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C636" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D636" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="6" t="inlineStr">
         <is>
-          <t>7019476</t>
+          <t>7013748</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D637" s="6" t="n">
@@ -18193,12 +18272,12 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>7013795</t>
+          <t>7011879</t>
         </is>
       </c>
       <c r="B638" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C638" s="5" t="inlineStr">
@@ -18213,12 +18292,12 @@
     <row r="639">
       <c r="A639" s="6" t="inlineStr">
         <is>
-          <t>7013796</t>
+          <t>7013749</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -18233,12 +18312,12 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>7013797</t>
+          <t>7011548</t>
         </is>
       </c>
       <c r="B640" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C640" s="5" t="inlineStr">
@@ -18253,12 +18332,12 @@
     <row r="641">
       <c r="A641" s="6" t="inlineStr">
         <is>
-          <t>7013798</t>
+          <t>7011549</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -18273,12 +18352,12 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>7018767</t>
+          <t>7011550</t>
         </is>
       </c>
       <c r="B642" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C642" s="5" t="inlineStr">
@@ -18293,12 +18372,12 @@
     <row r="643">
       <c r="A643" s="6" t="inlineStr">
         <is>
-          <t>7018768</t>
+          <t>7011554</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -18313,12 +18392,12 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>7018769</t>
+          <t>7010891</t>
         </is>
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
@@ -18333,12 +18412,12 @@
     <row r="645">
       <c r="A645" s="6" t="inlineStr">
         <is>
-          <t>7018771</t>
+          <t>7010892</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -18353,12 +18432,12 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>7019623</t>
+          <t>7010893</t>
         </is>
       </c>
       <c r="B646" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C646" s="5" t="inlineStr">
@@ -18373,12 +18452,12 @@
     <row r="647">
       <c r="A647" s="6" t="inlineStr">
         <is>
-          <t>7019624</t>
+          <t>7010894</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -18393,12 +18472,12 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>7019653</t>
+          <t>7010895</t>
         </is>
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
@@ -18413,12 +18492,12 @@
     <row r="649">
       <c r="A649" s="6" t="inlineStr">
         <is>
-          <t>7019654</t>
+          <t>7010896</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -18433,12 +18512,12 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>7011878</t>
+          <t>7010897</t>
         </is>
       </c>
       <c r="B650" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C650" s="5" t="inlineStr">
@@ -18453,12 +18532,12 @@
     <row r="651">
       <c r="A651" s="6" t="inlineStr">
         <is>
-          <t>7013748</t>
+          <t>7010898</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -18473,12 +18552,12 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>7011879</t>
+          <t>7016266</t>
         </is>
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
@@ -18493,12 +18572,12 @@
     <row r="653">
       <c r="A653" s="6" t="inlineStr">
         <is>
-          <t>7013749</t>
+          <t>7016267E</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -18513,12 +18592,12 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>7011548</t>
+          <t>7016268</t>
         </is>
       </c>
       <c r="B654" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C654" s="5" t="inlineStr">
@@ -18533,12 +18612,12 @@
     <row r="655">
       <c r="A655" s="6" t="inlineStr">
         <is>
-          <t>7011549</t>
+          <t>7016269</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -18553,12 +18632,12 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>7011550</t>
+          <t>7010869</t>
         </is>
       </c>
       <c r="B656" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C656" s="5" t="inlineStr">
@@ -18573,12 +18652,12 @@
     <row r="657">
       <c r="A657" s="6" t="inlineStr">
         <is>
-          <t>7011554</t>
+          <t>7010883</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18593,12 +18672,12 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>7010891</t>
+          <t>7010886</t>
         </is>
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C658" s="5" t="inlineStr">
@@ -18613,12 +18692,12 @@
     <row r="659">
       <c r="A659" s="6" t="inlineStr">
         <is>
-          <t>7010892</t>
+          <t>7010887</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18633,12 +18712,12 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>7010893</t>
+          <t>7054167</t>
         </is>
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C660" s="5" t="inlineStr">
@@ -18653,12 +18732,12 @@
     <row r="661">
       <c r="A661" s="6" t="inlineStr">
         <is>
-          <t>7010894</t>
+          <t>7054168</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18673,12 +18752,12 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>7010895</t>
+          <t>7054169</t>
         </is>
       </c>
       <c r="B662" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C662" s="5" t="inlineStr">
@@ -18693,12 +18772,12 @@
     <row r="663">
       <c r="A663" s="6" t="inlineStr">
         <is>
-          <t>7010896</t>
+          <t>7016931</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18713,12 +18792,12 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>7010897</t>
+          <t>7016932</t>
         </is>
       </c>
       <c r="B664" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C664" s="5" t="inlineStr">
@@ -18733,12 +18812,12 @@
     <row r="665">
       <c r="A665" s="6" t="inlineStr">
         <is>
-          <t>7010898</t>
+          <t>7016933</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18753,12 +18832,12 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>7016266</t>
+          <t>7016934</t>
         </is>
       </c>
       <c r="B666" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C666" s="5" t="inlineStr">
@@ -18773,12 +18852,12 @@
     <row r="667">
       <c r="A667" s="6" t="inlineStr">
         <is>
-          <t>7016267E</t>
+          <t>7027327</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18793,12 +18872,12 @@
     <row r="668">
       <c r="A668" s="4" t="inlineStr">
         <is>
-          <t>7016268</t>
+          <t>7010848</t>
         </is>
       </c>
       <c r="B668" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C668" s="5" t="inlineStr">
@@ -18813,12 +18892,12 @@
     <row r="669">
       <c r="A669" s="6" t="inlineStr">
         <is>
-          <t>7016269</t>
+          <t>7010849</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18833,12 +18912,12 @@
     <row r="670">
       <c r="A670" s="4" t="inlineStr">
         <is>
-          <t>7010869</t>
+          <t>7010851</t>
         </is>
       </c>
       <c r="B670" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C670" s="5" t="inlineStr">
@@ -18853,12 +18932,12 @@
     <row r="671">
       <c r="A671" s="6" t="inlineStr">
         <is>
-          <t>7010883</t>
+          <t>7010854</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18873,12 +18952,12 @@
     <row r="672">
       <c r="A672" s="4" t="inlineStr">
         <is>
-          <t>7010886</t>
+          <t>7010855</t>
         </is>
       </c>
       <c r="B672" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C672" s="5" t="inlineStr">
@@ -18893,12 +18972,12 @@
     <row r="673">
       <c r="A673" s="6" t="inlineStr">
         <is>
-          <t>7010887</t>
+          <t>7010857</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -18913,12 +18992,12 @@
     <row r="674">
       <c r="A674" s="4" t="inlineStr">
         <is>
-          <t>7054167</t>
+          <t>7010858</t>
         </is>
       </c>
       <c r="B674" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C674" s="5" t="inlineStr">
@@ -18933,12 +19012,12 @@
     <row r="675">
       <c r="A675" s="6" t="inlineStr">
         <is>
-          <t>7054168</t>
+          <t>7010859</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -18953,12 +19032,12 @@
     <row r="676">
       <c r="A676" s="4" t="inlineStr">
         <is>
-          <t>7054169</t>
+          <t>7019619</t>
         </is>
       </c>
       <c r="B676" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C676" s="5" t="inlineStr">
@@ -18973,12 +19052,12 @@
     <row r="677">
       <c r="A677" s="6" t="inlineStr">
         <is>
-          <t>7016931</t>
+          <t>7019620</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18993,12 +19072,12 @@
     <row r="678">
       <c r="A678" s="4" t="inlineStr">
         <is>
-          <t>7016932</t>
+          <t>7019621</t>
         </is>
       </c>
       <c r="B678" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C678" s="5" t="inlineStr">
@@ -19013,12 +19092,12 @@
     <row r="679">
       <c r="A679" s="6" t="inlineStr">
         <is>
-          <t>7016933</t>
+          <t>7019622</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -19033,12 +19112,12 @@
     <row r="680">
       <c r="A680" s="4" t="inlineStr">
         <is>
-          <t>7016934</t>
+          <t>7019479</t>
         </is>
       </c>
       <c r="B680" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C680" s="5" t="inlineStr">
@@ -19053,12 +19132,12 @@
     <row r="681">
       <c r="A681" s="6" t="inlineStr">
         <is>
-          <t>7027327</t>
+          <t>7010844E</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -19073,12 +19152,12 @@
     <row r="682">
       <c r="A682" s="4" t="inlineStr">
         <is>
-          <t>7010848</t>
+          <t>7010845</t>
         </is>
       </c>
       <c r="B682" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C682" s="5" t="inlineStr">
@@ -19093,12 +19172,12 @@
     <row r="683">
       <c r="A683" s="6" t="inlineStr">
         <is>
-          <t>7010849</t>
+          <t>7010846E</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -19113,12 +19192,12 @@
     <row r="684">
       <c r="A684" s="4" t="inlineStr">
         <is>
-          <t>7010851</t>
+          <t>7010847</t>
         </is>
       </c>
       <c r="B684" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C684" s="5" t="inlineStr">
@@ -19133,12 +19212,12 @@
     <row r="685">
       <c r="A685" s="6" t="inlineStr">
         <is>
-          <t>7010854</t>
+          <t>7054160</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -19153,12 +19232,12 @@
     <row r="686">
       <c r="A686" s="4" t="inlineStr">
         <is>
-          <t>7010855</t>
+          <t>7054163</t>
         </is>
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C686" s="5" t="inlineStr">
@@ -19173,12 +19252,12 @@
     <row r="687">
       <c r="A687" s="6" t="inlineStr">
         <is>
-          <t>7010857</t>
+          <t>7054166</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -19193,12 +19272,12 @@
     <row r="688">
       <c r="A688" s="4" t="inlineStr">
         <is>
-          <t>7010858</t>
+          <t>7010833</t>
         </is>
       </c>
       <c r="B688" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C688" s="5" t="inlineStr">
@@ -19213,12 +19292,12 @@
     <row r="689">
       <c r="A689" s="6" t="inlineStr">
         <is>
-          <t>7010859</t>
+          <t>7010842E</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19233,12 +19312,12 @@
     <row r="690">
       <c r="A690" s="4" t="inlineStr">
         <is>
-          <t>7019619</t>
+          <t>7010834</t>
         </is>
       </c>
       <c r="B690" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C690" s="5" t="inlineStr">
@@ -19253,12 +19332,12 @@
     <row r="691">
       <c r="A691" s="6" t="inlineStr">
         <is>
-          <t>7019620</t>
+          <t>7010843</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19273,12 +19352,12 @@
     <row r="692">
       <c r="A692" s="4" t="inlineStr">
         <is>
-          <t>7019621</t>
+          <t>7010829</t>
         </is>
       </c>
       <c r="B692" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C692" s="5" t="inlineStr">
@@ -19293,12 +19372,12 @@
     <row r="693">
       <c r="A693" s="6" t="inlineStr">
         <is>
-          <t>7019622</t>
+          <t>7010835</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19313,12 +19392,12 @@
     <row r="694">
       <c r="A694" s="4" t="inlineStr">
         <is>
-          <t>7019479</t>
+          <t>7010832</t>
         </is>
       </c>
       <c r="B694" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C694" s="5" t="inlineStr">
@@ -19333,12 +19412,12 @@
     <row r="695">
       <c r="A695" s="6" t="inlineStr">
         <is>
-          <t>7010844E</t>
+          <t>7010841</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19353,12 +19432,12 @@
     <row r="696">
       <c r="A696" s="4" t="inlineStr">
         <is>
-          <t>7010845</t>
+          <t>7054170</t>
         </is>
       </c>
       <c r="B696" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C696" s="5" t="inlineStr">
@@ -19373,12 +19452,12 @@
     <row r="697">
       <c r="A697" s="6" t="inlineStr">
         <is>
-          <t>7010846E</t>
+          <t>7054171</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -19393,12 +19472,12 @@
     <row r="698">
       <c r="A698" s="4" t="inlineStr">
         <is>
-          <t>7010847</t>
+          <t>7054172</t>
         </is>
       </c>
       <c r="B698" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C698" s="5" t="inlineStr">
@@ -19413,12 +19492,12 @@
     <row r="699">
       <c r="A699" s="6" t="inlineStr">
         <is>
-          <t>7054160</t>
+          <t>7054173</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19433,12 +19512,12 @@
     <row r="700">
       <c r="A700" s="4" t="inlineStr">
         <is>
-          <t>7054163</t>
+          <t>7054174</t>
         </is>
       </c>
       <c r="B700" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C700" s="5" t="inlineStr">
@@ -19453,12 +19532,12 @@
     <row r="701">
       <c r="A701" s="6" t="inlineStr">
         <is>
-          <t>7054166</t>
+          <t>7054175</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -19473,7 +19552,7 @@
     <row r="702">
       <c r="A702" s="4" t="inlineStr">
         <is>
-          <t>7010833</t>
+          <t>7054176</t>
         </is>
       </c>
       <c r="B702" s="5" t="inlineStr">
@@ -19493,7 +19572,7 @@
     <row r="703">
       <c r="A703" s="6" t="inlineStr">
         <is>
-          <t>7010842E</t>
+          <t>7016845</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -19513,7 +19592,7 @@
     <row r="704">
       <c r="A704" s="4" t="inlineStr">
         <is>
-          <t>7010834</t>
+          <t>7016846E</t>
         </is>
       </c>
       <c r="B704" s="5" t="inlineStr">
@@ -19533,7 +19612,7 @@
     <row r="705">
       <c r="A705" s="6" t="inlineStr">
         <is>
-          <t>7010843</t>
+          <t>7016847E</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19553,7 +19632,7 @@
     <row r="706">
       <c r="A706" s="4" t="inlineStr">
         <is>
-          <t>7010829</t>
+          <t>7016848E</t>
         </is>
       </c>
       <c r="B706" s="5" t="inlineStr">
@@ -19573,7 +19652,7 @@
     <row r="707">
       <c r="A707" s="6" t="inlineStr">
         <is>
-          <t>7010835</t>
+          <t>7015420</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19593,7 +19672,7 @@
     <row r="708">
       <c r="A708" s="4" t="inlineStr">
         <is>
-          <t>7010832</t>
+          <t>7015423</t>
         </is>
       </c>
       <c r="B708" s="5" t="inlineStr">
@@ -19613,7 +19692,7 @@
     <row r="709">
       <c r="A709" s="6" t="inlineStr">
         <is>
-          <t>7010841</t>
+          <t>7015428</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19633,7 +19712,7 @@
     <row r="710">
       <c r="A710" s="4" t="inlineStr">
         <is>
-          <t>7054170</t>
+          <t>7015429</t>
         </is>
       </c>
       <c r="B710" s="5" t="inlineStr">
@@ -19653,7 +19732,7 @@
     <row r="711">
       <c r="A711" s="6" t="inlineStr">
         <is>
-          <t>7054171</t>
+          <t>7018058</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19673,7 +19752,7 @@
     <row r="712">
       <c r="A712" s="4" t="inlineStr">
         <is>
-          <t>7054172</t>
+          <t>7018059</t>
         </is>
       </c>
       <c r="B712" s="5" t="inlineStr">
@@ -19693,7 +19772,7 @@
     <row r="713">
       <c r="A713" s="6" t="inlineStr">
         <is>
-          <t>7054173</t>
+          <t>7018060</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19713,7 +19792,7 @@
     <row r="714">
       <c r="A714" s="4" t="inlineStr">
         <is>
-          <t>7054174</t>
+          <t>7018061</t>
         </is>
       </c>
       <c r="B714" s="5" t="inlineStr">
@@ -19733,7 +19812,7 @@
     <row r="715">
       <c r="A715" s="6" t="inlineStr">
         <is>
-          <t>7054175</t>
+          <t>7019484</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19753,12 +19832,12 @@
     <row r="716">
       <c r="A716" s="4" t="inlineStr">
         <is>
-          <t>7054176</t>
+          <t>7013787</t>
         </is>
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
@@ -19773,12 +19852,12 @@
     <row r="717">
       <c r="A717" s="6" t="inlineStr">
         <is>
-          <t>7016845</t>
+          <t>7013788</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19793,12 +19872,12 @@
     <row r="718">
       <c r="A718" s="4" t="inlineStr">
         <is>
-          <t>7016846E</t>
+          <t>7013789</t>
         </is>
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
@@ -19813,12 +19892,12 @@
     <row r="719">
       <c r="A719" s="6" t="inlineStr">
         <is>
-          <t>7016847E</t>
+          <t>7013790</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19833,12 +19912,12 @@
     <row r="720">
       <c r="A720" s="4" t="inlineStr">
         <is>
-          <t>7016848E</t>
+          <t>7013791</t>
         </is>
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
@@ -19853,12 +19932,12 @@
     <row r="721">
       <c r="A721" s="6" t="inlineStr">
         <is>
-          <t>7015420</t>
+          <t>7013792</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19873,12 +19952,12 @@
     <row r="722">
       <c r="A722" s="4" t="inlineStr">
         <is>
-          <t>7015423</t>
+          <t>7013793</t>
         </is>
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
@@ -19893,12 +19972,12 @@
     <row r="723">
       <c r="A723" s="6" t="inlineStr">
         <is>
-          <t>7015428</t>
+          <t>7013794</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -19913,12 +19992,12 @@
     <row r="724">
       <c r="A724" s="4" t="inlineStr">
         <is>
-          <t>7015429</t>
+          <t>7017853</t>
         </is>
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
@@ -19933,12 +20012,12 @@
     <row r="725">
       <c r="A725" s="6" t="inlineStr">
         <is>
-          <t>7018058</t>
+          <t>7017854</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -19953,12 +20032,12 @@
     <row r="726">
       <c r="A726" s="4" t="inlineStr">
         <is>
-          <t>7018059</t>
+          <t>7017855</t>
         </is>
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
@@ -19973,12 +20052,12 @@
     <row r="727">
       <c r="A727" s="6" t="inlineStr">
         <is>
-          <t>7018060</t>
+          <t>7017856</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -19993,12 +20072,12 @@
     <row r="728">
       <c r="A728" s="4" t="inlineStr">
         <is>
-          <t>7018061</t>
+          <t>7015170</t>
         </is>
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
@@ -20013,12 +20092,12 @@
     <row r="729">
       <c r="A729" s="6" t="inlineStr">
         <is>
-          <t>7019484</t>
+          <t>7015171</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -20033,12 +20112,12 @@
     <row r="730">
       <c r="A730" s="4" t="inlineStr">
         <is>
-          <t>7013787</t>
+          <t>7015172</t>
         </is>
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
@@ -20053,12 +20132,12 @@
     <row r="731">
       <c r="A731" s="6" t="inlineStr">
         <is>
-          <t>7013788</t>
+          <t>7015173</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -20073,12 +20152,12 @@
     <row r="732">
       <c r="A732" s="4" t="inlineStr">
         <is>
-          <t>7013789</t>
+          <t>7029050</t>
         </is>
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
@@ -20093,12 +20172,12 @@
     <row r="733">
       <c r="A733" s="6" t="inlineStr">
         <is>
-          <t>7013790</t>
+          <t>7029051</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -20113,12 +20192,12 @@
     <row r="734">
       <c r="A734" s="4" t="inlineStr">
         <is>
-          <t>7013791</t>
+          <t>7029052</t>
         </is>
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
@@ -20133,12 +20212,12 @@
     <row r="735">
       <c r="A735" s="6" t="inlineStr">
         <is>
-          <t>7013792</t>
+          <t>7029053</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -20153,12 +20232,12 @@
     <row r="736">
       <c r="A736" s="4" t="inlineStr">
         <is>
-          <t>7013793</t>
+          <t>7029054</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -20173,12 +20252,12 @@
     <row r="737">
       <c r="A737" s="6" t="inlineStr">
         <is>
-          <t>7013794</t>
+          <t>7029055</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20193,12 +20272,12 @@
     <row r="738">
       <c r="A738" s="4" t="inlineStr">
         <is>
-          <t>7017853</t>
+          <t>7019046</t>
         </is>
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
@@ -20213,12 +20292,12 @@
     <row r="739">
       <c r="A739" s="6" t="inlineStr">
         <is>
-          <t>7017854</t>
+          <t>7019047</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20233,12 +20312,12 @@
     <row r="740">
       <c r="A740" s="4" t="inlineStr">
         <is>
-          <t>7017855</t>
+          <t>7019053</t>
         </is>
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
@@ -20253,12 +20332,12 @@
     <row r="741">
       <c r="A741" s="6" t="inlineStr">
         <is>
-          <t>7017856</t>
+          <t>7019058</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20273,12 +20352,12 @@
     <row r="742">
       <c r="A742" s="4" t="inlineStr">
         <is>
-          <t>7015170</t>
+          <t>7019059</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
@@ -20293,12 +20372,12 @@
     <row r="743">
       <c r="A743" s="6" t="inlineStr">
         <is>
-          <t>7015171</t>
+          <t>7019060</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20313,12 +20392,12 @@
     <row r="744">
       <c r="A744" s="4" t="inlineStr">
         <is>
-          <t>7015172</t>
+          <t>7019073</t>
         </is>
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
@@ -20333,12 +20412,12 @@
     <row r="745">
       <c r="A745" s="6" t="inlineStr">
         <is>
-          <t>7015173</t>
+          <t>7019074</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20353,12 +20432,12 @@
     <row r="746">
       <c r="A746" s="4" t="inlineStr">
         <is>
-          <t>7029050</t>
+          <t>7019315</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C746" s="5" t="inlineStr">
@@ -20373,12 +20452,12 @@
     <row r="747">
       <c r="A747" s="6" t="inlineStr">
         <is>
-          <t>7029051</t>
+          <t>7019344</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20393,12 +20472,12 @@
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>7029052</t>
+          <t>7019345</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C748" s="5" t="inlineStr">
@@ -20413,12 +20492,12 @@
     <row r="749">
       <c r="A749" s="6" t="inlineStr">
         <is>
-          <t>7029053</t>
+          <t>7019346</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20433,12 +20512,12 @@
     <row r="750">
       <c r="A750" s="4" t="inlineStr">
         <is>
-          <t>7029054</t>
+          <t>7019347</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
@@ -20453,12 +20532,12 @@
     <row r="751">
       <c r="A751" s="6" t="inlineStr">
         <is>
-          <t>7029055</t>
+          <t>7019358</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20473,12 +20552,12 @@
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>7019046</t>
+          <t>7019359</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C752" s="5" t="inlineStr">
@@ -20493,12 +20572,12 @@
     <row r="753">
       <c r="A753" s="6" t="inlineStr">
         <is>
-          <t>7019047</t>
+          <t>7019360</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20513,12 +20592,12 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>7019053</t>
+          <t>7019361</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C754" s="5" t="inlineStr">
@@ -20533,12 +20612,12 @@
     <row r="755">
       <c r="A755" s="6" t="inlineStr">
         <is>
-          <t>7019058</t>
+          <t>7019348</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -20553,12 +20632,12 @@
     <row r="756">
       <c r="A756" s="4" t="inlineStr">
         <is>
-          <t>7019059</t>
+          <t>7019349</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C756" s="5" t="inlineStr">
@@ -20573,12 +20652,12 @@
     <row r="757">
       <c r="A757" s="6" t="inlineStr">
         <is>
-          <t>7019060</t>
+          <t>7019350</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -20593,12 +20672,12 @@
     <row r="758">
       <c r="A758" s="4" t="inlineStr">
         <is>
-          <t>7019073</t>
+          <t>7019351</t>
         </is>
       </c>
       <c r="B758" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C758" s="5" t="inlineStr">
@@ -20613,12 +20692,12 @@
     <row r="759">
       <c r="A759" s="6" t="inlineStr">
         <is>
-          <t>7019074</t>
+          <t>7019352</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -20633,7 +20712,7 @@
     <row r="760">
       <c r="A760" s="4" t="inlineStr">
         <is>
-          <t>7019315</t>
+          <t>7019353</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -20653,7 +20732,7 @@
     <row r="761">
       <c r="A761" s="6" t="inlineStr">
         <is>
-          <t>7019344</t>
+          <t>7019354</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -20673,7 +20752,7 @@
     <row r="762">
       <c r="A762" s="4" t="inlineStr">
         <is>
-          <t>7019345</t>
+          <t>7019355</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -20693,7 +20772,7 @@
     <row r="763">
       <c r="A763" s="6" t="inlineStr">
         <is>
-          <t>7019346</t>
+          <t>7019356</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -20713,7 +20792,7 @@
     <row r="764">
       <c r="A764" s="4" t="inlineStr">
         <is>
-          <t>7019347</t>
+          <t>7019357</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -20733,12 +20812,12 @@
     <row r="765">
       <c r="A765" s="6" t="inlineStr">
         <is>
-          <t>7019358</t>
+          <t>7021449</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -20753,12 +20832,12 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>7019359</t>
+          <t>7021450</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C766" s="5" t="inlineStr">
@@ -20773,12 +20852,12 @@
     <row r="767">
       <c r="A767" s="6" t="inlineStr">
         <is>
-          <t>7019360</t>
+          <t>7021451</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -20793,12 +20872,12 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>7019361</t>
+          <t>7021452</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
@@ -20813,12 +20892,12 @@
     <row r="769">
       <c r="A769" s="6" t="inlineStr">
         <is>
-          <t>7019348</t>
+          <t>7021453</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -20833,12 +20912,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>7019349</t>
+          <t>7021454</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
@@ -20853,12 +20932,12 @@
     <row r="771">
       <c r="A771" s="6" t="inlineStr">
         <is>
-          <t>7019350</t>
+          <t>7021443</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -20873,12 +20952,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>7019351</t>
+          <t>7021444</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
@@ -20893,12 +20972,12 @@
     <row r="773">
       <c r="A773" s="6" t="inlineStr">
         <is>
-          <t>7019352</t>
+          <t>7021445</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -20913,12 +20992,12 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>7019353</t>
+          <t>7021446</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C774" s="5" t="inlineStr">
@@ -20933,12 +21012,12 @@
     <row r="775">
       <c r="A775" s="6" t="inlineStr">
         <is>
-          <t>7019354</t>
+          <t>7021447</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -20953,12 +21032,12 @@
     <row r="776">
       <c r="A776" s="4" t="inlineStr">
         <is>
-          <t>7019355</t>
+          <t>7021448</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C776" s="5" t="inlineStr">
@@ -20973,12 +21052,12 @@
     <row r="777">
       <c r="A777" s="6" t="inlineStr">
         <is>
-          <t>7019356</t>
+          <t>7018887</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -20993,12 +21072,12 @@
     <row r="778">
       <c r="A778" s="4" t="inlineStr">
         <is>
-          <t>7019357</t>
+          <t>7018888</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C778" s="5" t="inlineStr">
@@ -21013,12 +21092,12 @@
     <row r="779">
       <c r="A779" s="6" t="inlineStr">
         <is>
-          <t>7021449</t>
+          <t>7028566</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -21033,12 +21112,12 @@
     <row r="780">
       <c r="A780" s="4" t="inlineStr">
         <is>
-          <t>7021450</t>
+          <t>7028567</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C780" s="5" t="inlineStr">
@@ -21053,12 +21132,12 @@
     <row r="781">
       <c r="A781" s="6" t="inlineStr">
         <is>
-          <t>7021451</t>
+          <t>7028568</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21073,12 +21152,12 @@
     <row r="782">
       <c r="A782" s="4" t="inlineStr">
         <is>
-          <t>7021452</t>
+          <t>7028569</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C782" s="5" t="inlineStr">
@@ -21093,12 +21172,12 @@
     <row r="783">
       <c r="A783" s="6" t="inlineStr">
         <is>
-          <t>7021453</t>
+          <t>7028570</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21113,12 +21192,12 @@
     <row r="784">
       <c r="A784" s="4" t="inlineStr">
         <is>
-          <t>7021454</t>
+          <t>7028571</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C784" s="5" t="inlineStr">
@@ -21133,12 +21212,12 @@
     <row r="785">
       <c r="A785" s="6" t="inlineStr">
         <is>
-          <t>7021443</t>
+          <t>7028572</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -21153,12 +21232,12 @@
     <row r="786">
       <c r="A786" s="4" t="inlineStr">
         <is>
-          <t>7021444</t>
+          <t>7028573</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C786" s="5" t="inlineStr">
@@ -21173,12 +21252,12 @@
     <row r="787">
       <c r="A787" s="6" t="inlineStr">
         <is>
-          <t>7021445</t>
+          <t>7028574</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -21193,12 +21272,12 @@
     <row r="788">
       <c r="A788" s="4" t="inlineStr">
         <is>
-          <t>7021446</t>
+          <t>7028575</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C788" s="5" t="inlineStr">
@@ -21213,12 +21292,12 @@
     <row r="789">
       <c r="A789" s="6" t="inlineStr">
         <is>
-          <t>7021447</t>
+          <t>7028576</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -21233,12 +21312,12 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>7021448</t>
+          <t>7028577</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C790" s="5" t="inlineStr">
@@ -21253,12 +21332,12 @@
     <row r="791">
       <c r="A791" s="6" t="inlineStr">
         <is>
-          <t>7018887</t>
+          <t>7028578</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -21273,12 +21352,12 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>7018888</t>
+          <t>7028579</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C792" s="5" t="inlineStr">
@@ -21293,7 +21372,7 @@
     <row r="793">
       <c r="A793" s="6" t="inlineStr">
         <is>
-          <t>7028566</t>
+          <t>7028580</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -21313,7 +21392,7 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>7028567</t>
+          <t>7028581</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
@@ -21333,17 +21412,17 @@
     <row r="795">
       <c r="A795" s="6" t="inlineStr">
         <is>
-          <t>7028568</t>
+          <t>7029244</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D795" s="6" t="n">
@@ -21353,17 +21432,17 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>7028569</t>
+          <t>7029245</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C796" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D796" s="4" t="n">
@@ -21373,17 +21452,17 @@
     <row r="797">
       <c r="A797" s="6" t="inlineStr">
         <is>
-          <t>7028570</t>
+          <t>7029246</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D797" s="6" t="n">
@@ -21393,17 +21472,17 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>7028571</t>
+          <t>7029247</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C798" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D798" s="4" t="n">
@@ -21413,17 +21492,17 @@
     <row r="799">
       <c r="A799" s="6" t="inlineStr">
         <is>
-          <t>7028572</t>
+          <t>7029248</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D799" s="6" t="n">
@@ -21433,17 +21512,17 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>7028573</t>
+          <t>7029249</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D800" s="4" t="n">
@@ -21453,17 +21532,17 @@
     <row r="801">
       <c r="A801" s="6" t="inlineStr">
         <is>
-          <t>7028574</t>
+          <t>7029250</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D801" s="6" t="n">
@@ -21473,17 +21552,17 @@
     <row r="802">
       <c r="A802" s="4" t="inlineStr">
         <is>
-          <t>7028575</t>
+          <t>7029251</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D802" s="4" t="n">
@@ -21493,17 +21572,17 @@
     <row r="803">
       <c r="A803" s="6" t="inlineStr">
         <is>
-          <t>7028576</t>
+          <t>7028893</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Infälld Interiörarmatur Coreline Panel</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D803" s="6" t="n">
@@ -21513,17 +21592,17 @@
     <row r="804">
       <c r="A804" s="4" t="inlineStr">
         <is>
-          <t>7028577</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C804" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D804" s="4" t="n">
@@ -21533,17 +21612,17 @@
     <row r="805">
       <c r="A805" s="6" t="inlineStr">
         <is>
-          <t>7028578</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D805" s="6" t="n">
@@ -21553,17 +21632,17 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7028579</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D806" s="4" t="n">
@@ -21573,17 +21652,17 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7028580</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D807" s="6" t="n">
@@ -21593,17 +21672,17 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7028581</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D808" s="4" t="n">
@@ -21613,17 +21692,17 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7029244</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D809" s="6" t="n">
@@ -21633,17 +21712,17 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7029245</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D810" s="4" t="n">
@@ -21653,17 +21732,17 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7029246</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D811" s="6" t="n">
@@ -21673,17 +21752,17 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7029247</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D812" s="4" t="n">
@@ -21693,17 +21772,17 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7029248</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D813" s="6" t="n">
@@ -21713,17 +21792,17 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7029249</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C814" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D814" s="4" t="n">
@@ -21733,17 +21812,17 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7029250</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D815" s="6" t="n">
@@ -21753,17 +21832,17 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7029251</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C816" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D816" s="4" t="n">
@@ -21773,12 +21852,12 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -21793,12 +21872,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
@@ -21813,12 +21892,12 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -21833,12 +21912,12 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C820" s="5" t="inlineStr">
@@ -21853,12 +21932,12 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -21873,12 +21952,12 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C822" s="5" t="inlineStr">
@@ -21893,12 +21972,12 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -21913,12 +21992,12 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C824" s="5" t="inlineStr">
@@ -21933,12 +22012,12 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -21953,12 +22032,12 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C826" s="5" t="inlineStr">
@@ -21973,12 +22052,12 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -21993,12 +22072,12 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C828" s="5" t="inlineStr">
@@ -22013,12 +22092,12 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -22033,12 +22112,12 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C830" s="5" t="inlineStr">
@@ -22053,12 +22132,12 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22073,12 +22152,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -22093,12 +22172,12 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22113,12 +22192,12 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C834" s="5" t="inlineStr">
@@ -22133,12 +22212,12 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -22153,12 +22232,12 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C836" s="5" t="inlineStr">
@@ -22173,12 +22252,12 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -22193,12 +22272,12 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C838" s="5" t="inlineStr">
@@ -22213,12 +22292,12 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -22233,12 +22312,12 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C840" s="5" t="inlineStr">
@@ -22253,12 +22332,12 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -22273,12 +22352,12 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C842" s="5" t="inlineStr">
@@ -22293,12 +22372,12 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -22313,12 +22392,12 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
@@ -22333,12 +22412,12 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -22353,12 +22432,12 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
@@ -22373,12 +22452,12 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -22393,12 +22472,12 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
@@ -22413,17 +22492,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -22433,17 +22512,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -22453,17 +22532,17 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D851" s="6" t="n">
@@ -22473,17 +22552,17 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C852" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D852" s="4" t="n">
@@ -22493,17 +22572,17 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D853" s="6" t="n">
@@ -22513,17 +22592,17 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C854" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D854" s="4" t="n">
@@ -22533,17 +22612,17 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D855" s="6" t="n">
@@ -22553,17 +22632,17 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C856" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D856" s="4" t="n">
@@ -22573,17 +22652,17 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D857" s="6" t="n">
@@ -22593,17 +22672,17 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C858" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D858" s="4" t="n">
@@ -22613,17 +22692,17 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D859" s="6" t="n">
@@ -22633,17 +22712,17 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C860" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D860" s="4" t="n">
@@ -22653,17 +22732,17 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D861" s="6" t="n">
@@ -22673,17 +22752,17 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C862" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D862" s="4" t="n">
@@ -22693,7 +22772,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -22713,7 +22792,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -22733,7 +22812,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -22753,7 +22832,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -22773,7 +22852,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -22793,7 +22872,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -22813,7 +22892,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -22833,7 +22912,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -22853,7 +22932,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -22873,7 +22952,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -22893,7 +22972,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -22913,7 +22992,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -22933,12 +23012,12 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -22953,12 +23032,12 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -22973,12 +23052,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -22993,12 +23072,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -23013,12 +23092,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -23033,12 +23112,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -23047,18 +23126,18 @@
         </is>
       </c>
       <c r="D880" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -23067,18 +23146,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7019423</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -23093,12 +23172,12 @@
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7019424</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -23113,12 +23192,12 @@
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7019428</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -23133,12 +23212,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7019417</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -23153,12 +23232,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7019429</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -23173,12 +23252,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7019430</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Lineal infälld</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -23193,12 +23272,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -23213,12 +23292,12 @@
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -23233,12 +23312,12 @@
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -23253,12 +23332,12 @@
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -23273,12 +23352,12 @@
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -23293,12 +23372,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -23307,18 +23386,18 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C894" s="5" t="inlineStr">
@@ -23327,18 +23406,18 @@
         </is>
       </c>
       <c r="D894" s="4" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -23347,18 +23426,18 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7019423</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C896" s="5" t="inlineStr">
@@ -23373,12 +23452,12 @@
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7019424</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -23393,12 +23472,12 @@
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7019428</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -23413,12 +23492,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7019417</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -23433,12 +23512,12 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7019429</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -23453,12 +23532,12 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7019430</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -23473,12 +23552,12 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C902" s="5" t="inlineStr">
@@ -23493,12 +23572,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -23513,12 +23592,12 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -23533,12 +23612,12 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -23553,12 +23632,12 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C906" s="5" t="inlineStr">
@@ -23573,12 +23652,12 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -23587,18 +23666,18 @@
         </is>
       </c>
       <c r="D907" s="6" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C908" s="5" t="inlineStr">
@@ -23607,18 +23686,18 @@
         </is>
       </c>
       <c r="D908" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -23627,18 +23706,18 @@
         </is>
       </c>
       <c r="D909" s="6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C910" s="5" t="inlineStr">
@@ -23653,12 +23732,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -23673,12 +23752,12 @@
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -23693,12 +23772,12 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -23713,12 +23792,12 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C914" s="5" t="inlineStr">
@@ -23733,12 +23812,12 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -23747,18 +23826,18 @@
         </is>
       </c>
       <c r="D915" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C916" s="5" t="inlineStr">
@@ -23773,12 +23852,12 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -23793,12 +23872,12 @@
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C918" s="5" t="inlineStr">
@@ -23813,12 +23892,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -23833,12 +23912,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -23853,12 +23932,12 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -23867,18 +23946,18 @@
         </is>
       </c>
       <c r="D921" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C922" s="5" t="inlineStr">
@@ -23893,12 +23972,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -23913,12 +23992,12 @@
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -23933,12 +24012,12 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -23953,12 +24032,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -23973,12 +24052,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -23993,12 +24072,12 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C928" s="5" t="inlineStr">
@@ -24013,12 +24092,12 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -24027,18 +24106,18 @@
         </is>
       </c>
       <c r="D929" s="6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C930" s="5" t="inlineStr">
@@ -24053,12 +24132,12 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -24073,12 +24152,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -24093,12 +24172,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -24113,12 +24192,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -24133,12 +24212,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -24147,18 +24226,18 @@
         </is>
       </c>
       <c r="D935" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C936" s="5" t="inlineStr">
@@ -24173,12 +24252,12 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -24193,12 +24272,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -24213,12 +24292,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -24233,12 +24312,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -24253,12 +24332,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -24273,12 +24352,12 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C942" s="5" t="inlineStr">
@@ -24293,12 +24372,12 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -24313,12 +24392,12 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C944" s="5" t="inlineStr">
@@ -24333,12 +24412,12 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -24353,12 +24432,12 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
@@ -24373,12 +24452,12 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -24393,12 +24472,12 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C948" s="5" t="inlineStr">
@@ -24413,12 +24492,12 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -24433,12 +24512,12 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C950" s="5" t="inlineStr">
@@ -24453,12 +24532,12 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -24473,12 +24552,12 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C952" s="5" t="inlineStr">
@@ -24493,12 +24572,12 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -24513,17 +24592,17 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D954" s="4" t="n">
@@ -24533,17 +24612,17 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D955" s="6" t="n">
@@ -24553,17 +24632,17 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C956" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D956" s="4" t="n">
@@ -24573,17 +24652,17 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D957" s="6" t="n">
@@ -24593,17 +24672,17 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C958" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D958" s="4" t="n">
@@ -24613,17 +24692,17 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D959" s="6" t="n">
@@ -24633,17 +24712,17 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C960" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D960" s="4" t="n">
@@ -24653,17 +24732,17 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D961" s="6" t="n">
@@ -24673,17 +24752,17 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C962" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D962" s="4" t="n">
@@ -24693,17 +24772,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -24713,17 +24792,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -24733,17 +24812,17 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D965" s="6" t="n">
@@ -24753,17 +24832,17 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C966" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D966" s="4" t="n">
@@ -24773,17 +24852,17 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D967" s="6" t="n">
@@ -24793,17 +24872,17 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D968" s="4" t="n">
@@ -24813,17 +24892,17 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D969" s="6" t="n">
@@ -24833,17 +24912,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -24853,17 +24932,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -24873,17 +24952,17 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C972" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D972" s="4" t="n">
@@ -24893,17 +24972,17 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D973" s="6" t="n">
@@ -24913,17 +24992,17 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C974" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D974" s="4" t="n">
@@ -24933,17 +25012,17 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D975" s="6" t="n">
@@ -24953,17 +25032,17 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D976" s="4" t="n">
@@ -24973,77 +25052,77 @@
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D977" s="6" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C978" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D978" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C980" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D980" s="4" t="n">
@@ -25053,17 +25132,17 @@
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D981" s="6" t="n">
@@ -25073,17 +25152,17 @@
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D982" s="4" t="n">
@@ -25093,17 +25172,17 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D983" s="6" t="n">
@@ -25113,12 +25192,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -25133,12 +25212,12 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -25153,12 +25232,12 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C986" s="5" t="inlineStr">
@@ -25173,12 +25252,12 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -25193,12 +25272,12 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C988" s="5" t="inlineStr">
@@ -25213,17 +25292,17 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D989" s="6" t="n">
@@ -25233,17 +25312,17 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D990" s="4" t="n">
@@ -25253,77 +25332,77 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D991" s="6" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C992" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D992" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D993" s="6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D994" s="4" t="n">
@@ -25333,17 +25412,17 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D995" s="6" t="n">
@@ -25353,17 +25432,17 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D996" s="4" t="n">
@@ -25373,17 +25452,17 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D997" s="6" t="n">
@@ -25393,17 +25472,17 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D998" s="4" t="n">
@@ -25413,17 +25492,17 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D999" s="6" t="n">
@@ -25433,17 +25512,17 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1000" s="4" t="n">
@@ -25453,12 +25532,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -25473,12 +25552,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -25493,12 +25572,12 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -25513,12 +25592,12 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
@@ -25533,12 +25612,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -25553,12 +25632,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -25573,12 +25652,12 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -25593,12 +25672,12 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1008" s="5" t="inlineStr">
@@ -25613,12 +25692,12 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -25633,12 +25712,12 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
@@ -25653,12 +25732,12 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -25673,12 +25752,12 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1012" s="5" t="inlineStr">
@@ -25693,12 +25772,12 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -25713,12 +25792,12 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1014" s="5" t="inlineStr">
@@ -25733,12 +25812,12 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -25753,12 +25832,12 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1016" s="5" t="inlineStr">
@@ -25773,12 +25852,12 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -25793,12 +25872,12 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1018" s="5" t="inlineStr">
@@ -25813,12 +25892,12 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -25833,12 +25912,12 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1020" s="5" t="inlineStr">
@@ -25853,7 +25932,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -25873,7 +25952,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -25893,7 +25972,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -25913,7 +25992,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -25933,7 +26012,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -25953,7 +26032,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -25973,7 +26052,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -25993,7 +26072,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -26013,7 +26092,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -26033,7 +26112,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -26053,7 +26132,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -26073,7 +26152,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -26093,7 +26172,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -26113,7 +26192,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -26133,7 +26212,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -26153,7 +26232,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -26173,7 +26252,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -26193,7 +26272,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -26213,7 +26292,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -26233,7 +26312,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -26253,7 +26332,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -26273,7 +26352,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -26293,7 +26372,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -26313,7 +26392,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -26333,12 +26412,12 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -26353,12 +26432,12 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1046" s="5" t="inlineStr">
@@ -26373,12 +26452,12 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -26393,12 +26472,12 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1048" s="5" t="inlineStr">
@@ -26413,12 +26492,12 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -26433,12 +26512,12 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1050" s="5" t="inlineStr">
@@ -26453,12 +26532,12 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -26473,12 +26552,12 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1052" s="5" t="inlineStr">
@@ -26493,12 +26572,12 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -26513,12 +26592,12 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1054" s="5" t="inlineStr">
@@ -26533,12 +26612,12 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -26553,12 +26632,12 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1056" s="5" t="inlineStr">
@@ -26573,12 +26652,12 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -26593,12 +26672,12 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1058" s="5" t="inlineStr">
@@ -26613,12 +26692,12 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -26633,12 +26712,12 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1060" s="5" t="inlineStr">
@@ -26653,12 +26732,12 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -26673,12 +26752,12 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1062" s="5" t="inlineStr">
@@ -26693,12 +26772,12 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -26713,12 +26792,12 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1064" s="5" t="inlineStr">
@@ -26733,12 +26812,12 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -26753,12 +26832,12 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1066" s="5" t="inlineStr">
@@ -26773,12 +26852,12 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -26793,12 +26872,12 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1068" s="5" t="inlineStr">
@@ -26813,12 +26892,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -26833,12 +26912,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -26853,12 +26932,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -26873,12 +26952,12 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1072" s="5" t="inlineStr">
@@ -26893,12 +26972,12 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -26913,12 +26992,12 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1074" s="5" t="inlineStr">
@@ -26933,12 +27012,12 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -26953,12 +27032,12 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1076" s="5" t="inlineStr">
@@ -26973,12 +27052,12 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -26993,12 +27072,12 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1078" s="5" t="inlineStr">
@@ -27013,12 +27092,12 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -27033,12 +27112,12 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1080" s="5" t="inlineStr">
@@ -27053,7 +27132,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -27073,7 +27152,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -27093,7 +27172,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -27113,7 +27192,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -27133,17 +27212,17 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1085" s="6" t="n">
@@ -27153,17 +27232,17 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1086" s="4" t="n">
@@ -27173,17 +27252,17 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1087" s="6" t="n">
@@ -27193,57 +27272,57 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1088" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1089" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1090" s="4" t="n">
@@ -27253,57 +27332,57 @@
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1091" s="6" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1092" s="4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1093" s="6" t="n">
@@ -27313,17 +27392,17 @@
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7028002</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1094" s="4" t="n">
@@ -27333,280 +27412,40 @@
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7027999</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1095" s="6" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7028000</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>LED-panel aLight Office</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>a-collection</t>
         </is>
       </c>
       <c r="D1096" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" s="6" t="inlineStr">
-        <is>
-          <t>7028323</t>
-        </is>
-      </c>
-      <c r="B1097" t="inlineStr">
-        <is>
-          <t>Interiörarmatur Beta Force</t>
-        </is>
-      </c>
-      <c r="C1097" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="D1097" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" s="4" t="inlineStr">
-        <is>
-          <t>7028324</t>
-        </is>
-      </c>
-      <c r="B1098" s="5" t="inlineStr">
-        <is>
-          <t>Interiörarmatur Beta Force</t>
-        </is>
-      </c>
-      <c r="C1098" s="5" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="D1098" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" s="6" t="inlineStr">
-        <is>
-          <t>7028311</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr">
-        <is>
-          <t>Interiörarmatur Maya</t>
-        </is>
-      </c>
-      <c r="C1099" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="D1099" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" s="4" t="inlineStr">
-        <is>
-          <t>7013475</t>
-        </is>
-      </c>
-      <c r="B1100" s="5" t="inlineStr">
-        <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
-        </is>
-      </c>
-      <c r="C1100" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1100" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" s="6" t="inlineStr">
-        <is>
-          <t>7021097</t>
-        </is>
-      </c>
-      <c r="B1101" t="inlineStr">
-        <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
-        </is>
-      </c>
-      <c r="C1101" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1101" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" s="4" t="inlineStr">
-        <is>
-          <t>7018286</t>
-        </is>
-      </c>
-      <c r="B1102" s="5" t="inlineStr">
-        <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
-        </is>
-      </c>
-      <c r="C1102" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1102" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" s="6" t="inlineStr">
-        <is>
-          <t>7028368</t>
-        </is>
-      </c>
-      <c r="B1103" t="inlineStr">
-        <is>
-          <t>LED-Panel Flex</t>
-        </is>
-      </c>
-      <c r="C1103" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1103" s="6" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" s="4" t="inlineStr">
-        <is>
-          <t>7028369</t>
-        </is>
-      </c>
-      <c r="B1104" s="5" t="inlineStr">
-        <is>
-          <t>LED-Panel Flex</t>
-        </is>
-      </c>
-      <c r="C1104" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1104" s="4" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" s="6" t="inlineStr">
-        <is>
-          <t>7028001</t>
-        </is>
-      </c>
-      <c r="B1105" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1105" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1105" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" s="4" t="inlineStr">
-        <is>
-          <t>7028002</t>
-        </is>
-      </c>
-      <c r="B1106" s="5" t="inlineStr">
-        <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
-        </is>
-      </c>
-      <c r="C1106" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1106" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" s="6" t="inlineStr">
-        <is>
-          <t>7027999</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1107" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1107" s="6" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" s="4" t="inlineStr">
-        <is>
-          <t>7028000</t>
-        </is>
-      </c>
-      <c r="B1108" s="5" t="inlineStr">
-        <is>
-          <t>LED-panel aLight Office</t>
-        </is>
-      </c>
-      <c r="C1108" s="5" t="inlineStr">
-        <is>
-          <t>a-collection</t>
-        </is>
-      </c>
-      <c r="D1108" s="4" t="n">
         <v>359</v>
       </c>
     </row>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y63"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Esylux</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Exaktor</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Esylux</t>
-        </is>
-      </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Ledvance</t>
@@ -543,67 +543,67 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Norwesco</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Easyform</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>Westal</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Airam</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Norwesco</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Easyform</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
       <c r="Y1" s="3" t="inlineStr">
@@ -640,10 +640,10 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>25</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>17</v>
@@ -719,10 +719,10 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" t="n">
         <v>33</v>
-      </c>
-      <c r="J3" t="n">
-        <v>25</v>
       </c>
       <c r="K3" t="n">
         <v>17</v>
@@ -798,10 +798,10 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>25</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>17</v>
@@ -877,10 +877,10 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J5" t="n">
         <v>33</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>17</v>
@@ -956,10 +956,10 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>17</v>
@@ -1032,10 +1032,10 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" t="n">
         <v>33</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24</v>
       </c>
       <c r="K7" t="n">
         <v>17</v>
@@ -1111,10 +1111,10 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>17</v>
@@ -1190,10 +1190,10 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
         <v>33</v>
-      </c>
-      <c r="J9" t="n">
-        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>17</v>
@@ -1269,10 +1269,10 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>17</v>
@@ -1348,10 +1348,10 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
         <v>33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>24</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1427,10 +1427,10 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>17</v>
@@ -1506,10 +1506,10 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" t="n">
         <v>33</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
       </c>
       <c r="K13" t="n">
         <v>17</v>
@@ -1585,10 +1585,10 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>6</v>
@@ -1664,10 +1664,10 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>24</v>
+      </c>
+      <c r="J15" t="n">
         <v>33</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24</v>
       </c>
       <c r="K15" t="n">
         <v>17</v>
@@ -1743,10 +1743,10 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>17</v>
@@ -1822,10 +1822,10 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
         <v>33</v>
-      </c>
-      <c r="J17" t="n">
-        <v>24</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
@@ -1901,10 +1901,10 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>17</v>
@@ -1980,10 +1980,10 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
         <v>33</v>
-      </c>
-      <c r="J19" t="n">
-        <v>24</v>
       </c>
       <c r="K19" t="n">
         <v>17</v>
@@ -2059,10 +2059,10 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>17</v>
@@ -2138,10 +2138,10 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" t="n">
         <v>33</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24</v>
       </c>
       <c r="K21" t="n">
         <v>17</v>
@@ -2217,10 +2217,10 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>17</v>
@@ -2296,10 +2296,10 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>24</v>
+      </c>
+      <c r="J23" t="n">
         <v>33</v>
-      </c>
-      <c r="J23" t="n">
-        <v>24</v>
       </c>
       <c r="K23" t="n">
         <v>17</v>
@@ -2375,10 +2375,10 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>17</v>
@@ -2454,10 +2454,10 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" t="n">
         <v>33</v>
-      </c>
-      <c r="J25" t="n">
-        <v>24</v>
       </c>
       <c r="K25" t="n">
         <v>17</v>
@@ -2533,10 +2533,10 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>17</v>
@@ -2612,10 +2612,10 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>24</v>
+      </c>
+      <c r="J27" t="n">
         <v>33</v>
-      </c>
-      <c r="J27" t="n">
-        <v>24</v>
       </c>
       <c r="K27" t="n">
         <v>17</v>
@@ -2691,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>17</v>
@@ -2770,10 +2770,10 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
         <v>33</v>
-      </c>
-      <c r="J29" t="n">
-        <v>24</v>
       </c>
       <c r="K29" t="n">
         <v>17</v>
@@ -2849,10 +2849,10 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>17</v>
@@ -2928,10 +2928,10 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" t="n">
         <v>33</v>
-      </c>
-      <c r="J31" t="n">
-        <v>24</v>
       </c>
       <c r="K31" t="n">
         <v>17</v>
@@ -3007,10 +3007,10 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>17</v>
@@ -3086,10 +3086,10 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>24</v>
+      </c>
+      <c r="J33" t="n">
         <v>33</v>
-      </c>
-      <c r="J33" t="n">
-        <v>24</v>
       </c>
       <c r="K33" t="n">
         <v>17</v>
@@ -3165,10 +3165,10 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>17</v>
@@ -3244,10 +3244,10 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>24</v>
+      </c>
+      <c r="J35" t="n">
         <v>33</v>
-      </c>
-      <c r="J35" t="n">
-        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>17</v>
@@ -3323,10 +3323,10 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>17</v>
@@ -3402,10 +3402,10 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>24</v>
+      </c>
+      <c r="J37" t="n">
         <v>33</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24</v>
       </c>
       <c r="K37" t="n">
         <v>17</v>
@@ -3481,10 +3481,10 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>17</v>
@@ -3560,10 +3560,10 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>24</v>
+      </c>
+      <c r="J39" t="n">
         <v>33</v>
-      </c>
-      <c r="J39" t="n">
-        <v>24</v>
       </c>
       <c r="K39" t="n">
         <v>17</v>
@@ -3639,10 +3639,10 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>17</v>
@@ -3718,10 +3718,10 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>24</v>
+      </c>
+      <c r="J41" t="n">
         <v>33</v>
-      </c>
-      <c r="J41" t="n">
-        <v>24</v>
       </c>
       <c r="K41" t="n">
         <v>17</v>
@@ -3797,10 +3797,10 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>17</v>
@@ -3876,10 +3876,10 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="n">
         <v>33</v>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
       </c>
       <c r="K43" t="n">
         <v>17</v>
@@ -3955,10 +3955,10 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K44" s="5" t="n">
         <v>17</v>
@@ -4034,10 +4034,10 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" t="n">
         <v>33</v>
-      </c>
-      <c r="J45" t="n">
-        <v>24</v>
       </c>
       <c r="K45" t="n">
         <v>17</v>
@@ -4113,10 +4113,10 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>17</v>
@@ -4192,10 +4192,10 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>24</v>
+      </c>
+      <c r="J47" t="n">
         <v>33</v>
-      </c>
-      <c r="J47" t="n">
-        <v>24</v>
       </c>
       <c r="K47" t="n">
         <v>17</v>
@@ -4271,10 +4271,10 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>17</v>
@@ -4350,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>24</v>
+      </c>
+      <c r="J49" t="n">
         <v>33</v>
-      </c>
-      <c r="J49" t="n">
-        <v>24</v>
       </c>
       <c r="K49" t="n">
         <v>17</v>
@@ -4429,10 +4429,10 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>17</v>
@@ -4508,10 +4508,10 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>24</v>
+      </c>
+      <c r="J51" t="n">
         <v>33</v>
-      </c>
-      <c r="J51" t="n">
-        <v>24</v>
       </c>
       <c r="K51" t="n">
         <v>17</v>
@@ -4587,10 +4587,10 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>17</v>
@@ -4666,10 +4666,10 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>24</v>
+      </c>
+      <c r="J53" t="n">
         <v>30</v>
-      </c>
-      <c r="J53" t="n">
-        <v>24</v>
       </c>
       <c r="K53" t="n">
         <v>17</v>
@@ -4745,10 +4745,10 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>17</v>
@@ -4824,10 +4824,10 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>24</v>
+      </c>
+      <c r="J55" t="n">
         <v>30</v>
-      </c>
-      <c r="J55" t="n">
-        <v>24</v>
       </c>
       <c r="K55" t="n">
         <v>17</v>
@@ -4903,10 +4903,10 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>17</v>
@@ -5061,10 +5061,10 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>26</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>22</v>
@@ -5140,10 +5140,10 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>24</v>
+      </c>
+      <c r="J59" t="n">
         <v>26</v>
-      </c>
-      <c r="J59" t="n">
-        <v>24</v>
       </c>
       <c r="K59" t="n">
         <v>16</v>
@@ -5219,10 +5219,10 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>23</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>16</v>
@@ -5298,10 +5298,10 @@
         <v>43</v>
       </c>
       <c r="I61" t="n">
+        <v>24</v>
+      </c>
+      <c r="J61" t="n">
         <v>29</v>
-      </c>
-      <c r="J61" t="n">
-        <v>24</v>
       </c>
       <c r="K61" t="n">
         <v>16</v>
@@ -5377,10 +5377,10 @@
         <v>43</v>
       </c>
       <c r="I62" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J62" s="5" t="n">
         <v>29</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>24</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>16</v>
@@ -5456,10 +5456,10 @@
         <v>43</v>
       </c>
       <c r="I63" t="n">
+        <v>24</v>
+      </c>
+      <c r="J63" t="n">
         <v>29</v>
-      </c>
-      <c r="J63" t="n">
-        <v>24</v>
       </c>
       <c r="K63" t="n">
         <v>16</v>
@@ -5504,6 +5504,85 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>855</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>469</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5518,7 +5597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1096"/>
+  <dimension ref="A1:D1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5545,7 +5624,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-07)</t>
+          <t>Lager (2026-09-08)</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5645,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
@@ -9566,7 +9645,7 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203">
@@ -13746,7 +13825,7 @@
         </is>
       </c>
       <c r="D411" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="412">
@@ -14206,7 +14285,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="435">
@@ -16872,12 +16951,12 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>7026608</t>
+          <t>7029928</t>
         </is>
       </c>
       <c r="B568" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C568" s="5" t="inlineStr">
@@ -16892,12 +16971,12 @@
     <row r="569">
       <c r="A569" s="6" t="inlineStr">
         <is>
-          <t>7026609</t>
+          <t>7029929</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -16912,12 +16991,12 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>7026610</t>
+          <t>7029930</t>
         </is>
       </c>
       <c r="B570" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C570" s="5" t="inlineStr">
@@ -16932,12 +17011,12 @@
     <row r="571">
       <c r="A571" s="6" t="inlineStr">
         <is>
-          <t>7026611</t>
+          <t>7029931</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -16952,12 +17031,12 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>7026612</t>
+          <t>7029932</t>
         </is>
       </c>
       <c r="B572" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C572" s="5" t="inlineStr">
@@ -16972,12 +17051,12 @@
     <row r="573">
       <c r="A573" s="6" t="inlineStr">
         <is>
-          <t>7026613</t>
+          <t>7029933</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Interiörarmatur Protect</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -16992,12 +17071,12 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>7029551</t>
+          <t>7029934</t>
         </is>
       </c>
       <c r="B574" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBTW</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C574" s="5" t="inlineStr">
@@ -17012,12 +17091,12 @@
     <row r="575">
       <c r="A575" s="6" t="inlineStr">
         <is>
-          <t>7029548</t>
+          <t>7029935</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBW</t>
+          <t>Interiörarmatur Print Sky Gen2</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -17032,12 +17111,12 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>7029549</t>
+          <t>7026608</t>
         </is>
       </c>
       <c r="B576" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBW</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C576" s="5" t="inlineStr">
@@ -17052,12 +17131,12 @@
     <row r="577">
       <c r="A577" s="6" t="inlineStr">
         <is>
-          <t>7029550</t>
+          <t>7026609</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Interiörarmatur Smart + Panel RGBW</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -17072,17 +17151,17 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>7028787</t>
+          <t>7026610</t>
         </is>
       </c>
       <c r="B578" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C578" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D578" s="4" t="n">
@@ -17092,17 +17171,17 @@
     <row r="579">
       <c r="A579" s="6" t="inlineStr">
         <is>
-          <t>7028795</t>
+          <t>7026611</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D579" s="6" t="n">
@@ -17112,17 +17191,17 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>7028788</t>
+          <t>7026612</t>
         </is>
       </c>
       <c r="B580" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D580" s="4" t="n">
@@ -17132,17 +17211,17 @@
     <row r="581">
       <c r="A581" s="6" t="inlineStr">
         <is>
-          <t>7028796</t>
+          <t>7026613</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Protect</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D581" s="6" t="n">
@@ -17152,17 +17231,17 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>7028783</t>
+          <t>7029551</t>
         </is>
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Smart + Panel RGBTW</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D582" s="4" t="n">
@@ -17172,17 +17251,17 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>7028791</t>
+          <t>7029548</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Smart + Panel RGBW</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D583" s="6" t="n">
@@ -17192,17 +17271,17 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>7028784</t>
+          <t>7029549</t>
         </is>
       </c>
       <c r="B584" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Smart + Panel RGBW</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D584" s="4" t="n">
@@ -17212,17 +17291,17 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>7028792</t>
+          <t>7029550</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
+          <t>Interiörarmatur Smart + Panel RGBW</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="D585" s="6" t="n">
@@ -17232,7 +17311,7 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>7028807</t>
+          <t>7028787</t>
         </is>
       </c>
       <c r="B586" s="5" t="inlineStr">
@@ -17252,7 +17331,7 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>7028808</t>
+          <t>7028795</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -17272,7 +17351,7 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>7028809</t>
+          <t>7028788</t>
         </is>
       </c>
       <c r="B588" s="5" t="inlineStr">
@@ -17292,7 +17371,7 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>7028810</t>
+          <t>7028796</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -17312,7 +17391,7 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>7028799</t>
+          <t>7028783</t>
         </is>
       </c>
       <c r="B590" s="5" t="inlineStr">
@@ -17332,7 +17411,7 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>7028800</t>
+          <t>7028791</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -17352,7 +17431,7 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>7028801</t>
+          <t>7028784</t>
         </is>
       </c>
       <c r="B592" s="5" t="inlineStr">
@@ -17372,7 +17451,7 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>7028802</t>
+          <t>7028792</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -17392,7 +17471,7 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>7028816</t>
+          <t>7028807</t>
         </is>
       </c>
       <c r="B594" s="5" t="inlineStr">
@@ -17412,7 +17491,7 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>7028815</t>
+          <t>7028808</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -17432,7 +17511,7 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>7028819</t>
+          <t>7028809</t>
         </is>
       </c>
       <c r="B596" s="5" t="inlineStr">
@@ -17452,7 +17531,7 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>7028820</t>
+          <t>7028810</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -17472,12 +17551,12 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>7028789</t>
+          <t>7028799</t>
         </is>
       </c>
       <c r="B598" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C598" s="5" t="inlineStr">
@@ -17492,12 +17571,12 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>7028797</t>
+          <t>7028800</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -17512,12 +17591,12 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>7028790</t>
+          <t>7028801</t>
         </is>
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C600" s="5" t="inlineStr">
@@ -17532,12 +17611,12 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>7028798</t>
+          <t>7028802</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -17552,12 +17631,12 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>7028785</t>
+          <t>7028816</t>
         </is>
       </c>
       <c r="B602" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C602" s="5" t="inlineStr">
@@ -17572,12 +17651,12 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>7028793</t>
+          <t>7028815</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -17592,12 +17671,12 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>7028786</t>
+          <t>7028819</t>
         </is>
       </c>
       <c r="B604" s="5" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C604" s="5" t="inlineStr">
@@ -17612,12 +17691,12 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>7028794</t>
+          <t>7028820</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Dora opal</t>
+          <t>Infälld Interiörarmatur Dora mikroprismatisk</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -17632,7 +17711,7 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>7028811</t>
+          <t>7028789</t>
         </is>
       </c>
       <c r="B606" s="5" t="inlineStr">
@@ -17652,7 +17731,7 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>7028812</t>
+          <t>7028797</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -17672,7 +17751,7 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>7028813</t>
+          <t>7028790</t>
         </is>
       </c>
       <c r="B608" s="5" t="inlineStr">
@@ -17692,7 +17771,7 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>7028814</t>
+          <t>7028798</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -17712,7 +17791,7 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>7028803</t>
+          <t>7028785</t>
         </is>
       </c>
       <c r="B610" s="5" t="inlineStr">
@@ -17732,7 +17811,7 @@
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>7028804</t>
+          <t>7028793</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -17752,7 +17831,7 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>7028805</t>
+          <t>7028786</t>
         </is>
       </c>
       <c r="B612" s="5" t="inlineStr">
@@ -17772,7 +17851,7 @@
     <row r="613">
       <c r="A613" s="6" t="inlineStr">
         <is>
-          <t>7028806</t>
+          <t>7028794</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -17792,7 +17871,7 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>7028818</t>
+          <t>7028811</t>
         </is>
       </c>
       <c r="B614" s="5" t="inlineStr">
@@ -17812,7 +17891,7 @@
     <row r="615">
       <c r="A615" s="6" t="inlineStr">
         <is>
-          <t>7028817</t>
+          <t>7028812</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -17832,7 +17911,7 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>7028821</t>
+          <t>7028813</t>
         </is>
       </c>
       <c r="B616" s="5" t="inlineStr">
@@ -17852,7 +17931,7 @@
     <row r="617">
       <c r="A617" s="6" t="inlineStr">
         <is>
-          <t>7028822</t>
+          <t>7028814</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -17872,17 +17951,17 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>7019477</t>
+          <t>7028803</t>
         </is>
       </c>
       <c r="B618" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Cefalu</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D618" s="4" t="n">
@@ -17892,17 +17971,17 @@
     <row r="619">
       <c r="A619" s="6" t="inlineStr">
         <is>
-          <t>7021120</t>
+          <t>7028804</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Grönby</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D619" s="6" t="n">
@@ -17912,77 +17991,77 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>7021121</t>
+          <t>7028805</t>
         </is>
       </c>
       <c r="B620" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Grönby</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D620" s="4" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="6" t="inlineStr">
         <is>
-          <t>7021122</t>
+          <t>7028806</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Grönby</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D621" s="6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>7019475</t>
+          <t>7028818</t>
         </is>
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D622" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="6" t="inlineStr">
         <is>
-          <t>7019476</t>
+          <t>7028817</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Let it light</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D623" s="6" t="n">
@@ -17992,17 +18071,17 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>7013795</t>
+          <t>7028821</t>
         </is>
       </c>
       <c r="B624" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D624" s="4" t="n">
@@ -18012,17 +18091,17 @@
     <row r="625">
       <c r="A625" s="6" t="inlineStr">
         <is>
-          <t>7013796</t>
+          <t>7028822</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld Interiörarmatur Dora opal</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="D625" s="6" t="n">
@@ -18032,17 +18111,17 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>7013797</t>
+          <t>7019477</t>
         </is>
       </c>
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld interiörarmatur Cefalu</t>
         </is>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D626" s="4" t="n">
@@ -18052,17 +18131,17 @@
     <row r="627">
       <c r="A627" s="6" t="inlineStr">
         <is>
-          <t>7013798</t>
+          <t>7021120</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld interiörarmatur Grönby</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D627" s="6" t="n">
@@ -18072,77 +18151,77 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>7018767</t>
+          <t>7021121</t>
         </is>
       </c>
       <c r="B628" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld interiörarmatur Grönby</t>
         </is>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D628" s="4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="6" t="inlineStr">
         <is>
-          <t>7018768</t>
+          <t>7021122</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Infälld interiörarmatur Grönby</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D629" s="6" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>7018769</t>
+          <t>7019475</t>
         </is>
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D630" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="6" t="inlineStr">
         <is>
-          <t>7018771</t>
+          <t>7019476</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Infälld armatur CentiLED</t>
+          <t>Interiörarmatur LED-panel 600X600 Cefalu</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Nokalux</t>
+          <t>Let it light</t>
         </is>
       </c>
       <c r="D631" s="6" t="n">
@@ -18152,7 +18231,7 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>7019623</t>
+          <t>7013795</t>
         </is>
       </c>
       <c r="B632" s="5" t="inlineStr">
@@ -18172,7 +18251,7 @@
     <row r="633">
       <c r="A633" s="6" t="inlineStr">
         <is>
-          <t>7019624</t>
+          <t>7013796</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -18192,7 +18271,7 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>7019653</t>
+          <t>7013797</t>
         </is>
       </c>
       <c r="B634" s="5" t="inlineStr">
@@ -18212,7 +18291,7 @@
     <row r="635">
       <c r="A635" s="6" t="inlineStr">
         <is>
-          <t>7019654</t>
+          <t>7013798</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -18232,12 +18311,12 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>7011878</t>
+          <t>7018767</t>
         </is>
       </c>
       <c r="B636" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C636" s="5" t="inlineStr">
@@ -18252,12 +18331,12 @@
     <row r="637">
       <c r="A637" s="6" t="inlineStr">
         <is>
-          <t>7013748</t>
+          <t>7018768</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -18272,12 +18351,12 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>7011879</t>
+          <t>7018769</t>
         </is>
       </c>
       <c r="B638" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C638" s="5" t="inlineStr">
@@ -18292,12 +18371,12 @@
     <row r="639">
       <c r="A639" s="6" t="inlineStr">
         <is>
-          <t>7013749</t>
+          <t>7018771</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -18312,12 +18391,12 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>7011548</t>
+          <t>7019623</t>
         </is>
       </c>
       <c r="B640" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C640" s="5" t="inlineStr">
@@ -18332,12 +18411,12 @@
     <row r="641">
       <c r="A641" s="6" t="inlineStr">
         <is>
-          <t>7011549</t>
+          <t>7019624</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -18352,12 +18431,12 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>7011550</t>
+          <t>7019653</t>
         </is>
       </c>
       <c r="B642" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C642" s="5" t="inlineStr">
@@ -18372,12 +18451,12 @@
     <row r="643">
       <c r="A643" s="6" t="inlineStr">
         <is>
-          <t>7011554</t>
+          <t>7019654</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Infälld armatur IR95</t>
+          <t>Infälld armatur CentiLED</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -18392,12 +18471,12 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>7010891</t>
+          <t>7011878</t>
         </is>
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
@@ -18412,12 +18491,12 @@
     <row r="645">
       <c r="A645" s="6" t="inlineStr">
         <is>
-          <t>7010892</t>
+          <t>7013748</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -18432,12 +18511,12 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>7010893</t>
+          <t>7011879</t>
         </is>
       </c>
       <c r="B646" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C646" s="5" t="inlineStr">
@@ -18452,12 +18531,12 @@
     <row r="647">
       <c r="A647" s="6" t="inlineStr">
         <is>
-          <t>7010894</t>
+          <t>7013749</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -18472,12 +18551,12 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>7010895</t>
+          <t>7011548</t>
         </is>
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
@@ -18492,12 +18571,12 @@
     <row r="649">
       <c r="A649" s="6" t="inlineStr">
         <is>
-          <t>7010896</t>
+          <t>7011549</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -18512,12 +18591,12 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>7010897</t>
+          <t>7011550</t>
         </is>
       </c>
       <c r="B650" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C650" s="5" t="inlineStr">
@@ -18532,12 +18611,12 @@
     <row r="651">
       <c r="A651" s="6" t="inlineStr">
         <is>
-          <t>7010898</t>
+          <t>7011554</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.1</t>
+          <t>Infälld armatur IR95</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -18552,7 +18631,7 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>7016266</t>
+          <t>7010891</t>
         </is>
       </c>
       <c r="B652" s="5" t="inlineStr">
@@ -18572,7 +18651,7 @@
     <row r="653">
       <c r="A653" s="6" t="inlineStr">
         <is>
-          <t>7016267E</t>
+          <t>7010892</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -18592,7 +18671,7 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>7016268</t>
+          <t>7010893</t>
         </is>
       </c>
       <c r="B654" s="5" t="inlineStr">
@@ -18612,7 +18691,7 @@
     <row r="655">
       <c r="A655" s="6" t="inlineStr">
         <is>
-          <t>7016269</t>
+          <t>7010894</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -18632,12 +18711,12 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>7010869</t>
+          <t>7010895</t>
         </is>
       </c>
       <c r="B656" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C656" s="5" t="inlineStr">
@@ -18652,12 +18731,12 @@
     <row r="657">
       <c r="A657" s="6" t="inlineStr">
         <is>
-          <t>7010883</t>
+          <t>7010896</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -18672,12 +18751,12 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>7010886</t>
+          <t>7010897</t>
         </is>
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C658" s="5" t="inlineStr">
@@ -18692,12 +18771,12 @@
     <row r="659">
       <c r="A659" s="6" t="inlineStr">
         <is>
-          <t>7010887</t>
+          <t>7010898</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -18712,12 +18791,12 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>7054167</t>
+          <t>7016266</t>
         </is>
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C660" s="5" t="inlineStr">
@@ -18732,12 +18811,12 @@
     <row r="661">
       <c r="A661" s="6" t="inlineStr">
         <is>
-          <t>7054168</t>
+          <t>7016267E</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -18752,12 +18831,12 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>7054169</t>
+          <t>7016268</t>
         </is>
       </c>
       <c r="B662" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C662" s="5" t="inlineStr">
@@ -18772,12 +18851,12 @@
     <row r="663">
       <c r="A663" s="6" t="inlineStr">
         <is>
-          <t>7016931</t>
+          <t>7016269</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 12.2</t>
+          <t>Infälld armatur InLED 12.1</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18792,7 +18871,7 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>7016932</t>
+          <t>7010869</t>
         </is>
       </c>
       <c r="B664" s="5" t="inlineStr">
@@ -18812,7 +18891,7 @@
     <row r="665">
       <c r="A665" s="6" t="inlineStr">
         <is>
-          <t>7016933</t>
+          <t>7010883</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -18832,7 +18911,7 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>7016934</t>
+          <t>7010886</t>
         </is>
       </c>
       <c r="B666" s="5" t="inlineStr">
@@ -18852,7 +18931,7 @@
     <row r="667">
       <c r="A667" s="6" t="inlineStr">
         <is>
-          <t>7027327</t>
+          <t>7010887</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -18872,12 +18951,12 @@
     <row r="668">
       <c r="A668" s="4" t="inlineStr">
         <is>
-          <t>7010848</t>
+          <t>7054167</t>
         </is>
       </c>
       <c r="B668" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C668" s="5" t="inlineStr">
@@ -18892,12 +18971,12 @@
     <row r="669">
       <c r="A669" s="6" t="inlineStr">
         <is>
-          <t>7010849</t>
+          <t>7054168</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18912,12 +18991,12 @@
     <row r="670">
       <c r="A670" s="4" t="inlineStr">
         <is>
-          <t>7010851</t>
+          <t>7054169</t>
         </is>
       </c>
       <c r="B670" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C670" s="5" t="inlineStr">
@@ -18932,12 +19011,12 @@
     <row r="671">
       <c r="A671" s="6" t="inlineStr">
         <is>
-          <t>7010854</t>
+          <t>7016931</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18952,12 +19031,12 @@
     <row r="672">
       <c r="A672" s="4" t="inlineStr">
         <is>
-          <t>7010855</t>
+          <t>7016932</t>
         </is>
       </c>
       <c r="B672" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C672" s="5" t="inlineStr">
@@ -18972,12 +19051,12 @@
     <row r="673">
       <c r="A673" s="6" t="inlineStr">
         <is>
-          <t>7010857</t>
+          <t>7016933</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -18992,12 +19071,12 @@
     <row r="674">
       <c r="A674" s="4" t="inlineStr">
         <is>
-          <t>7010858</t>
+          <t>7016934</t>
         </is>
       </c>
       <c r="B674" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C674" s="5" t="inlineStr">
@@ -19012,12 +19091,12 @@
     <row r="675">
       <c r="A675" s="6" t="inlineStr">
         <is>
-          <t>7010859</t>
+          <t>7027327</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.1</t>
+          <t>Infälld armatur InLED 12.2</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -19032,7 +19111,7 @@
     <row r="676">
       <c r="A676" s="4" t="inlineStr">
         <is>
-          <t>7019619</t>
+          <t>7010848</t>
         </is>
       </c>
       <c r="B676" s="5" t="inlineStr">
@@ -19052,7 +19131,7 @@
     <row r="677">
       <c r="A677" s="6" t="inlineStr">
         <is>
-          <t>7019620</t>
+          <t>7010849</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -19072,7 +19151,7 @@
     <row r="678">
       <c r="A678" s="4" t="inlineStr">
         <is>
-          <t>7019621</t>
+          <t>7010851</t>
         </is>
       </c>
       <c r="B678" s="5" t="inlineStr">
@@ -19092,7 +19171,7 @@
     <row r="679">
       <c r="A679" s="6" t="inlineStr">
         <is>
-          <t>7019622</t>
+          <t>7010854</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -19112,12 +19191,12 @@
     <row r="680">
       <c r="A680" s="4" t="inlineStr">
         <is>
-          <t>7019479</t>
+          <t>7010855</t>
         </is>
       </c>
       <c r="B680" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C680" s="5" t="inlineStr">
@@ -19132,12 +19211,12 @@
     <row r="681">
       <c r="A681" s="6" t="inlineStr">
         <is>
-          <t>7010844E</t>
+          <t>7010857</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -19152,12 +19231,12 @@
     <row r="682">
       <c r="A682" s="4" t="inlineStr">
         <is>
-          <t>7010845</t>
+          <t>7010858</t>
         </is>
       </c>
       <c r="B682" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C682" s="5" t="inlineStr">
@@ -19172,12 +19251,12 @@
     <row r="683">
       <c r="A683" s="6" t="inlineStr">
         <is>
-          <t>7010846E</t>
+          <t>7010859</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -19192,12 +19271,12 @@
     <row r="684">
       <c r="A684" s="4" t="inlineStr">
         <is>
-          <t>7010847</t>
+          <t>7019619</t>
         </is>
       </c>
       <c r="B684" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C684" s="5" t="inlineStr">
@@ -19212,12 +19291,12 @@
     <row r="685">
       <c r="A685" s="6" t="inlineStr">
         <is>
-          <t>7054160</t>
+          <t>7019620</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -19232,12 +19311,12 @@
     <row r="686">
       <c r="A686" s="4" t="inlineStr">
         <is>
-          <t>7054163</t>
+          <t>7019621</t>
         </is>
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C686" s="5" t="inlineStr">
@@ -19252,12 +19331,12 @@
     <row r="687">
       <c r="A687" s="6" t="inlineStr">
         <is>
-          <t>7054166</t>
+          <t>7019622</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.2</t>
+          <t>Infälld armatur InLED 6.1</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -19272,12 +19351,12 @@
     <row r="688">
       <c r="A688" s="4" t="inlineStr">
         <is>
-          <t>7010833</t>
+          <t>7019479</t>
         </is>
       </c>
       <c r="B688" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C688" s="5" t="inlineStr">
@@ -19292,12 +19371,12 @@
     <row r="689">
       <c r="A689" s="6" t="inlineStr">
         <is>
-          <t>7010842E</t>
+          <t>7010844E</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19312,12 +19391,12 @@
     <row r="690">
       <c r="A690" s="4" t="inlineStr">
         <is>
-          <t>7010834</t>
+          <t>7010845</t>
         </is>
       </c>
       <c r="B690" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C690" s="5" t="inlineStr">
@@ -19332,12 +19411,12 @@
     <row r="691">
       <c r="A691" s="6" t="inlineStr">
         <is>
-          <t>7010843</t>
+          <t>7010846E</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19352,12 +19431,12 @@
     <row r="692">
       <c r="A692" s="4" t="inlineStr">
         <is>
-          <t>7010829</t>
+          <t>7010847</t>
         </is>
       </c>
       <c r="B692" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C692" s="5" t="inlineStr">
@@ -19372,12 +19451,12 @@
     <row r="693">
       <c r="A693" s="6" t="inlineStr">
         <is>
-          <t>7010835</t>
+          <t>7054160</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -19392,12 +19471,12 @@
     <row r="694">
       <c r="A694" s="4" t="inlineStr">
         <is>
-          <t>7010832</t>
+          <t>7054163</t>
         </is>
       </c>
       <c r="B694" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C694" s="5" t="inlineStr">
@@ -19412,12 +19491,12 @@
     <row r="695">
       <c r="A695" s="6" t="inlineStr">
         <is>
-          <t>7010841</t>
+          <t>7054166</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Infälld armatur InLED 6.6</t>
+          <t>Infälld armatur InLED 6.2</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -19432,7 +19511,7 @@
     <row r="696">
       <c r="A696" s="4" t="inlineStr">
         <is>
-          <t>7054170</t>
+          <t>7010833</t>
         </is>
       </c>
       <c r="B696" s="5" t="inlineStr">
@@ -19452,7 +19531,7 @@
     <row r="697">
       <c r="A697" s="6" t="inlineStr">
         <is>
-          <t>7054171</t>
+          <t>7010842E</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -19472,7 +19551,7 @@
     <row r="698">
       <c r="A698" s="4" t="inlineStr">
         <is>
-          <t>7054172</t>
+          <t>7010834</t>
         </is>
       </c>
       <c r="B698" s="5" t="inlineStr">
@@ -19492,7 +19571,7 @@
     <row r="699">
       <c r="A699" s="6" t="inlineStr">
         <is>
-          <t>7054173</t>
+          <t>7010843</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -19512,7 +19591,7 @@
     <row r="700">
       <c r="A700" s="4" t="inlineStr">
         <is>
-          <t>7054174</t>
+          <t>7010829</t>
         </is>
       </c>
       <c r="B700" s="5" t="inlineStr">
@@ -19532,7 +19611,7 @@
     <row r="701">
       <c r="A701" s="6" t="inlineStr">
         <is>
-          <t>7054175</t>
+          <t>7010835</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -19552,7 +19631,7 @@
     <row r="702">
       <c r="A702" s="4" t="inlineStr">
         <is>
-          <t>7054176</t>
+          <t>7010832</t>
         </is>
       </c>
       <c r="B702" s="5" t="inlineStr">
@@ -19572,7 +19651,7 @@
     <row r="703">
       <c r="A703" s="6" t="inlineStr">
         <is>
-          <t>7016845</t>
+          <t>7010841</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -19592,7 +19671,7 @@
     <row r="704">
       <c r="A704" s="4" t="inlineStr">
         <is>
-          <t>7016846E</t>
+          <t>7054170</t>
         </is>
       </c>
       <c r="B704" s="5" t="inlineStr">
@@ -19612,7 +19691,7 @@
     <row r="705">
       <c r="A705" s="6" t="inlineStr">
         <is>
-          <t>7016847E</t>
+          <t>7054171</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -19632,7 +19711,7 @@
     <row r="706">
       <c r="A706" s="4" t="inlineStr">
         <is>
-          <t>7016848E</t>
+          <t>7054172</t>
         </is>
       </c>
       <c r="B706" s="5" t="inlineStr">
@@ -19652,7 +19731,7 @@
     <row r="707">
       <c r="A707" s="6" t="inlineStr">
         <is>
-          <t>7015420</t>
+          <t>7054173</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -19672,7 +19751,7 @@
     <row r="708">
       <c r="A708" s="4" t="inlineStr">
         <is>
-          <t>7015423</t>
+          <t>7054174</t>
         </is>
       </c>
       <c r="B708" s="5" t="inlineStr">
@@ -19692,7 +19771,7 @@
     <row r="709">
       <c r="A709" s="6" t="inlineStr">
         <is>
-          <t>7015428</t>
+          <t>7054175</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -19712,7 +19791,7 @@
     <row r="710">
       <c r="A710" s="4" t="inlineStr">
         <is>
-          <t>7015429</t>
+          <t>7054176</t>
         </is>
       </c>
       <c r="B710" s="5" t="inlineStr">
@@ -19732,7 +19811,7 @@
     <row r="711">
       <c r="A711" s="6" t="inlineStr">
         <is>
-          <t>7018058</t>
+          <t>7016845</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -19752,7 +19831,7 @@
     <row r="712">
       <c r="A712" s="4" t="inlineStr">
         <is>
-          <t>7018059</t>
+          <t>7016846E</t>
         </is>
       </c>
       <c r="B712" s="5" t="inlineStr">
@@ -19772,7 +19851,7 @@
     <row r="713">
       <c r="A713" s="6" t="inlineStr">
         <is>
-          <t>7018060</t>
+          <t>7016847E</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -19792,7 +19871,7 @@
     <row r="714">
       <c r="A714" s="4" t="inlineStr">
         <is>
-          <t>7018061</t>
+          <t>7016848E</t>
         </is>
       </c>
       <c r="B714" s="5" t="inlineStr">
@@ -19812,7 +19891,7 @@
     <row r="715">
       <c r="A715" s="6" t="inlineStr">
         <is>
-          <t>7019484</t>
+          <t>7015420</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -19832,12 +19911,12 @@
     <row r="716">
       <c r="A716" s="4" t="inlineStr">
         <is>
-          <t>7013787</t>
+          <t>7015423</t>
         </is>
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
@@ -19852,12 +19931,12 @@
     <row r="717">
       <c r="A717" s="6" t="inlineStr">
         <is>
-          <t>7013788</t>
+          <t>7015428</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -19872,12 +19951,12 @@
     <row r="718">
       <c r="A718" s="4" t="inlineStr">
         <is>
-          <t>7013789</t>
+          <t>7015429</t>
         </is>
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
@@ -19892,12 +19971,12 @@
     <row r="719">
       <c r="A719" s="6" t="inlineStr">
         <is>
-          <t>7013790</t>
+          <t>7018058</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -19912,12 +19991,12 @@
     <row r="720">
       <c r="A720" s="4" t="inlineStr">
         <is>
-          <t>7013791</t>
+          <t>7018059</t>
         </is>
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
@@ -19932,12 +20011,12 @@
     <row r="721">
       <c r="A721" s="6" t="inlineStr">
         <is>
-          <t>7013792</t>
+          <t>7018060</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -19952,12 +20031,12 @@
     <row r="722">
       <c r="A722" s="4" t="inlineStr">
         <is>
-          <t>7013793</t>
+          <t>7018061</t>
         </is>
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
@@ -19972,12 +20051,12 @@
     <row r="723">
       <c r="A723" s="6" t="inlineStr">
         <is>
-          <t>7013794</t>
+          <t>7019484</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid</t>
+          <t>Infälld armatur InLED 6.6</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -19992,7 +20071,7 @@
     <row r="724">
       <c r="A724" s="4" t="inlineStr">
         <is>
-          <t>7017853</t>
+          <t>7013787</t>
         </is>
       </c>
       <c r="B724" s="5" t="inlineStr">
@@ -20012,7 +20091,7 @@
     <row r="725">
       <c r="A725" s="6" t="inlineStr">
         <is>
-          <t>7017854</t>
+          <t>7013788</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -20032,7 +20111,7 @@
     <row r="726">
       <c r="A726" s="4" t="inlineStr">
         <is>
-          <t>7017855</t>
+          <t>7013789</t>
         </is>
       </c>
       <c r="B726" s="5" t="inlineStr">
@@ -20052,7 +20131,7 @@
     <row r="727">
       <c r="A727" s="6" t="inlineStr">
         <is>
-          <t>7017856</t>
+          <t>7013790</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -20072,12 +20151,12 @@
     <row r="728">
       <c r="A728" s="4" t="inlineStr">
         <is>
-          <t>7015170</t>
+          <t>7013791</t>
         </is>
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
@@ -20092,12 +20171,12 @@
     <row r="729">
       <c r="A729" s="6" t="inlineStr">
         <is>
-          <t>7015171</t>
+          <t>7013792</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -20112,12 +20191,12 @@
     <row r="730">
       <c r="A730" s="4" t="inlineStr">
         <is>
-          <t>7015172</t>
+          <t>7013793</t>
         </is>
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
@@ -20132,12 +20211,12 @@
     <row r="731">
       <c r="A731" s="6" t="inlineStr">
         <is>
-          <t>7015173</t>
+          <t>7013794</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Infälld armatur Invoid "Hörn"</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -20152,12 +20231,12 @@
     <row r="732">
       <c r="A732" s="4" t="inlineStr">
         <is>
-          <t>7029050</t>
+          <t>7017853</t>
         </is>
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
@@ -20172,12 +20251,12 @@
     <row r="733">
       <c r="A733" s="6" t="inlineStr">
         <is>
-          <t>7029051</t>
+          <t>7017854</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -20192,12 +20271,12 @@
     <row r="734">
       <c r="A734" s="4" t="inlineStr">
         <is>
-          <t>7029052</t>
+          <t>7017855</t>
         </is>
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
@@ -20212,12 +20291,12 @@
     <row r="735">
       <c r="A735" s="6" t="inlineStr">
         <is>
-          <t>7029053</t>
+          <t>7017856</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -20232,12 +20311,12 @@
     <row r="736">
       <c r="A736" s="4" t="inlineStr">
         <is>
-          <t>7029054</t>
+          <t>7015170</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -20252,12 +20331,12 @@
     <row r="737">
       <c r="A737" s="6" t="inlineStr">
         <is>
-          <t>7029055</t>
+          <t>7015171</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Interiörarmatur IR 92</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -20272,12 +20351,12 @@
     <row r="738">
       <c r="A738" s="4" t="inlineStr">
         <is>
-          <t>7019046</t>
+          <t>7015172</t>
         </is>
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
@@ -20292,12 +20371,12 @@
     <row r="739">
       <c r="A739" s="6" t="inlineStr">
         <is>
-          <t>7019047</t>
+          <t>7015173</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Infälld armatur Invoid "Hörn"</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -20312,12 +20391,12 @@
     <row r="740">
       <c r="A740" s="4" t="inlineStr">
         <is>
-          <t>7019053</t>
+          <t>7029050</t>
         </is>
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
@@ -20332,12 +20411,12 @@
     <row r="741">
       <c r="A741" s="6" t="inlineStr">
         <is>
-          <t>7019058</t>
+          <t>7029051</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -20352,12 +20431,12 @@
     <row r="742">
       <c r="A742" s="4" t="inlineStr">
         <is>
-          <t>7019059</t>
+          <t>7029052</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
@@ -20372,12 +20451,12 @@
     <row r="743">
       <c r="A743" s="6" t="inlineStr">
         <is>
-          <t>7019060</t>
+          <t>7029053</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20392,12 +20471,12 @@
     <row r="744">
       <c r="A744" s="4" t="inlineStr">
         <is>
-          <t>7019073</t>
+          <t>7029054</t>
         </is>
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
@@ -20412,12 +20491,12 @@
     <row r="745">
       <c r="A745" s="6" t="inlineStr">
         <is>
-          <t>7019074</t>
+          <t>7029055</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Interiörarmatur InLED infälld</t>
+          <t>Interiörarmatur IR 92</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -20432,12 +20511,12 @@
     <row r="746">
       <c r="A746" s="4" t="inlineStr">
         <is>
-          <t>7019315</t>
+          <t>7019046</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C746" s="5" t="inlineStr">
@@ -20452,12 +20531,12 @@
     <row r="747">
       <c r="A747" s="6" t="inlineStr">
         <is>
-          <t>7019344</t>
+          <t>7019047</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20472,12 +20551,12 @@
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>7019345</t>
+          <t>7019053</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C748" s="5" t="inlineStr">
@@ -20492,12 +20571,12 @@
     <row r="749">
       <c r="A749" s="6" t="inlineStr">
         <is>
-          <t>7019346</t>
+          <t>7019058</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -20512,12 +20591,12 @@
     <row r="750">
       <c r="A750" s="4" t="inlineStr">
         <is>
-          <t>7019347</t>
+          <t>7019059</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
@@ -20532,12 +20611,12 @@
     <row r="751">
       <c r="A751" s="6" t="inlineStr">
         <is>
-          <t>7019358</t>
+          <t>7019060</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -20552,12 +20631,12 @@
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>7019359</t>
+          <t>7019073</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C752" s="5" t="inlineStr">
@@ -20572,12 +20651,12 @@
     <row r="753">
       <c r="A753" s="6" t="inlineStr">
         <is>
-          <t>7019360</t>
+          <t>7019074</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Interiörarmatur InMY infälld</t>
+          <t>Interiörarmatur InLED infälld</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -20592,7 +20671,7 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>7019361</t>
+          <t>7019315</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
@@ -20612,7 +20691,7 @@
     <row r="755">
       <c r="A755" s="6" t="inlineStr">
         <is>
-          <t>7019348</t>
+          <t>7019344</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -20632,7 +20711,7 @@
     <row r="756">
       <c r="A756" s="4" t="inlineStr">
         <is>
-          <t>7019349</t>
+          <t>7019345</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
@@ -20652,7 +20731,7 @@
     <row r="757">
       <c r="A757" s="6" t="inlineStr">
         <is>
-          <t>7019350</t>
+          <t>7019346</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -20672,7 +20751,7 @@
     <row r="758">
       <c r="A758" s="4" t="inlineStr">
         <is>
-          <t>7019351</t>
+          <t>7019347</t>
         </is>
       </c>
       <c r="B758" s="5" t="inlineStr">
@@ -20692,7 +20771,7 @@
     <row r="759">
       <c r="A759" s="6" t="inlineStr">
         <is>
-          <t>7019352</t>
+          <t>7019358</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -20712,7 +20791,7 @@
     <row r="760">
       <c r="A760" s="4" t="inlineStr">
         <is>
-          <t>7019353</t>
+          <t>7019359</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -20732,7 +20811,7 @@
     <row r="761">
       <c r="A761" s="6" t="inlineStr">
         <is>
-          <t>7019354</t>
+          <t>7019360</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -20752,7 +20831,7 @@
     <row r="762">
       <c r="A762" s="4" t="inlineStr">
         <is>
-          <t>7019355</t>
+          <t>7019361</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -20772,7 +20851,7 @@
     <row r="763">
       <c r="A763" s="6" t="inlineStr">
         <is>
-          <t>7019356</t>
+          <t>7019348</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -20792,7 +20871,7 @@
     <row r="764">
       <c r="A764" s="4" t="inlineStr">
         <is>
-          <t>7019357</t>
+          <t>7019349</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -20812,12 +20891,12 @@
     <row r="765">
       <c r="A765" s="6" t="inlineStr">
         <is>
-          <t>7021449</t>
+          <t>7019350</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -20832,12 +20911,12 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>7021450</t>
+          <t>7019351</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C766" s="5" t="inlineStr">
@@ -20852,12 +20931,12 @@
     <row r="767">
       <c r="A767" s="6" t="inlineStr">
         <is>
-          <t>7021451</t>
+          <t>7019352</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -20872,12 +20951,12 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>7021452</t>
+          <t>7019353</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
@@ -20892,12 +20971,12 @@
     <row r="769">
       <c r="A769" s="6" t="inlineStr">
         <is>
-          <t>7021453</t>
+          <t>7019354</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -20912,12 +20991,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>7021454</t>
+          <t>7019355</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
@@ -20932,12 +21011,12 @@
     <row r="771">
       <c r="A771" s="6" t="inlineStr">
         <is>
-          <t>7021443</t>
+          <t>7019356</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -20952,12 +21031,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>7021444</t>
+          <t>7019357</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Inlens</t>
+          <t>Interiörarmatur InMY infälld</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
@@ -20972,7 +21051,7 @@
     <row r="773">
       <c r="A773" s="6" t="inlineStr">
         <is>
-          <t>7021445</t>
+          <t>7021449</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -20992,7 +21071,7 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>7021446</t>
+          <t>7021450</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
@@ -21012,7 +21091,7 @@
     <row r="775">
       <c r="A775" s="6" t="inlineStr">
         <is>
-          <t>7021447</t>
+          <t>7021451</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -21032,7 +21111,7 @@
     <row r="776">
       <c r="A776" s="4" t="inlineStr">
         <is>
-          <t>7021448</t>
+          <t>7021452</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
@@ -21052,12 +21131,12 @@
     <row r="777">
       <c r="A777" s="6" t="inlineStr">
         <is>
-          <t>7018887</t>
+          <t>7021453</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -21072,12 +21151,12 @@
     <row r="778">
       <c r="A778" s="4" t="inlineStr">
         <is>
-          <t>7018888</t>
+          <t>7021454</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Pi infälld</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C778" s="5" t="inlineStr">
@@ -21092,12 +21171,12 @@
     <row r="779">
       <c r="A779" s="6" t="inlineStr">
         <is>
-          <t>7028566</t>
+          <t>7021443</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -21112,12 +21191,12 @@
     <row r="780">
       <c r="A780" s="4" t="inlineStr">
         <is>
-          <t>7028567</t>
+          <t>7021444</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C780" s="5" t="inlineStr">
@@ -21132,12 +21211,12 @@
     <row r="781">
       <c r="A781" s="6" t="inlineStr">
         <is>
-          <t>7028568</t>
+          <t>7021445</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -21152,12 +21231,12 @@
     <row r="782">
       <c r="A782" s="4" t="inlineStr">
         <is>
-          <t>7028569</t>
+          <t>7021446</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C782" s="5" t="inlineStr">
@@ -21172,12 +21251,12 @@
     <row r="783">
       <c r="A783" s="6" t="inlineStr">
         <is>
-          <t>7028570</t>
+          <t>7021447</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -21192,12 +21271,12 @@
     <row r="784">
       <c r="A784" s="4" t="inlineStr">
         <is>
-          <t>7028571</t>
+          <t>7021448</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Inlens</t>
         </is>
       </c>
       <c r="C784" s="5" t="inlineStr">
@@ -21212,12 +21291,12 @@
     <row r="785">
       <c r="A785" s="6" t="inlineStr">
         <is>
-          <t>7028572</t>
+          <t>7018887</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -21232,12 +21311,12 @@
     <row r="786">
       <c r="A786" s="4" t="inlineStr">
         <is>
-          <t>7028573</t>
+          <t>7018888</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Safe</t>
+          <t>Interiörarmatur Pi infälld</t>
         </is>
       </c>
       <c r="C786" s="5" t="inlineStr">
@@ -21252,7 +21331,7 @@
     <row r="787">
       <c r="A787" s="6" t="inlineStr">
         <is>
-          <t>7028574</t>
+          <t>7028566</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -21272,7 +21351,7 @@
     <row r="788">
       <c r="A788" s="4" t="inlineStr">
         <is>
-          <t>7028575</t>
+          <t>7028567</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
@@ -21292,7 +21371,7 @@
     <row r="789">
       <c r="A789" s="6" t="inlineStr">
         <is>
-          <t>7028576</t>
+          <t>7028568</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -21312,7 +21391,7 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>7028577</t>
+          <t>7028569</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
@@ -21332,7 +21411,7 @@
     <row r="791">
       <c r="A791" s="6" t="inlineStr">
         <is>
-          <t>7028578</t>
+          <t>7028570</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -21352,7 +21431,7 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>7028579</t>
+          <t>7028571</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
@@ -21372,7 +21451,7 @@
     <row r="793">
       <c r="A793" s="6" t="inlineStr">
         <is>
-          <t>7028580</t>
+          <t>7028572</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -21392,7 +21471,7 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>7028581</t>
+          <t>7028573</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
@@ -21412,17 +21491,17 @@
     <row r="795">
       <c r="A795" s="6" t="inlineStr">
         <is>
-          <t>7029244</t>
+          <t>7028574</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D795" s="6" t="n">
@@ -21432,17 +21511,17 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>7029245</t>
+          <t>7028575</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C796" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D796" s="4" t="n">
@@ -21452,17 +21531,17 @@
     <row r="797">
       <c r="A797" s="6" t="inlineStr">
         <is>
-          <t>7029246</t>
+          <t>7028576</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D797" s="6" t="n">
@@ -21472,17 +21551,17 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>7029247</t>
+          <t>7028577</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Easyfit</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C798" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D798" s="4" t="n">
@@ -21492,17 +21571,17 @@
     <row r="799">
       <c r="A799" s="6" t="inlineStr">
         <is>
-          <t>7029248</t>
+          <t>7028578</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D799" s="6" t="n">
@@ -21512,17 +21591,17 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>7029249</t>
+          <t>7028579</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D800" s="4" t="n">
@@ -21532,17 +21611,17 @@
     <row r="801">
       <c r="A801" s="6" t="inlineStr">
         <is>
-          <t>7029250</t>
+          <t>7028580</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D801" s="6" t="n">
@@ -21552,17 +21631,17 @@
     <row r="802">
       <c r="A802" s="4" t="inlineStr">
         <is>
-          <t>7029251</t>
+          <t>7028581</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
         <is>
-          <t>LED-panel Orion</t>
+          <t>Interiörarmatur Safe</t>
         </is>
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>Norwesco</t>
+          <t>Nokalux</t>
         </is>
       </c>
       <c r="D802" s="4" t="n">
@@ -21572,17 +21651,17 @@
     <row r="803">
       <c r="A803" s="6" t="inlineStr">
         <is>
-          <t>7028893</t>
+          <t>7029244</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Infälld Interiörarmatur Coreline Panel</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D803" s="6" t="n">
@@ -21592,17 +21671,17 @@
     <row r="804">
       <c r="A804" s="4" t="inlineStr">
         <is>
-          <t>7023008</t>
+          <t>7029245</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C804" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D804" s="4" t="n">
@@ -21612,17 +21691,17 @@
     <row r="805">
       <c r="A805" s="6" t="inlineStr">
         <is>
-          <t>7028892</t>
+          <t>7029246</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Coreline Panel Interact</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D805" s="6" t="n">
@@ -21632,17 +21711,17 @@
     <row r="806">
       <c r="A806" s="4" t="inlineStr">
         <is>
-          <t>7042301</t>
+          <t>7029247</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Easyfit</t>
         </is>
       </c>
       <c r="C806" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D806" s="4" t="n">
@@ -21652,17 +21731,17 @@
     <row r="807">
       <c r="A807" s="6" t="inlineStr">
         <is>
-          <t>7042305</t>
+          <t>7029248</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D807" s="6" t="n">
@@ -21672,17 +21751,17 @@
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>7042306</t>
+          <t>7029249</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D808" s="4" t="n">
@@ -21692,17 +21771,17 @@
     <row r="809">
       <c r="A809" s="6" t="inlineStr">
         <is>
-          <t>7042310</t>
+          <t>7029250</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D809" s="6" t="n">
@@ -21712,17 +21791,17 @@
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>7042311</t>
+          <t>7029251</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>LED-panel Orion</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Norwesco</t>
         </is>
       </c>
       <c r="D810" s="4" t="n">
@@ -21732,12 +21811,12 @@
     <row r="811">
       <c r="A811" s="6" t="inlineStr">
         <is>
-          <t>7042315</t>
+          <t>7028893</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld Interiörarmatur Coreline Panel</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -21752,12 +21831,12 @@
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>7042318</t>
+          <t>7023008</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
+          <t>Infälld interiörarmatur CoreLine Panel, 600x600</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
@@ -21772,12 +21851,12 @@
     <row r="813">
       <c r="A813" s="6" t="inlineStr">
         <is>
-          <t>7042302</t>
+          <t>7028892</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Infälld interiörarmatur Coreline Panel Interact</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -21792,12 +21871,12 @@
     <row r="814">
       <c r="A814" s="4" t="inlineStr">
         <is>
-          <t>7042303</t>
+          <t>7042301</t>
         </is>
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C814" s="5" t="inlineStr">
@@ -21812,12 +21891,12 @@
     <row r="815">
       <c r="A815" s="6" t="inlineStr">
         <is>
-          <t>7042304</t>
+          <t>7042305</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -21832,12 +21911,12 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>7042307</t>
+          <t>7042306</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C816" s="5" t="inlineStr">
@@ -21852,12 +21931,12 @@
     <row r="817">
       <c r="A817" s="6" t="inlineStr">
         <is>
-          <t>7042308</t>
+          <t>7042310</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -21872,12 +21951,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>7042309</t>
+          <t>7042311</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
@@ -21892,12 +21971,12 @@
     <row r="819">
       <c r="A819" s="6" t="inlineStr">
         <is>
-          <t>7042312</t>
+          <t>7042315</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -21912,12 +21991,12 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>7042313</t>
+          <t>7042318</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 30x120</t>
         </is>
       </c>
       <c r="C820" s="5" t="inlineStr">
@@ -21932,7 +22011,7 @@
     <row r="821">
       <c r="A821" s="6" t="inlineStr">
         <is>
-          <t>7042314</t>
+          <t>7042302</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -21952,7 +22031,7 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>7042316</t>
+          <t>7042303</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -21972,7 +22051,7 @@
     <row r="823">
       <c r="A823" s="6" t="inlineStr">
         <is>
-          <t>7042317</t>
+          <t>7042304</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -21992,7 +22071,7 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>7042319</t>
+          <t>7042307</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -22012,7 +22091,7 @@
     <row r="825">
       <c r="A825" s="6" t="inlineStr">
         <is>
-          <t>7042321</t>
+          <t>7042308</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -22032,7 +22111,7 @@
     <row r="826">
       <c r="A826" s="4" t="inlineStr">
         <is>
-          <t>7042322</t>
+          <t>7042309</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
@@ -22052,12 +22131,12 @@
     <row r="827">
       <c r="A827" s="6" t="inlineStr">
         <is>
-          <t>7027241</t>
+          <t>7042312</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -22072,12 +22151,12 @@
     <row r="828">
       <c r="A828" s="4" t="inlineStr">
         <is>
-          <t>7027242</t>
+          <t>7042313</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C828" s="5" t="inlineStr">
@@ -22092,12 +22171,12 @@
     <row r="829">
       <c r="A829" s="6" t="inlineStr">
         <is>
-          <t>7027245</t>
+          <t>7042314</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -22112,12 +22191,12 @@
     <row r="830">
       <c r="A830" s="4" t="inlineStr">
         <is>
-          <t>7024515</t>
+          <t>7042316</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C830" s="5" t="inlineStr">
@@ -22132,12 +22211,12 @@
     <row r="831">
       <c r="A831" s="6" t="inlineStr">
         <is>
-          <t>7024516</t>
+          <t>7042317</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -22152,12 +22231,12 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>7024517</t>
+          <t>7042319</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C832" s="5" t="inlineStr">
@@ -22172,12 +22251,12 @@
     <row r="833">
       <c r="A833" s="6" t="inlineStr">
         <is>
-          <t>7024518</t>
+          <t>7042321</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -22192,12 +22271,12 @@
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>7024519</t>
+          <t>7042322</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Coreline RC132V infälld, 60x60</t>
         </is>
       </c>
       <c r="C834" s="5" t="inlineStr">
@@ -22212,12 +22291,12 @@
     <row r="835">
       <c r="A835" s="6" t="inlineStr">
         <is>
-          <t>7024520</t>
+          <t>7027241</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -22232,12 +22311,12 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>7024521</t>
+          <t>7027242</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C836" s="5" t="inlineStr">
@@ -22252,12 +22331,12 @@
     <row r="837">
       <c r="A837" s="6" t="inlineStr">
         <is>
-          <t>7024522</t>
+          <t>7027245</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Interiörarmatur SlimBlend infälld</t>
+          <t>Interiörarmatur Ledinaire All-in, 3K/4K</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -22272,7 +22351,7 @@
     <row r="838">
       <c r="A838" s="4" t="inlineStr">
         <is>
-          <t>7024523</t>
+          <t>7024515</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
@@ -22292,7 +22371,7 @@
     <row r="839">
       <c r="A839" s="6" t="inlineStr">
         <is>
-          <t>7024524</t>
+          <t>7024516</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -22312,7 +22391,7 @@
     <row r="840">
       <c r="A840" s="4" t="inlineStr">
         <is>
-          <t>7024525</t>
+          <t>7024517</t>
         </is>
       </c>
       <c r="B840" s="5" t="inlineStr">
@@ -22332,12 +22411,12 @@
     <row r="841">
       <c r="A841" s="6" t="inlineStr">
         <is>
-          <t>7024527</t>
+          <t>7024518</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -22352,12 +22431,12 @@
     <row r="842">
       <c r="A842" s="4" t="inlineStr">
         <is>
-          <t>7024528</t>
+          <t>7024519</t>
         </is>
       </c>
       <c r="B842" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C842" s="5" t="inlineStr">
@@ -22372,12 +22451,12 @@
     <row r="843">
       <c r="A843" s="6" t="inlineStr">
         <is>
-          <t>7024529</t>
+          <t>7024520</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -22392,12 +22471,12 @@
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>7024530</t>
+          <t>7024521</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C844" s="5" t="inlineStr">
@@ -22412,12 +22491,12 @@
     <row r="845">
       <c r="A845" s="6" t="inlineStr">
         <is>
-          <t>7024531</t>
+          <t>7024522</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -22432,12 +22511,12 @@
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>7024532</t>
+          <t>7024523</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C846" s="5" t="inlineStr">
@@ -22452,12 +22531,12 @@
     <row r="847">
       <c r="A847" s="6" t="inlineStr">
         <is>
-          <t>7024533</t>
+          <t>7024524</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -22472,12 +22551,12 @@
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>7024534</t>
+          <t>7024525</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur TrueLine infälld</t>
+          <t>Interiörarmatur SlimBlend infälld</t>
         </is>
       </c>
       <c r="C848" s="5" t="inlineStr">
@@ -22492,17 +22571,17 @@
     <row r="849">
       <c r="A849" s="6" t="inlineStr">
         <is>
-          <t>7015063</t>
+          <t>7024527</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D849" s="6" t="n">
@@ -22512,17 +22591,17 @@
     <row r="850">
       <c r="A850" s="4" t="inlineStr">
         <is>
-          <t>7015064</t>
+          <t>7024528</t>
         </is>
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C850" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D850" s="4" t="n">
@@ -22532,17 +22611,17 @@
     <row r="851">
       <c r="A851" s="6" t="inlineStr">
         <is>
-          <t>7016290</t>
+          <t>7024529</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D851" s="6" t="n">
@@ -22552,17 +22631,17 @@
     <row r="852">
       <c r="A852" s="4" t="inlineStr">
         <is>
-          <t>7015271</t>
+          <t>7024530</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C852" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D852" s="4" t="n">
@@ -22572,17 +22651,17 @@
     <row r="853">
       <c r="A853" s="6" t="inlineStr">
         <is>
-          <t>7015272</t>
+          <t>7024531</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D853" s="6" t="n">
@@ -22592,17 +22671,17 @@
     <row r="854">
       <c r="A854" s="4" t="inlineStr">
         <is>
-          <t>7016291E</t>
+          <t>7024532</t>
         </is>
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C854" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D854" s="4" t="n">
@@ -22612,17 +22691,17 @@
     <row r="855">
       <c r="A855" s="6" t="inlineStr">
         <is>
-          <t>7015065</t>
+          <t>7024533</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D855" s="6" t="n">
@@ -22632,17 +22711,17 @@
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>7015066</t>
+          <t>7024534</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
         <is>
-          <t>Infälld interörarmatur LED Sence Round</t>
+          <t>Interiörarmatur TrueLine infälld</t>
         </is>
       </c>
       <c r="C856" s="5" t="inlineStr">
         <is>
-          <t>SG Armaturen</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="D856" s="4" t="n">
@@ -22652,7 +22731,7 @@
     <row r="857">
       <c r="A857" s="6" t="inlineStr">
         <is>
-          <t>7016292</t>
+          <t>7015063</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -22672,7 +22751,7 @@
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>7015273</t>
+          <t>7015064</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -22692,7 +22771,7 @@
     <row r="859">
       <c r="A859" s="6" t="inlineStr">
         <is>
-          <t>7015274</t>
+          <t>7016290</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -22712,7 +22791,7 @@
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>7016293</t>
+          <t>7015271</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -22732,7 +22811,7 @@
     <row r="861">
       <c r="A861" s="6" t="inlineStr">
         <is>
-          <t>7015067</t>
+          <t>7015272</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -22752,7 +22831,7 @@
     <row r="862">
       <c r="A862" s="4" t="inlineStr">
         <is>
-          <t>7015068</t>
+          <t>7016291E</t>
         </is>
       </c>
       <c r="B862" s="5" t="inlineStr">
@@ -22772,7 +22851,7 @@
     <row r="863">
       <c r="A863" s="6" t="inlineStr">
         <is>
-          <t>7015069</t>
+          <t>7015065</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -22792,7 +22871,7 @@
     <row r="864">
       <c r="A864" s="4" t="inlineStr">
         <is>
-          <t>7015275</t>
+          <t>7015066</t>
         </is>
       </c>
       <c r="B864" s="5" t="inlineStr">
@@ -22812,7 +22891,7 @@
     <row r="865">
       <c r="A865" s="6" t="inlineStr">
         <is>
-          <t>7015276</t>
+          <t>7016292</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -22832,7 +22911,7 @@
     <row r="866">
       <c r="A866" s="4" t="inlineStr">
         <is>
-          <t>7015277</t>
+          <t>7015273</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
@@ -22852,7 +22931,7 @@
     <row r="867">
       <c r="A867" s="6" t="inlineStr">
         <is>
-          <t>7015070</t>
+          <t>7015274</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -22872,7 +22951,7 @@
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>7015071</t>
+          <t>7016293</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -22892,7 +22971,7 @@
     <row r="869">
       <c r="A869" s="6" t="inlineStr">
         <is>
-          <t>7015278</t>
+          <t>7015067</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -22912,7 +22991,7 @@
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>7015279</t>
+          <t>7015068</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -22932,7 +23011,7 @@
     <row r="871">
       <c r="A871" s="6" t="inlineStr">
         <is>
-          <t>7028329</t>
+          <t>7015069</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -22952,7 +23031,7 @@
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>7028330</t>
+          <t>7015275</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -22972,7 +23051,7 @@
     <row r="873">
       <c r="A873" s="6" t="inlineStr">
         <is>
-          <t>7028331</t>
+          <t>7015276</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -22992,7 +23071,7 @@
     <row r="874">
       <c r="A874" s="4" t="inlineStr">
         <is>
-          <t>7028332</t>
+          <t>7015277</t>
         </is>
       </c>
       <c r="B874" s="5" t="inlineStr">
@@ -23012,12 +23091,12 @@
     <row r="875">
       <c r="A875" s="6" t="inlineStr">
         <is>
-          <t>7018001</t>
+          <t>7015070</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -23032,12 +23111,12 @@
     <row r="876">
       <c r="A876" s="4" t="inlineStr">
         <is>
-          <t>7018002</t>
+          <t>7015071</t>
         </is>
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x1200</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C876" s="5" t="inlineStr">
@@ -23052,12 +23131,12 @@
     <row r="877">
       <c r="A877" s="6" t="inlineStr">
         <is>
-          <t>7015072</t>
+          <t>7015278</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -23072,12 +23151,12 @@
     <row r="878">
       <c r="A878" s="4" t="inlineStr">
         <is>
-          <t>7015280</t>
+          <t>7015279</t>
         </is>
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C878" s="5" t="inlineStr">
@@ -23092,12 +23171,12 @@
     <row r="879">
       <c r="A879" s="6" t="inlineStr">
         <is>
-          <t>7016295</t>
+          <t>7028329</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 300x300</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -23112,12 +23191,12 @@
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>7017938</t>
+          <t>7028330</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C880" s="5" t="inlineStr">
@@ -23126,18 +23205,18 @@
         </is>
       </c>
       <c r="D880" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="6" t="inlineStr">
         <is>
-          <t>7017939</t>
+          <t>7028331</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Interiörarmatur LED Sense 600x600</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -23146,18 +23225,18 @@
         </is>
       </c>
       <c r="D881" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>7019423</t>
+          <t>7028332</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Infälld interörarmatur LED Sence Round</t>
         </is>
       </c>
       <c r="C882" s="5" t="inlineStr">
@@ -23172,12 +23251,12 @@
     <row r="883">
       <c r="A883" s="6" t="inlineStr">
         <is>
-          <t>7019424</t>
+          <t>7018001</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -23192,12 +23271,12 @@
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>7019428</t>
+          <t>7018002</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur LED Sense 300x1200</t>
         </is>
       </c>
       <c r="C884" s="5" t="inlineStr">
@@ -23212,12 +23291,12 @@
     <row r="885">
       <c r="A885" s="6" t="inlineStr">
         <is>
-          <t>7019417</t>
+          <t>7015072</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -23232,12 +23311,12 @@
     <row r="886">
       <c r="A886" s="4" t="inlineStr">
         <is>
-          <t>7019429</t>
+          <t>7015280</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C886" s="5" t="inlineStr">
@@ -23252,12 +23331,12 @@
     <row r="887">
       <c r="A887" s="6" t="inlineStr">
         <is>
-          <t>7019430</t>
+          <t>7016295</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lineal infälld</t>
+          <t>Interiörarmatur LED Sense 300x300</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -23272,12 +23351,12 @@
     <row r="888">
       <c r="A888" s="4" t="inlineStr">
         <is>
-          <t>7019572</t>
+          <t>7017938</t>
         </is>
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C888" s="5" t="inlineStr">
@@ -23286,18 +23365,18 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="6" t="inlineStr">
         <is>
-          <t>7019573</t>
+          <t>7017939</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic</t>
+          <t>Interiörarmatur LED Sense 600x600</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -23306,18 +23385,18 @@
         </is>
       </c>
       <c r="D889" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="inlineStr">
         <is>
-          <t>7028217</t>
+          <t>7019572</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C890" s="5" t="inlineStr">
@@ -23332,12 +23411,12 @@
     <row r="891">
       <c r="A891" s="6" t="inlineStr">
         <is>
-          <t>7028218</t>
+          <t>7019573</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic Connect</t>
+          <t>Interiörarmatur Sense Basic</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -23352,12 +23431,12 @@
     <row r="892">
       <c r="A892" s="4" t="inlineStr">
         <is>
-          <t>7028197</t>
+          <t>7028217</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C892" s="5" t="inlineStr">
@@ -23372,12 +23451,12 @@
     <row r="893">
       <c r="A893" s="6" t="inlineStr">
         <is>
-          <t>7028033</t>
+          <t>7028218</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Basic gen2</t>
+          <t>Interiörarmatur Sense Basic Connect</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -23386,13 +23465,13 @@
         </is>
       </c>
       <c r="D893" s="6" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="inlineStr">
         <is>
-          <t>7028035</t>
+          <t>7028197</t>
         </is>
       </c>
       <c r="B894" s="5" t="inlineStr">
@@ -23406,13 +23485,13 @@
         </is>
       </c>
       <c r="D894" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="6" t="inlineStr">
         <is>
-          <t>7028034</t>
+          <t>7028033</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -23426,13 +23505,13 @@
         </is>
       </c>
       <c r="D895" s="6" t="n">
-        <v>28</v>
+        <v>366</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="inlineStr">
         <is>
-          <t>7028044</t>
+          <t>7028035</t>
         </is>
       </c>
       <c r="B896" s="5" t="inlineStr">
@@ -23446,18 +23525,18 @@
         </is>
       </c>
       <c r="D896" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="6" t="inlineStr">
         <is>
-          <t>7019665</t>
+          <t>7028034</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -23466,18 +23545,18 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="4" t="inlineStr">
         <is>
-          <t>7019659</t>
+          <t>7028044</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65</t>
+          <t>Interiörarmatur Sense Basic gen2</t>
         </is>
       </c>
       <c r="C898" s="5" t="inlineStr">
@@ -23492,12 +23571,12 @@
     <row r="899">
       <c r="A899" s="6" t="inlineStr">
         <is>
-          <t>7021278</t>
+          <t>7019665</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -23512,12 +23591,12 @@
     <row r="900">
       <c r="A900" s="4" t="inlineStr">
         <is>
-          <t>7021279</t>
+          <t>7019659</t>
         </is>
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense IP65 Eco</t>
+          <t>Interiörarmatur Sense IP65</t>
         </is>
       </c>
       <c r="C900" s="5" t="inlineStr">
@@ -23532,7 +23611,7 @@
     <row r="901">
       <c r="A901" s="6" t="inlineStr">
         <is>
-          <t>7028952</t>
+          <t>7021278</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -23552,7 +23631,7 @@
     <row r="902">
       <c r="A902" s="4" t="inlineStr">
         <is>
-          <t>7028953</t>
+          <t>7021279</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
@@ -23572,12 +23651,12 @@
     <row r="903">
       <c r="A903" s="6" t="inlineStr">
         <is>
-          <t>7024921</t>
+          <t>7028952</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -23592,12 +23671,12 @@
     <row r="904">
       <c r="A904" s="4" t="inlineStr">
         <is>
-          <t>7024922</t>
+          <t>7028953</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Line</t>
+          <t>Interiörarmatur Sense IP65 Eco</t>
         </is>
       </c>
       <c r="C904" s="5" t="inlineStr">
@@ -23612,7 +23691,7 @@
     <row r="905">
       <c r="A905" s="6" t="inlineStr">
         <is>
-          <t>7024923</t>
+          <t>7024921</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -23632,7 +23711,7 @@
     <row r="906">
       <c r="A906" s="4" t="inlineStr">
         <is>
-          <t>7024924</t>
+          <t>7024922</t>
         </is>
       </c>
       <c r="B906" s="5" t="inlineStr">
@@ -23652,7 +23731,7 @@
     <row r="907">
       <c r="A907" s="6" t="inlineStr">
         <is>
-          <t>7024925</t>
+          <t>7024923</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -23672,7 +23751,7 @@
     <row r="908">
       <c r="A908" s="4" t="inlineStr">
         <is>
-          <t>7024926</t>
+          <t>7024924</t>
         </is>
       </c>
       <c r="B908" s="5" t="inlineStr">
@@ -23692,7 +23771,7 @@
     <row r="909">
       <c r="A909" s="6" t="inlineStr">
         <is>
-          <t>7024927</t>
+          <t>7024925</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -23712,7 +23791,7 @@
     <row r="910">
       <c r="A910" s="4" t="inlineStr">
         <is>
-          <t>7024928</t>
+          <t>7024926</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
@@ -23732,12 +23811,12 @@
     <row r="911">
       <c r="A911" s="6" t="inlineStr">
         <is>
-          <t>7017941</t>
+          <t>7024927</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -23752,12 +23831,12 @@
     <row r="912">
       <c r="A912" s="4" t="inlineStr">
         <is>
-          <t>7017942</t>
+          <t>7024928</t>
         </is>
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Opalprismatisk</t>
+          <t>Interiörarmatur Sense Line</t>
         </is>
       </c>
       <c r="C912" s="5" t="inlineStr">
@@ -23772,7 +23851,7 @@
     <row r="913">
       <c r="A913" s="6" t="inlineStr">
         <is>
-          <t>7024625</t>
+          <t>7017941</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -23792,7 +23871,7 @@
     <row r="914">
       <c r="A914" s="4" t="inlineStr">
         <is>
-          <t>7024626</t>
+          <t>7017942</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
@@ -23812,7 +23891,7 @@
     <row r="915">
       <c r="A915" s="6" t="inlineStr">
         <is>
-          <t>7024627</t>
+          <t>7024625</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -23826,13 +23905,13 @@
         </is>
       </c>
       <c r="D915" s="6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="4" t="inlineStr">
         <is>
-          <t>7024628</t>
+          <t>7024626</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
@@ -23852,7 +23931,7 @@
     <row r="917">
       <c r="A917" s="6" t="inlineStr">
         <is>
-          <t>7024633</t>
+          <t>7024627</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -23866,13 +23945,13 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="4" t="inlineStr">
         <is>
-          <t>7024634</t>
+          <t>7024628</t>
         </is>
       </c>
       <c r="B918" s="5" t="inlineStr">
@@ -23892,12 +23971,12 @@
     <row r="919">
       <c r="A919" s="6" t="inlineStr">
         <is>
-          <t>7019797</t>
+          <t>7024633</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -23912,12 +23991,12 @@
     <row r="920">
       <c r="A920" s="4" t="inlineStr">
         <is>
-          <t>7019798</t>
+          <t>7024634</t>
         </is>
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pir</t>
+          <t>Interiörarmatur Sense Opalprismatisk</t>
         </is>
       </c>
       <c r="C920" s="5" t="inlineStr">
@@ -23932,7 +24011,7 @@
     <row r="921">
       <c r="A921" s="6" t="inlineStr">
         <is>
-          <t>7024635</t>
+          <t>7019797</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -23946,13 +24025,13 @@
         </is>
       </c>
       <c r="D921" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="4" t="inlineStr">
         <is>
-          <t>7024636</t>
+          <t>7019798</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
@@ -23972,12 +24051,12 @@
     <row r="923">
       <c r="A923" s="6" t="inlineStr">
         <is>
-          <t>7024631</t>
+          <t>7024635</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -23986,18 +24065,18 @@
         </is>
       </c>
       <c r="D923" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="4" t="inlineStr">
         <is>
-          <t>7024632</t>
+          <t>7024636</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro</t>
+          <t>Interiörarmatur Sense Pir</t>
         </is>
       </c>
       <c r="C924" s="5" t="inlineStr">
@@ -24012,7 +24091,7 @@
     <row r="925">
       <c r="A925" s="6" t="inlineStr">
         <is>
-          <t>7028741</t>
+          <t>7024631</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -24032,12 +24111,12 @@
     <row r="926">
       <c r="A926" s="4" t="inlineStr">
         <is>
-          <t>7026638</t>
+          <t>7024632</t>
         </is>
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C926" s="5" t="inlineStr">
@@ -24052,12 +24131,12 @@
     <row r="927">
       <c r="A927" s="6" t="inlineStr">
         <is>
-          <t>7026639</t>
+          <t>7028741</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Connect</t>
+          <t>Interiörarmatur Sense Pro</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -24072,7 +24151,7 @@
     <row r="928">
       <c r="A928" s="4" t="inlineStr">
         <is>
-          <t>7026640</t>
+          <t>7026638</t>
         </is>
       </c>
       <c r="B928" s="5" t="inlineStr">
@@ -24092,7 +24171,7 @@
     <row r="929">
       <c r="A929" s="6" t="inlineStr">
         <is>
-          <t>7026641</t>
+          <t>7026639</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -24112,7 +24191,7 @@
     <row r="930">
       <c r="A930" s="4" t="inlineStr">
         <is>
-          <t>7028954</t>
+          <t>7026640</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
@@ -24132,7 +24211,7 @@
     <row r="931">
       <c r="A931" s="6" t="inlineStr">
         <is>
-          <t>7028955</t>
+          <t>7026641</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -24152,12 +24231,12 @@
     <row r="932">
       <c r="A932" s="4" t="inlineStr">
         <is>
-          <t>7024629</t>
+          <t>7028954</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C932" s="5" t="inlineStr">
@@ -24172,12 +24251,12 @@
     <row r="933">
       <c r="A933" s="6" t="inlineStr">
         <is>
-          <t>7024630</t>
+          <t>7028955</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro Round</t>
+          <t>Interiörarmatur Sense Pro Connect</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -24192,12 +24271,12 @@
     <row r="934">
       <c r="A934" s="4" t="inlineStr">
         <is>
-          <t>7026783</t>
+          <t>7024629</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C934" s="5" t="inlineStr">
@@ -24212,12 +24291,12 @@
     <row r="935">
       <c r="A935" s="6" t="inlineStr">
         <is>
-          <t>7026784</t>
+          <t>7024630</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Pro X</t>
+          <t>Interiörarmatur Sense Pro Round</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -24232,7 +24311,7 @@
     <row r="936">
       <c r="A936" s="4" t="inlineStr">
         <is>
-          <t>7028122</t>
+          <t>7026783</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
@@ -24252,7 +24331,7 @@
     <row r="937">
       <c r="A937" s="6" t="inlineStr">
         <is>
-          <t>7028123</t>
+          <t>7026784</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -24272,12 +24351,12 @@
     <row r="938">
       <c r="A938" s="4" t="inlineStr">
         <is>
-          <t>7018057</t>
+          <t>7028122</t>
         </is>
       </c>
       <c r="B938" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C938" s="5" t="inlineStr">
@@ -24292,12 +24371,12 @@
     <row r="939">
       <c r="A939" s="6" t="inlineStr">
         <is>
-          <t>7018056</t>
+          <t>7028123</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW</t>
+          <t>Interiörarmatur Sense Pro X</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -24312,12 +24391,12 @@
     <row r="940">
       <c r="A940" s="4" t="inlineStr">
         <is>
-          <t>7016803</t>
+          <t>7018057</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C940" s="5" t="inlineStr">
@@ -24332,12 +24411,12 @@
     <row r="941">
       <c r="A941" s="6" t="inlineStr">
         <is>
-          <t>7016818</t>
+          <t>7018056</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense TW rund</t>
+          <t>Interiörarmatur Sense TW</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -24352,7 +24431,7 @@
     <row r="942">
       <c r="A942" s="4" t="inlineStr">
         <is>
-          <t>7016819</t>
+          <t>7016803</t>
         </is>
       </c>
       <c r="B942" s="5" t="inlineStr">
@@ -24372,7 +24451,7 @@
     <row r="943">
       <c r="A943" s="6" t="inlineStr">
         <is>
-          <t>7016820</t>
+          <t>7016818</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -24392,7 +24471,7 @@
     <row r="944">
       <c r="A944" s="4" t="inlineStr">
         <is>
-          <t>7016822</t>
+          <t>7016819</t>
         </is>
       </c>
       <c r="B944" s="5" t="inlineStr">
@@ -24412,7 +24491,7 @@
     <row r="945">
       <c r="A945" s="6" t="inlineStr">
         <is>
-          <t>7016821</t>
+          <t>7016820</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -24432,12 +24511,12 @@
     <row r="946">
       <c r="A946" s="4" t="inlineStr">
         <is>
-          <t>7028408</t>
+          <t>7016822</t>
         </is>
       </c>
       <c r="B946" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C946" s="5" t="inlineStr">
@@ -24452,12 +24531,12 @@
     <row r="947">
       <c r="A947" s="6" t="inlineStr">
         <is>
-          <t>7028409</t>
+          <t>7016821</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Interiörarmatur Sense Velios</t>
+          <t>Interiörarmatur Sense TW rund</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -24472,7 +24551,7 @@
     <row r="948">
       <c r="A948" s="4" t="inlineStr">
         <is>
-          <t>7028410</t>
+          <t>7028408</t>
         </is>
       </c>
       <c r="B948" s="5" t="inlineStr">
@@ -24492,7 +24571,7 @@
     <row r="949">
       <c r="A949" s="6" t="inlineStr">
         <is>
-          <t>7028411</t>
+          <t>7028409</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -24512,7 +24591,7 @@
     <row r="950">
       <c r="A950" s="4" t="inlineStr">
         <is>
-          <t>7028412</t>
+          <t>7028410</t>
         </is>
       </c>
       <c r="B950" s="5" t="inlineStr">
@@ -24532,7 +24611,7 @@
     <row r="951">
       <c r="A951" s="6" t="inlineStr">
         <is>
-          <t>7028413</t>
+          <t>7028411</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -24552,7 +24631,7 @@
     <row r="952">
       <c r="A952" s="4" t="inlineStr">
         <is>
-          <t>7028414</t>
+          <t>7028412</t>
         </is>
       </c>
       <c r="B952" s="5" t="inlineStr">
@@ -24572,7 +24651,7 @@
     <row r="953">
       <c r="A953" s="6" t="inlineStr">
         <is>
-          <t>7028415</t>
+          <t>7028413</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -24592,17 +24671,17 @@
     <row r="954">
       <c r="A954" s="4" t="inlineStr">
         <is>
-          <t>7026760</t>
+          <t>7028414</t>
         </is>
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C954" s="5" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D954" s="4" t="n">
@@ -24612,17 +24691,17 @@
     <row r="955">
       <c r="A955" s="6" t="inlineStr">
         <is>
-          <t>7027137</t>
+          <t>7028415</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Interiörarmatur Apollon 21</t>
+          <t>Interiörarmatur Sense Velios</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Siteco</t>
+          <t>SG Armaturen</t>
         </is>
       </c>
       <c r="D955" s="6" t="n">
@@ -24632,7 +24711,7 @@
     <row r="956">
       <c r="A956" s="4" t="inlineStr">
         <is>
-          <t>7027138</t>
+          <t>7026760</t>
         </is>
       </c>
       <c r="B956" s="5" t="inlineStr">
@@ -24652,7 +24731,7 @@
     <row r="957">
       <c r="A957" s="6" t="inlineStr">
         <is>
-          <t>7027139</t>
+          <t>7027137</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -24672,7 +24751,7 @@
     <row r="958">
       <c r="A958" s="4" t="inlineStr">
         <is>
-          <t>7027140</t>
+          <t>7027138</t>
         </is>
       </c>
       <c r="B958" s="5" t="inlineStr">
@@ -24692,7 +24771,7 @@
     <row r="959">
       <c r="A959" s="6" t="inlineStr">
         <is>
-          <t>7027141</t>
+          <t>7027139</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -24712,7 +24791,7 @@
     <row r="960">
       <c r="A960" s="4" t="inlineStr">
         <is>
-          <t>7027142</t>
+          <t>7027140</t>
         </is>
       </c>
       <c r="B960" s="5" t="inlineStr">
@@ -24732,7 +24811,7 @@
     <row r="961">
       <c r="A961" s="6" t="inlineStr">
         <is>
-          <t>7027143</t>
+          <t>7027141</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -24752,7 +24831,7 @@
     <row r="962">
       <c r="A962" s="4" t="inlineStr">
         <is>
-          <t>7027144</t>
+          <t>7027142</t>
         </is>
       </c>
       <c r="B962" s="5" t="inlineStr">
@@ -24772,17 +24851,17 @@
     <row r="963">
       <c r="A963" s="6" t="inlineStr">
         <is>
-          <t>7077510</t>
+          <t>7027143</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D963" s="6" t="n">
@@ -24792,17 +24871,17 @@
     <row r="964">
       <c r="A964" s="4" t="inlineStr">
         <is>
-          <t>7077516</t>
+          <t>7027144</t>
         </is>
       </c>
       <c r="B964" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur IQ Wave</t>
+          <t>Interiörarmatur Apollon 21</t>
         </is>
       </c>
       <c r="C964" s="5" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Siteco</t>
         </is>
       </c>
       <c r="D964" s="4" t="n">
@@ -24812,7 +24891,7 @@
     <row r="965">
       <c r="A965" s="6" t="inlineStr">
         <is>
-          <t>7077513</t>
+          <t>7077510</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -24832,7 +24911,7 @@
     <row r="966">
       <c r="A966" s="4" t="inlineStr">
         <is>
-          <t>7077517</t>
+          <t>7077516</t>
         </is>
       </c>
       <c r="B966" s="5" t="inlineStr">
@@ -24852,7 +24931,7 @@
     <row r="967">
       <c r="A967" s="6" t="inlineStr">
         <is>
-          <t>7077577</t>
+          <t>7077513</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -24872,12 +24951,12 @@
     <row r="968">
       <c r="A968" s="4" t="inlineStr">
         <is>
-          <t>7018153</t>
+          <t>7077517</t>
         </is>
       </c>
       <c r="B968" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C968" s="5" t="inlineStr">
@@ -24892,12 +24971,12 @@
     <row r="969">
       <c r="A969" s="6" t="inlineStr">
         <is>
-          <t>7018765</t>
+          <t>7077577</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur Omega Pro 2</t>
+          <t>Infälld interiörarmatur IQ Wave</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -24912,17 +24991,17 @@
     <row r="970">
       <c r="A970" s="4" t="inlineStr">
         <is>
-          <t>7022037</t>
+          <t>7018153</t>
         </is>
       </c>
       <c r="B970" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C970" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D970" s="4" t="n">
@@ -24932,17 +25011,17 @@
     <row r="971">
       <c r="A971" s="6" t="inlineStr">
         <is>
-          <t>7022038</t>
+          <t>7018765</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Circle infälld</t>
+          <t>Infälld interiörarmatur Omega Pro 2</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="D971" s="6" t="n">
@@ -24952,7 +25031,7 @@
     <row r="972">
       <c r="A972" s="4" t="inlineStr">
         <is>
-          <t>7021686</t>
+          <t>7022037</t>
         </is>
       </c>
       <c r="B972" s="5" t="inlineStr">
@@ -24972,7 +25051,7 @@
     <row r="973">
       <c r="A973" s="6" t="inlineStr">
         <is>
-          <t>7021687</t>
+          <t>7022038</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -24992,7 +25071,7 @@
     <row r="974">
       <c r="A974" s="4" t="inlineStr">
         <is>
-          <t>7022043</t>
+          <t>7021686</t>
         </is>
       </c>
       <c r="B974" s="5" t="inlineStr">
@@ -25012,7 +25091,7 @@
     <row r="975">
       <c r="A975" s="6" t="inlineStr">
         <is>
-          <t>7022045</t>
+          <t>7021687</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -25032,12 +25111,12 @@
     <row r="976">
       <c r="A976" s="4" t="inlineStr">
         <is>
-          <t>7026483</t>
+          <t>7022043</t>
         </is>
       </c>
       <c r="B976" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C976" s="5" t="inlineStr">
@@ -25052,12 +25131,12 @@
     <row r="977">
       <c r="A977" s="6" t="inlineStr">
         <is>
-          <t>7021611</t>
+          <t>7022045</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Eco Infälld</t>
+          <t>Interiörarmatur US Circle infälld</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -25066,13 +25145,13 @@
         </is>
       </c>
       <c r="D977" s="6" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="inlineStr">
         <is>
-          <t>7029355</t>
+          <t>7026483</t>
         </is>
       </c>
       <c r="B978" s="5" t="inlineStr">
@@ -25086,13 +25165,13 @@
         </is>
       </c>
       <c r="D978" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" s="6" t="inlineStr">
         <is>
-          <t>7029356</t>
+          <t>7021611</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -25106,13 +25185,13 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>40</v>
+        <v>217</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="inlineStr">
         <is>
-          <t>7029357</t>
+          <t>7029355</t>
         </is>
       </c>
       <c r="B980" s="5" t="inlineStr">
@@ -25126,18 +25205,18 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" s="6" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7029356</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -25146,18 +25225,18 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" s="4" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7029357</t>
         </is>
       </c>
       <c r="B982" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US Eco Infälld</t>
         </is>
       </c>
       <c r="C982" s="5" t="inlineStr">
@@ -25172,12 +25251,12 @@
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021628</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -25192,12 +25271,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021629</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Interiörarmatur US Sens infälld med grundljus</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -25212,7 +25291,7 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -25232,7 +25311,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
@@ -25252,7 +25331,7 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -25272,7 +25351,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -25292,17 +25371,17 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D989" s="6" t="n">
@@ -25312,17 +25391,17 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
         <is>
-          <t>Westal</t>
+          <t>Tupex</t>
         </is>
       </c>
       <c r="D990" s="4" t="n">
@@ -25332,7 +25411,7 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -25352,7 +25431,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
@@ -25372,12 +25451,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -25392,12 +25471,12 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
@@ -25412,12 +25491,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -25432,12 +25511,12 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
@@ -25452,7 +25531,7 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -25472,7 +25551,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
@@ -25492,12 +25571,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -25512,12 +25591,12 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
@@ -25532,12 +25611,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -25552,12 +25631,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -25572,7 +25651,7 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -25592,7 +25671,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -25612,12 +25691,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -25632,12 +25711,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -25652,7 +25731,7 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -25672,7 +25751,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -25692,12 +25771,12 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -25712,12 +25791,12 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
@@ -25732,7 +25811,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -25752,7 +25831,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -25772,7 +25851,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -25792,7 +25871,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -25812,7 +25891,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -25832,7 +25911,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -25852,7 +25931,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -25872,7 +25951,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -25892,7 +25971,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -25912,7 +25991,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -25932,7 +26011,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -25952,7 +26031,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -25972,7 +26051,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -25992,7 +26071,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -26012,7 +26091,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -26032,7 +26111,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -26052,7 +26131,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -26072,7 +26151,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -26092,7 +26171,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -26112,7 +26191,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -26132,7 +26211,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -26152,7 +26231,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -26172,7 +26251,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -26192,7 +26271,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -26212,7 +26291,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -26232,7 +26311,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -26252,7 +26331,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -26272,7 +26351,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -26292,7 +26371,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -26312,7 +26391,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -26332,7 +26411,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -26352,7 +26431,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -26372,7 +26451,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -26392,7 +26471,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -26412,12 +26491,12 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -26432,12 +26511,12 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1046" s="5" t="inlineStr">
@@ -26452,7 +26531,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -26472,7 +26551,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -26492,7 +26571,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -26512,7 +26591,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -26532,7 +26611,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -26552,7 +26631,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -26572,7 +26651,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -26592,7 +26671,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -26612,7 +26691,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -26632,7 +26711,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -26652,12 +26731,12 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -26672,12 +26751,12 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1058" s="5" t="inlineStr">
@@ -26692,7 +26771,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -26712,7 +26791,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -26732,12 +26811,12 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -26752,12 +26831,12 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1062" s="5" t="inlineStr">
@@ -26772,12 +26851,12 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -26792,7 +26871,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -26812,7 +26891,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -26832,12 +26911,12 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1066" s="5" t="inlineStr">
@@ -26852,12 +26931,12 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -26872,12 +26951,12 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1068" s="5" t="inlineStr">
@@ -26892,12 +26971,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -26912,12 +26991,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -26932,7 +27011,7 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -26952,7 +27031,7 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
@@ -26972,7 +27051,7 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -26992,7 +27071,7 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
@@ -27012,7 +27091,7 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -27032,7 +27111,7 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
@@ -27052,7 +27131,7 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -27072,7 +27151,7 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
@@ -27092,7 +27171,7 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -27112,7 +27191,7 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
@@ -27132,7 +27211,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -27152,7 +27231,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -27172,7 +27251,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -27192,7 +27271,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -27212,17 +27291,17 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1085" s="6" t="n">
@@ -27232,17 +27311,17 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1086" s="4" t="n">
@@ -27252,12 +27331,12 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -27272,52 +27351,52 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7028324</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1088" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7028311</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Interiörarmatur Maya</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1089" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7013475</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Infälld interiörarmatur aLight Office LED</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
@@ -27326,18 +27405,18 @@
         </is>
       </c>
       <c r="D1090" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7021097</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -27346,18 +27425,18 @@
         </is>
       </c>
       <c r="D1091" s="6" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7018286</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
@@ -27366,18 +27445,18 @@
         </is>
       </c>
       <c r="D1092" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7028368</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -27386,18 +27465,18 @@
         </is>
       </c>
       <c r="D1093" s="6" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7028369</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>LED-Panel Flex</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
@@ -27406,18 +27485,18 @@
         </is>
       </c>
       <c r="D1094" s="4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028001</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>LED-Panel aLight Office Rektangulär</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -27426,27 +27505,67 @@
         </is>
       </c>
       <c r="D1095" s="6" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
+          <t>7028002</t>
+        </is>
+      </c>
+      <c r="B1096" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1096" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1096" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="6" t="inlineStr">
+        <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1097" s="6" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="4" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1096" s="5" t="inlineStr">
+      <c r="B1098" s="5" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1096" s="5" t="inlineStr">
+      <c r="C1098" s="5" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1096" s="4" t="n">
-        <v>359</v>
+      <c r="D1098" s="4" t="n">
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -533,82 +533,82 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
+          <t>Ledvance</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
           <t>Exaktor</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Ledvance</t>
-        </is>
-      </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>ANETA LIGHTING</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Nokalux</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Ensto</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>ANETA LIGHTING</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Black Box</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Bergdahls</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
         </is>
       </c>
     </row>
@@ -643,10 +643,10 @@
         <v>25</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>25</v>
       </c>
       <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="n">
         <v>33</v>
-      </c>
-      <c r="K3" t="n">
-        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>25</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
@@ -880,10 +880,10 @@
         <v>24</v>
       </c>
       <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="n">
         <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>24</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>24</v>
       </c>
       <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="n">
         <v>33</v>
-      </c>
-      <c r="K7" t="n">
-        <v>17</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>24</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         <v>24</v>
       </c>
       <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
         <v>33</v>
-      </c>
-      <c r="K9" t="n">
-        <v>17</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         <v>24</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
@@ -1351,10 +1351,10 @@
         <v>24</v>
       </c>
       <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" t="n">
         <v>33</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>24</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
@@ -1509,10 +1509,10 @@
         <v>24</v>
       </c>
       <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="n">
         <v>33</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1588,10 +1588,10 @@
         <v>24</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K15" t="n">
         <v>33</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>24</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0</v>
@@ -1825,10 +1825,10 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
+        <v>17</v>
+      </c>
+      <c r="K17" t="n">
         <v>33</v>
-      </c>
-      <c r="K17" t="n">
-        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1904,10 +1904,10 @@
         <v>24</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
@@ -1983,10 +1983,10 @@
         <v>24</v>
       </c>
       <c r="J19" t="n">
+        <v>17</v>
+      </c>
+      <c r="K19" t="n">
         <v>33</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>24</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" t="n">
         <v>33</v>
-      </c>
-      <c r="K21" t="n">
-        <v>17</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2220,10 +2220,10 @@
         <v>24</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
@@ -2299,10 +2299,10 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
+        <v>17</v>
+      </c>
+      <c r="K23" t="n">
         <v>33</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2378,10 +2378,10 @@
         <v>24</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
@@ -2457,10 +2457,10 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" t="n">
         <v>33</v>
-      </c>
-      <c r="K25" t="n">
-        <v>17</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2536,10 +2536,10 @@
         <v>24</v>
       </c>
       <c r="J26" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
@@ -2615,10 +2615,10 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" t="n">
         <v>33</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2773,10 +2773,10 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
         <v>33</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>24</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" t="n">
         <v>33</v>
-      </c>
-      <c r="K31" t="n">
-        <v>17</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3010,10 +3010,10 @@
         <v>24</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K32" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" t="n">
         <v>33</v>
-      </c>
-      <c r="K33" t="n">
-        <v>17</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3168,10 +3168,10 @@
         <v>24</v>
       </c>
       <c r="J34" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
@@ -3247,10 +3247,10 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" t="n">
         <v>33</v>
-      </c>
-      <c r="K35" t="n">
-        <v>17</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>24</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
@@ -3405,10 +3405,10 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
         <v>33</v>
-      </c>
-      <c r="K37" t="n">
-        <v>17</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>24</v>
       </c>
       <c r="J38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
@@ -3563,10 +3563,10 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
+        <v>17</v>
+      </c>
+      <c r="K39" t="n">
         <v>33</v>
-      </c>
-      <c r="K39" t="n">
-        <v>17</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3642,10 +3642,10 @@
         <v>24</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
@@ -3721,10 +3721,10 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
+        <v>17</v>
+      </c>
+      <c r="K41" t="n">
         <v>33</v>
-      </c>
-      <c r="K41" t="n">
-        <v>17</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>24</v>
       </c>
       <c r="J42" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K42" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
@@ -3879,10 +3879,10 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" t="n">
         <v>33</v>
-      </c>
-      <c r="K43" t="n">
-        <v>17</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3958,10 +3958,10 @@
         <v>24</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
@@ -4037,10 +4037,10 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
+        <v>17</v>
+      </c>
+      <c r="K45" t="n">
         <v>33</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4116,10 +4116,10 @@
         <v>24</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
+        <v>17</v>
+      </c>
+      <c r="K47" t="n">
         <v>33</v>
-      </c>
-      <c r="K47" t="n">
-        <v>17</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>24</v>
       </c>
       <c r="J48" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
@@ -4353,10 +4353,10 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
+        <v>17</v>
+      </c>
+      <c r="K49" t="n">
         <v>33</v>
-      </c>
-      <c r="K49" t="n">
-        <v>17</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4432,10 +4432,10 @@
         <v>24</v>
       </c>
       <c r="J50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>33</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
@@ -4511,10 +4511,10 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
+        <v>17</v>
+      </c>
+      <c r="K51" t="n">
         <v>33</v>
-      </c>
-      <c r="K51" t="n">
-        <v>17</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4590,10 +4590,10 @@
         <v>24</v>
       </c>
       <c r="J52" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
@@ -4669,10 +4669,10 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
+        <v>17</v>
+      </c>
+      <c r="K53" t="n">
         <v>30</v>
-      </c>
-      <c r="K53" t="n">
-        <v>17</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4748,10 +4748,10 @@
         <v>24</v>
       </c>
       <c r="J54" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
@@ -4827,10 +4827,10 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" t="n">
         <v>30</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4906,10 +4906,10 @@
         <v>24</v>
       </c>
       <c r="J56" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K56" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>17</v>
       </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
@@ -4985,10 +4985,10 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>22</v>
+      </c>
+      <c r="K57" t="n">
         <v>24</v>
-      </c>
-      <c r="K57" t="n">
-        <v>22</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5064,10 +5064,10 @@
         <v>24</v>
       </c>
       <c r="J58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K58" s="5" t="n">
         <v>26</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>22</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
@@ -5143,10 +5143,10 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
+        <v>16</v>
+      </c>
+      <c r="K59" t="n">
         <v>26</v>
-      </c>
-      <c r="K59" t="n">
-        <v>16</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>24</v>
       </c>
       <c r="J60" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K60" s="5" t="n">
         <v>23</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>16</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
@@ -5301,10 +5301,10 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
+        <v>16</v>
+      </c>
+      <c r="K61" t="n">
         <v>29</v>
-      </c>
-      <c r="K61" t="n">
-        <v>16</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -5380,10 +5380,10 @@
         <v>24</v>
       </c>
       <c r="J62" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K62" s="5" t="n">
         <v>29</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>16</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
+        <v>16</v>
+      </c>
+      <c r="K63" t="n">
         <v>29</v>
-      </c>
-      <c r="K63" t="n">
-        <v>16</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -5538,11 +5538,11 @@
         <v>24</v>
       </c>
       <c r="J64" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K64" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
@@ -5583,6 +5583,85 @@
         <v>0</v>
       </c>
       <c r="Y64" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>839</v>
+      </c>
+      <c r="C65" t="n">
+        <v>534</v>
+      </c>
+      <c r="D65" t="n">
+        <v>471</v>
+      </c>
+      <c r="E65" t="n">
+        <v>356</v>
+      </c>
+      <c r="F65" t="n">
+        <v>211</v>
+      </c>
+      <c r="G65" t="n">
+        <v>101</v>
+      </c>
+      <c r="H65" t="n">
+        <v>46</v>
+      </c>
+      <c r="I65" t="n">
+        <v>24</v>
+      </c>
+      <c r="J65" t="n">
+        <v>21</v>
+      </c>
+      <c r="K65" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5624,7 +5703,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-08)</t>
+          <t>Lager (2026-09-09)</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5724,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3">
@@ -6371,7 +6450,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6391,7 +6470,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6411,7 +6490,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6431,7 +6510,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6451,7 +6530,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6471,7 +6550,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -6491,7 +6570,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6511,7 +6590,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6531,7 +6610,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6551,7 +6630,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -6571,7 +6650,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6591,7 +6670,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -6611,7 +6690,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6631,7 +6710,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -9645,7 +9724,7 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203">
@@ -14285,7 +14364,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="435">
@@ -15285,7 +15364,7 @@
         </is>
       </c>
       <c r="D484" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="485">
@@ -23365,7 +23444,7 @@
         </is>
       </c>
       <c r="D888" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="889">
@@ -23545,7 +23624,7 @@
         </is>
       </c>
       <c r="D897" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="898">
@@ -25185,7 +25264,7 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>217</v>
+        <v>177</v>
       </c>
     </row>
     <row r="980">
@@ -25205,7 +25284,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="981">
@@ -25225,7 +25304,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="982">
@@ -27545,7 +27624,7 @@
         </is>
       </c>
       <c r="D1097" s="6" t="n">
-        <v>413</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1098">

--- a/data/ahlsell_led_panel_inventory.xlsx
+++ b/data/ahlsell_led_panel_inventory.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y65"/>
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,87 +528,87 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
+          <t>Exaktor</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
           <t>Esylux</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Ledvance</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Exaktor</t>
-        </is>
-      </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Ensto</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Siteco</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>THORN</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>ANETA LIGHTING</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Siteco</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Legrand</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Westal</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Airam</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Nokalux</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Norwesco</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Legrand</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>THORN</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>ZG Lighting</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Bergdahls</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Easyform</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Westal</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Black Box</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Nokalux</t>
-        </is>
-      </c>
-      <c r="V1" s="3" t="inlineStr">
-        <is>
-          <t>Airam</t>
-        </is>
-      </c>
-      <c r="W1" s="3" t="inlineStr">
-        <is>
-          <t>Ensto</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Philips</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Bergdahls</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
         <v>52</v>
       </c>
       <c r="I2" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J2" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0</v>
@@ -719,13 +719,13 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J3" t="n">
         <v>25</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>33</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         <v>52</v>
       </c>
       <c r="I4" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>52</v>
       </c>
       <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="n">
         <v>24</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>33</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>52</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>14</v>
       </c>
       <c r="I7" t="n">
+        <v>33</v>
+      </c>
+      <c r="J7" t="n">
         <v>24</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>33</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
@@ -1190,13 +1190,13 @@
         <v>52</v>
       </c>
       <c r="I9" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1269,13 +1269,13 @@
         <v>52</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
@@ -1348,13 +1348,13 @@
         <v>52</v>
       </c>
       <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
         <v>24</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1427,13 +1427,13 @@
         <v>52</v>
       </c>
       <c r="I12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
@@ -1506,13 +1506,13 @@
         <v>52</v>
       </c>
       <c r="I13" t="n">
+        <v>33</v>
+      </c>
+      <c r="J13" t="n">
         <v>24</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
+        <v>33</v>
+      </c>
+      <c r="J15" t="n">
         <v>24</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>33</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         <v>52</v>
       </c>
       <c r="I16" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>52</v>
       </c>
       <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="n">
         <v>24</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>17</v>
-      </c>
-      <c r="K17" t="n">
-        <v>33</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         <v>52</v>
       </c>
       <c r="I18" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="K18" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>50</v>
       </c>
       <c r="I19" t="n">
+        <v>33</v>
+      </c>
+      <c r="J19" t="n">
         <v>24</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>17</v>
-      </c>
-      <c r="K19" t="n">
-        <v>33</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2059,13 +2059,13 @@
         <v>50</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0</v>
@@ -2138,13 +2138,13 @@
         <v>14</v>
       </c>
       <c r="I21" t="n">
+        <v>33</v>
+      </c>
+      <c r="J21" t="n">
         <v>24</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>17</v>
-      </c>
-      <c r="K21" t="n">
-        <v>33</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         <v>50</v>
       </c>
       <c r="I22" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J22" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="K22" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>50</v>
       </c>
       <c r="I23" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" t="n">
         <v>24</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>17</v>
-      </c>
-      <c r="K23" t="n">
-        <v>33</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2375,13 +2375,13 @@
         <v>48</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
@@ -2454,13 +2454,13 @@
         <v>48</v>
       </c>
       <c r="I25" t="n">
+        <v>33</v>
+      </c>
+      <c r="J25" t="n">
         <v>24</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>17</v>
-      </c>
-      <c r="K25" t="n">
-        <v>33</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         <v>48</v>
       </c>
       <c r="I26" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0</v>
@@ -2612,13 +2612,13 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
+        <v>33</v>
+      </c>
+      <c r="J27" t="n">
         <v>24</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>17</v>
-      </c>
-      <c r="K27" t="n">
-        <v>33</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J29" t="n">
         <v>24</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>33</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2849,13 +2849,13 @@
         <v>48</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="K30" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0</v>
@@ -2928,13 +2928,13 @@
         <v>48</v>
       </c>
       <c r="I31" t="n">
+        <v>33</v>
+      </c>
+      <c r="J31" t="n">
         <v>24</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>17</v>
-      </c>
-      <c r="K31" t="n">
-        <v>33</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3007,13 +3007,13 @@
         <v>48</v>
       </c>
       <c r="I32" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="K32" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>48</v>
       </c>
       <c r="I33" t="n">
+        <v>33</v>
+      </c>
+      <c r="J33" t="n">
         <v>24</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>17</v>
-      </c>
-      <c r="K33" t="n">
-        <v>33</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3165,13 +3165,13 @@
         <v>48</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="K34" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
@@ -3244,13 +3244,13 @@
         <v>48</v>
       </c>
       <c r="I35" t="n">
+        <v>33</v>
+      </c>
+      <c r="J35" t="n">
         <v>24</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>33</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3323,13 +3323,13 @@
         <v>48</v>
       </c>
       <c r="I36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J36" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="K36" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0</v>
@@ -3402,13 +3402,13 @@
         <v>48</v>
       </c>
       <c r="I37" t="n">
+        <v>33</v>
+      </c>
+      <c r="J37" t="n">
         <v>24</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>33</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3481,13 +3481,13 @@
         <v>48</v>
       </c>
       <c r="I38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="K38" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
@@ -3560,13 +3560,13 @@
         <v>48</v>
       </c>
       <c r="I39" t="n">
+        <v>33</v>
+      </c>
+      <c r="J39" t="n">
         <v>24</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>17</v>
-      </c>
-      <c r="K39" t="n">
-        <v>33</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>48</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="K40" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
@@ -3718,13 +3718,13 @@
         <v>48</v>
       </c>
       <c r="I41" t="n">
+        <v>33</v>
+      </c>
+      <c r="J41" t="n">
         <v>24</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>17</v>
-      </c>
-      <c r="K41" t="n">
-        <v>33</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3797,13 +3797,13 @@
         <v>46</v>
       </c>
       <c r="I42" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J42" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="K42" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
@@ -3876,13 +3876,13 @@
         <v>48</v>
       </c>
       <c r="I43" t="n">
+        <v>33</v>
+      </c>
+      <c r="J43" t="n">
         <v>24</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>33</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3955,13 +3955,13 @@
         <v>48</v>
       </c>
       <c r="I44" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J44" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
@@ -4034,13 +4034,13 @@
         <v>48</v>
       </c>
       <c r="I45" t="n">
+        <v>33</v>
+      </c>
+      <c r="J45" t="n">
         <v>24</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>17</v>
-      </c>
-      <c r="K45" t="n">
-        <v>33</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4113,13 +4113,13 @@
         <v>48</v>
       </c>
       <c r="I46" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J46" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="K46" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
@@ -4192,13 +4192,13 @@
         <v>48</v>
       </c>
       <c r="I47" t="n">
+        <v>33</v>
+      </c>
+      <c r="J47" t="n">
         <v>24</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>17</v>
-      </c>
-      <c r="K47" t="n">
-        <v>33</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4271,13 +4271,13 @@
         <v>48</v>
       </c>
       <c r="I48" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="K48" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
@@ -4350,13 +4350,13 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>33</v>
+      </c>
+      <c r="J49" t="n">
         <v>24</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>17</v>
-      </c>
-      <c r="K49" t="n">
-        <v>33</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4429,13 +4429,13 @@
         <v>48</v>
       </c>
       <c r="I50" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J50" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="K50" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>33</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
@@ -4508,13 +4508,13 @@
         <v>48</v>
       </c>
       <c r="I51" t="n">
+        <v>33</v>
+      </c>
+      <c r="J51" t="n">
         <v>24</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>33</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4587,13 +4587,13 @@
         <v>48</v>
       </c>
       <c r="I52" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J52" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="K52" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
@@ -4666,13 +4666,13 @@
         <v>48</v>
       </c>
       <c r="I53" t="n">
+        <v>30</v>
+      </c>
+      <c r="J53" t="n">
         <v>24</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>17</v>
-      </c>
-      <c r="K53" t="n">
-        <v>30</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4745,13 +4745,13 @@
         <v>48</v>
       </c>
       <c r="I54" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J54" s="5" t="n">
+      <c r="K54" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
@@ -4824,13 +4824,13 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
+        <v>30</v>
+      </c>
+      <c r="J55" t="n">
         <v>24</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>17</v>
-      </c>
-      <c r="K55" t="n">
-        <v>30</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>48</v>
       </c>
       <c r="I56" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J56" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J56" s="5" t="n">
+      <c r="K56" s="5" t="n">
         <v>17</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
@@ -4985,10 +4985,10 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
+        <v>24</v>
+      </c>
+      <c r="K57" t="n">
         <v>22</v>
-      </c>
-      <c r="K57" t="n">
-        <v>24</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5061,13 +5061,13 @@
         <v>47</v>
       </c>
       <c r="I58" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J58" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J58" s="5" t="n">
+      <c r="K58" s="5" t="n">
         <v>22</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>26</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
@@ -5140,13 +5140,13 @@
         <v>47</v>
       </c>
       <c r="I59" t="n">
+        <v>26</v>
+      </c>
+      <c r="J59" t="n">
         <v>24</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>16</v>
-      </c>
-      <c r="K59" t="n">
-        <v>26</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>46</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J60" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J60" s="5" t="n">
+      <c r="K60" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>23</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
@@ -5298,13 +5298,13 @@
         <v>43</v>
       </c>
       <c r="I61" t="n">
+        <v>29</v>
+      </c>
+      <c r="J61" t="n">
         <v>24</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>16</v>
-      </c>
-      <c r="K61" t="n">
-        <v>29</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -5377,13 +5377,13 @@
         <v>43</v>
       </c>
       <c r="I62" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="J62" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J62" s="5" t="n">
+      <c r="K62" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>29</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
@@ -5456,13 +5456,13 @@
         <v>43</v>
       </c>
       <c r="I63" t="n">
+        <v>29</v>
+      </c>
+      <c r="J63" t="n">
         <v>24</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>16</v>
-      </c>
-      <c r="K63" t="n">
-        <v>29</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -5535,13 +5535,13 @@
         <v>42</v>
       </c>
       <c r="I64" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="J64" s="5" t="n">
+      <c r="K64" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>20</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
@@ -5614,14 +5614,14 @@
         <v>46</v>
       </c>
       <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
         <v>24</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>21</v>
       </c>
-      <c r="K65" t="n">
-        <v>20</v>
-      </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
@@ -5662,6 +5662,85 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>815</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>521</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5676,7 +5755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1098"/>
+  <dimension ref="A1:D1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5703,7 +5782,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Lager (2026-09-09)</t>
+          <t>Lager (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5803,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3">
@@ -6450,7 +6529,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>7018181</t>
+          <t>7018180</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6470,7 +6549,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>7018183</t>
+          <t>7018182</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6490,7 +6569,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>7018185</t>
+          <t>7018184</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6510,7 +6589,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>7018187</t>
+          <t>7018186</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6530,7 +6609,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>7018189</t>
+          <t>7018188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6550,7 +6629,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>7018191</t>
+          <t>7018190</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -6570,7 +6649,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>7018180</t>
+          <t>7018192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6590,7 +6669,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>7018182</t>
+          <t>7018194</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6610,7 +6689,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>7018184</t>
+          <t>7018181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6630,7 +6709,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>7018186</t>
+          <t>7018183</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -6650,7 +6729,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>7018188</t>
+          <t>7018185</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6670,7 +6749,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7018190</t>
+          <t>7018187</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -6690,7 +6769,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>7018192</t>
+          <t>7018189</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6710,7 +6789,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>7018194</t>
+          <t>7018191</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -9724,7 +9803,7 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203">
@@ -13904,7 +13983,7 @@
         </is>
       </c>
       <c r="D411" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="412">
@@ -14364,7 +14443,7 @@
         </is>
       </c>
       <c r="D434" s="4" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="435">
@@ -14444,7 +14523,7 @@
         </is>
       </c>
       <c r="D438" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="439">
@@ -18244,7 +18323,7 @@
         </is>
       </c>
       <c r="D628" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="629">
@@ -24024,7 +24103,7 @@
         </is>
       </c>
       <c r="D917" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="918">
@@ -25264,7 +25343,7 @@
         </is>
       </c>
       <c r="D979" s="6" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="980">
@@ -25284,7 +25363,7 @@
         </is>
       </c>
       <c r="D980" s="4" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="981">
@@ -25304,7 +25383,7 @@
         </is>
       </c>
       <c r="D981" s="6" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="982">
@@ -25324,18 +25403,18 @@
         </is>
       </c>
       <c r="D982" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" s="6" t="inlineStr">
         <is>
-          <t>7021628</t>
+          <t>7021996</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -25350,12 +25429,12 @@
     <row r="984">
       <c r="A984" s="4" t="inlineStr">
         <is>
-          <t>7021629</t>
+          <t>7021997</t>
         </is>
       </c>
       <c r="B984" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US Sens infälld med grundljus</t>
+          <t>Interiörarmatur US infälld</t>
         </is>
       </c>
       <c r="C984" s="5" t="inlineStr">
@@ -25370,7 +25449,7 @@
     <row r="985">
       <c r="A985" s="6" t="inlineStr">
         <is>
-          <t>7021996</t>
+          <t>7021617</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -25390,7 +25469,7 @@
     <row r="986">
       <c r="A986" s="4" t="inlineStr">
         <is>
-          <t>7021997</t>
+          <t>7021618</t>
         </is>
       </c>
       <c r="B986" s="5" t="inlineStr">
@@ -25410,7 +25489,7 @@
     <row r="987">
       <c r="A987" s="6" t="inlineStr">
         <is>
-          <t>7021617</t>
+          <t>7022019</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -25430,7 +25509,7 @@
     <row r="988">
       <c r="A988" s="4" t="inlineStr">
         <is>
-          <t>7021618</t>
+          <t>7022021</t>
         </is>
       </c>
       <c r="B988" s="5" t="inlineStr">
@@ -25450,17 +25529,17 @@
     <row r="989">
       <c r="A989" s="6" t="inlineStr">
         <is>
-          <t>7022019</t>
+          <t>7015332</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D989" s="6" t="n">
@@ -25470,17 +25549,17 @@
     <row r="990">
       <c r="A990" s="4" t="inlineStr">
         <is>
-          <t>7022021</t>
+          <t>7018758</t>
         </is>
       </c>
       <c r="B990" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur US infälld</t>
+          <t>Infälld interiörarmatur WLP</t>
         </is>
       </c>
       <c r="C990" s="5" t="inlineStr">
         <is>
-          <t>Tupex</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D990" s="4" t="n">
@@ -25490,7 +25569,7 @@
     <row r="991">
       <c r="A991" s="6" t="inlineStr">
         <is>
-          <t>7015332</t>
+          <t>7015333</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -25510,7 +25589,7 @@
     <row r="992">
       <c r="A992" s="4" t="inlineStr">
         <is>
-          <t>7018758</t>
+          <t>7016779</t>
         </is>
       </c>
       <c r="B992" s="5" t="inlineStr">
@@ -25530,12 +25609,12 @@
     <row r="993">
       <c r="A993" s="6" t="inlineStr">
         <is>
-          <t>7015333</t>
+          <t>7018294</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -25550,12 +25629,12 @@
     <row r="994">
       <c r="A994" s="4" t="inlineStr">
         <is>
-          <t>7016779</t>
+          <t>7021000</t>
         </is>
       </c>
       <c r="B994" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP</t>
+          <t>Infälld interiörarmatur WLP tunable</t>
         </is>
       </c>
       <c r="C994" s="5" t="inlineStr">
@@ -25570,12 +25649,12 @@
     <row r="995">
       <c r="A995" s="6" t="inlineStr">
         <is>
-          <t>7018294</t>
+          <t>7020998</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -25590,12 +25669,12 @@
     <row r="996">
       <c r="A996" s="4" t="inlineStr">
         <is>
-          <t>7021000</t>
+          <t>7020999</t>
         </is>
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP tunable</t>
+          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
@@ -25610,7 +25689,7 @@
     <row r="997">
       <c r="A997" s="6" t="inlineStr">
         <is>
-          <t>7020998</t>
+          <t>7024828</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -25630,7 +25709,7 @@
     <row r="998">
       <c r="A998" s="4" t="inlineStr">
         <is>
-          <t>7020999</t>
+          <t>7024829</t>
         </is>
       </c>
       <c r="B998" s="5" t="inlineStr">
@@ -25650,12 +25729,12 @@
     <row r="999">
       <c r="A999" s="6" t="inlineStr">
         <is>
-          <t>7024828</t>
+          <t>7018759</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -25670,12 +25749,12 @@
     <row r="1000">
       <c r="A1000" s="4" t="inlineStr">
         <is>
-          <t>7024829</t>
+          <t>7018764</t>
         </is>
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP, ActiveAhead</t>
+          <t>Infälld interiörarmatur WLP-D IP65</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
@@ -25690,12 +25769,12 @@
     <row r="1001">
       <c r="A1001" s="6" t="inlineStr">
         <is>
-          <t>7018759</t>
+          <t>7025805</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -25710,12 +25789,12 @@
     <row r="1002">
       <c r="A1002" s="4" t="inlineStr">
         <is>
-          <t>7018764</t>
+          <t>7025806</t>
         </is>
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur WLP-D IP65</t>
+          <t>Interiörarmatur Lino infälld L-stycke</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
@@ -25730,7 +25809,7 @@
     <row r="1003">
       <c r="A1003" s="6" t="inlineStr">
         <is>
-          <t>7025805</t>
+          <t>7025817</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -25750,7 +25829,7 @@
     <row r="1004">
       <c r="A1004" s="4" t="inlineStr">
         <is>
-          <t>7025806</t>
+          <t>7025818</t>
         </is>
       </c>
       <c r="B1004" s="5" t="inlineStr">
@@ -25770,12 +25849,12 @@
     <row r="1005">
       <c r="A1005" s="6" t="inlineStr">
         <is>
-          <t>7025817</t>
+          <t>7025809</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -25790,12 +25869,12 @@
     <row r="1006">
       <c r="A1006" s="4" t="inlineStr">
         <is>
-          <t>7025818</t>
+          <t>7025810</t>
         </is>
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld L-stycke</t>
+          <t>Interiörarmatur Lino infälld X-stycke</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
@@ -25810,7 +25889,7 @@
     <row r="1007">
       <c r="A1007" s="6" t="inlineStr">
         <is>
-          <t>7025809</t>
+          <t>7025821</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -25830,7 +25909,7 @@
     <row r="1008">
       <c r="A1008" s="4" t="inlineStr">
         <is>
-          <t>7025810</t>
+          <t>7025822</t>
         </is>
       </c>
       <c r="B1008" s="5" t="inlineStr">
@@ -25850,12 +25929,12 @@
     <row r="1009">
       <c r="A1009" s="6" t="inlineStr">
         <is>
-          <t>7025821</t>
+          <t>7025689</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -25870,12 +25949,12 @@
     <row r="1010">
       <c r="A1010" s="4" t="inlineStr">
         <is>
-          <t>7025822</t>
+          <t>7025690</t>
         </is>
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld X-stycke</t>
+          <t>Interiörarmatur Lino infälld start/slut sektion</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
@@ -25890,7 +25969,7 @@
     <row r="1011">
       <c r="A1011" s="6" t="inlineStr">
         <is>
-          <t>7025689</t>
+          <t>7025691</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -25910,7 +25989,7 @@
     <row r="1012">
       <c r="A1012" s="4" t="inlineStr">
         <is>
-          <t>7025690</t>
+          <t>7025692</t>
         </is>
       </c>
       <c r="B1012" s="5" t="inlineStr">
@@ -25930,7 +26009,7 @@
     <row r="1013">
       <c r="A1013" s="6" t="inlineStr">
         <is>
-          <t>7025691</t>
+          <t>7025693</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -25950,7 +26029,7 @@
     <row r="1014">
       <c r="A1014" s="4" t="inlineStr">
         <is>
-          <t>7025692</t>
+          <t>7025694</t>
         </is>
       </c>
       <c r="B1014" s="5" t="inlineStr">
@@ -25970,7 +26049,7 @@
     <row r="1015">
       <c r="A1015" s="6" t="inlineStr">
         <is>
-          <t>7025693</t>
+          <t>7025695</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -25990,7 +26069,7 @@
     <row r="1016">
       <c r="A1016" s="4" t="inlineStr">
         <is>
-          <t>7025694</t>
+          <t>7025696</t>
         </is>
       </c>
       <c r="B1016" s="5" t="inlineStr">
@@ -26010,7 +26089,7 @@
     <row r="1017">
       <c r="A1017" s="6" t="inlineStr">
         <is>
-          <t>7025695</t>
+          <t>7025697</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -26030,7 +26109,7 @@
     <row r="1018">
       <c r="A1018" s="4" t="inlineStr">
         <is>
-          <t>7025696</t>
+          <t>7025698</t>
         </is>
       </c>
       <c r="B1018" s="5" t="inlineStr">
@@ -26050,7 +26129,7 @@
     <row r="1019">
       <c r="A1019" s="6" t="inlineStr">
         <is>
-          <t>7025697</t>
+          <t>7025699</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -26070,7 +26149,7 @@
     <row r="1020">
       <c r="A1020" s="4" t="inlineStr">
         <is>
-          <t>7025698</t>
+          <t>7025700</t>
         </is>
       </c>
       <c r="B1020" s="5" t="inlineStr">
@@ -26090,7 +26169,7 @@
     <row r="1021">
       <c r="A1021" s="6" t="inlineStr">
         <is>
-          <t>7025699</t>
+          <t>7025701</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -26110,7 +26189,7 @@
     <row r="1022">
       <c r="A1022" s="4" t="inlineStr">
         <is>
-          <t>7025700</t>
+          <t>7025702</t>
         </is>
       </c>
       <c r="B1022" s="5" t="inlineStr">
@@ -26130,7 +26209,7 @@
     <row r="1023">
       <c r="A1023" s="6" t="inlineStr">
         <is>
-          <t>7025701</t>
+          <t>7025703</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -26150,7 +26229,7 @@
     <row r="1024">
       <c r="A1024" s="4" t="inlineStr">
         <is>
-          <t>7025702</t>
+          <t>7025704</t>
         </is>
       </c>
       <c r="B1024" s="5" t="inlineStr">
@@ -26170,7 +26249,7 @@
     <row r="1025">
       <c r="A1025" s="6" t="inlineStr">
         <is>
-          <t>7025703</t>
+          <t>7025705</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -26190,7 +26269,7 @@
     <row r="1026">
       <c r="A1026" s="4" t="inlineStr">
         <is>
-          <t>7025704</t>
+          <t>7025706</t>
         </is>
       </c>
       <c r="B1026" s="5" t="inlineStr">
@@ -26210,7 +26289,7 @@
     <row r="1027">
       <c r="A1027" s="6" t="inlineStr">
         <is>
-          <t>7025705</t>
+          <t>7025725</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -26230,7 +26309,7 @@
     <row r="1028">
       <c r="A1028" s="4" t="inlineStr">
         <is>
-          <t>7025706</t>
+          <t>7025726</t>
         </is>
       </c>
       <c r="B1028" s="5" t="inlineStr">
@@ -26250,7 +26329,7 @@
     <row r="1029">
       <c r="A1029" s="6" t="inlineStr">
         <is>
-          <t>7025725</t>
+          <t>7025727</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -26270,7 +26349,7 @@
     <row r="1030">
       <c r="A1030" s="4" t="inlineStr">
         <is>
-          <t>7025726</t>
+          <t>7025728</t>
         </is>
       </c>
       <c r="B1030" s="5" t="inlineStr">
@@ -26290,7 +26369,7 @@
     <row r="1031">
       <c r="A1031" s="6" t="inlineStr">
         <is>
-          <t>7025727</t>
+          <t>7025729</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -26310,7 +26389,7 @@
     <row r="1032">
       <c r="A1032" s="4" t="inlineStr">
         <is>
-          <t>7025728</t>
+          <t>7025730</t>
         </is>
       </c>
       <c r="B1032" s="5" t="inlineStr">
@@ -26330,7 +26409,7 @@
     <row r="1033">
       <c r="A1033" s="6" t="inlineStr">
         <is>
-          <t>7025729</t>
+          <t>7025731</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -26350,7 +26429,7 @@
     <row r="1034">
       <c r="A1034" s="4" t="inlineStr">
         <is>
-          <t>7025730</t>
+          <t>7025732</t>
         </is>
       </c>
       <c r="B1034" s="5" t="inlineStr">
@@ -26370,7 +26449,7 @@
     <row r="1035">
       <c r="A1035" s="6" t="inlineStr">
         <is>
-          <t>7025731</t>
+          <t>7025733</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -26390,7 +26469,7 @@
     <row r="1036">
       <c r="A1036" s="4" t="inlineStr">
         <is>
-          <t>7025732</t>
+          <t>7025734</t>
         </is>
       </c>
       <c r="B1036" s="5" t="inlineStr">
@@ -26410,7 +26489,7 @@
     <row r="1037">
       <c r="A1037" s="6" t="inlineStr">
         <is>
-          <t>7025733</t>
+          <t>7025735E</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -26430,7 +26509,7 @@
     <row r="1038">
       <c r="A1038" s="4" t="inlineStr">
         <is>
-          <t>7025734</t>
+          <t>7025736E</t>
         </is>
       </c>
       <c r="B1038" s="5" t="inlineStr">
@@ -26450,7 +26529,7 @@
     <row r="1039">
       <c r="A1039" s="6" t="inlineStr">
         <is>
-          <t>7025735E</t>
+          <t>7025737</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
@@ -26470,7 +26549,7 @@
     <row r="1040">
       <c r="A1040" s="4" t="inlineStr">
         <is>
-          <t>7025736E</t>
+          <t>7025738</t>
         </is>
       </c>
       <c r="B1040" s="5" t="inlineStr">
@@ -26490,7 +26569,7 @@
     <row r="1041">
       <c r="A1041" s="6" t="inlineStr">
         <is>
-          <t>7025737</t>
+          <t>7025739</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
@@ -26510,7 +26589,7 @@
     <row r="1042">
       <c r="A1042" s="4" t="inlineStr">
         <is>
-          <t>7025738</t>
+          <t>7025740</t>
         </is>
       </c>
       <c r="B1042" s="5" t="inlineStr">
@@ -26530,7 +26609,7 @@
     <row r="1043">
       <c r="A1043" s="6" t="inlineStr">
         <is>
-          <t>7025739</t>
+          <t>7025741</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
@@ -26550,7 +26629,7 @@
     <row r="1044">
       <c r="A1044" s="4" t="inlineStr">
         <is>
-          <t>7025740</t>
+          <t>7025742</t>
         </is>
       </c>
       <c r="B1044" s="5" t="inlineStr">
@@ -26570,12 +26649,12 @@
     <row r="1045">
       <c r="A1045" s="6" t="inlineStr">
         <is>
-          <t>7025741</t>
+          <t>7510324</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -26590,12 +26669,12 @@
     <row r="1046">
       <c r="A1046" s="4" t="inlineStr">
         <is>
-          <t>7025742</t>
+          <t>7510325</t>
         </is>
       </c>
       <c r="B1046" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Lino infälld start/slut sektion</t>
+          <t>Interiörarmatur Mira 1x28 infälld</t>
         </is>
       </c>
       <c r="C1046" s="5" t="inlineStr">
@@ -26610,7 +26689,7 @@
     <row r="1047">
       <c r="A1047" s="6" t="inlineStr">
         <is>
-          <t>7510324</t>
+          <t>7510326</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
@@ -26630,7 +26709,7 @@
     <row r="1048">
       <c r="A1048" s="4" t="inlineStr">
         <is>
-          <t>7510325</t>
+          <t>7510327</t>
         </is>
       </c>
       <c r="B1048" s="5" t="inlineStr">
@@ -26650,7 +26729,7 @@
     <row r="1049">
       <c r="A1049" s="6" t="inlineStr">
         <is>
-          <t>7510326</t>
+          <t>7510328</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
@@ -26670,7 +26749,7 @@
     <row r="1050">
       <c r="A1050" s="4" t="inlineStr">
         <is>
-          <t>7510327</t>
+          <t>7510329</t>
         </is>
       </c>
       <c r="B1050" s="5" t="inlineStr">
@@ -26690,7 +26769,7 @@
     <row r="1051">
       <c r="A1051" s="6" t="inlineStr">
         <is>
-          <t>7510328</t>
+          <t>7510344</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -26710,7 +26789,7 @@
     <row r="1052">
       <c r="A1052" s="4" t="inlineStr">
         <is>
-          <t>7510329</t>
+          <t>7510345</t>
         </is>
       </c>
       <c r="B1052" s="5" t="inlineStr">
@@ -26730,7 +26809,7 @@
     <row r="1053">
       <c r="A1053" s="6" t="inlineStr">
         <is>
-          <t>7510344</t>
+          <t>7510346</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
@@ -26750,7 +26829,7 @@
     <row r="1054">
       <c r="A1054" s="4" t="inlineStr">
         <is>
-          <t>7510345</t>
+          <t>7510347</t>
         </is>
       </c>
       <c r="B1054" s="5" t="inlineStr">
@@ -26770,7 +26849,7 @@
     <row r="1055">
       <c r="A1055" s="6" t="inlineStr">
         <is>
-          <t>7510346</t>
+          <t>7510348</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
@@ -26790,7 +26869,7 @@
     <row r="1056">
       <c r="A1056" s="4" t="inlineStr">
         <is>
-          <t>7510347</t>
+          <t>7510349</t>
         </is>
       </c>
       <c r="B1056" s="5" t="inlineStr">
@@ -26810,12 +26889,12 @@
     <row r="1057">
       <c r="A1057" s="6" t="inlineStr">
         <is>
-          <t>7510348</t>
+          <t>7021294</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -26830,12 +26909,12 @@
     <row r="1058">
       <c r="A1058" s="4" t="inlineStr">
         <is>
-          <t>7510349</t>
+          <t>7021295</t>
         </is>
       </c>
       <c r="B1058" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Mira 1x28 infälld</t>
+          <t>Interiörarmatur WLP Backlit</t>
         </is>
       </c>
       <c r="C1058" s="5" t="inlineStr">
@@ -26850,7 +26929,7 @@
     <row r="1059">
       <c r="A1059" s="6" t="inlineStr">
         <is>
-          <t>7021294</t>
+          <t>7024767</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
@@ -26870,7 +26949,7 @@
     <row r="1060">
       <c r="A1060" s="4" t="inlineStr">
         <is>
-          <t>7021295</t>
+          <t>7024768</t>
         </is>
       </c>
       <c r="B1060" s="5" t="inlineStr">
@@ -26890,12 +26969,12 @@
     <row r="1061">
       <c r="A1061" s="6" t="inlineStr">
         <is>
-          <t>7024767</t>
+          <t>7028545</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit PIR</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -26910,12 +26989,12 @@
     <row r="1062">
       <c r="A1062" s="4" t="inlineStr">
         <is>
-          <t>7024768</t>
+          <t>7024616</t>
         </is>
       </c>
       <c r="B1062" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1062" s="5" t="inlineStr">
@@ -26930,12 +27009,12 @@
     <row r="1063">
       <c r="A1063" s="6" t="inlineStr">
         <is>
-          <t>7028545</t>
+          <t>7024617</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit PIR</t>
+          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -26950,7 +27029,7 @@
     <row r="1064">
       <c r="A1064" s="4" t="inlineStr">
         <is>
-          <t>7024616</t>
+          <t>7024816</t>
         </is>
       </c>
       <c r="B1064" s="5" t="inlineStr">
@@ -26970,7 +27049,7 @@
     <row r="1065">
       <c r="A1065" s="6" t="inlineStr">
         <is>
-          <t>7024617</t>
+          <t>7024817</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
@@ -26990,12 +27069,12 @@
     <row r="1066">
       <c r="A1066" s="4" t="inlineStr">
         <is>
-          <t>7024816</t>
+          <t>7026165</t>
         </is>
       </c>
       <c r="B1066" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1066" s="5" t="inlineStr">
@@ -27010,12 +27089,12 @@
     <row r="1067">
       <c r="A1067" s="6" t="inlineStr">
         <is>
-          <t>7024817</t>
+          <t>7026166</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Backlit, ActiveAhead</t>
+          <t>Interiörarmatur WLP Cleanroom</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -27030,12 +27109,12 @@
     <row r="1068">
       <c r="A1068" s="4" t="inlineStr">
         <is>
-          <t>7026165</t>
+          <t>7027313</t>
         </is>
       </c>
       <c r="B1068" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Interiörarmatur WLP-B</t>
         </is>
       </c>
       <c r="C1068" s="5" t="inlineStr">
@@ -27050,12 +27129,12 @@
     <row r="1069">
       <c r="A1069" s="6" t="inlineStr">
         <is>
-          <t>7026166</t>
+          <t>7510127</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP Cleanroom</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -27070,12 +27149,12 @@
     <row r="1070">
       <c r="A1070" s="4" t="inlineStr">
         <is>
-          <t>7027313</t>
+          <t>7510128</t>
         </is>
       </c>
       <c r="B1070" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur WLP-B</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1070" s="5" t="inlineStr">
@@ -27090,12 +27169,12 @@
     <row r="1071">
       <c r="A1071" s="6" t="inlineStr">
         <is>
-          <t>7510073</t>
+          <t>7510129</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -27110,12 +27189,12 @@
     <row r="1072">
       <c r="A1072" s="4" t="inlineStr">
         <is>
-          <t>7510075</t>
+          <t>7510130</t>
         </is>
       </c>
       <c r="B1072" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1072" s="5" t="inlineStr">
@@ -27130,12 +27209,12 @@
     <row r="1073">
       <c r="A1073" s="6" t="inlineStr">
         <is>
-          <t>7510077</t>
+          <t>7510131</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -27150,12 +27229,12 @@
     <row r="1074">
       <c r="A1074" s="4" t="inlineStr">
         <is>
-          <t>7510079</t>
+          <t>7510132</t>
         </is>
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1074" s="5" t="inlineStr">
@@ -27170,12 +27249,12 @@
     <row r="1075">
       <c r="A1075" s="6" t="inlineStr">
         <is>
-          <t>7510081</t>
+          <t>7510139</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -27190,12 +27269,12 @@
     <row r="1076">
       <c r="A1076" s="4" t="inlineStr">
         <is>
-          <t>7510083</t>
+          <t>7510140</t>
         </is>
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1076" s="5" t="inlineStr">
@@ -27210,12 +27289,12 @@
     <row r="1077">
       <c r="A1077" s="6" t="inlineStr">
         <is>
-          <t>7510085</t>
+          <t>7510141</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -27230,12 +27309,12 @@
     <row r="1078">
       <c r="A1078" s="4" t="inlineStr">
         <is>
-          <t>7510087</t>
+          <t>7510142</t>
         </is>
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1078" s="5" t="inlineStr">
@@ -27250,12 +27329,12 @@
     <row r="1079">
       <c r="A1079" s="6" t="inlineStr">
         <is>
-          <t>7510112</t>
+          <t>7510143</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -27270,12 +27349,12 @@
     <row r="1080">
       <c r="A1080" s="4" t="inlineStr">
         <is>
-          <t>7510114</t>
+          <t>7510144</t>
         </is>
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Takarmatur Mira 2x2 infälld</t>
+          <t>Takarmatur Mira 1x7 infälld</t>
         </is>
       </c>
       <c r="C1080" s="5" t="inlineStr">
@@ -27290,7 +27369,7 @@
     <row r="1081">
       <c r="A1081" s="6" t="inlineStr">
         <is>
-          <t>7510115</t>
+          <t>7510073</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
@@ -27310,7 +27389,7 @@
     <row r="1082">
       <c r="A1082" s="4" t="inlineStr">
         <is>
-          <t>7510116</t>
+          <t>7510075</t>
         </is>
       </c>
       <c r="B1082" s="5" t="inlineStr">
@@ -27330,7 +27409,7 @@
     <row r="1083">
       <c r="A1083" s="6" t="inlineStr">
         <is>
-          <t>7510117</t>
+          <t>7510077</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -27350,7 +27429,7 @@
     <row r="1084">
       <c r="A1084" s="4" t="inlineStr">
         <is>
-          <t>7510118</t>
+          <t>7510079</t>
         </is>
       </c>
       <c r="B1084" s="5" t="inlineStr">
@@ -27370,7 +27449,7 @@
     <row r="1085">
       <c r="A1085" s="6" t="inlineStr">
         <is>
-          <t>7510119</t>
+          <t>7510081</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
@@ -27390,7 +27469,7 @@
     <row r="1086">
       <c r="A1086" s="4" t="inlineStr">
         <is>
-          <t>7510120</t>
+          <t>7510083</t>
         </is>
       </c>
       <c r="B1086" s="5" t="inlineStr">
@@ -27410,17 +27489,17 @@
     <row r="1087">
       <c r="A1087" s="6" t="inlineStr">
         <is>
-          <t>7028323</t>
+          <t>7510085</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1087" s="6" t="n">
@@ -27430,17 +27509,17 @@
     <row r="1088">
       <c r="A1088" s="4" t="inlineStr">
         <is>
-          <t>7028324</t>
+          <t>7510087</t>
         </is>
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>Interiörarmatur Beta Force</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1088" s="4" t="n">
@@ -27450,17 +27529,17 @@
     <row r="1089">
       <c r="A1089" s="6" t="inlineStr">
         <is>
-          <t>7028311</t>
+          <t>7510112</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Interiörarmatur Maya</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>ZG Lighting</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1089" s="6" t="n">
@@ -27470,57 +27549,57 @@
     <row r="1090">
       <c r="A1090" s="4" t="inlineStr">
         <is>
-          <t>7013475</t>
+          <t>7510114</t>
         </is>
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1090" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="6" t="inlineStr">
         <is>
-          <t>7021097</t>
+          <t>7510115</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1091" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="4" t="inlineStr">
         <is>
-          <t>7018286</t>
+          <t>7510116</t>
         </is>
       </c>
       <c r="B1092" s="5" t="inlineStr">
         <is>
-          <t>Infälld interiörarmatur aLight Office aPerture</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1092" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1092" s="4" t="n">
@@ -27530,57 +27609,57 @@
     <row r="1093">
       <c r="A1093" s="6" t="inlineStr">
         <is>
-          <t>7028368</t>
+          <t>7510117</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1093" s="6" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" s="4" t="inlineStr">
         <is>
-          <t>7028369</t>
+          <t>7510118</t>
         </is>
       </c>
       <c r="B1094" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel Flex</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1094" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1094" s="4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" s="6" t="inlineStr">
         <is>
-          <t>7028001</t>
+          <t>7510119</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1095" s="6" t="n">
@@ -27590,17 +27669,17 @@
     <row r="1096">
       <c r="A1096" s="4" t="inlineStr">
         <is>
-          <t>7028002</t>
+          <t>7510120</t>
         </is>
       </c>
       <c r="B1096" s="5" t="inlineStr">
         <is>
-          <t>LED-Panel aLight Office Rektangulär</t>
+          <t>Takarmatur Mira 2x2 infälld</t>
         </is>
       </c>
       <c r="C1096" s="5" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>Westal</t>
         </is>
       </c>
       <c r="D1096" s="4" t="n">
@@ -27610,41 +27689,241 @@
     <row r="1097">
       <c r="A1097" s="6" t="inlineStr">
         <is>
-          <t>7027999</t>
+          <t>7028323</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>LED-panel aLight Office</t>
+          <t>Interiörarmatur Beta Force</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>a-collection</t>
+          <t>ZG Lighting</t>
         </is>
       </c>
       <c r="D1097" s="6" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
+          <t>7028324</t>
+        </is>
+      </c>
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Beta Force</t>
+        </is>
+      </c>
+      <c r="C1098" s="5" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1098" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="6" t="inlineStr">
+        <is>
+          <t>7028311</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Interiörarmatur Maya</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>ZG Lighting</t>
+        </is>
+      </c>
+      <c r="D1099" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="4" t="inlineStr">
+        <is>
+          <t>7013475</t>
+        </is>
+      </c>
+      <c r="B1100" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED</t>
+        </is>
+      </c>
+      <c r="C1100" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="6" t="inlineStr">
+        <is>
+          <t>7021097</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office LED Tec rektangulär</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1101" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="4" t="inlineStr">
+        <is>
+          <t>7018286</t>
+        </is>
+      </c>
+      <c r="B1102" s="5" t="inlineStr">
+        <is>
+          <t>Infälld interiörarmatur aLight Office aPerture</t>
+        </is>
+      </c>
+      <c r="C1102" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="6" t="inlineStr">
+        <is>
+          <t>7028368</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1103" s="6" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="4" t="inlineStr">
+        <is>
+          <t>7028369</t>
+        </is>
+      </c>
+      <c r="B1104" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel Flex</t>
+        </is>
+      </c>
+      <c r="C1104" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="6" t="inlineStr">
+        <is>
+          <t>7028001</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1105" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="4" t="inlineStr">
+        <is>
+          <t>7028002</t>
+        </is>
+      </c>
+      <c r="B1106" s="5" t="inlineStr">
+        <is>
+          <t>LED-Panel aLight Office Rektangulär</t>
+        </is>
+      </c>
+      <c r="C1106" s="5" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="6" t="inlineStr">
+        <is>
+          <t>7027999</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>LED-panel aLight Office</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>a-collection</t>
+        </is>
+      </c>
+      <c r="D1107" s="6" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="4" t="inlineStr">
+        <is>
           <t>7028000</t>
         </is>
       </c>
-      <c r="B1098" s="5" t="inlineStr">
+      <c r="B1108" s="5" t="inlineStr">
         <is>
           <t>LED-panel aLight Office</t>
         </is>
       </c>
-      <c r="C1098" s="5" t="inlineStr">
+      <c r="C1108" s="5" t="inlineStr">
         <is>
           <t>a-collection</t>
         </is>
       </c>
-      <c r="D1098" s="4" t="n">
-        <v>355</v>
+      <c r="D1108" s="4" t="n">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
